--- a/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
+++ b/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
@@ -169,8 +169,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -959,7 +959,7 @@
           <t>&lt;0,20</t>
         </is>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="18">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -995,7 +995,7 @@
           <t>&gt;5 %</t>
         </is>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="17">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -1031,7 +1031,7 @@
           <t>&gt;30 %</t>
         </is>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="17">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -1103,7 +1103,7 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="17">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -1139,7 +1139,7 @@
           <t>&gt;14 %</t>
         </is>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="17">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -1175,7 +1175,7 @@
           <t>&gt;4 %</t>
         </is>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="17">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -1283,7 +1283,7 @@
           <t>&lt;4 %</t>
         </is>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="17">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -2046,7 +2046,7 @@
         </is>
       </c>
       <c r="C7" s="35">
-        <f>IF(ISERROR(SUM('Embudo'!C5:I60)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -2798,7 +2798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:J24"/>
+  <dimension ref="B2:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2806,24 +2806,23 @@
     <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="50" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Embudo: todos los pasos, cuántos, qué porcentaje pasa y cuánto cuesta cada uno</t>
+          <t>Embudo: todos los pasos, cuántos pasan y, por cada uno, qué pagás, qué te queda y hasta cuánto podrías pagar</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). El costo por paso es inversión ÷ cantidad; el techo por paso es lo máximo que podrías pagar por él si lo demás se mantiene. Los pasos sin costo propio ya se pagaron con el CPA: mejoran el AOV.</t>
+          <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). Tres números por paso: lo que pagás hoy por cada uno (inversión ÷ cantidad), lo que te queda por cada uno (ganancia ÷ cantidad) y lo máximo que podrías pagar (el techo: lo que cada uno genera en cash neto). Techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
@@ -2845,30 +2844,25 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>% que se pierde</t>
+          <t>% acumulado</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>% acumulado</t>
+          <t>Costo por paso (pagás hoy)</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Costo por paso</t>
+          <t>Ganancia por paso (te queda)</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>Techo por paso</t>
+          <t>Techo por paso (máximo a pagar)</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia por paso</t>
-        </is>
-      </c>
-      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Qué se paga acá / cómo se lee</t>
         </is>
@@ -2889,28 +2883,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F6" s="16">
+      <c r="E6" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$8/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F6" s="11">
+        <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$8)</f>
+        <v/>
+      </c>
       <c r="G6" s="11">
-        <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$8)</f>
-        <v/>
-      </c>
-      <c r="H6" s="17">
+        <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$41*1/'Modelo'!$C$8)</f>
+        <v/>
+      </c>
+      <c r="H6" s="11">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$47*'Modelo'!$C$8*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="I6" s="11">
-        <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$41*1/'Modelo'!$C$8)</f>
-        <v/>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="I6" s="4" t="inlineStr">
         <is>
           <t>La unidad que compra la pauta. Costo por visita.</t>
         </is>
@@ -2926,31 +2915,27 @@
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="18">
-        <f>IF('Modelo'!$C$8=0,0,1-'Modelo'!$C$9/'Modelo'!$C$8)</f>
-        <v/>
-      </c>
-      <c r="F7" s="16">
+      <c r="E7" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F7" s="11">
+        <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
+        <v/>
+      </c>
       <c r="G7" s="11">
-        <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
+        <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41*1/'Modelo'!$C$9)</f>
+        <v/>
+      </c>
+      <c r="H7" s="11">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$47*'Modelo'!$C$8*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="I7" s="11">
-        <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41*1/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+      <c r="I7" s="4" t="inlineStr">
         <is>
           <t>Costo por checkout. Si se pierde mucho acá, es la VSL.</t>
         </is>
@@ -2966,31 +2951,27 @@
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$10/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="18">
-        <f>IF('Modelo'!$C$9=0,0,1-'Modelo'!$C$10/'Modelo'!$C$9)</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
+      <c r="E8" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F8" s="11">
+        <f>IF('Modelo'!$C$10=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$10)</f>
+        <v/>
+      </c>
       <c r="G8" s="11">
-        <f>IF('Modelo'!$C$10=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
+        <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$41*1/'Modelo'!$C$10)</f>
+        <v/>
+      </c>
+      <c r="H8" s="11">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$47*'Modelo'!$C$8*1/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="I8" s="11">
-        <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$41*1/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="I8" s="4" t="inlineStr">
         <is>
           <t>CPA: costo por comprador. Si se pierde mucho acá, es el checkout o la oferta.</t>
         </is>
@@ -3006,21 +2987,22 @@
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$15/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E9" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$15/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
+      <c r="E9" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$15/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -3028,12 +3010,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Sobre compradores del principal. Se pagó con el CPA; suma al AOV.</t>
         </is>
@@ -3049,21 +3026,22 @@
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$17/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E10" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$17/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F10" s="16">
+      <c r="E10" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$17/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -3071,12 +3049,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
         <is>
           <t>Sobre compradores del principal.</t>
         </is>
@@ -3092,21 +3065,22 @@
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$19/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E11" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$19/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F11" s="16">
+      <c r="E11" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$19/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3114,12 +3088,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
+      <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Página 1 después del pago.</t>
         </is>
@@ -3135,21 +3104,22 @@
         <f>'Modelo'!$C$21</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$21/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E12" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$21/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F12" s="16">
+      <c r="E12" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$21/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3157,12 +3127,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Página 2 (downsell de la OTO 1).</t>
         </is>
@@ -3178,21 +3143,22 @@
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$23/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E13" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$23/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
+      <c r="E13" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$23/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3200,12 +3166,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="I13" s="4" t="inlineStr">
         <is>
           <t>Página 3.</t>
         </is>
@@ -3221,21 +3182,22 @@
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$25/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E14" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$25/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F14" s="16">
+      <c r="E14" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$25/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -3243,12 +3205,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Página 4.</t>
         </is>
@@ -3264,21 +3221,22 @@
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="17">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$27/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E15" s="18">
-        <f>IF('Modelo'!$C$10=0,0,1-'Modelo'!$C$27/'Modelo'!$C$10)</f>
-        <v/>
-      </c>
-      <c r="F15" s="16">
+      <c r="E15" s="16">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$27/'Modelo'!$C$8)</f>
         <v/>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>sin costo propio</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>sin costo propio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -3286,12 +3244,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
+      <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Sobre compradores del principal. El AOV neto resultante contra el CPA es lo que decide el embudo.</t>
         </is>
@@ -3300,53 +3253,70 @@
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
+          <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
+        </is>
+      </c>
+      <c r="F17" s="18">
+        <f>F6</f>
+        <v/>
+      </c>
+      <c r="G17" s="18">
+        <f>G6</f>
+        <v/>
+      </c>
+      <c r="H17" s="11">
+        <f>F6+G6+'Supuestos'!$C$37/'Modelo'!$C$8</f>
+        <v/>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Techo = costo + ganancia + fijos ÷ unidades. Lo que falta entre (costo + ganancia) y el techo son los costos fijos repartidos entre las unidades.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
           <t>Cómo se lee</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+    <row r="19" ht="28" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cantidad: cuántas acciones o personas hubo en ese paso con los supuestos del escenario en uso.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="26" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % que se pierde es el complemento.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="26" customHeight="1">
+    <row r="20" ht="28" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>% acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
+          <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="28" customHeight="1">
       <c r="B21" s="4" t="inlineStr">
         <is>
           <t>Costo por paso: inversión ÷ cantidad. Es lo que te está costando hoy cada persona que llega a ese paso.</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="26" customHeight="1">
+    <row r="22" ht="28" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Techo por paso: lo máximo que podrías pagar por ese paso sin perder plata, si lo demás se mantiene. Comparalo con el costo por paso: si el costo está por encima del techo, ese paso está caro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
+          <t>Ganancia por paso: ganancia del período ÷ cantidad. Lo que te queda por cada persona de ese paso después de pagar la pauta, las comisiones, los reembolsos y los fijos. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="28" customHeight="1">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Ganancia por paso: la ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo: cuánto te queda por cada visita, por cada lead, por cada comprador. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
+          <t>Techo por paso: lo que cada persona de ese paso genera en cash neto (cash neto menos costos por unidad, dividido por la cantidad). Es lo máximo que podrías pagar por ese paso antes de que la ganancia llegue a cero, si lo demás se mantiene. Por eso siempre es mayor que la ganancia: techo = costo + ganancia + fijos repartidos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="28" customHeight="1">
       <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Los bumps, las OTOs y la ascensión no tienen costo propio: se pagan con el CPA del comprador principal y se miden por lo que suman al AOV.</t>
@@ -3354,14 +3324,13 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B19:J19"/>
-    <mergeCell ref="B20:J20"/>
-    <mergeCell ref="B22:J22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B18:J18"/>
-    <mergeCell ref="B21:J21"/>
+  <mergeCells count="6">
+    <mergeCell ref="B21:I21"/>
+    <mergeCell ref="B24:I24"/>
+    <mergeCell ref="B20:I20"/>
+    <mergeCell ref="B22:I22"/>
+    <mergeCell ref="B19:I19"/>
+    <mergeCell ref="B23:I23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -3504,7 +3473,7 @@
           <t>Costo por visita a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="18">
         <f>IF('Supuestos'!$C$6=1,D9,IF('Supuestos'!$C$6=2,E9,F9))</f>
         <v/>
       </c>
@@ -3547,7 +3516,7 @@
           <t>% de visitas que llegan al checkout</t>
         </is>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="17">
         <f>IF('Supuestos'!$C$6=1,D12,IF('Supuestos'!$C$6=2,E12,F12))</f>
         <v/>
       </c>
@@ -3577,7 +3546,7 @@
           <t>% de checkouts que terminan en compra</t>
         </is>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="17">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
@@ -3660,7 +3629,7 @@
           <t>Bump 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
@@ -3706,7 +3675,7 @@
           <t>Bump 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="17">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
@@ -3752,7 +3721,7 @@
           <t>OTO 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="17">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
@@ -3798,7 +3767,7 @@
           <t>OTO 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="17">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
@@ -3844,7 +3813,7 @@
           <t>OTO 3: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="17">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
@@ -3890,7 +3859,7 @@
           <t>OTO 4: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="17">
         <f>IF('Supuestos'!$C$6=1,D28,IF('Supuestos'!$C$6=2,E28,F28))</f>
         <v/>
       </c>
@@ -3936,7 +3905,7 @@
           <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="17">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
@@ -4329,7 +4298,7 @@
           <t>Costo por visita (unidad de adquisición)</t>
         </is>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="18">
         <f>'Supuestos'!$C$9</f>
         <v/>
       </c>
@@ -4738,7 +4707,7 @@
           <t>Facturado por visita</t>
         </is>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="18">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$29/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -4907,7 +4876,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="17">
         <f>IF('Modelo'!$C$35=0,0,'Modelo'!$C$41/'Modelo'!$C$35)</f>
         <v/>
       </c>
@@ -4996,7 +4965,7 @@
           <t>Techo de costo por checkout</t>
         </is>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="18">
         <f>IF('Supuestos'!$C$12=0,0,'Modelo'!$C$47/'Supuestos'!$C$12)</f>
         <v/>
       </c>
@@ -5028,7 +4997,7 @@
           <t>Objetivo de CPA</t>
         </is>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="18">
         <f>'Modelo'!$C$51/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
@@ -5044,7 +5013,7 @@
           <t>Cash neto por comprador (AOV neto)</t>
         </is>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="18">
         <f>IF('Modelo'!$C$10=0,0,('Modelo'!$C$39-'Modelo'!$C$40)/'Modelo'!$C$10)</f>
         <v/>
       </c>
@@ -5158,7 +5127,7 @@
           <t>Ganancia por checkout</t>
         </is>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -5906,23 +5875,23 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="18">
         <f>IF(C45=0,0,'Modelo'!$C$33/C45)</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="18">
         <f>IF(D45=0,0,'Modelo'!$C$33/D45)</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="18">
         <f>IF(E45=0,0,'Modelo'!$C$33/E45)</f>
         <v/>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="18">
         <f>IF(F45=0,0,'Modelo'!$C$33/F45)</f>
         <v/>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="18">
         <f>IF(G45=0,0,'Modelo'!$C$33/G45)</f>
         <v/>
       </c>
@@ -6196,7 +6165,7 @@
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="17">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
@@ -6224,7 +6193,7 @@
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="17">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
@@ -6252,7 +6221,7 @@
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="17">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
@@ -6280,7 +6249,7 @@
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="17">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
@@ -6308,7 +6277,7 @@
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="17">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
@@ -6336,7 +6305,7 @@
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="17">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
@@ -6364,7 +6333,7 @@
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="17">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
@@ -6392,7 +6361,7 @@
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="17">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
@@ -7774,15 +7743,15 @@
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N7/N8))</f>
         <v/>
       </c>
-      <c r="O17" s="17">
+      <c r="O17" s="18">
         <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
         <v/>
       </c>
-      <c r="P17" s="17">
+      <c r="P17" s="18">
         <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
         <v/>
       </c>
-      <c r="Q17" s="17">
+      <c r="Q17" s="18">
         <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
         <v/>
       </c>
@@ -7793,63 +7762,63 @@
           <t>% visitas → checkout</t>
         </is>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="17">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D18" s="18">
+      <c r="D18" s="17">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="17">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F18" s="18">
+      <c r="F18" s="17">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G18" s="18">
+      <c r="G18" s="17">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="17">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I18" s="18">
+      <c r="I18" s="17">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="17">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K18" s="18">
+      <c r="K18" s="17">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L18" s="18">
+      <c r="L18" s="17">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M18" s="18">
+      <c r="M18" s="17">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N18" s="18">
+      <c r="N18" s="17">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O18" s="18">
+      <c r="O18" s="17">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="18">
+      <c r="P18" s="17">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="18">
+      <c r="Q18" s="17">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
@@ -7860,63 +7829,63 @@
           <t>% checkout → compra</t>
         </is>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="17">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
         <v/>
       </c>
-      <c r="D19" s="18">
+      <c r="D19" s="17">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
         <v/>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="17">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
         <v/>
       </c>
-      <c r="F19" s="18">
+      <c r="F19" s="17">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
         <v/>
       </c>
-      <c r="G19" s="18">
+      <c r="G19" s="17">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
         <v/>
       </c>
-      <c r="H19" s="18">
+      <c r="H19" s="17">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
         <v/>
       </c>
-      <c r="I19" s="18">
+      <c r="I19" s="17">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
         <v/>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="17">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
         <v/>
       </c>
-      <c r="K19" s="18">
+      <c r="K19" s="17">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
         <v/>
       </c>
-      <c r="L19" s="18">
+      <c r="L19" s="17">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
         <v/>
       </c>
-      <c r="M19" s="18">
+      <c r="M19" s="17">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
         <v/>
       </c>
-      <c r="N19" s="18">
+      <c r="N19" s="17">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
         <v/>
       </c>
-      <c r="O19" s="18">
+      <c r="O19" s="17">
         <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
         <v/>
       </c>
-      <c r="P19" s="18">
+      <c r="P19" s="17">
         <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
         <v/>
       </c>
-      <c r="Q19" s="18">
+      <c r="Q19" s="17">
         <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
         <v/>
       </c>
@@ -7927,63 +7896,63 @@
           <t>CPA real</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C7/C10))</f>
         <v/>
       </c>
-      <c r="D20" s="17">
+      <c r="D20" s="18">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D7/D10))</f>
         <v/>
       </c>
-      <c r="E20" s="17">
+      <c r="E20" s="18">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E7/E10))</f>
         <v/>
       </c>
-      <c r="F20" s="17">
+      <c r="F20" s="18">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F7/F10))</f>
         <v/>
       </c>
-      <c r="G20" s="17">
+      <c r="G20" s="18">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G7/G10))</f>
         <v/>
       </c>
-      <c r="H20" s="17">
+      <c r="H20" s="18">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H7/H10))</f>
         <v/>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="18">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I7/I10))</f>
         <v/>
       </c>
-      <c r="J20" s="17">
+      <c r="J20" s="18">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J7/J10))</f>
         <v/>
       </c>
-      <c r="K20" s="17">
+      <c r="K20" s="18">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K7/K10))</f>
         <v/>
       </c>
-      <c r="L20" s="17">
+      <c r="L20" s="18">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L7/L10))</f>
         <v/>
       </c>
-      <c r="M20" s="17">
+      <c r="M20" s="18">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M7/M10))</f>
         <v/>
       </c>
-      <c r="N20" s="17">
+      <c r="N20" s="18">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N7/N10))</f>
         <v/>
       </c>
-      <c r="O20" s="17">
+      <c r="O20" s="18">
         <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
         <v/>
       </c>
-      <c r="P20" s="17">
+      <c r="P20" s="18">
         <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
         <v/>
       </c>
-      <c r="Q20" s="17">
+      <c r="Q20" s="18">
         <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
         <v/>
       </c>
@@ -7994,63 +7963,63 @@
           <t>Cash por comprador</t>
         </is>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="18">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C15/C10))</f>
         <v/>
       </c>
-      <c r="D21" s="17">
+      <c r="D21" s="18">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D15/D10))</f>
         <v/>
       </c>
-      <c r="E21" s="17">
+      <c r="E21" s="18">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E15/E10))</f>
         <v/>
       </c>
-      <c r="F21" s="17">
+      <c r="F21" s="18">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F15/F10))</f>
         <v/>
       </c>
-      <c r="G21" s="17">
+      <c r="G21" s="18">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G15/G10))</f>
         <v/>
       </c>
-      <c r="H21" s="17">
+      <c r="H21" s="18">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H15/H10))</f>
         <v/>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="18">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I15/I10))</f>
         <v/>
       </c>
-      <c r="J21" s="17">
+      <c r="J21" s="18">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J15/J10))</f>
         <v/>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="18">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K15/K10))</f>
         <v/>
       </c>
-      <c r="L21" s="17">
+      <c r="L21" s="18">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L15/L10))</f>
         <v/>
       </c>
-      <c r="M21" s="17">
+      <c r="M21" s="18">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M15/M10))</f>
         <v/>
       </c>
-      <c r="N21" s="17">
+      <c r="N21" s="18">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N15/N10))</f>
         <v/>
       </c>
-      <c r="O21" s="17">
+      <c r="O21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="17">
+      <c r="P21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="17">
+      <c r="Q21" s="18">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
@@ -8109,15 +8078,15 @@
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
         <v/>
       </c>
-      <c r="O22" s="17">
+      <c r="O22" s="18">
         <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
         <v/>
       </c>
-      <c r="P22" s="17">
+      <c r="P22" s="18">
         <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
         <v/>
       </c>
-      <c r="Q22" s="17">
+      <c r="Q22" s="18">
         <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
         <v/>
       </c>
@@ -8310,15 +8279,15 @@
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
         <v/>
       </c>
-      <c r="O25" s="17">
+      <c r="O25" s="18">
         <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
         <v/>
       </c>
-      <c r="P25" s="17">
+      <c r="P25" s="18">
         <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
         <v/>
       </c>
-      <c r="Q25" s="17">
+      <c r="Q25" s="18">
         <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
         <v/>
       </c>
@@ -8463,63 +8432,63 @@
           <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
         </is>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="18">
         <f>IF(COUNT(C7:C15)&lt;9,"",'Modelo'!$C$48)</f>
         <v/>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="18">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(COUNT(C22:C22)&gt;0,MEDIAN(C22:C22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="18">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(COUNT(C22:D22)&gt;0,MEDIAN(C22:D22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="18">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(COUNT(C22:E22)&gt;0,MEDIAN(C22:E22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="18">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(COUNT(C22:F22)&gt;0,MEDIAN(C22:F22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="18">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(COUNT(D22:G22)&gt;0,MEDIAN(D22:G22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="18">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(COUNT(E22:H22)&gt;0,MEDIAN(E22:H22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="J28" s="17">
+      <c r="J28" s="18">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(COUNT(F22:I22)&gt;0,MEDIAN(F22:I22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="18">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(COUNT(G22:J22)&gt;0,MEDIAN(G22:J22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="L28" s="17">
+      <c r="L28" s="18">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(COUNT(H22:K22)&gt;0,MEDIAN(H22:K22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="M28" s="17">
+      <c r="M28" s="18">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(COUNT(I22:L22)&gt;0,MEDIAN(I22:L22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="N28" s="17">
+      <c r="N28" s="18">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(COUNT(J22:M22)&gt;0,MEDIAN(J22:M22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="O28" s="17">
+      <c r="O28" s="18">
         <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
         <v/>
       </c>
-      <c r="P28" s="17">
+      <c r="P28" s="18">
         <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
         <v/>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q28" s="18">
         <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
         <v/>
       </c>

--- a/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
+++ b/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
@@ -19,8 +19,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="Autor_Jesus_Tassarolo">"Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro"</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -34,7 +37,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot;x&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +59,11 @@
     <font>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008C8C8C"/>
+      <sz val="8"/>
     </font>
   </fonts>
   <fills count="6">
@@ -145,8 +153,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -577,274 +586,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B46"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
     <col width="118" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Modelo financiero · Embudo low-ticket con bumps y upsells</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Anuncios → página de ventas (VSL) → checkout → producto principal + bumps + OTOs + ascenso</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Para qué sirve este modelo</t>
         </is>
       </c>
     </row>
     <row r="6" ht="75" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Es el modelo financiero de un embudo de venta directa: anuncios que llevan a una página de ventas con video (VSL), un producto principal de precio bajo y una escalera de bumps, OTOs y un programa de ascenso. Con tus números (o con el ejemplo cargado) te dice cuánto vale cada visita que comprás con publicidad, hasta cuánto podés pagar por visita y por cada etapa siguiente, cuánto invertir para una meta de ventas, cuánta caja necesitás y qué palanca mejora más la ganancia.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>La unidad que comprás es la visita a la página. El número que manda es la diferencia entre lo que deja cada comprador sumando toda la escalera (AOV neto) y lo que te cuesta conseguirlo (CPA).</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Cómo usarlo en 6 pasos</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>1. Andá a Supuestos y reemplazá el ejemplo por tus números. Si todavía no tenés datos, dejá el escenario en 1 (conservador) y usá Benchmarks como referencia.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>2. Mirá Resumen: ganancia del mes, ROAS, el techo y el objetivo de costo por visita, y el semáforo. Después Embudo: todos los pasos en orden con cuántos pasan, qué porcentaje se pierde y cuánto cuesta cada paso.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>3. Abrí Escenarios para ver qué pasa si cambia el precio, la conversión o el costo. Las celdas amarillas de cada tabla se pueden cambiar.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>4. Abrí Sensibilidad para saber qué variable conviene trabajar primero.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>5. Antes de invertir, mirá Proyección 12 meses: la caja necesaria es la plata que tenés que tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>6. Cuando el embudo esté andando, completá una columna de Seguimiento por mes. El semáforo te dice si estás pagando de más por cada visita.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Colores y hojas</t>
         </is>
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Amarillo = celda que editás vos. Azul = resultado calculado: no lo toques, se recalcula solo.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Resumen, Embudo y Modelo leen de Supuestos. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Chequeos avisa si un supuesto quedó fuera de rango. Si dice REVISAR, arreglalo antes de leer los resultados.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Cómo elegir escenario: en Supuestos, la celda 'Escenario en uso' (1, 2 o 3) elige la columna conservador, base u optimista de cada fila que tiene tres valores. Las filas con un solo valor se usan tal cual.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>El ejemplo que viene cargado</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Un curso de 37 USD vendido con VSL a tráfico frío. Se invierten 9.000 USD por mes a 0,30 por visita (30.000 visitas). El 3,5 % llega al checkout y el 26 % de esos compra: 273 ventas al mes, CPA de 33 USD.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>La escalera: dos bumps de 17 (25 % y 18 %); cuatro OTOs después del pago, una por página: 47 (10 %), 17 (6 %), 97 (3 %) y 27 (4 %); y la ascensión a un programa de 297 que toma el 2 %. El AOV queda cerca de 60 USD: la escalera multiplica el precio del principal por 1,6.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Costos: pasarela 10 %, reembolsos 5 %, fijos 1.500 por mes. Pago único: la cobranza entra 100 % el primer mes.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="60" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Resultado: ganancia mensual positiva y ROAS sobre cash neto de 1,5, con techo de costo por visita cerca de 0,46 y objetivo cerca de 0,36. El semáforo queda en amarillo: el costo por visita está bien, pero el ROAS no llega al objetivo de 2. Sensibilidad dice que las palancas son el costo por visita y la conversión de la página, no el precio. Cambiá los números por los tuyos.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Reglas de decisión (el protocolo corto)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>1. Antes de invertir: cargá tus números en Supuestos (si no tenés datos, escenario 1, conservador) y mirá en Resumen el techo y el objetivo de costo por visita.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>2. Primeros días: compará tu costo real por visita con el objetivo. Verde: seguí. Amarillo: no subas la inversión y revisá en este orden: CPM (público y frecuencia), creativo (CTR) y página (conversión). Rojo: bajá un escalón (−25 %) y arreglá antes de volver a subir.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>3. Cada mes: completá una columna de Seguimiento. El semáforo compara tu costo con el techo móvil (lo que rindieron tus últimas 4 columnas), no con un número fijo.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>4. Subí la inversión de a 25 % y esperá 7 días (o 3 a 4 eventos si vendés por llamada) antes de volver a subir. Un día bueno o malo no decide nada.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>5. Si el costo está en verde y aun así no hay ganancia, el problema no es el tráfico: mirá asistencia, conversión de la oferta y cobranza, en ese orden.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>6. Cambiá una sola cosa por vez. Si cambiás precio, creativo y página la misma semana no vas a saber qué funcionó.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>7. Trabajá siempre con cash neto (lo que entra menos comisiones y reembolsos), nunca con facturado. En Proyección ves cuánta caja necesitás para sostener la pauta mientras cobrás.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>8. En este embudo el techo de CPA es el AOV neto. Si tu CPA se acerca al AOV neto, subir los bumps y las OTOs es la forma más rápida de recuperar margen sin tocar el tráfico.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Lo que este modelo no hace</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>No adivina tus conversiones: usa las que cargás. Cuando una conversión cambia, el techo cambia; por eso Seguimiento recalcula el techo móvil con tus últimas 4 columnas.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>No reemplaza la decisión: la informa. Las reglas de arriba dicen qué hacer con cada color.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="B42" s="4" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Los benchmarks son orden de magnitud para tráfico frío en español. Tus datos mandan.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Autor y versión</t>
         </is>
       </c>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="4" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro. v1.2 · octubre 2026. Fórmulas compatibles con Excel, Google Sheets y Numbers. Sin macros.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Este modelo se comparte para que lo uses con tus números. Si lo compartís, dejá esta línea: es la forma de saber de dónde salió.</t>
         </is>
@@ -853,10 +869,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -869,7 +885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -882,52 +898,59 @@
     <col width="60" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Benchmarks: contra qué comparar tus números</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Valores de referencia para tráfico frío en español. Son orden de magnitud, no objetivo: tus propios datos de Seguimiento mandan.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Métrica</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Malo</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Bueno</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Ganador</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Tu valor (Modelo)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Fuente / nota</t>
         </is>
@@ -959,11 +982,11 @@
           <t>&lt;0,20</t>
         </is>
       </c>
-      <c r="G6" s="18">
+      <c r="G6" s="19">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Embudos hispanos de venta directa a tráfico frío, 2025 a 2026.</t>
         </is>
@@ -995,11 +1018,11 @@
           <t>&gt;5 %</t>
         </is>
       </c>
-      <c r="G7" s="17">
+      <c r="G7" s="18">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
-      <c r="H7" s="4" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Idem.</t>
         </is>
@@ -1031,11 +1054,11 @@
           <t>&gt;30 %</t>
         </is>
       </c>
-      <c r="G8" s="17">
+      <c r="G8" s="18">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Idem.</t>
         </is>
@@ -1067,11 +1090,11 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="17">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Idem.</t>
         </is>
@@ -1103,11 +1126,11 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G10" s="17">
+      <c r="G10" s="18">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
-      <c r="H10" s="4" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr">
         <is>
           <t>Mercado USA: 30 a 40 % (SamCart, sobre miles de millones procesados). Hispano: 17 a 25 % es lo común.</t>
         </is>
@@ -1139,11 +1162,11 @@
           <t>&gt;14 %</t>
         </is>
       </c>
-      <c r="G11" s="17">
+      <c r="G11" s="18">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
         <is>
           <t>Mercado: 8 a 18 % en info-productos.</t>
         </is>
@@ -1175,11 +1198,11 @@
           <t>&gt;4 %</t>
         </is>
       </c>
-      <c r="G12" s="17">
+      <c r="G12" s="18">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Ascenso front → programa de 300 a 1.000 USD.</t>
         </is>
@@ -1211,11 +1234,11 @@
           <t>&gt;1,7</t>
         </is>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Cuánto multiplica la escalera.</t>
         </is>
@@ -1247,11 +1270,11 @@
           <t>&gt;2,5</t>
         </is>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="28">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
-      <c r="H14" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>Tráfico frío. Con backend por llamada sube.</t>
         </is>
@@ -1283,11 +1306,11 @@
           <t>&lt;4 %</t>
         </is>
       </c>
-      <c r="G15" s="17">
+      <c r="G15" s="18">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="H15" s="4" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Más de 10 % es un problema de oferta.</t>
         </is>
@@ -1296,10 +1319,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -1312,7 +1335,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D41"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1321,44 +1344,51 @@
     <col width="26" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Glosario</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Los términos que usa este modelo, en el orden del embudo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Término</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Qué es</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Dónde aparece</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>CPM</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
         </is>
@@ -1370,12 +1400,12 @@
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>CTR</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
         </is>
@@ -1387,12 +1417,12 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Clic → visita</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
         </is>
@@ -1404,12 +1434,12 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Unidad de adquisición</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
         </is>
@@ -1421,12 +1451,12 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Costo por unidad</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
         </is>
@@ -1438,12 +1468,12 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Conversión</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
         </is>
@@ -1455,12 +1485,12 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Show rate</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
         </is>
@@ -1472,12 +1502,12 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Bump</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
         </is>
@@ -1489,12 +1519,12 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>OTO / upsell</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
         </is>
@@ -1506,12 +1536,12 @@
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Backend</t>
         </is>
       </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
         </is>
@@ -1523,12 +1553,12 @@
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>AOV</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
         </is>
@@ -1540,12 +1570,12 @@
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>CPA / CAC</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
         </is>
@@ -1557,12 +1587,12 @@
       </c>
     </row>
     <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Facturado</t>
         </is>
       </c>
-      <c r="C18" s="4" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
         </is>
@@ -1574,12 +1604,12 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Cash cobrado</t>
         </is>
       </c>
-      <c r="C19" s="4" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
         </is>
@@ -1591,12 +1621,12 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Cash neto</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
         </is>
@@ -1608,12 +1638,12 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t>ROAS</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
         </is>
@@ -1625,12 +1655,12 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Valor neto por unidad (VPU)</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
         </is>
@@ -1642,12 +1672,12 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Techo</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
         </is>
@@ -1659,12 +1689,12 @@
       </c>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Objetivo</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
         </is>
@@ -1676,12 +1706,12 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
         </is>
@@ -1693,12 +1723,12 @@
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>Semáforo</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
         </is>
@@ -1710,12 +1740,12 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Techo móvil</t>
         </is>
       </c>
-      <c r="C27" s="4" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
         </is>
@@ -1727,12 +1757,12 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Escenario</t>
         </is>
       </c>
-      <c r="C28" s="4" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
         </is>
@@ -1744,12 +1774,12 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Sensibilidad</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
         </is>
@@ -1761,12 +1791,12 @@
       </c>
     </row>
     <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Ganancia por visita / por lead / por cliente</t>
         </is>
       </c>
-      <c r="C30" s="4" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
         </is>
@@ -1778,12 +1808,12 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Order value (AOV)</t>
         </is>
       </c>
-      <c r="C31" s="4" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
         </is>
@@ -1795,12 +1825,12 @@
       </c>
     </row>
     <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Caja necesaria</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
         </is>
@@ -1812,12 +1842,12 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="4" t="inlineStr">
         <is>
           <t>Unit economics</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
         </is>
@@ -1829,12 +1859,12 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Tráfico frío</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
         </is>
@@ -1846,12 +1876,12 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>Front / producto principal</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
         </is>
@@ -1863,12 +1893,12 @@
       </c>
     </row>
     <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Pitch</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
         </is>
@@ -1880,12 +1910,12 @@
       </c>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>VSL</t>
         </is>
       </c>
-      <c r="C37" s="4" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
         </is>
@@ -1897,12 +1927,12 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>B2B</t>
         </is>
       </c>
-      <c r="C38" s="4" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
         </is>
@@ -1914,12 +1944,12 @@
       </c>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Self-serve</t>
         </is>
       </c>
-      <c r="C39" s="4" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
         </is>
@@ -1931,12 +1961,12 @@
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="3" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>OTO 1 a 4</t>
         </is>
       </c>
-      <c r="C40" s="4" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>La secuencia de hasta cuatro páginas después del pago: upsell, downsell, upsell, downsell. Cada una se mide como % de los compradores del principal.</t>
         </is>
@@ -1948,12 +1978,12 @@
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Ascensión</t>
         </is>
       </c>
-      <c r="C41" s="4" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>El upsell de mayor valor que se ofrece después del embudo (un programa de 300 a 1.000 USD), por checkout o por llamada.</t>
         </is>
@@ -1967,10 +1997,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -1983,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1992,32 +2022,39 @@
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Chequeos: el modelo se revisa solo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Si alguna fila dice REVISAR, hay un supuesto fuera de rango o un dato inconsistente.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Chequeo</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Qué revisar</t>
         </is>
@@ -2029,11 +2066,11 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="36">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2045,11 +2082,11 @@
           <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="36">
         <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2061,11 +2098,11 @@
           <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2077,11 +2114,11 @@
           <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2093,11 +2130,11 @@
           <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="36">
         <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2109,11 +2146,11 @@
           <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
@@ -2125,11 +2162,11 @@
           <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="36">
         <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$12&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
         </is>
@@ -2141,11 +2178,11 @@
           <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="36">
         <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
         </is>
@@ -2157,11 +2194,11 @@
           <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Si suman más, revisá los porcentajes.</t>
         </is>
@@ -2173,11 +2210,11 @@
           <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Supuestos → celda 'Escenario en uso'.</t>
         </is>
@@ -2189,11 +2226,11 @@
           <t>La inversión es mayor a cero</t>
         </is>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="36">
         <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr"/>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -2201,11 +2238,11 @@
           <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="36">
         <f>IF('Modelo'!$C$11&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
         </is>
@@ -2217,11 +2254,11 @@
           <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="36">
         <f>IF(AND('Supuestos'!$C$12&gt;=0,'Supuestos'!$C$12&lt;=1,'Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$28&gt;=0,'Supuestos'!$C$28&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
         </is>
@@ -2233,11 +2270,11 @@
           <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="36">
         <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr"/>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
@@ -2245,11 +2282,11 @@
           <t>El crecimiento mensual está entre −50 % y 100 %</t>
         </is>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Más de 100 % por mes no es realista para una proyección.</t>
         </is>
@@ -2261,23 +2298,23 @@
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="36">
         <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$8,'Modelo'!$C$10&lt;='Modelo'!$C$9),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Si falla, alguna conversión está por encima de 100 %.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C23" s="36">
+      <c r="C23" s="37">
         <f>IF(COUNTIF(C6:C21,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -2293,13 +2330,87 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001F3864"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="B2:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Autoría y licencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero · Embudo low-ticket con bumps y upsells</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>v1.2 · octubre 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Licencia Creative Commons BY-NC-ND 4.0: podés usar este archivo con tus números y compartirlo tal cual, citando al autor. No podés venderlo, modificar su estructura para redistribuirlo ni quitar la línea de autoría.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Este archivo, sus fórmulas, sus umbrales y su método son obra de Jesús Tassarolo (TooAudience). Si lo compartís, compartilo entero y con esta hoja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Canal: youtube.com/@JesusTassaroloSinFiltro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -2309,7 +2420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D36"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2318,45 +2429,52 @@
     <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Resumen: lo que hay que mirar</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Todo sale de Modelo con los supuestos del escenario en uso. Cambiá Supuestos y esto se actualiza.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Qué significa</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Resultado del mes</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -2364,11 +2482,11 @@
           <t>Ganancia del período</t>
         </is>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="9">
         <f>'Modelo'!$C$41</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Cash neto menos costos y menos inversión. Lo que queda.</t>
         </is>
@@ -2380,11 +2498,11 @@
           <t>ROAS sobre cash neto</t>
         </is>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="10">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Cada dólar invertido vuelve como esto, ya neto.</t>
         </is>
@@ -2396,11 +2514,11 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="10">
         <f>'Modelo'!$C$42</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Sobre facturado. Se infla con cuotas y comisiones: no decidas con este.</t>
         </is>
@@ -2412,24 +2530,24 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Ventas del producto principal por mes.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Unit economics</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -2437,11 +2555,11 @@
           <t>Facturado por comprador (AOV)</t>
         </is>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <f>'Modelo'!$C$30</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Facturado por comprador sumando toda la escalera.</t>
         </is>
@@ -2453,11 +2571,11 @@
           <t>Costo por comprador (CPA)</t>
         </is>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="12">
         <f>'Modelo'!$C$12</f>
         <v/>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Lo que te cuesta cada comprador.</t>
         </is>
@@ -2469,11 +2587,11 @@
           <t>AOV neto − CPA (lo que queda por comprador)</t>
         </is>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="12">
         <f>'Modelo'!$C$54</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Si es negativo, cada venta pierde plata.</t>
         </is>
@@ -2485,24 +2603,24 @@
           <t>Valor neto por visita</t>
         </is>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="12">
         <f>'Modelo'!$C$47</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Lo que vale una visita en cash neto.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Las dos caras de cada número</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
@@ -2510,11 +2628,11 @@
           <t>Costo por visita</t>
         </is>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="12">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Lo que pagás por cada visita.</t>
         </is>
@@ -2526,11 +2644,11 @@
           <t>Ganancia por visita</t>
         </is>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="12">
         <f>'Modelo'!$C$60</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada visita después de todo. La métrica más valiosa del embudo.</t>
         </is>
@@ -2542,11 +2660,11 @@
           <t>Costo por cliente (CPA)</t>
         </is>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="12">
         <f>'Modelo'!$C$12</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Lo que pagás por cada comprador.</t>
         </is>
@@ -2558,11 +2676,11 @@
           <t>Ganancia por cliente</t>
         </is>
       </c>
-      <c r="C20" s="11">
+      <c r="C20" s="12">
         <f>'Modelo'!$C$62</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Lo que te queda por cada comprador después de todo.</t>
         </is>
@@ -2574,11 +2692,11 @@
           <t>Order value (AOV)</t>
         </is>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="12">
         <f>'Modelo'!$C$30</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Facturado por comprador con toda la escalera.</t>
         </is>
@@ -2590,24 +2708,24 @@
           <t>Order value neto (AOV neto)</t>
         </is>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="12">
         <f>'Modelo'!$C$53</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Lo mismo después de comisiones, reembolsos y costos por unidad.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Hasta cuánto pagar</t>
         </is>
       </c>
-      <c r="C23" s="7" t="n"/>
-      <c r="D23" s="7" t="n"/>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
@@ -2615,11 +2733,11 @@
           <t>Techo de costo por visita (break-even)</t>
         </is>
       </c>
-      <c r="C24" s="11">
+      <c r="C24" s="12">
         <f>'Modelo'!$C$48</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Costo por visita donde no ganás ni perdés.</t>
         </is>
@@ -2631,11 +2749,11 @@
           <t>Objetivo de costo por visita</t>
         </is>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="12">
         <f>'Modelo'!$C$49</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>A este costo o menos estás en verde.</t>
         </is>
@@ -2647,11 +2765,11 @@
           <t>Techo de costo por comprador (CPA máximo)</t>
         </is>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="12">
         <f>'Modelo'!$C$51</f>
         <v/>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>CPA máximo si lo demás se mantiene.</t>
         </is>
@@ -2663,24 +2781,24 @@
           <t>Semáforo del costo por visita actual</t>
         </is>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="13">
         <f>'Modelo'!$C$56</f>
         <v/>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Tu costo por visita actual contra techo y objetivo.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>Cuánto invertir y cuánta caja</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n"/>
-      <c r="D28" s="7" t="n"/>
+      <c r="C28" s="8" t="n"/>
+      <c r="D28" s="8" t="n"/>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -2688,11 +2806,11 @@
           <t>Inversión necesaria para la meta de ventas (al costo actual)</t>
         </is>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="9">
         <f>'Modelo'!$C$57</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Para llegar a la meta de ventas de Supuestos, al costo actual.</t>
         </is>
@@ -2704,11 +2822,11 @@
           <t>Caja que hay que tener (peor momento de la proyección)</t>
         </is>
       </c>
-      <c r="C30" s="8">
+      <c r="C30" s="9">
         <f>'Proyección 12 meses'!$C$18</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Si da 0, el embudo se autofinancia: cada mes cobra más de lo que invierte.</t>
         </is>
@@ -2720,11 +2838,11 @@
           <t>Saldo mínimo de caja con tu caja inicial</t>
         </is>
       </c>
-      <c r="C31" s="8">
+      <c r="C31" s="9">
         <f>'Proyección 12 meses'!$C$19</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Si es negativo, la caja inicial no alcanza.</t>
         </is>
@@ -2736,30 +2854,30 @@
           <t>Ganancia acumulada en 12 meses</t>
         </is>
       </c>
-      <c r="C32" s="8">
+      <c r="C32" s="9">
         <f>'Proyección 12 meses'!$C$20</f>
         <v/>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Con la inversión creciendo según el supuesto.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="32" customHeight="1">
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Recomendación según el semáforo</t>
         </is>
       </c>
-      <c r="C34" s="13">
+      <c r="C34" s="14">
         <f>IF('Modelo'!$C$56="VERDE","Sostener o subir un escalón (+25 %) y medir 7 días",IF('Modelo'!$C$56="AMARILLO","No subir. Si el costo está bien, el ROAS no llega al objetivo: mirá Sensibilidad. Si no, revisar en orden: CPM, creativo, página",IF('Modelo'!$C$56="ROJO","Bajar un escalón (−25 %) y arreglar antes de volver a subir","")))</f>
         <v/>
       </c>
-      <c r="D34" s="14" t="n"/>
+      <c r="D34" s="15" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="3" t="inlineStr">
         <is>
           <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · v1.2 · octubre 2026</t>
         </is>
@@ -2782,10 +2900,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -2798,7 +2916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2812,69 +2930,76 @@
     <col width="50" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Embudo: todos los pasos, cuántos pasan y, por cada uno, qué pagás, qué te queda y hasta cuánto podrías pagar</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila es un paso del embudo en orden. '% que pasa' compara con el paso anterior (o con el que dice la nota). Tres números por paso: lo que pagás hoy por cada uno (inversión ÷ cantidad), lo que te queda por cada uno (ganancia ÷ cantidad) y lo máximo que podrías pagar (el techo: lo que cada uno genera en cash neto). Techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Paso</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cantidad</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>% que pasa</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>% acumulado</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Costo por paso (pagás hoy)</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Ganancia por paso (te queda)</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Techo por paso (máximo a pagar)</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Qué se paga acá / cómo se lee</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Visitas a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="16">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
@@ -2883,23 +3008,23 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$8/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="12">
         <f>IF('Modelo'!$C$8=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="12">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$41*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="12">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$47*'Modelo'!$C$8*1/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
         <is>
           <t>La unidad que compra la pauta. Costo por visita.</t>
         </is>
@@ -2911,67 +3036,67 @@
           <t>Abren el checkout</t>
         </is>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="16">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="18">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="12">
         <f>IF('Modelo'!$C$9=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="12">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="12">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$47*'Modelo'!$C$8*1/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>Costo por checkout. Si se pierde mucho acá, es la VSL.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Compran el producto principal</t>
         </is>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="16">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="17">
+      <c r="D8" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$10/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="16">
+      <c r="E8" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Supuestos'!$C$8*1/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$41*1/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$47*'Modelo'!$C$8*1/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="I8" s="4" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>CPA: costo por comprador. Si se pierde mucho acá, es el checkout o la oferta.</t>
         </is>
@@ -2983,15 +3108,15 @@
           <t>Toman el bump 1</t>
         </is>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="16">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D9" s="17">
+      <c r="D9" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$15/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E9" s="16">
+      <c r="E9" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$15/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3010,7 +3135,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores del principal. Se pagó con el CPA; suma al AOV.</t>
         </is>
@@ -3022,15 +3147,15 @@
           <t>Toman el bump 2</t>
         </is>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="16">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D10" s="17">
+      <c r="D10" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$17/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E10" s="16">
+      <c r="E10" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$17/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3049,7 +3174,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I10" s="4" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores del principal.</t>
         </is>
@@ -3061,15 +3186,15 @@
           <t>Toman la OTO 1</t>
         </is>
       </c>
-      <c r="C11" s="15">
+      <c r="C11" s="16">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="17">
+      <c r="D11" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$19/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E11" s="16">
+      <c r="E11" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$19/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3088,7 +3213,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>Página 1 después del pago.</t>
         </is>
@@ -3100,15 +3225,15 @@
           <t>Toman la OTO 2</t>
         </is>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="16">
         <f>'Modelo'!$C$21</f>
         <v/>
       </c>
-      <c r="D12" s="17">
+      <c r="D12" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$21/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E12" s="16">
+      <c r="E12" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$21/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3127,7 +3252,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>Página 2 (downsell de la OTO 1).</t>
         </is>
@@ -3139,15 +3264,15 @@
           <t>Toman la OTO 3</t>
         </is>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="16">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="17">
+      <c r="D13" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$23/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E13" s="16">
+      <c r="E13" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$23/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3166,7 +3291,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>Página 3.</t>
         </is>
@@ -3178,15 +3303,15 @@
           <t>Toman la OTO 4</t>
         </is>
       </c>
-      <c r="C14" s="15">
+      <c r="C14" s="16">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="D14" s="17">
+      <c r="D14" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$25/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E14" s="16">
+      <c r="E14" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$25/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3205,7 +3330,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>Página 4.</t>
         </is>
@@ -3217,15 +3342,15 @@
           <t>Ascienden al programa</t>
         </is>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="16">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="17">
+      <c r="D15" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$27/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E15" s="16">
+      <c r="E15" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$27/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3244,80 +3369,80 @@
           <t>—</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>Sobre compradores del principal. El AOV neto resultante contra el CPA es lo que decide el embudo.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
         </is>
       </c>
-      <c r="F17" s="18">
+      <c r="F17" s="19">
         <f>F6</f>
         <v/>
       </c>
-      <c r="G17" s="18">
+      <c r="G17" s="19">
         <f>G6</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="12">
         <f>F6+G6+'Supuestos'!$C$37/'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>Techo = costo + ganancia + fijos ÷ unidades. Lo que falta entre (costo + ganancia) y el techo son los costos fijos repartidos entre las unidades.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Cómo se lee</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Cantidad: cuántas acciones o personas hubo en ese paso con los supuestos del escenario en uso.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>% que pasa: de los que estaban en el paso anterior (o en el paso que indica la nota), cuántos llegan a este. % acumulado: cuántos llegan a este paso por cada 100 unidades que compra la pauta.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Costo por paso: inversión ÷ cantidad. Es lo que te está costando hoy cada persona que llega a ese paso.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="28" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Ganancia por paso: ganancia del período ÷ cantidad. Lo que te queda por cada persona de ese paso después de pagar la pauta, las comisiones, los reembolsos y los fijos. La ganancia por visita es la métrica más valiosa del embudo: resume todo lo que pasa después.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="28" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Techo por paso: lo que cada persona de ese paso genera en cash neto (cash neto menos costos por unidad, dividido por la cantidad). Es lo máximo que podrías pagar por ese paso antes de que la ganancia llegue a cero, si lo demás se mantiene. Por eso siempre es mayor que la ganancia: techo = costo + ganancia + fijos repartidos.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="28" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Los bumps, las OTOs y la ascensión no tienen costo propio: se pagan con el CPA del comprador principal y se miden por lo que suman al AOV.</t>
         </is>
@@ -3334,10 +3459,10 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -3350,7 +3475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H49"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3363,64 +3488,71 @@
     <col width="70" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Supuestos</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Celdas amarillas = las editás vos. Celdas azules = se calculan solas. Cada fila dice en qué unidad va y de dónde sale el valor del ejemplo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Supuesto</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor en uso</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Conservador</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Base</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Optimista</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Unidad</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Nota / fuente del ejemplo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="19" t="n">
+      <c r="C6" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -3428,24 +3560,24 @@
           <t>1 / 2 / 3</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Cambia todas las filas que tienen tres valores. Si una fila no tiene tres valores, se usa el de 'Valor en uso'.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>1. Inversión y tráfico</t>
         </is>
       </c>
-      <c r="C7" s="7" t="n"/>
-      <c r="D7" s="7" t="n"/>
-      <c r="E7" s="7" t="n"/>
-      <c r="F7" s="7" t="n"/>
-      <c r="G7" s="7" t="n"/>
-      <c r="H7" s="7" t="n"/>
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="8" t="n"/>
+      <c r="F7" s="8" t="n"/>
+      <c r="G7" s="8" t="n"/>
+      <c r="H7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -3453,7 +3585,7 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="20" t="n">
+      <c r="C8" s="21" t="n">
         <v>9000</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -3461,7 +3593,7 @@
           <t>USD / mes</t>
         </is>
       </c>
-      <c r="H8" s="4" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>El ejemplo invierte 300 USD por día.</t>
         </is>
@@ -3473,17 +3605,17 @@
           <t>Costo por visita a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>IF('Supuestos'!$C$6=1,D9,IF('Supuestos'!$C$6=2,E9,F9))</f>
         <v/>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="22" t="n">
         <v>0.3</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="22" t="n">
         <v>0.22</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -3491,24 +3623,24 @@
           <t>USD / visita</t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr">
         <is>
           <t>Lo que pagás por cada persona que llega a la página. En tráfico frío hispano se mueve entre 0,20 y 0,50.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>2. Conversión de la página de ventas</t>
         </is>
       </c>
-      <c r="C11" s="7" t="n"/>
-      <c r="D11" s="7" t="n"/>
-      <c r="E11" s="7" t="n"/>
-      <c r="F11" s="7" t="n"/>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="7" t="n"/>
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="8" t="n"/>
+      <c r="E11" s="8" t="n"/>
+      <c r="F11" s="8" t="n"/>
+      <c r="G11" s="8" t="n"/>
+      <c r="H11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -3516,17 +3648,17 @@
           <t>% de visitas que llegan al checkout</t>
         </is>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="18">
         <f>IF('Supuestos'!$C$6=1,D12,IF('Supuestos'!$C$6=2,E12,F12))</f>
         <v/>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>0.025</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>0.035</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>0.045</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -3534,7 +3666,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>Visitas que tocan 'comprar' y abren el checkout.</t>
         </is>
@@ -3546,17 +3678,17 @@
           <t>% de checkouts que terminan en compra</t>
         </is>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="18">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="23" t="n">
         <v>0.26</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -3564,24 +3696,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>Checkouts que pagan.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>3. Escalera: producto principal → bumps 1 y 2 → OTO 1 a 4 → ascensión (precio y % sobre compradores del principal)</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n"/>
-      <c r="D15" s="7" t="n"/>
-      <c r="E15" s="7" t="n"/>
-      <c r="F15" s="7" t="n"/>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="7" t="n"/>
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="8" t="n"/>
+      <c r="F15" s="8" t="n"/>
+      <c r="G15" s="8" t="n"/>
+      <c r="H15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
@@ -3589,7 +3721,7 @@
           <t>Producto principal: precio</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="22" t="n">
         <v>37</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -3597,7 +3729,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H16" s="4" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>El producto que vende la VSL. Todo lo demás se mide como % de sus compradores.</t>
         </is>
@@ -3609,7 +3741,7 @@
           <t>Bump 1: precio</t>
         </is>
       </c>
-      <c r="C17" s="21" t="n">
+      <c r="C17" s="22" t="n">
         <v>17</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -3617,7 +3749,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr">
         <is>
           <t>Oferta extra en el checkout del principal (una casilla). % sobre compradores del principal.</t>
         </is>
@@ -3629,17 +3761,17 @@
           <t>Bump 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="23" t="n">
         <v>0.35</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -3647,7 +3779,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H18" s="4" t="inlineStr"/>
+      <c r="H18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -3655,7 +3787,7 @@
           <t>Bump 2: precio</t>
         </is>
       </c>
-      <c r="C19" s="21" t="n">
+      <c r="C19" s="22" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -3663,7 +3795,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H19" s="4" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>Segundo bump en el mismo checkout. Rinde algo menos que el primero.</t>
         </is>
@@ -3675,17 +3807,17 @@
           <t>Bump 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="18">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.12</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F20" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -3693,7 +3825,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr"/>
+      <c r="H20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -3701,7 +3833,7 @@
           <t>OTO 1: precio</t>
         </is>
       </c>
-      <c r="C21" s="21" t="n">
+      <c r="C21" s="22" t="n">
         <v>47</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -3709,7 +3841,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr">
         <is>
           <t>Página 1 después del pago: el primer upsell. % sobre compradores del principal.</t>
         </is>
@@ -3721,17 +3853,17 @@
           <t>OTO 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="18">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="23" t="n">
         <v>0.14</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -3739,7 +3871,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -3747,7 +3879,7 @@
           <t>OTO 2: precio</t>
         </is>
       </c>
-      <c r="C23" s="21" t="n">
+      <c r="C23" s="22" t="n">
         <v>17</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -3755,7 +3887,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H23" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>Página 2: suele ser el downsell de la OTO 1 (más barato). El % va sobre todos los compradores, para simplificar.</t>
         </is>
@@ -3767,17 +3899,17 @@
           <t>OTO 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="18">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.04</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="23" t="n">
         <v>0.06</v>
       </c>
-      <c r="F24" s="22" t="n">
+      <c r="F24" s="23" t="n">
         <v>0.09</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -3785,7 +3917,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H24" s="4" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -3793,7 +3925,7 @@
           <t>OTO 3: precio</t>
         </is>
       </c>
-      <c r="C25" s="21" t="n">
+      <c r="C25" s="22" t="n">
         <v>97</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -3801,7 +3933,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
         <is>
           <t>Página 3: el segundo upsell.</t>
         </is>
@@ -3813,17 +3945,17 @@
           <t>OTO 3: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="18">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <v>0.02</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -3831,7 +3963,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr"/>
+      <c r="H26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -3839,7 +3971,7 @@
           <t>OTO 4: precio</t>
         </is>
       </c>
-      <c r="C27" s="21" t="n">
+      <c r="C27" s="22" t="n">
         <v>27</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -3847,7 +3979,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H27" s="4" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr">
         <is>
           <t>Página 4: el downsell del segundo upsell.</t>
         </is>
@@ -3859,17 +3991,17 @@
           <t>OTO 4: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="18">
         <f>IF('Supuestos'!$C$6=1,D28,IF('Supuestos'!$C$6=2,E28,F28))</f>
         <v/>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="23" t="n">
         <v>0.04</v>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="23" t="n">
         <v>0.06</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -3877,7 +4009,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H28" s="4" t="inlineStr"/>
+      <c r="H28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -3885,7 +4017,7 @@
           <t>Ascensión (programa de mayor valor): precio</t>
         </is>
       </c>
-      <c r="C29" s="21" t="n">
+      <c r="C29" s="22" t="n">
         <v>297</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -3893,7 +4025,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
         <is>
           <t>El upsell de ascensión: el programa que se vende después del embudo, por checkout o por llamada. % sobre compradores del principal.</t>
         </is>
@@ -3905,17 +4037,17 @@
           <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="18">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.01</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.02</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="23" t="n">
         <v>0.04</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -3923,20 +4055,20 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H30" s="4" t="inlineStr"/>
+      <c r="H30" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>4. Costos</t>
         </is>
       </c>
-      <c r="C32" s="7" t="n"/>
-      <c r="D32" s="7" t="n"/>
-      <c r="E32" s="7" t="n"/>
-      <c r="F32" s="7" t="n"/>
-      <c r="G32" s="7" t="n"/>
-      <c r="H32" s="7" t="n"/>
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="8" t="n"/>
+      <c r="F32" s="8" t="n"/>
+      <c r="G32" s="8" t="n"/>
+      <c r="H32" s="8" t="n"/>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -3944,7 +4076,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -3952,7 +4084,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H33" s="4" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
         <is>
           <t>Hotmart, Stripe, Mercado Pago: lo que se queda la plataforma.</t>
         </is>
@@ -3964,7 +4096,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -3972,7 +4104,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
         <is>
           <t>Sobre el cash cobrado. En este embudo no hay llamadas: 0 %.</t>
         </is>
@@ -3984,7 +4116,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -3992,7 +4124,7 @@
           <t>% del cash</t>
         </is>
       </c>
-      <c r="H35" s="4" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
         <is>
           <t>5 % es normal en productos digitales. Más de 10 % es un problema de oferta o de expectativa.</t>
         </is>
@@ -4004,7 +4136,7 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C36" s="21" t="n">
+      <c r="C36" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -4012,7 +4144,7 @@
           <t>USD / visita</t>
         </is>
       </c>
-      <c r="H36" s="4" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
         <is>
           <t>Costos que crecen con el volumen. En venta directa suele ser 0.</t>
         </is>
@@ -4024,7 +4156,7 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C37" s="20" t="n">
+      <c r="C37" s="21" t="n">
         <v>1500</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -4032,24 +4164,24 @@
           <t>USD / mes</t>
         </is>
       </c>
-      <c r="H37" s="4" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr">
         <is>
           <t>Equipo, herramientas, edición: lo que pagás aunque no vendas.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>5. Cobranza</t>
         </is>
       </c>
-      <c r="C39" s="7" t="n"/>
-      <c r="D39" s="7" t="n"/>
-      <c r="E39" s="7" t="n"/>
-      <c r="F39" s="7" t="n"/>
-      <c r="G39" s="7" t="n"/>
-      <c r="H39" s="7" t="n"/>
+      <c r="C39" s="8" t="n"/>
+      <c r="D39" s="8" t="n"/>
+      <c r="E39" s="8" t="n"/>
+      <c r="F39" s="8" t="n"/>
+      <c r="G39" s="8" t="n"/>
+      <c r="H39" s="8" t="n"/>
     </row>
     <row r="40">
       <c r="B40" t="inlineStr">
@@ -4057,7 +4189,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C40" s="22" t="n">
+      <c r="C40" s="23" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -4065,7 +4197,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H40" s="4" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr">
         <is>
           <t>Pago único digital: 100 % en el mes 1.</t>
         </is>
@@ -4077,7 +4209,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -4085,7 +4217,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H41" s="4" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr">
         <is>
           <t>Cuotas o pagos diferidos.</t>
         </is>
@@ -4097,7 +4229,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n">
+      <c r="C42" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -4105,24 +4237,24 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H42" s="4" t="inlineStr">
+      <c r="H42" s="5" t="inlineStr">
         <is>
           <t>Los tres deben sumar 100 %.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>6. Objetivos y proyección</t>
         </is>
       </c>
-      <c r="C44" s="7" t="n"/>
-      <c r="D44" s="7" t="n"/>
-      <c r="E44" s="7" t="n"/>
-      <c r="F44" s="7" t="n"/>
-      <c r="G44" s="7" t="n"/>
-      <c r="H44" s="7" t="n"/>
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="8" t="n"/>
+      <c r="E44" s="8" t="n"/>
+      <c r="F44" s="8" t="n"/>
+      <c r="G44" s="8" t="n"/>
+      <c r="H44" s="8" t="n"/>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -4130,7 +4262,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C45" s="23" t="n">
+      <c r="C45" s="24" t="n">
         <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -4138,7 +4270,7 @@
           <t>x</t>
         </is>
       </c>
-      <c r="H45" s="4" t="inlineStr">
+      <c r="H45" s="5" t="inlineStr">
         <is>
           <t>El retorno mínimo que querés por cada dólar invertido, después de comisiones y reembolsos. Entra en el semáforo: sin llegar a este ROAS no hay verde.</t>
         </is>
@@ -4150,7 +4282,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n">
+      <c r="C46" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -4158,7 +4290,7 @@
           <t>%</t>
         </is>
       </c>
-      <c r="H46" s="4" t="inlineStr">
+      <c r="H46" s="5" t="inlineStr">
         <is>
           <t>Colchón entre el techo (donde no ganás ni perdés) y el objetivo. 30 % es el estándar que usamos.</t>
         </is>
@@ -4170,7 +4302,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C47" s="19" t="n">
+      <c r="C47" s="20" t="n">
         <v>500</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -4178,7 +4310,7 @@
           <t>ventas / mes</t>
         </is>
       </c>
-      <c r="H47" s="4" t="inlineStr">
+      <c r="H47" s="5" t="inlineStr">
         <is>
           <t>Para calcular cuánto invertir.</t>
         </is>
@@ -4190,7 +4322,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C48" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -4198,7 +4330,7 @@
           <t>% / mes</t>
         </is>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="H48" s="5" t="inlineStr">
         <is>
           <t>Cuánto sube la inversión cada mes en la proyección. 10 % por mes es un ritmo prudente; más de 25 % suele encarecer el CPM.</t>
         </is>
@@ -4210,7 +4342,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C49" s="20" t="n">
+      <c r="C49" s="21" t="n">
         <v>5000</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -4218,7 +4350,7 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="H49" s="4" t="inlineStr">
+      <c r="H49" s="5" t="inlineStr">
         <is>
           <t>Con cuánta plata arrancás. La proyección te dice si alcanza.</t>
         </is>
@@ -4227,10 +4359,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -4243,7 +4375,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D62"/>
+  <dimension ref="A1:D62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4252,45 +4384,52 @@
     <col width="72" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Modelo: la cadena completa del embudo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila es una etapa o un resultado. No se edita: todo sale de Supuestos. La columna de la derecha dice cómo se calcula.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Etapa / resultado</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Valor</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Tráfico y unidades</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -4298,27 +4437,27 @@
           <t>Costo por visita (unidad de adquisición)</t>
         </is>
       </c>
-      <c r="C7" s="18">
+      <c r="C7" s="19">
         <f>'Supuestos'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>El supuesto 'costo por visita'.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ costo por visita.</t>
         </is>
@@ -4330,27 +4469,27 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="16">
         <f>'Modelo'!$C$8*'Supuestos'!$C$12</f>
         <v/>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Visitas × % que llega al checkout.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C10" s="10">
+      <c r="C10" s="11">
         <f>'Modelo'!$C$9*'Supuestos'!$C$13</f>
         <v/>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Checkouts × % que compra.</t>
         </is>
@@ -4362,40 +4501,40 @@
           <t>% de visitas que compran</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Ventas ÷ visitas. Las dos conversiones multiplicadas.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Costo por comprador (CPA)</t>
         </is>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Supuestos'!$C$8/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D12" s="4" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Inversión ÷ ventas del principal.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Facturación por producto</t>
         </is>
       </c>
-      <c r="C13" s="7" t="n"/>
-      <c r="D13" s="7" t="n"/>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
@@ -4403,11 +4542,11 @@
           <t>Facturado: producto principal</t>
         </is>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>'Modelo'!$C$10*'Supuestos'!$C$16</f>
         <v/>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4419,11 +4558,11 @@
           <t>Ventas: Bump 1</t>
         </is>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$18</f>
         <v/>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4435,11 +4574,11 @@
           <t>Facturado: Bump 1</t>
         </is>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Modelo'!$C$15*'Supuestos'!$C$17</f>
         <v/>
       </c>
-      <c r="D16" s="4" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4451,11 +4590,11 @@
           <t>Ventas: Bump 2</t>
         </is>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$20</f>
         <v/>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4467,11 +4606,11 @@
           <t>Facturado: Bump 2</t>
         </is>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <f>'Modelo'!$C$17*'Supuestos'!$C$19</f>
         <v/>
       </c>
-      <c r="D18" s="4" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4483,11 +4622,11 @@
           <t>Ventas: OTO 1</t>
         </is>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$22</f>
         <v/>
       </c>
-      <c r="D19" s="4" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4499,11 +4638,11 @@
           <t>Facturado: OTO 1</t>
         </is>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>'Modelo'!$C$19*'Supuestos'!$C$21</f>
         <v/>
       </c>
-      <c r="D20" s="4" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4515,11 +4654,11 @@
           <t>Ventas: OTO 2</t>
         </is>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$24</f>
         <v/>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4531,11 +4670,11 @@
           <t>Facturado: OTO 2</t>
         </is>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <f>'Modelo'!$C$21*'Supuestos'!$C$23</f>
         <v/>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4547,11 +4686,11 @@
           <t>Ventas: OTO 3</t>
         </is>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$26</f>
         <v/>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4563,11 +4702,11 @@
           <t>Facturado: OTO 3</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>'Modelo'!$C$23*'Supuestos'!$C$25</f>
         <v/>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4579,11 +4718,11 @@
           <t>Ventas: OTO 4</t>
         </is>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$28</f>
         <v/>
       </c>
-      <c r="D25" s="4" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4595,11 +4734,11 @@
           <t>Facturado: OTO 4</t>
         </is>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <f>'Modelo'!$C$25*'Supuestos'!$C$27</f>
         <v/>
       </c>
-      <c r="D26" s="4" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
@@ -4611,11 +4750,11 @@
           <t>Ventas: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$30</f>
         <v/>
       </c>
-      <c r="D27" s="4" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Compradores del principal × % que lo toma.</t>
         </is>
@@ -4627,43 +4766,43 @@
           <t>Facturado: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C28" s="25">
+      <c r="C28" s="26">
         <f>'Modelo'!$C$27*'Supuestos'!$C$29</f>
         <v/>
       </c>
-      <c r="D28" s="4" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Ventas × precio.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Facturado total</t>
         </is>
       </c>
-      <c r="C29" s="8">
+      <c r="C29" s="9">
         <f>'Modelo'!$C$14+'Modelo'!$C$16+'Modelo'!$C$18+'Modelo'!$C$20+'Modelo'!$C$22+'Modelo'!$C$24+'Modelo'!$C$26+'Modelo'!$C$28</f>
         <v/>
       </c>
-      <c r="D29" s="4" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Suma de todos los productos.</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Facturado por comprador (AOV)</t>
         </is>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$29/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D30" s="4" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Facturado total ÷ ventas del principal.</t>
         </is>
@@ -4675,11 +4814,11 @@
           <t>AOV ÷ precio del principal</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>IF('Supuestos'!$C$16=0,0,'Modelo'!$C$30/'Supuestos'!$C$16)</f>
         <v/>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Cuánto multiplica la escalera al precio del front.</t>
         </is>
@@ -4691,11 +4830,11 @@
           <t>Ventas del principal por visita (para la proyección)</t>
         </is>
       </c>
-      <c r="C32" s="16">
+      <c r="C32" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>Igual a '% de visitas que compran'.</t>
         </is>
@@ -4707,24 +4846,24 @@
           <t>Facturado por visita</t>
         </is>
       </c>
-      <c r="C33" s="18">
+      <c r="C33" s="19">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$29/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Facturado total ÷ visitas.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>Cash, costos y ganancia del período</t>
         </is>
       </c>
-      <c r="C34" s="7" t="n"/>
-      <c r="D34" s="7" t="n"/>
+      <c r="C34" s="8" t="n"/>
+      <c r="D34" s="8" t="n"/>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -4732,11 +4871,11 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>'Modelo'!$C$29*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42)</f>
         <v/>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Facturado × (mes 1 + mes 2 + mes 3). Si la cobranza suma 100 %, es igual al facturado.</t>
         </is>
@@ -4748,11 +4887,11 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <f>'Modelo'!$C$29*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Facturado × % del mes 1.</t>
         </is>
@@ -4764,11 +4903,11 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="26">
         <f>'Modelo'!$C$35*('Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
-      <c r="D37" s="4" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Cash × (pasarela + equipo de ventas).</t>
         </is>
@@ -4780,27 +4919,27 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="26">
         <f>'Modelo'!$C$35*'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D38" s="4" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Cash × % de reembolsos.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="3" t="inlineStr">
+      <c r="B39" s="4" t="inlineStr">
         <is>
           <t>Cash neto</t>
         </is>
       </c>
-      <c r="C39" s="8">
+      <c r="C39" s="9">
         <f>'Modelo'!$C$35*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D39" s="4" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Cash − comisiones − reembolsos. La base de verdad.</t>
         </is>
@@ -4812,27 +4951,27 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C40" s="25">
+      <c r="C40" s="26">
         <f>'Modelo'!$C$8*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D40" s="4" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Visitas × costo por visita.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="3" t="inlineStr">
+      <c r="B41" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período</t>
         </is>
       </c>
-      <c r="C41" s="8">
+      <c r="C41" s="9">
         <f>'Modelo'!$C$39-'Modelo'!$C$40-'Supuestos'!$C$37-'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Cash neto − costos por unidad − fijos − inversión.</t>
         </is>
@@ -4844,27 +4983,27 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$29/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D42" s="4" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Facturado ÷ inversión. El número que más se infla: no decidas con este.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B43" s="4" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto</t>
         </is>
       </c>
-      <c r="C43" s="9">
+      <c r="C43" s="10">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$39/'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Cash neto ÷ inversión. Con este se decide.</t>
         </is>
@@ -4876,11 +5015,11 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C44" s="17">
+      <c r="C44" s="18">
         <f>IF('Modelo'!$C$35=0,0,'Modelo'!$C$41/'Modelo'!$C$35)</f>
         <v/>
       </c>
-      <c r="D44" s="4" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Ganancia ÷ cash.</t>
         </is>
@@ -4892,68 +5031,68 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>IF('Modelo'!$C$43&gt;='Supuestos'!$C$45,"SÍ","NO")</f>
         <v/>
       </c>
-      <c r="D45" s="4" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto contra el objetivo de Supuestos.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Cuánto vale cada unidad y hasta cuánto pagar</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n"/>
-      <c r="D46" s="7" t="n"/>
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="8" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
         <is>
           <t>Valor neto por visita</t>
         </is>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="12">
         <f>IF('Modelo'!$C$8=0,0,('Modelo'!$C$39-'Modelo'!$C$40)/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D47" s="4" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>(Cash neto − costos por unidad) ÷ visitas. Lo que vale una visita.</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Techo de costo por visita (break-even)</t>
         </is>
       </c>
-      <c r="C48" s="11">
+      <c r="C48" s="12">
         <f>'Modelo'!$C$47</f>
         <v/>
       </c>
-      <c r="D48" s="4" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Igual al valor neto por visita: pagando esto no ganás ni perdés.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Objetivo de costo por visita</t>
         </is>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="12">
         <f>'Modelo'!$C$48/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D49" s="5" t="inlineStr">
         <is>
           <t>Techo ÷ (1 + margen de seguridad).</t>
         </is>
@@ -4965,27 +5104,27 @@
           <t>Techo de costo por checkout</t>
         </is>
       </c>
-      <c r="C50" s="18">
+      <c r="C50" s="19">
         <f>IF('Supuestos'!$C$12=0,0,'Modelo'!$C$47/'Supuestos'!$C$12)</f>
         <v/>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D50" s="5" t="inlineStr">
         <is>
           <t>Valor por visita ÷ % que llega al checkout.</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Techo de costo por comprador (CPA máximo)</t>
         </is>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="12">
         <f>IF('Modelo'!$C$11=0,0,'Modelo'!$C$47/'Modelo'!$C$11)</f>
         <v/>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
         <is>
           <t>Valor por visita ÷ % de visitas que compran.</t>
         </is>
@@ -4997,11 +5136,11 @@
           <t>Objetivo de CPA</t>
         </is>
       </c>
-      <c r="C52" s="18">
+      <c r="C52" s="19">
         <f>'Modelo'!$C$51/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
-      <c r="D52" s="4" t="inlineStr">
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>CPA máximo ÷ (1 + margen de seguridad).</t>
         </is>
@@ -5013,68 +5152,68 @@
           <t>Cash neto por comprador (AOV neto)</t>
         </is>
       </c>
-      <c r="C53" s="18">
+      <c r="C53" s="19">
         <f>IF('Modelo'!$C$10=0,0,('Modelo'!$C$39-'Modelo'!$C$40)/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D53" s="4" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Lo que deja cada comprador después de comisiones y reembolsos.</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>AOV neto − CPA (lo que queda por comprador)</t>
         </is>
       </c>
-      <c r="C54" s="11">
+      <c r="C54" s="12">
         <f>'Modelo'!$C$53-'Modelo'!$C$12</f>
         <v/>
       </c>
-      <c r="D54" s="4" t="inlineStr">
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Si es negativo, perdés plata con cada venta.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>Semáforo y cuánto invertir</t>
         </is>
       </c>
-      <c r="C55" s="7" t="n"/>
-      <c r="D55" s="7" t="n"/>
+      <c r="C55" s="8" t="n"/>
+      <c r="D55" s="8" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="3" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Semáforo del costo por visita actual</t>
         </is>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="13">
         <f>IF('Modelo'!$C$7&gt;'Modelo'!$C$48,"ROJO",IF(AND('Modelo'!$C$7&lt;='Modelo'!$C$49,'Modelo'!$C$43&gt;='Supuestos'!$C$45),"VERDE","AMARILLO"))</f>
         <v/>
       </c>
-      <c r="D56" s="4" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>Rojo: costo &gt; techo. Verde: costo ≤ objetivo y ROAS sobre cash neto ≥ objetivo. Amarillo: el resto.</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="3" t="inlineStr">
+      <c r="B57" s="4" t="inlineStr">
         <is>
           <t>Inversión necesaria para la meta de ventas (al costo actual)</t>
         </is>
       </c>
-      <c r="C57" s="8">
+      <c r="C57" s="9">
         <f>IF('Modelo'!$C$11=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$11*'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D57" s="4" t="inlineStr">
+      <c r="D57" s="5" t="inlineStr">
         <is>
           <t>Meta ÷ % de visitas que compran × costo por visita.</t>
         </is>
@@ -5086,36 +5225,36 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C58" s="25">
+      <c r="C58" s="26">
         <f>IF('Modelo'!$C$11=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$11*'Modelo'!$C$49)</f>
         <v/>
       </c>
-      <c r="D58" s="4" t="inlineStr">
+      <c r="D58" s="5" t="inlineStr">
         <is>
           <t>Lo mismo, al costo objetivo.</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>Ganancia por paso (las dos caras de cada número: costo por X y ganancia por X)</t>
         </is>
       </c>
-      <c r="C59" s="7" t="n"/>
-      <c r="D59" s="7" t="n"/>
+      <c r="C59" s="8" t="n"/>
+      <c r="D59" s="8" t="n"/>
     </row>
     <row r="60">
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Ganancia por visita</t>
         </is>
       </c>
-      <c r="C60" s="11">
+      <c r="C60" s="12">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$41/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ visitas. La métrica más valiosa del embudo: resume todo lo que pasa después de la página. Su par es el costo por visita.</t>
         </is>
@@ -5127,27 +5266,27 @@
           <t>Ganancia por checkout</t>
         </is>
       </c>
-      <c r="C61" s="18">
+      <c r="C61" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D61" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ checkouts. Su par es el costo por checkout.</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="3" t="inlineStr">
+      <c r="B62" s="4" t="inlineStr">
         <is>
           <t>Ganancia por cliente</t>
         </is>
       </c>
-      <c r="C62" s="11">
+      <c r="C62" s="12">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$41/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>Ganancia del período ÷ compradores del principal. Su par es el CPA; la diferencia entre AOV neto y CPA es lo que queda por cliente antes de fijos.</t>
         </is>
@@ -5167,10 +5306,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -5183,7 +5322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:H57"/>
+  <dimension ref="A1:H57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -5199,15 +5338,22 @@
     <col width="15" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Escenarios: qué pasa si cambian el precio, la conversión o el costo</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Las celdas amarillas de cada tabla (fila y columna) se pueden cambiar. Verde = ganancia, amarillo = cerca del cero, rojo = pérdida. Todo lo demás queda como en Supuestos.</t>
         </is>
@@ -5219,653 +5365,653 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$46</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Precio del producto principal × % de checkouts que compran → ganancia del mes</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Subir el precio suele bajar la conversión: la tabla muestra qué combinación gana.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Precio ↓  /  % checkout → compra →</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.18</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.22</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.26</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="G9" s="29" t="n">
+      <c r="G9" s="30" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="30" t="n">
+      <c r="B10" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="30" t="n">
+      <c r="B11" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="30" t="n">
+      <c r="B12" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="30" t="n">
+      <c r="B13" s="31" t="n">
         <v>67</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="30" t="n">
+      <c r="B14" s="31" t="n">
         <v>97</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Costo por visita × % de visitas que llegan al checkout → ganancia del mes</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>La tabla del tráfico: cuánto podés pagar por visita según lo que convierte la página.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Costo por visita ↓  /  % visita → checkout →</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.02</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.025</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.03</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.035</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="30" t="n">
         <v>0.04</v>
       </c>
-      <c r="H19" s="29" t="n">
+      <c r="H19" s="30" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="31" t="n">
+      <c r="B20" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G20" s="25">
+      <c r="G20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="31" t="n">
+      <c r="B21" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="25">
+      <c r="G21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="31" t="n">
+      <c r="B22" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="C22" s="25">
+      <c r="C22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="25">
+      <c r="E22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="25">
+      <c r="F22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="25">
+      <c r="G22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="31" t="n">
+      <c r="B23" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="25">
+      <c r="D23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="25">
+      <c r="E23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="25">
+      <c r="F23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="25">
+      <c r="G23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="31" t="n">
+      <c r="B25" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="25">
+      <c r="G25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="31" t="n">
+      <c r="B26" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G26" s="25">
+      <c r="G26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Cuánto invertir para una facturación objetivo, según el ROAS que querés</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>Inversión = facturación ÷ ROAS. Debajo: cuántas visitas hacen falta y cuánto podés pagar por cada una.</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C31" s="32" t="n">
+      <c r="C31" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="D31" s="32" t="n">
+      <c r="D31" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="32" t="n">
+      <c r="E31" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F31" s="32" t="n">
+      <c r="F31" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="32" t="n">
+      <c r="G31" s="33" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="30" t="n">
+      <c r="B32" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>$B32/C$31</f>
         <v/>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="26">
         <f>$B32/D$31</f>
         <v/>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="26">
         <f>$B32/E$31</f>
         <v/>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="26">
         <f>$B32/F$31</f>
         <v/>
       </c>
-      <c r="G32" s="25">
+      <c r="G32" s="26">
         <f>$B32/G$31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="30" t="n">
+      <c r="B33" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="25">
+      <c r="C33" s="26">
         <f>$B33/C$31</f>
         <v/>
       </c>
-      <c r="D33" s="25">
+      <c r="D33" s="26">
         <f>$B33/D$31</f>
         <v/>
       </c>
-      <c r="E33" s="25">
+      <c r="E33" s="26">
         <f>$B33/E$31</f>
         <v/>
       </c>
-      <c r="F33" s="25">
+      <c r="F33" s="26">
         <f>$B33/F$31</f>
         <v/>
       </c>
-      <c r="G33" s="25">
+      <c r="G33" s="26">
         <f>$B33/G$31</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="30" t="n">
+      <c r="B34" s="31" t="n">
         <v>30000</v>
       </c>
-      <c r="C34" s="25">
+      <c r="C34" s="26">
         <f>$B34/C$31</f>
         <v/>
       </c>
-      <c r="D34" s="25">
+      <c r="D34" s="26">
         <f>$B34/D$31</f>
         <v/>
       </c>
-      <c r="E34" s="25">
+      <c r="E34" s="26">
         <f>$B34/E$31</f>
         <v/>
       </c>
-      <c r="F34" s="25">
+      <c r="F34" s="26">
         <f>$B34/F$31</f>
         <v/>
       </c>
-      <c r="G34" s="25">
+      <c r="G34" s="26">
         <f>$B34/G$31</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="30" t="n">
+      <c r="B35" s="31" t="n">
         <v>50000</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <f>$B35/C$31</f>
         <v/>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="26">
         <f>$B35/D$31</f>
         <v/>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <f>$B35/E$31</f>
         <v/>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <f>$B35/F$31</f>
         <v/>
       </c>
-      <c r="G35" s="25">
+      <c r="G35" s="26">
         <f>$B35/G$31</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="30" t="n">
+      <c r="B36" s="31" t="n">
         <v>100000</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <f>$B36/C$31</f>
         <v/>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="26">
         <f>$B36/D$31</f>
         <v/>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="26">
         <f>$B36/E$31</f>
         <v/>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="26">
         <f>$B36/F$31</f>
         <v/>
       </c>
-      <c r="G36" s="25">
+      <c r="G36" s="26">
         <f>$B36/G$31</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Cantidad de visitas necesaria para esa facturación</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="33">
+      <c r="B38" s="34">
         <f>$B32</f>
         <v/>
       </c>
-      <c r="C38" s="15">
+      <c r="C38" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B32/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="33">
+      <c r="B39" s="34">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B33/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="33">
+      <c r="B40" s="34">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B34/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="33">
+      <c r="B41" s="34">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B35/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="33">
+      <c r="B42" s="34">
         <f>$B36</f>
         <v/>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B36/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="3" t="inlineStr">
+      <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Costo máximo por visita para cumplir cada ROAS (sobre facturado)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="34" t="n">
+      <c r="C45" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="D45" s="34" t="n">
+      <c r="D45" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="34" t="n">
+      <c r="E45" s="35" t="n">
         <v>2.5</v>
       </c>
-      <c r="F45" s="34" t="n">
+      <c r="F45" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="34" t="n">
+      <c r="G45" s="35" t="n">
         <v>4</v>
       </c>
     </row>
@@ -5875,65 +6021,65 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C46" s="18">
+      <c r="C46" s="19">
         <f>IF(C45=0,0,'Modelo'!$C$33/C45)</f>
         <v/>
       </c>
-      <c r="D46" s="18">
+      <c r="D46" s="19">
         <f>IF(D45=0,0,'Modelo'!$C$33/D45)</f>
         <v/>
       </c>
-      <c r="E46" s="18">
+      <c r="E46" s="19">
         <f>IF(E45=0,0,'Modelo'!$C$33/E45)</f>
         <v/>
       </c>
-      <c r="F46" s="18">
+      <c r="F46" s="19">
         <f>IF(F45=0,0,'Modelo'!$C$33/F45)</f>
         <v/>
       </c>
-      <c r="G46" s="18">
+      <c r="G46" s="19">
         <f>IF(G45=0,0,'Modelo'!$C$33/G45)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B47" s="3" t="inlineStr">
         <is>
           <t>Sobre cash neto, el techo real está en Modelo (ya descuenta comisiones y reembolsos).</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Guardarraíl: el ROAS mínimo que tiene que dar cada nivel de inversión para que subir valga la pena</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B51" s="3" t="inlineStr">
         <is>
           <t>Parte de tu inversión y tu ROAS actuales. Cada dólar extra tiene que devolver al menos 1,3 neto. Si al subir un escalón el ROAS real queda por debajo del mínimo de esa fila, volvé al escalón anterior.</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>Nivel de inversión</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>Inversión del período</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>ROAS mínimo (cash neto)</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>Ganancia mínima</t>
         </is>
@@ -5945,15 +6091,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C53" s="25">
+      <c r="C53" s="26">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="28">
         <f>IF(C53=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C53-'Supuestos'!$C$8))/C53)</f>
         <v/>
       </c>
-      <c r="E53" s="25">
+      <c r="E53" s="26">
         <f>C53*(D53-1)</f>
         <v/>
       </c>
@@ -5964,15 +6110,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C54" s="25">
+      <c r="C54" s="26">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="28">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="25">
+      <c r="E54" s="26">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -5983,15 +6129,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C55" s="25">
+      <c r="C55" s="26">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="25">
+      <c r="E55" s="26">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -6002,15 +6148,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C56" s="25">
+      <c r="C56" s="26">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="28">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="25">
+      <c r="E56" s="26">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -6021,15 +6167,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C57" s="25">
+      <c r="C57" s="26">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="28">
         <f>IF(C57=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C57-'Supuestos'!$C$8))/C57)</f>
         <v/>
       </c>
-      <c r="E57" s="25">
+      <c r="E57" s="26">
         <f>C57*(D57-1)</f>
         <v/>
       </c>
@@ -6061,10 +6207,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -6077,7 +6223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6089,59 +6235,66 @@
     <col width="10" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Sensibilidad: qué palanca mueve más la ganancia</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cada fila mejora una sola variable un 10 % (o baja un costo un 10 %) y recalcula la ganancia del período. El ranking dice qué conviene trabajar primero.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Palanca</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Cambio</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Ganancia nueva</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Diferencia</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Dif. %</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Ranking</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período con los supuestos actuales</t>
         </is>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="9">
         <f>'Modelo'!$C$41</f>
         <v/>
       </c>
@@ -6157,19 +6310,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <f>((((((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="17">
+      <c r="F7" s="18">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="16">
         <f>RANK(E7,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6185,19 +6338,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="17">
+      <c r="F8" s="18">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="15">
+      <c r="G8" s="16">
         <f>RANK(E8,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6213,19 +6366,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="17">
+      <c r="F9" s="18">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="15">
+      <c r="G9" s="16">
         <f>RANK(E9,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6241,19 +6394,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$16*1.1))+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="17">
+      <c r="F10" s="18">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="15">
+      <c r="G10" s="16">
         <f>RANK(E10,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6269,19 +6422,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$18*1.1))*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="17">
+      <c r="F11" s="18">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="15">
+      <c r="G11" s="16">
         <f>RANK(E11,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6297,19 +6450,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$22*1.1))*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="18">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="15">
+      <c r="G12" s="16">
         <f>RANK(E12,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6325,19 +6478,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$30*1.1))*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="17">
+      <c r="F13" s="18">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="15">
+      <c r="G13" s="16">
         <f>RANK(E13,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6353,19 +6506,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-('Supuestos'!$C$35*0.9)))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="17">
+      <c r="F14" s="18">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="15">
+      <c r="G14" s="16">
         <f>RANK(E14,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6373,10 +6526,10 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -6389,7 +6542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:O20"/>
+  <dimension ref="A1:O20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6409,87 +6562,94 @@
     <col width="15" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Proyección a 12 meses y caja</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>La inversión crece cada mes según el supuesto de crecimiento. El cash entra según la curva de cobranza (mes 1 / 2 / 3). La ganancia acumulada muestra cuánto dinero hace falta para sostener la pauta.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Mes 3</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Mes 4</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Mes 5</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Mes 6</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Mes 7</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Mes 8</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Mes 9</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Mes 10</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mes 11</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Mes 12</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
@@ -6501,55 +6661,55 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <f>'Supuestos'!$C$8*1</f>
         <v/>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <f>C6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>D6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <f>E6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="26">
         <f>F6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <f>G6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="26">
         <f>H6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="26">
         <f>I6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="26">
         <f>J6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="L6" s="25">
+      <c r="L6" s="26">
         <f>K6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="M6" s="25">
+      <c r="M6" s="26">
         <f>L6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="N6" s="25">
+      <c r="N6" s="26">
         <f>M6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="9">
         <f>SUM(C6:N6)</f>
         <v/>
       </c>
@@ -6560,55 +6720,55 @@
           <t>Visitas compradas</t>
         </is>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="16">
         <f>IF('Modelo'!$C$7=0,0,C6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D7" s="15">
+      <c r="D7" s="16">
         <f>IF('Modelo'!$C$7=0,0,D6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="16">
         <f>IF('Modelo'!$C$7=0,0,E6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="16">
         <f>IF('Modelo'!$C$7=0,0,F6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="16">
         <f>IF('Modelo'!$C$7=0,0,G6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="H7" s="15">
+      <c r="H7" s="16">
         <f>IF('Modelo'!$C$7=0,0,H6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I7" s="15">
+      <c r="I7" s="16">
         <f>IF('Modelo'!$C$7=0,0,I6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="J7" s="15">
+      <c r="J7" s="16">
         <f>IF('Modelo'!$C$7=0,0,J6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="K7" s="15">
+      <c r="K7" s="16">
         <f>IF('Modelo'!$C$7=0,0,K6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="L7" s="15">
+      <c r="L7" s="16">
         <f>IF('Modelo'!$C$7=0,0,L6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="M7" s="15">
+      <c r="M7" s="16">
         <f>IF('Modelo'!$C$7=0,0,M6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="N7" s="15">
+      <c r="N7" s="16">
         <f>IF('Modelo'!$C$7=0,0,N6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="O7" s="24">
+      <c r="O7" s="25">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
@@ -6619,55 +6779,55 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <f>C7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="27">
         <f>D7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f>E7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="F8" s="26">
+      <c r="F8" s="27">
         <f>F7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G8" s="26">
+      <c r="G8" s="27">
         <f>G7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="H8" s="26">
+      <c r="H8" s="27">
         <f>H7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="27">
         <f>I7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="J8" s="26">
+      <c r="J8" s="27">
         <f>J7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="K8" s="26">
+      <c r="K8" s="27">
         <f>K7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="L8" s="26">
+      <c r="L8" s="27">
         <f>L7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="M8" s="26">
+      <c r="M8" s="27">
         <f>M7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="N8" s="26">
+      <c r="N8" s="27">
         <f>N7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="O8" s="10">
+      <c r="O8" s="11">
         <f>SUM(C8:N8)</f>
         <v/>
       </c>
@@ -6678,55 +6838,55 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <f>C7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <f>D7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>E7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <f>F7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <f>G7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <f>H7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="26">
         <f>I7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="26">
         <f>J7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <f>K7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="26">
         <f>L7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="26">
         <f>M7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="26">
         <f>N7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="9">
         <f>SUM(C9:N9)</f>
         <v/>
       </c>
@@ -6737,55 +6897,55 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <f>C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <f>D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41+C9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <f>F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41+D9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="26">
         <f>G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41+E9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="26">
         <f>H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41+F9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="26">
         <f>I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41+G9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="26">
         <f>J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41+H9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="26">
         <f>K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41+I9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="L10" s="25">
+      <c r="L10" s="26">
         <f>L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41+J9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="M10" s="25">
+      <c r="M10" s="26">
         <f>M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41+K9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="N10" s="25">
+      <c r="N10" s="26">
         <f>N9*'Supuestos'!$C$40+M9*'Supuestos'!$C$41+L9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="9">
         <f>SUM(C10:N10)</f>
         <v/>
       </c>
@@ -6796,55 +6956,55 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>C10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <f>D10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>E10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <f>F10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="26">
         <f>G10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="26">
         <f>H10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="26">
         <f>I10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="26">
         <f>J10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="26">
         <f>K10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="26">
         <f>L10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="M11" s="25">
+      <c r="M11" s="26">
         <f>M10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="N11" s="25">
+      <c r="N11" s="26">
         <f>N10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="9">
         <f>SUM(C11:N11)</f>
         <v/>
       </c>
@@ -6855,55 +7015,55 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <f>C7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <f>D7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>E7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <f>F7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="G12" s="25">
+      <c r="G12" s="26">
         <f>G7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="26">
         <f>H7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="26">
         <f>I7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="26">
         <f>J7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="26">
         <f>K7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="L12" s="25">
+      <c r="L12" s="26">
         <f>L7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="M12" s="25">
+      <c r="M12" s="26">
         <f>M7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="N12" s="25">
+      <c r="N12" s="26">
         <f>N7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="9">
         <f>SUM(C12:N12)</f>
         <v/>
       </c>
@@ -6914,169 +7074,169 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="L13" s="25">
+      <c r="L13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="M13" s="25">
+      <c r="M13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="N13" s="25">
+      <c r="N13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="9">
         <f>SUM(C13:N13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja del mes</t>
         </is>
       </c>
-      <c r="C14" s="8">
+      <c r="C14" s="9">
         <f>C10-C11-C12-C13-C6</f>
         <v/>
       </c>
-      <c r="D14" s="8">
+      <c r="D14" s="9">
         <f>D10-D11-D12-D13-D6</f>
         <v/>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="9">
         <f>E10-E11-E12-E13-E6</f>
         <v/>
       </c>
-      <c r="F14" s="8">
+      <c r="F14" s="9">
         <f>F10-F11-F12-F13-F6</f>
         <v/>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="9">
         <f>G10-G11-G12-G13-G6</f>
         <v/>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="9">
         <f>H10-H11-H12-H13-H6</f>
         <v/>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="9">
         <f>I10-I11-I12-I13-I6</f>
         <v/>
       </c>
-      <c r="J14" s="8">
+      <c r="J14" s="9">
         <f>J10-J11-J12-J13-J6</f>
         <v/>
       </c>
-      <c r="K14" s="8">
+      <c r="K14" s="9">
         <f>K10-K11-K12-K13-K6</f>
         <v/>
       </c>
-      <c r="L14" s="8">
+      <c r="L14" s="9">
         <f>L10-L11-L12-L13-L6</f>
         <v/>
       </c>
-      <c r="M14" s="8">
+      <c r="M14" s="9">
         <f>M10-M11-M12-M13-M6</f>
         <v/>
       </c>
-      <c r="N14" s="8">
+      <c r="N14" s="9">
         <f>N10-N11-N12-N13-N6</f>
         <v/>
       </c>
-      <c r="O14" s="8">
+      <c r="O14" s="9">
         <f>SUM(C14:N14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja acumulada (desde cero)</t>
         </is>
       </c>
-      <c r="C15" s="8">
+      <c r="C15" s="9">
         <f>C14</f>
         <v/>
       </c>
-      <c r="D15" s="8">
+      <c r="D15" s="9">
         <f>C15+D14</f>
         <v/>
       </c>
-      <c r="E15" s="8">
+      <c r="E15" s="9">
         <f>D15+E14</f>
         <v/>
       </c>
-      <c r="F15" s="8">
+      <c r="F15" s="9">
         <f>E15+F14</f>
         <v/>
       </c>
-      <c r="G15" s="8">
+      <c r="G15" s="9">
         <f>F15+G14</f>
         <v/>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="9">
         <f>G15+H14</f>
         <v/>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="9">
         <f>H15+I14</f>
         <v/>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="9">
         <f>I15+J14</f>
         <v/>
       </c>
-      <c r="K15" s="8">
+      <c r="K15" s="9">
         <f>J15+K14</f>
         <v/>
       </c>
-      <c r="L15" s="8">
+      <c r="L15" s="9">
         <f>K15+L14</f>
         <v/>
       </c>
-      <c r="M15" s="8">
+      <c r="M15" s="9">
         <f>L15+M14</f>
         <v/>
       </c>
-      <c r="N15" s="8">
+      <c r="N15" s="9">
         <f>M15+N14</f>
         <v/>
       </c>
@@ -7087,84 +7247,84 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <f>'Supuestos'!$C$49+C15</f>
         <v/>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <f>'Supuestos'!$C$49+D15</f>
         <v/>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <f>'Supuestos'!$C$49+E15</f>
         <v/>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <f>'Supuestos'!$C$49+F15</f>
         <v/>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="26">
         <f>'Supuestos'!$C$49+G15</f>
         <v/>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <f>'Supuestos'!$C$49+H15</f>
         <v/>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="26">
         <f>'Supuestos'!$C$49+I15</f>
         <v/>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="26">
         <f>'Supuestos'!$C$49+J15</f>
         <v/>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="26">
         <f>'Supuestos'!$C$49+K15</f>
         <v/>
       </c>
-      <c r="L16" s="25">
+      <c r="L16" s="26">
         <f>'Supuestos'!$C$49+L15</f>
         <v/>
       </c>
-      <c r="M16" s="25">
+      <c r="M16" s="26">
         <f>'Supuestos'!$C$49+M15</f>
         <v/>
       </c>
-      <c r="N16" s="25">
+      <c r="N16" s="26">
         <f>'Supuestos'!$C$49+N15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Caja necesaria para no frenar la pauta (el peor momento de la ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C18" s="8">
+      <c r="C18" s="9">
         <f>MAX(0,-MIN(C15:N15))</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Saldo mínimo de caja con tu caja inicial</t>
         </is>
       </c>
-      <c r="C19" s="8">
+      <c r="C19" s="9">
         <f>MIN(C16:N16)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Ganancia de caja acumulada en 12 meses</t>
         </is>
       </c>
-      <c r="C20" s="8">
+      <c r="C20" s="9">
         <f>O14</f>
         <v/>
       </c>
@@ -7184,10 +7344,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
@@ -7200,7 +7360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:Q29"/>
+  <dimension ref="A1:Q29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -7222,120 +7382,127 @@
     <col width="13" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Seguimiento: una columna por mes</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por visita con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>Mes 1</t>
         </is>
       </c>
-      <c r="D5" s="5" t="inlineStr">
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>Mes 2</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>Mes 3</t>
         </is>
       </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>Mes 4</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Mes 5</t>
         </is>
       </c>
-      <c r="H5" s="5" t="inlineStr">
+      <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Mes 6</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Mes 7</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="J5" s="6" t="inlineStr">
         <is>
           <t>Mes 8</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Mes 9</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="L5" s="6" t="inlineStr">
         <is>
           <t>Mes 10</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Mes 11</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="N5" s="6" t="inlineStr">
         <is>
           <t>Mes 12</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="O5" s="6" t="inlineStr">
         <is>
           <t>Promedio</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>Máximo</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>Mínimo</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Datos que cargás</t>
         </is>
       </c>
-      <c r="C6" s="7" t="n"/>
-      <c r="D6" s="7" t="n"/>
-      <c r="E6" s="7" t="n"/>
-      <c r="F6" s="7" t="n"/>
-      <c r="G6" s="7" t="n"/>
-      <c r="H6" s="7" t="n"/>
-      <c r="I6" s="7" t="n"/>
-      <c r="J6" s="7" t="n"/>
-      <c r="K6" s="7" t="n"/>
-      <c r="L6" s="7" t="n"/>
-      <c r="M6" s="7" t="n"/>
-      <c r="N6" s="7" t="n"/>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
@@ -7343,33 +7510,33 @@
           <t>Inversión en publicidad</t>
         </is>
       </c>
-      <c r="C7" s="20" t="n">
+      <c r="C7" s="21" t="n">
         <v>9000</v>
       </c>
-      <c r="D7" s="20" t="n">
+      <c r="D7" s="21" t="n">
         <v>9500</v>
       </c>
-      <c r="E7" s="20" t="n">
+      <c r="E7" s="21" t="n">
         <v>10500</v>
       </c>
-      <c r="F7" s="20" t="n"/>
-      <c r="G7" s="20" t="n"/>
-      <c r="H7" s="20" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="20" t="n"/>
-      <c r="K7" s="20" t="n"/>
-      <c r="L7" s="20" t="n"/>
-      <c r="M7" s="20" t="n"/>
-      <c r="N7" s="20" t="n"/>
-      <c r="O7" s="25">
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="26">
         <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
         <v/>
       </c>
-      <c r="P7" s="25">
+      <c r="P7" s="26">
         <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
         <v/>
       </c>
-      <c r="Q7" s="25">
+      <c r="Q7" s="26">
         <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
         <v/>
       </c>
@@ -7380,33 +7547,33 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="20" t="n">
         <v>30000</v>
       </c>
-      <c r="D8" s="19" t="n">
+      <c r="D8" s="20" t="n">
         <v>30200</v>
       </c>
-      <c r="E8" s="19" t="n">
+      <c r="E8" s="20" t="n">
         <v>29000</v>
       </c>
-      <c r="F8" s="19" t="n"/>
-      <c r="G8" s="19" t="n"/>
-      <c r="H8" s="19" t="n"/>
-      <c r="I8" s="19" t="n"/>
-      <c r="J8" s="19" t="n"/>
-      <c r="K8" s="19" t="n"/>
-      <c r="L8" s="19" t="n"/>
-      <c r="M8" s="19" t="n"/>
-      <c r="N8" s="19" t="n"/>
-      <c r="O8" s="15">
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="16">
         <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
         <v/>
       </c>
-      <c r="P8" s="15">
+      <c r="P8" s="16">
         <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
         <v/>
       </c>
-      <c r="Q8" s="15">
+      <c r="Q8" s="16">
         <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
         <v/>
       </c>
@@ -7417,33 +7584,33 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="C9" s="19" t="n">
+      <c r="C9" s="20" t="n">
         <v>1050</v>
       </c>
-      <c r="D9" s="19" t="n">
+      <c r="D9" s="20" t="n">
         <v>1030</v>
       </c>
-      <c r="E9" s="19" t="n">
+      <c r="E9" s="20" t="n">
         <v>980</v>
       </c>
-      <c r="F9" s="19" t="n"/>
-      <c r="G9" s="19" t="n"/>
-      <c r="H9" s="19" t="n"/>
-      <c r="I9" s="19" t="n"/>
-      <c r="J9" s="19" t="n"/>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="19" t="n"/>
-      <c r="O9" s="15">
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="20" t="n"/>
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="16">
         <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
         <v/>
       </c>
-      <c r="P9" s="15">
+      <c r="P9" s="16">
         <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
         <v/>
       </c>
-      <c r="Q9" s="15">
+      <c r="Q9" s="16">
         <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
         <v/>
       </c>
@@ -7454,33 +7621,33 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C10" s="19" t="n">
+      <c r="C10" s="20" t="n">
         <v>273</v>
       </c>
-      <c r="D10" s="19" t="n">
+      <c r="D10" s="20" t="n">
         <v>262</v>
       </c>
-      <c r="E10" s="19" t="n">
+      <c r="E10" s="20" t="n">
         <v>240</v>
       </c>
-      <c r="F10" s="19" t="n"/>
-      <c r="G10" s="19" t="n"/>
-      <c r="H10" s="19" t="n"/>
-      <c r="I10" s="19" t="n"/>
-      <c r="J10" s="19" t="n"/>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="15">
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="16">
         <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
         <v/>
       </c>
-      <c r="P10" s="15">
+      <c r="P10" s="16">
         <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
         <v/>
       </c>
-      <c r="Q10" s="15">
+      <c r="Q10" s="16">
         <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
         <v/>
       </c>
@@ -7491,33 +7658,33 @@
           <t>Ventas de bumps (1 + 2)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="n">
+      <c r="C11" s="20" t="n">
         <v>117</v>
       </c>
-      <c r="D11" s="19" t="n">
+      <c r="D11" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="E11" s="19" t="n">
+      <c r="E11" s="20" t="n">
         <v>95</v>
       </c>
-      <c r="F11" s="19" t="n"/>
-      <c r="G11" s="19" t="n"/>
-      <c r="H11" s="19" t="n"/>
-      <c r="I11" s="19" t="n"/>
-      <c r="J11" s="19" t="n"/>
-      <c r="K11" s="19" t="n"/>
-      <c r="L11" s="19" t="n"/>
-      <c r="M11" s="19" t="n"/>
-      <c r="N11" s="19" t="n"/>
-      <c r="O11" s="15">
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="20" t="n"/>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="16">
         <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
         <v/>
       </c>
-      <c r="P11" s="15">
+      <c r="P11" s="16">
         <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
         <v/>
       </c>
-      <c r="Q11" s="15">
+      <c r="Q11" s="16">
         <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
         <v/>
       </c>
@@ -7528,33 +7695,33 @@
           <t>Ventas de OTOs (1 a 4)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="n">
+      <c r="C12" s="20" t="n">
         <v>63</v>
       </c>
-      <c r="D12" s="19" t="n">
+      <c r="D12" s="20" t="n">
         <v>58</v>
       </c>
-      <c r="E12" s="19" t="n">
+      <c r="E12" s="20" t="n">
         <v>52</v>
       </c>
-      <c r="F12" s="19" t="n"/>
-      <c r="G12" s="19" t="n"/>
-      <c r="H12" s="19" t="n"/>
-      <c r="I12" s="19" t="n"/>
-      <c r="J12" s="19" t="n"/>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="15">
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="n"/>
+      <c r="O12" s="16">
         <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
         <v/>
       </c>
-      <c r="P12" s="15">
+      <c r="P12" s="16">
         <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
         <v/>
       </c>
-      <c r="Q12" s="15">
+      <c r="Q12" s="16">
         <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
         <v/>
       </c>
@@ -7565,33 +7732,33 @@
           <t>Ventas de la ascensión (programa)</t>
         </is>
       </c>
-      <c r="C13" s="19" t="n">
+      <c r="C13" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="19" t="n">
+      <c r="D13" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="19" t="n">
+      <c r="E13" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="19" t="n"/>
-      <c r="G13" s="19" t="n"/>
-      <c r="H13" s="19" t="n"/>
-      <c r="I13" s="19" t="n"/>
-      <c r="J13" s="19" t="n"/>
-      <c r="K13" s="19" t="n"/>
-      <c r="L13" s="19" t="n"/>
-      <c r="M13" s="19" t="n"/>
-      <c r="N13" s="19" t="n"/>
-      <c r="O13" s="15">
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="20" t="n"/>
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="20" t="n"/>
+      <c r="O13" s="16">
         <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
         <v/>
       </c>
-      <c r="P13" s="15">
+      <c r="P13" s="16">
         <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
         <v/>
       </c>
-      <c r="Q13" s="15">
+      <c r="Q13" s="16">
         <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
         <v/>
       </c>
@@ -7602,33 +7769,33 @@
           <t>Facturado del mes (a precio de lista)</t>
         </is>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="21" t="n">
         <v>15900</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="21" t="n">
         <v>15400</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="21" t="n">
         <v>13700</v>
       </c>
-      <c r="F14" s="20" t="n"/>
-      <c r="G14" s="20" t="n"/>
-      <c r="H14" s="20" t="n"/>
-      <c r="I14" s="20" t="n"/>
-      <c r="J14" s="20" t="n"/>
-      <c r="K14" s="20" t="n"/>
-      <c r="L14" s="20" t="n"/>
-      <c r="M14" s="20" t="n"/>
-      <c r="N14" s="20" t="n"/>
-      <c r="O14" s="25">
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="26">
         <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
         <v/>
       </c>
-      <c r="P14" s="25">
+      <c r="P14" s="26">
         <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
         <v/>
       </c>
-      <c r="Q14" s="25">
+      <c r="Q14" s="26">
         <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
         <v/>
       </c>
@@ -7639,119 +7806,119 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C15" s="20" t="n">
+      <c r="C15" s="21" t="n">
         <v>15900</v>
       </c>
-      <c r="D15" s="20" t="n">
+      <c r="D15" s="21" t="n">
         <v>15400</v>
       </c>
-      <c r="E15" s="20" t="n">
+      <c r="E15" s="21" t="n">
         <v>13700</v>
       </c>
-      <c r="F15" s="20" t="n"/>
-      <c r="G15" s="20" t="n"/>
-      <c r="H15" s="20" t="n"/>
-      <c r="I15" s="20" t="n"/>
-      <c r="J15" s="20" t="n"/>
-      <c r="K15" s="20" t="n"/>
-      <c r="L15" s="20" t="n"/>
-      <c r="M15" s="20" t="n"/>
-      <c r="N15" s="20" t="n"/>
-      <c r="O15" s="25">
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="26">
         <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
         <v/>
       </c>
-      <c r="P15" s="25">
+      <c r="P15" s="26">
         <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
         <v/>
       </c>
-      <c r="Q15" s="25">
+      <c r="Q15" s="26">
         <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Lo que calcula el modelo</t>
         </is>
       </c>
-      <c r="C16" s="7" t="n"/>
-      <c r="D16" s="7" t="n"/>
-      <c r="E16" s="7" t="n"/>
-      <c r="F16" s="7" t="n"/>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="7" t="n"/>
-      <c r="I16" s="7" t="n"/>
-      <c r="J16" s="7" t="n"/>
-      <c r="K16" s="7" t="n"/>
-      <c r="L16" s="7" t="n"/>
-      <c r="M16" s="7" t="n"/>
-      <c r="N16" s="7" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Costo por visita real</t>
         </is>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="12">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C7/C8))</f>
         <v/>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="12">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D7/D8))</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="12">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E7/E8))</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="12">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F7/F8))</f>
         <v/>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="12">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G7/G8))</f>
         <v/>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="12">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H7/H8))</f>
         <v/>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="12">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I7/I8))</f>
         <v/>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="12">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J7/J8))</f>
         <v/>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="12">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K7/K8))</f>
         <v/>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="12">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L7/L8))</f>
         <v/>
       </c>
-      <c r="M17" s="11">
+      <c r="M17" s="12">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M7/M8))</f>
         <v/>
       </c>
-      <c r="N17" s="11">
+      <c r="N17" s="12">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N7/N8))</f>
         <v/>
       </c>
-      <c r="O17" s="18">
+      <c r="O17" s="19">
         <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
         <v/>
       </c>
-      <c r="P17" s="18">
+      <c r="P17" s="19">
         <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
         <v/>
       </c>
-      <c r="Q17" s="18">
+      <c r="Q17" s="19">
         <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
         <v/>
       </c>
@@ -7762,63 +7929,63 @@
           <t>% visitas → checkout</t>
         </is>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="18">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D18" s="17">
+      <c r="D18" s="18">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E18" s="17">
+      <c r="E18" s="18">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F18" s="17">
+      <c r="F18" s="18">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G18" s="17">
+      <c r="G18" s="18">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H18" s="17">
+      <c r="H18" s="18">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="18">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J18" s="17">
+      <c r="J18" s="18">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="18">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L18" s="17">
+      <c r="L18" s="18">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M18" s="17">
+      <c r="M18" s="18">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N18" s="17">
+      <c r="N18" s="18">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O18" s="17">
+      <c r="O18" s="18">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="17">
+      <c r="P18" s="18">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="17">
+      <c r="Q18" s="18">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
@@ -7829,63 +7996,63 @@
           <t>% checkout → compra</t>
         </is>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="18">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
         <v/>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="18">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
         <v/>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="18">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
         <v/>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="18">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
         <v/>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="18">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
         <v/>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="18">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
         <v/>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="18">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
         <v/>
       </c>
-      <c r="J19" s="17">
+      <c r="J19" s="18">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
         <v/>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="18">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
         <v/>
       </c>
-      <c r="L19" s="17">
+      <c r="L19" s="18">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
         <v/>
       </c>
-      <c r="M19" s="17">
+      <c r="M19" s="18">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
         <v/>
       </c>
-      <c r="N19" s="17">
+      <c r="N19" s="18">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
         <v/>
       </c>
-      <c r="O19" s="17">
+      <c r="O19" s="18">
         <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
         <v/>
       </c>
-      <c r="P19" s="17">
+      <c r="P19" s="18">
         <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
         <v/>
       </c>
-      <c r="Q19" s="17">
+      <c r="Q19" s="18">
         <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
         <v/>
       </c>
@@ -7896,63 +8063,63 @@
           <t>CPA real</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="19">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C7/C10))</f>
         <v/>
       </c>
-      <c r="D20" s="18">
+      <c r="D20" s="19">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D7/D10))</f>
         <v/>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="19">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E7/E10))</f>
         <v/>
       </c>
-      <c r="F20" s="18">
+      <c r="F20" s="19">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F7/F10))</f>
         <v/>
       </c>
-      <c r="G20" s="18">
+      <c r="G20" s="19">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G7/G10))</f>
         <v/>
       </c>
-      <c r="H20" s="18">
+      <c r="H20" s="19">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H7/H10))</f>
         <v/>
       </c>
-      <c r="I20" s="18">
+      <c r="I20" s="19">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I7/I10))</f>
         <v/>
       </c>
-      <c r="J20" s="18">
+      <c r="J20" s="19">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J7/J10))</f>
         <v/>
       </c>
-      <c r="K20" s="18">
+      <c r="K20" s="19">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K7/K10))</f>
         <v/>
       </c>
-      <c r="L20" s="18">
+      <c r="L20" s="19">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L7/L10))</f>
         <v/>
       </c>
-      <c r="M20" s="18">
+      <c r="M20" s="19">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M7/M10))</f>
         <v/>
       </c>
-      <c r="N20" s="18">
+      <c r="N20" s="19">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N7/N10))</f>
         <v/>
       </c>
-      <c r="O20" s="18">
+      <c r="O20" s="19">
         <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
         <v/>
       </c>
-      <c r="P20" s="18">
+      <c r="P20" s="19">
         <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
         <v/>
       </c>
-      <c r="Q20" s="18">
+      <c r="Q20" s="19">
         <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
         <v/>
       </c>
@@ -7963,197 +8130,197 @@
           <t>Cash por comprador</t>
         </is>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="19">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C15/C10))</f>
         <v/>
       </c>
-      <c r="D21" s="18">
+      <c r="D21" s="19">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D15/D10))</f>
         <v/>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="19">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E15/E10))</f>
         <v/>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="19">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F15/F10))</f>
         <v/>
       </c>
-      <c r="G21" s="18">
+      <c r="G21" s="19">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G15/G10))</f>
         <v/>
       </c>
-      <c r="H21" s="18">
+      <c r="H21" s="19">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H15/H10))</f>
         <v/>
       </c>
-      <c r="I21" s="18">
+      <c r="I21" s="19">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I15/I10))</f>
         <v/>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="19">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J15/J10))</f>
         <v/>
       </c>
-      <c r="K21" s="18">
+      <c r="K21" s="19">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K15/K10))</f>
         <v/>
       </c>
-      <c r="L21" s="18">
+      <c r="L21" s="19">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L15/L10))</f>
         <v/>
       </c>
-      <c r="M21" s="18">
+      <c r="M21" s="19">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M15/M10))</f>
         <v/>
       </c>
-      <c r="N21" s="18">
+      <c r="N21" s="19">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N15/N10))</f>
         <v/>
       </c>
-      <c r="O21" s="18">
+      <c r="O21" s="19">
         <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
         <v/>
       </c>
-      <c r="P21" s="18">
+      <c r="P21" s="19">
         <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
         <v/>
       </c>
-      <c r="Q21" s="18">
+      <c r="Q21" s="19">
         <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
         </is>
       </c>
-      <c r="C22" s="11">
+      <c r="C22" s="12">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36)/C8))</f>
         <v/>
       </c>
-      <c r="D22" s="11">
+      <c r="D22" s="12">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36)/D8))</f>
         <v/>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="12">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36)/E8))</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="12">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36)/F8))</f>
         <v/>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="12">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36)/G8))</f>
         <v/>
       </c>
-      <c r="H22" s="11">
+      <c r="H22" s="12">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36)/H8))</f>
         <v/>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="12">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36)/I8))</f>
         <v/>
       </c>
-      <c r="J22" s="11">
+      <c r="J22" s="12">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36)/J8))</f>
         <v/>
       </c>
-      <c r="K22" s="11">
+      <c r="K22" s="12">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36)/K8))</f>
         <v/>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36)/L8))</f>
         <v/>
       </c>
-      <c r="M22" s="11">
+      <c r="M22" s="12">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36)/M8))</f>
         <v/>
       </c>
-      <c r="N22" s="11">
+      <c r="N22" s="12">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
         <v/>
       </c>
-      <c r="O22" s="18">
+      <c r="O22" s="19">
         <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
         <v/>
       </c>
-      <c r="P22" s="18">
+      <c r="P22" s="19">
         <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
         <v/>
       </c>
-      <c r="Q22" s="18">
+      <c r="Q22" s="19">
         <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Ganancia del período al completar la cobranza</t>
         </is>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="9">
         <f>IF(COUNT(C7:C15)&lt;9,"",C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
         <v/>
       </c>
-      <c r="D23" s="8">
+      <c r="D23" s="9">
         <f>IF(COUNT(D7:D15)&lt;9,"",D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
         <v/>
       </c>
-      <c r="E23" s="8">
+      <c r="E23" s="9">
         <f>IF(COUNT(E7:E15)&lt;9,"",E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
         <v/>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="9">
         <f>IF(COUNT(F7:F15)&lt;9,"",F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
         <v/>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="9">
         <f>IF(COUNT(G7:G15)&lt;9,"",G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
         <v/>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="9">
         <f>IF(COUNT(H7:H15)&lt;9,"",H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
         <v/>
       </c>
-      <c r="I23" s="8">
+      <c r="I23" s="9">
         <f>IF(COUNT(I7:I15)&lt;9,"",I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
         <v/>
       </c>
-      <c r="J23" s="8">
+      <c r="J23" s="9">
         <f>IF(COUNT(J7:J15)&lt;9,"",J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
         <v/>
       </c>
-      <c r="K23" s="8">
+      <c r="K23" s="9">
         <f>IF(COUNT(K7:K15)&lt;9,"",K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
         <v/>
       </c>
-      <c r="L23" s="8">
+      <c r="L23" s="9">
         <f>IF(COUNT(L7:L15)&lt;9,"",L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
         <v/>
       </c>
-      <c r="M23" s="8">
+      <c r="M23" s="9">
         <f>IF(COUNT(M7:M15)&lt;9,"",M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
         <v/>
       </c>
-      <c r="N23" s="8">
+      <c r="N23" s="9">
         <f>IF(COUNT(N7:N15)&lt;9,"",N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O23" s="25">
+      <c r="O23" s="26">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="25">
+      <c r="P23" s="26">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="25">
+      <c r="Q23" s="26">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -8164,197 +8331,197 @@
           <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C24" s="25">
+      <c r="C24" s="26">
         <f>IF(COUNT(C7:C15)&lt;9,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
         <v/>
       </c>
-      <c r="D24" s="25">
+      <c r="D24" s="26">
         <f>IF(COUNT(D7:D15)&lt;9,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
         <v/>
       </c>
-      <c r="E24" s="25">
+      <c r="E24" s="26">
         <f>IF(COUNT(E7:E15)&lt;9,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
         <v/>
       </c>
-      <c r="F24" s="25">
+      <c r="F24" s="26">
         <f>IF(COUNT(F7:F15)&lt;9,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
         <v/>
       </c>
-      <c r="G24" s="25">
+      <c r="G24" s="26">
         <f>IF(COUNT(G7:G15)&lt;9,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
         <v/>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="26">
         <f>IF(COUNT(H7:H15)&lt;9,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
         <v/>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="26">
         <f>IF(COUNT(I7:I15)&lt;9,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
         <v/>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="26">
         <f>IF(COUNT(J7:J15)&lt;9,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
         <v/>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="26">
         <f>IF(COUNT(K7:K15)&lt;9,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
         <v/>
       </c>
-      <c r="L24" s="25">
+      <c r="L24" s="26">
         <f>IF(COUNT(L7:L15)&lt;9,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
         <v/>
       </c>
-      <c r="M24" s="25">
+      <c r="M24" s="26">
         <f>IF(COUNT(M7:M15)&lt;9,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
         <v/>
       </c>
-      <c r="N24" s="25">
+      <c r="N24" s="26">
         <f>IF(COUNT(N7:N15)&lt;9,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O24" s="25">
+      <c r="O24" s="26">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="25">
+      <c r="P24" s="26">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="25">
+      <c r="Q24" s="26">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
         <is>
           <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
         </is>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="12">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)/C8))</f>
         <v/>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="12">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)/D8))</f>
         <v/>
       </c>
-      <c r="E25" s="11">
+      <c r="E25" s="12">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)/E8))</f>
         <v/>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="12">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)/F8))</f>
         <v/>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="12">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)/G8))</f>
         <v/>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="12">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)/H8))</f>
         <v/>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="12">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)/I8))</f>
         <v/>
       </c>
-      <c r="J25" s="11">
+      <c r="J25" s="12">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)/J8))</f>
         <v/>
       </c>
-      <c r="K25" s="11">
+      <c r="K25" s="12">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)/K8))</f>
         <v/>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="12">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)/L8))</f>
         <v/>
       </c>
-      <c r="M25" s="11">
+      <c r="M25" s="12">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)/M8))</f>
         <v/>
       </c>
-      <c r="N25" s="11">
+      <c r="N25" s="12">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
         <v/>
       </c>
-      <c r="O25" s="18">
+      <c r="O25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
         <v/>
       </c>
-      <c r="P25" s="18">
+      <c r="P25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
         <v/>
       </c>
-      <c r="Q25" s="18">
+      <c r="Q25" s="19">
         <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="4" t="inlineStr">
         <is>
           <t>ROAS sobre cash neto (cobranza completa)</t>
         </is>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="10">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
         <v/>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="10">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
         <v/>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="10">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
         <v/>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="10">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
         <v/>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="10">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
         <v/>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
         <v/>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="10">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
         <v/>
       </c>
-      <c r="J26" s="9">
+      <c r="J26" s="10">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
         <v/>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="10">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
         <v/>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="10">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
         <v/>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="10">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
         <v/>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="10">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O26" s="27">
+      <c r="O26" s="28">
         <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
         <v/>
       </c>
-      <c r="P26" s="27">
+      <c r="P26" s="28">
         <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
         <v/>
       </c>
-      <c r="Q26" s="27">
+      <c r="Q26" s="28">
         <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
         <v/>
       </c>
@@ -8365,63 +8532,63 @@
           <t>ROAS de caja (cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="28">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
         <v/>
       </c>
-      <c r="D27" s="27">
+      <c r="D27" s="28">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
         <v/>
       </c>
-      <c r="E27" s="27">
+      <c r="E27" s="28">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
         <v/>
       </c>
-      <c r="F27" s="27">
+      <c r="F27" s="28">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
         <v/>
       </c>
-      <c r="G27" s="27">
+      <c r="G27" s="28">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
         <v/>
       </c>
-      <c r="H27" s="27">
+      <c r="H27" s="28">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
         <v/>
       </c>
-      <c r="I27" s="27">
+      <c r="I27" s="28">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
         <v/>
       </c>
-      <c r="J27" s="27">
+      <c r="J27" s="28">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
         <v/>
       </c>
-      <c r="K27" s="27">
+      <c r="K27" s="28">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
         <v/>
       </c>
-      <c r="L27" s="27">
+      <c r="L27" s="28">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
         <v/>
       </c>
-      <c r="M27" s="27">
+      <c r="M27" s="28">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
         <v/>
       </c>
-      <c r="N27" s="27">
+      <c r="N27" s="28">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O27" s="27">
+      <c r="O27" s="28">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="27">
+      <c r="P27" s="28">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="27">
+      <c r="Q27" s="28">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
@@ -8432,118 +8599,118 @@
           <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
         </is>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="19">
         <f>IF(COUNT(C7:C15)&lt;9,"",'Modelo'!$C$48)</f>
         <v/>
       </c>
-      <c r="D28" s="18">
+      <c r="D28" s="19">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(COUNT(C22:C22)&gt;0,MEDIAN(C22:C22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="19">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(COUNT(C22:D22)&gt;0,MEDIAN(C22:D22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="F28" s="18">
+      <c r="F28" s="19">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(COUNT(C22:E22)&gt;0,MEDIAN(C22:E22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="G28" s="18">
+      <c r="G28" s="19">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(COUNT(C22:F22)&gt;0,MEDIAN(C22:F22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="H28" s="18">
+      <c r="H28" s="19">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(COUNT(D22:G22)&gt;0,MEDIAN(D22:G22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="I28" s="18">
+      <c r="I28" s="19">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(COUNT(E22:H22)&gt;0,MEDIAN(E22:H22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="19">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(COUNT(F22:I22)&gt;0,MEDIAN(F22:I22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="K28" s="18">
+      <c r="K28" s="19">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(COUNT(G22:J22)&gt;0,MEDIAN(G22:J22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="L28" s="18">
+      <c r="L28" s="19">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(COUNT(H22:K22)&gt;0,MEDIAN(H22:K22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="M28" s="18">
+      <c r="M28" s="19">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(COUNT(I22:L22)&gt;0,MEDIAN(I22:L22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="N28" s="18">
+      <c r="N28" s="19">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(COUNT(J22:M22)&gt;0,MEDIAN(J22:M22),'Modelo'!$C$48))</f>
         <v/>
       </c>
-      <c r="O28" s="18">
+      <c r="O28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
         <v/>
       </c>
-      <c r="P28" s="18">
+      <c r="P28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
         <v/>
       </c>
-      <c r="Q28" s="18">
+      <c r="Q28" s="19">
         <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
         </is>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C17&gt;C28,"ROJO",IF(AND(C17&lt;=C28/(1+'Supuestos'!$C$46),C26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="D29" s="12">
+      <c r="D29" s="13">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D17&gt;D28,"ROJO",IF(AND(D17&lt;=D28/(1+'Supuestos'!$C$46),D26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="13">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E17&gt;E28,"ROJO",IF(AND(E17&lt;=E28/(1+'Supuestos'!$C$46),E26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="13">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F17&gt;F28,"ROJO",IF(AND(F17&lt;=F28/(1+'Supuestos'!$C$46),F26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="13">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G17&gt;G28,"ROJO",IF(AND(G17&lt;=G28/(1+'Supuestos'!$C$46),G26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="13">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H17&gt;H28,"ROJO",IF(AND(H17&lt;=H28/(1+'Supuestos'!$C$46),H26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="13">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I17&gt;I28,"ROJO",IF(AND(I17&lt;=I28/(1+'Supuestos'!$C$46),I26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="13">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J17&gt;J28,"ROJO",IF(AND(J17&lt;=J28/(1+'Supuestos'!$C$46),J26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="13">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K17&gt;K28,"ROJO",IF(AND(K17&lt;=K28/(1+'Supuestos'!$C$46),K26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="13">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L17&gt;L28,"ROJO",IF(AND(L17&lt;=L28/(1+'Supuestos'!$C$46),L26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="M29" s="12">
+      <c r="M29" s="13">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M17&gt;M28,"ROJO",IF(AND(M17&lt;=M28/(1+'Supuestos'!$C$46),M26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
-      <c r="N29" s="12">
+      <c r="N29" s="13">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N17&gt;N28,"ROJO",IF(AND(N17&lt;=N28/(1+'Supuestos'!$C$46),N26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
         <v/>
       </c>
@@ -8562,10 +8729,10 @@
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</oddFooter>
-    <evenHeader/>
-    <evenFooter>&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro</evenFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>

--- a/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
+++ b/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
@@ -9,17 +9,18 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embudo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyección 12 meses" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulador" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embudo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyección 12 meses" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="Autor_Jesus_Tassarolo">"Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro"</definedName>
@@ -176,20 +177,20 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -202,7 +203,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -221,6 +222,13 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00F8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -586,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -638,7 +646,7 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Cómo usarlo en 6 pasos</t>
+          <t>Cómo usarlo en 7 pasos</t>
         </is>
       </c>
     </row>
@@ -649,24 +657,24 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="45" customHeight="1">
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>2. Mirá Resumen: ganancia del mes, ROAS, el techo y el objetivo de costo por visita, y el semáforo. Después Embudo: todos los pasos en orden con cuántos pasan, qué porcentaje se pierde y cuánto cuesta cada paso.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+          <t>2. Mirá Resumen: ganancia del mes, ROAS, el techo y el objetivo de costo por visita, y el semáforo. Después Embudo: todos los pasos en orden con cuántos pasan, lo que pagás, lo que te queda y lo máximo que podrías pagar por cada uno.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>3. Abrí Escenarios para ver qué pasa si cambia el precio, la conversión o el costo. Las celdas amarillas de cada tabla se pueden cambiar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1">
+          <t>3. Abrí Simulador para jugar: cada supuesto está en orden de embudo (inversión, CPM, CTR, visitas, conversión de la landing, asistencia, solicitudes, cierre, precios, costos) con tu número en amarillo al lado de la base. Cambiá uno y mirá cómo se mueven todos los demás contra la base; la columna Diferencia te dice cuánto. No toca Supuestos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>4. Abrí Sensibilidad para saber qué variable conviene trabajar primero.</t>
+          <t>4. Abrí Escenarios para ver qué pasa si cambia el precio, la conversión o el costo en tablas de dos variables, y Sensibilidad para saber qué variable conviene trabajar primero.</t>
         </is>
       </c>
     </row>
@@ -684,183 +692,190 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>7. Una decisión por semana, anotada. A los 7 días, mirá qué pasó.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Colores y hojas</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Amarillo = celda que editás vos. Azul = resultado calculado: no lo toques, se recalcula solo.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="45" customHeight="1">
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>Resumen, Embudo y Modelo leen de Supuestos. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
+    <row r="20" ht="45" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
+          <t>Resumen, Embudo y Modelo leen de Supuestos. Simulador es la mesa de pruebas: copia Supuestos en orden de embudo y vos escribís encima. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
           <t>Chequeos avisa si un supuesto quedó fuera de rango. Si dice REVISAR, arreglalo antes de leer los resultados.</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="5" t="inlineStr">
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Cómo elegir escenario: en Supuestos, la celda 'Escenario en uso' (1, 2 o 3) elige la columna conservador, base u optimista de cada fila que tiene tres valores. Las filas con un solo valor se usan tal cual.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>El ejemplo que viene cargado</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="B24" s="5" t="inlineStr">
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Un curso de 37 USD vendido con VSL a tráfico frío. Se invierten 9.000 USD por mes a 0,30 por visita (30.000 visitas). El 3,5 % llega al checkout y el 26 % de esos compra: 273 ventas al mes, CPA de 33 USD.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="45" customHeight="1">
-      <c r="B25" s="5" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>La escalera: dos bumps de 17 (25 % y 18 %); cuatro OTOs después del pago, una por página: 47 (10 %), 17 (6 %), 97 (3 %) y 27 (4 %); y la ascensión a un programa de 297 que toma el 2 %. El AOV queda cerca de 60 USD: la escalera multiplica el precio del principal por 1,6.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="B26" s="5" t="inlineStr">
+    <row r="27" ht="15" customHeight="1">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Costos: pasarela 10 %, reembolsos 5 %, fijos 1.500 por mes. Pago único: la cobranza entra 100 % el primer mes.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="60" customHeight="1">
-      <c r="B27" s="5" t="inlineStr">
+    <row r="28" ht="60" customHeight="1">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Resultado: ganancia mensual positiva y ROAS sobre cash neto de 1,5, con techo de costo por visita cerca de 0,46 y objetivo cerca de 0,36. El semáforo queda en amarillo: el costo por visita está bien, pero el ROAS no llega al objetivo de 2. Sensibilidad dice que las palancas son el costo por visita y la conversión de la página, no el precio. Cambiá los números por los tuyos.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Reglas de decisión (el protocolo corto)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="B30" s="5" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>1. Antes de invertir: cargá tus números en Supuestos (si no tenés datos, escenario 1, conservador) y mirá en Resumen el techo y el objetivo de costo por visita.</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="45" customHeight="1">
-      <c r="B31" s="5" t="inlineStr">
+    <row r="32" ht="45" customHeight="1">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>2. Primeros días: compará tu costo real por visita con el objetivo. Verde: seguí. Amarillo: no subas la inversión y revisá en este orden: CPM (público y frecuencia), creativo (CTR) y página (conversión). Rojo: bajá un escalón (−25 %) y arreglá antes de volver a subir.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>3. Cada mes: completá una columna de Seguimiento. El semáforo compara tu costo con el techo móvil (lo que rindieron tus últimas 4 columnas), no con un número fijo.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>4. Subí la inversión de a 25 % y esperá 7 días (o 3 a 4 eventos si vendés por llamada) antes de volver a subir. Un día bueno o malo no decide nada.</t>
+          <t>3. Cada mes: completá una columna de Seguimiento. El semáforo compara tu costo con el techo móvil (lo que rindieron tus últimas 4 columnas), no con un número fijo.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="B34" s="5" t="inlineStr">
         <is>
+          <t>4. Subí la inversión de a 25 % y esperá 7 días (o 3 a 4 eventos si vendés por llamada) antes de volver a subir. Un día bueno o malo no decide nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
           <t>5. Si el costo está en verde y aun así no hay ganancia, el problema no es el tráfico: mirá asistencia, conversión de la oferta y cobranza, en ese orden.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1">
-      <c r="B35" s="5" t="inlineStr">
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>6. Cambiá una sola cosa por vez. Si cambiás precio, creativo y página la misma semana no vas a saber qué funcionó.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>7. Trabajá siempre con cash neto (lo que entra menos comisiones y reembolsos), nunca con facturado. En Proyección ves cuánta caja necesitás para sostener la pauta mientras cobrás.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="B37" s="5" t="inlineStr">
         <is>
+          <t>7. Trabajá siempre con cash neto (lo que entra menos comisiones y reembolsos), nunca con facturado. En Proyección ves cuánta caja necesitás para sostener la pauta mientras cobrás.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
           <t>8. En este embudo el techo de CPA es el AOV neto. Si tu CPA se acerca al AOV neto, subir los bumps y las OTOs es la forma más rápida de recuperar margen sin tocar el tráfico.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="4" t="inlineStr">
+    <row r="40">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Lo que este modelo no hace</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="5" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>No adivina tus conversiones: usa las que cargás. Cuando una conversión cambia, el techo cambia; por eso Seguimiento recalcula el techo móvil con tus últimas 4 columnas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="15" customHeight="1">
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>No reemplaza la decisión: la informa. Las reglas de arriba dicen qué hacer con cada color.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="B42" s="5" t="inlineStr">
         <is>
+          <t>No reemplaza la decisión: la informa. Las reglas de arriba dicen qué hacer con cada color.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>Los benchmarks son orden de magnitud para tráfico frío en español. Tus datos mandan.</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="B44" s="4" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="4" t="inlineStr">
         <is>
           <t>Autor y versión</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="30" customHeight="1">
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro. v1.2 · octubre 2026. Fórmulas compatibles con Excel, Google Sheets y Numbers. Sin macros.</t>
         </is>
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
       <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro. v1.2 · octubre 2026. Fórmulas compatibles con Excel, Google Sheets y Numbers. Sin macros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Este modelo se comparte para que lo uses con tus números. Si lo compartís, dejá esta línea: es la forma de saber de dónde salió.</t>
         </is>
@@ -880,6 +895,1391 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Seguimiento: una columna por mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por visita con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 4</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 5</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 6</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 7</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 8</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 9</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 10</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 11</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 12</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>Máximo</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Datos que cargás</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Inversión en publicidad</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D7" s="18" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>10500</v>
+      </c>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="18" t="n"/>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="19">
+        <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
+        <v/>
+      </c>
+      <c r="P7" s="19">
+        <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="19">
+        <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Visitas a la página</t>
+        </is>
+      </c>
+      <c r="C8" s="29" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D8" s="29" t="n">
+        <v>30200</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F8" s="29" t="n"/>
+      <c r="G8" s="29" t="n"/>
+      <c r="H8" s="29" t="n"/>
+      <c r="I8" s="29" t="n"/>
+      <c r="J8" s="29" t="n"/>
+      <c r="K8" s="29" t="n"/>
+      <c r="L8" s="29" t="n"/>
+      <c r="M8" s="29" t="n"/>
+      <c r="N8" s="29" t="n"/>
+      <c r="O8" s="21">
+        <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
+        <v/>
+      </c>
+      <c r="P8" s="21">
+        <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="21">
+        <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Checkouts iniciados</t>
+        </is>
+      </c>
+      <c r="C9" s="29" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>980</v>
+      </c>
+      <c r="F9" s="29" t="n"/>
+      <c r="G9" s="29" t="n"/>
+      <c r="H9" s="29" t="n"/>
+      <c r="I9" s="29" t="n"/>
+      <c r="J9" s="29" t="n"/>
+      <c r="K9" s="29" t="n"/>
+      <c r="L9" s="29" t="n"/>
+      <c r="M9" s="29" t="n"/>
+      <c r="N9" s="29" t="n"/>
+      <c r="O9" s="21">
+        <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
+        <v/>
+      </c>
+      <c r="P9" s="21">
+        <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="21">
+        <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ventas del producto principal</t>
+        </is>
+      </c>
+      <c r="C10" s="29" t="n">
+        <v>273</v>
+      </c>
+      <c r="D10" s="29" t="n">
+        <v>262</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>240</v>
+      </c>
+      <c r="F10" s="29" t="n"/>
+      <c r="G10" s="29" t="n"/>
+      <c r="H10" s="29" t="n"/>
+      <c r="I10" s="29" t="n"/>
+      <c r="J10" s="29" t="n"/>
+      <c r="K10" s="29" t="n"/>
+      <c r="L10" s="29" t="n"/>
+      <c r="M10" s="29" t="n"/>
+      <c r="N10" s="29" t="n"/>
+      <c r="O10" s="21">
+        <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
+        <v/>
+      </c>
+      <c r="P10" s="21">
+        <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="21">
+        <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ventas de bumps (1 + 2)</t>
+        </is>
+      </c>
+      <c r="C11" s="29" t="n">
+        <v>117</v>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>110</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>95</v>
+      </c>
+      <c r="F11" s="29" t="n"/>
+      <c r="G11" s="29" t="n"/>
+      <c r="H11" s="29" t="n"/>
+      <c r="I11" s="29" t="n"/>
+      <c r="J11" s="29" t="n"/>
+      <c r="K11" s="29" t="n"/>
+      <c r="L11" s="29" t="n"/>
+      <c r="M11" s="29" t="n"/>
+      <c r="N11" s="29" t="n"/>
+      <c r="O11" s="21">
+        <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
+        <v/>
+      </c>
+      <c r="P11" s="21">
+        <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="21">
+        <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ventas de OTOs (1 a 4)</t>
+        </is>
+      </c>
+      <c r="C12" s="29" t="n">
+        <v>63</v>
+      </c>
+      <c r="D12" s="29" t="n">
+        <v>58</v>
+      </c>
+      <c r="E12" s="29" t="n">
+        <v>52</v>
+      </c>
+      <c r="F12" s="29" t="n"/>
+      <c r="G12" s="29" t="n"/>
+      <c r="H12" s="29" t="n"/>
+      <c r="I12" s="29" t="n"/>
+      <c r="J12" s="29" t="n"/>
+      <c r="K12" s="29" t="n"/>
+      <c r="L12" s="29" t="n"/>
+      <c r="M12" s="29" t="n"/>
+      <c r="N12" s="29" t="n"/>
+      <c r="O12" s="21">
+        <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
+        <v/>
+      </c>
+      <c r="P12" s="21">
+        <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="21">
+        <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ventas de la ascensión (programa)</t>
+        </is>
+      </c>
+      <c r="C13" s="29" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="29" t="n"/>
+      <c r="G13" s="29" t="n"/>
+      <c r="H13" s="29" t="n"/>
+      <c r="I13" s="29" t="n"/>
+      <c r="J13" s="29" t="n"/>
+      <c r="K13" s="29" t="n"/>
+      <c r="L13" s="29" t="n"/>
+      <c r="M13" s="29" t="n"/>
+      <c r="N13" s="29" t="n"/>
+      <c r="O13" s="21">
+        <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
+        <v/>
+      </c>
+      <c r="P13" s="21">
+        <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="21">
+        <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Facturado del mes (a precio de lista)</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>15400</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>13700</v>
+      </c>
+      <c r="F14" s="18" t="n"/>
+      <c r="G14" s="18" t="n"/>
+      <c r="H14" s="18" t="n"/>
+      <c r="I14" s="18" t="n"/>
+      <c r="J14" s="18" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="M14" s="18" t="n"/>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="19">
+        <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
+        <v/>
+      </c>
+      <c r="P14" s="19">
+        <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="19">
+        <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cash cobrado en el mes</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>15400</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>13700</v>
+      </c>
+      <c r="F15" s="18" t="n"/>
+      <c r="G15" s="18" t="n"/>
+      <c r="H15" s="18" t="n"/>
+      <c r="I15" s="18" t="n"/>
+      <c r="J15" s="18" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="M15" s="18" t="n"/>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="19">
+        <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
+        <v/>
+      </c>
+      <c r="P15" s="19">
+        <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="19">
+        <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Lo que calcula el modelo</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Costo por visita real</t>
+        </is>
+      </c>
+      <c r="C17" s="12">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C7/C8))</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D7/D8))</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E7/E8))</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F7/F8))</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G7/G8))</f>
+        <v/>
+      </c>
+      <c r="H17" s="12">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H7/H8))</f>
+        <v/>
+      </c>
+      <c r="I17" s="12">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I7/I8))</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J7/J8))</f>
+        <v/>
+      </c>
+      <c r="K17" s="12">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K7/K8))</f>
+        <v/>
+      </c>
+      <c r="L17" s="12">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L7/L8))</f>
+        <v/>
+      </c>
+      <c r="M17" s="12">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M7/M8))</f>
+        <v/>
+      </c>
+      <c r="N17" s="12">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N7/N8))</f>
+        <v/>
+      </c>
+      <c r="O17" s="17">
+        <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
+        <v/>
+      </c>
+      <c r="P17" s="17">
+        <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="17">
+        <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>% visitas → checkout</t>
+        </is>
+      </c>
+      <c r="C18" s="23">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
+        <v/>
+      </c>
+      <c r="D18" s="23">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
+        <v/>
+      </c>
+      <c r="E18" s="23">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
+        <v/>
+      </c>
+      <c r="F18" s="23">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
+        <v/>
+      </c>
+      <c r="G18" s="23">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
+        <v/>
+      </c>
+      <c r="H18" s="23">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
+        <v/>
+      </c>
+      <c r="I18" s="23">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
+        <v/>
+      </c>
+      <c r="J18" s="23">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
+        <v/>
+      </c>
+      <c r="K18" s="23">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
+        <v/>
+      </c>
+      <c r="L18" s="23">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
+        <v/>
+      </c>
+      <c r="M18" s="23">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
+        <v/>
+      </c>
+      <c r="N18" s="23">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
+        <v/>
+      </c>
+      <c r="O18" s="23">
+        <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
+        <v/>
+      </c>
+      <c r="P18" s="23">
+        <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="23">
+        <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>% checkout → compra</t>
+        </is>
+      </c>
+      <c r="C19" s="23">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
+        <v/>
+      </c>
+      <c r="D19" s="23">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
+        <v/>
+      </c>
+      <c r="E19" s="23">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
+        <v/>
+      </c>
+      <c r="F19" s="23">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
+        <v/>
+      </c>
+      <c r="G19" s="23">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
+        <v/>
+      </c>
+      <c r="H19" s="23">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
+        <v/>
+      </c>
+      <c r="I19" s="23">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
+        <v/>
+      </c>
+      <c r="J19" s="23">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
+        <v/>
+      </c>
+      <c r="K19" s="23">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
+        <v/>
+      </c>
+      <c r="L19" s="23">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
+        <v/>
+      </c>
+      <c r="M19" s="23">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
+        <v/>
+      </c>
+      <c r="N19" s="23">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
+        <v/>
+      </c>
+      <c r="O19" s="23">
+        <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
+        <v/>
+      </c>
+      <c r="P19" s="23">
+        <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="23">
+        <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CPA real</t>
+        </is>
+      </c>
+      <c r="C20" s="17">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C7/C10))</f>
+        <v/>
+      </c>
+      <c r="D20" s="17">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D7/D10))</f>
+        <v/>
+      </c>
+      <c r="E20" s="17">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E7/E10))</f>
+        <v/>
+      </c>
+      <c r="F20" s="17">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F7/F10))</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G7/G10))</f>
+        <v/>
+      </c>
+      <c r="H20" s="17">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H7/H10))</f>
+        <v/>
+      </c>
+      <c r="I20" s="17">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I7/I10))</f>
+        <v/>
+      </c>
+      <c r="J20" s="17">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J7/J10))</f>
+        <v/>
+      </c>
+      <c r="K20" s="17">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K7/K10))</f>
+        <v/>
+      </c>
+      <c r="L20" s="17">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L7/L10))</f>
+        <v/>
+      </c>
+      <c r="M20" s="17">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M7/M10))</f>
+        <v/>
+      </c>
+      <c r="N20" s="17">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N7/N10))</f>
+        <v/>
+      </c>
+      <c r="O20" s="17">
+        <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
+        <v/>
+      </c>
+      <c r="P20" s="17">
+        <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="17">
+        <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cash por comprador</t>
+        </is>
+      </c>
+      <c r="C21" s="17">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C15/C10))</f>
+        <v/>
+      </c>
+      <c r="D21" s="17">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D15/D10))</f>
+        <v/>
+      </c>
+      <c r="E21" s="17">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E15/E10))</f>
+        <v/>
+      </c>
+      <c r="F21" s="17">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F15/F10))</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G15/G10))</f>
+        <v/>
+      </c>
+      <c r="H21" s="17">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H15/H10))</f>
+        <v/>
+      </c>
+      <c r="I21" s="17">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I15/I10))</f>
+        <v/>
+      </c>
+      <c r="J21" s="17">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J15/J10))</f>
+        <v/>
+      </c>
+      <c r="K21" s="17">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K15/K10))</f>
+        <v/>
+      </c>
+      <c r="L21" s="17">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L15/L10))</f>
+        <v/>
+      </c>
+      <c r="M21" s="17">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M15/M10))</f>
+        <v/>
+      </c>
+      <c r="N21" s="17">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N15/N10))</f>
+        <v/>
+      </c>
+      <c r="O21" s="17">
+        <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
+        <v/>
+      </c>
+      <c r="P21" s="17">
+        <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="17">
+        <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
+        </is>
+      </c>
+      <c r="C22" s="12">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36)/C8))</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36)/D8))</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36)/E8))</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36)/F8))</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36)/G8))</f>
+        <v/>
+      </c>
+      <c r="H22" s="12">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36)/H8))</f>
+        <v/>
+      </c>
+      <c r="I22" s="12">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36)/I8))</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36)/J8))</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36)/K8))</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36)/L8))</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36)/M8))</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
+        <v/>
+      </c>
+      <c r="O22" s="17">
+        <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
+        <v/>
+      </c>
+      <c r="P22" s="17">
+        <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="17">
+        <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia del período al completar la cobranza</t>
+        </is>
+      </c>
+      <c r="C23" s="9">
+        <f>IF(COUNT(C7:C15)&lt;9,"",C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
+        <v/>
+      </c>
+      <c r="D23" s="9">
+        <f>IF(COUNT(D7:D15)&lt;9,"",D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
+        <v/>
+      </c>
+      <c r="E23" s="9">
+        <f>IF(COUNT(E7:E15)&lt;9,"",E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>IF(COUNT(F7:F15)&lt;9,"",F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>IF(COUNT(G7:G15)&lt;9,"",G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF(COUNT(H7:H15)&lt;9,"",H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>IF(COUNT(I7:I15)&lt;9,"",I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
+        <v/>
+      </c>
+      <c r="J23" s="9">
+        <f>IF(COUNT(J7:J15)&lt;9,"",J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
+        <v/>
+      </c>
+      <c r="K23" s="9">
+        <f>IF(COUNT(K7:K15)&lt;9,"",K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
+        <v/>
+      </c>
+      <c r="L23" s="9">
+        <f>IF(COUNT(L7:L15)&lt;9,"",L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
+        <v/>
+      </c>
+      <c r="M23" s="9">
+        <f>IF(COUNT(M7:M15)&lt;9,"",M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
+        <v/>
+      </c>
+      <c r="N23" s="9">
+        <f>IF(COUNT(N7:N15)&lt;9,"",N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
+        <v/>
+      </c>
+      <c r="O23" s="19">
+        <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
+        <v/>
+      </c>
+      <c r="P23" s="19">
+        <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="19">
+        <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
+        </is>
+      </c>
+      <c r="C24" s="19">
+        <f>IF(COUNT(C7:C15)&lt;9,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
+        <v/>
+      </c>
+      <c r="D24" s="19">
+        <f>IF(COUNT(D7:D15)&lt;9,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
+        <v/>
+      </c>
+      <c r="E24" s="19">
+        <f>IF(COUNT(E7:E15)&lt;9,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
+        <v/>
+      </c>
+      <c r="F24" s="19">
+        <f>IF(COUNT(F7:F15)&lt;9,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
+        <v/>
+      </c>
+      <c r="G24" s="19">
+        <f>IF(COUNT(G7:G15)&lt;9,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
+        <v/>
+      </c>
+      <c r="H24" s="19">
+        <f>IF(COUNT(H7:H15)&lt;9,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
+        <v/>
+      </c>
+      <c r="I24" s="19">
+        <f>IF(COUNT(I7:I15)&lt;9,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
+        <v/>
+      </c>
+      <c r="J24" s="19">
+        <f>IF(COUNT(J7:J15)&lt;9,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
+        <v/>
+      </c>
+      <c r="K24" s="19">
+        <f>IF(COUNT(K7:K15)&lt;9,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
+        <v/>
+      </c>
+      <c r="L24" s="19">
+        <f>IF(COUNT(L7:L15)&lt;9,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
+        <v/>
+      </c>
+      <c r="M24" s="19">
+        <f>IF(COUNT(M7:M15)&lt;9,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
+        <v/>
+      </c>
+      <c r="N24" s="19">
+        <f>IF(COUNT(N7:N15)&lt;9,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
+        <v/>
+      </c>
+      <c r="O24" s="19">
+        <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
+        <v/>
+      </c>
+      <c r="P24" s="19">
+        <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="19">
+        <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
+        </is>
+      </c>
+      <c r="C25" s="12">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)/C8))</f>
+        <v/>
+      </c>
+      <c r="D25" s="12">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)/D8))</f>
+        <v/>
+      </c>
+      <c r="E25" s="12">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)/E8))</f>
+        <v/>
+      </c>
+      <c r="F25" s="12">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)/F8))</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)/G8))</f>
+        <v/>
+      </c>
+      <c r="H25" s="12">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)/H8))</f>
+        <v/>
+      </c>
+      <c r="I25" s="12">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)/I8))</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)/J8))</f>
+        <v/>
+      </c>
+      <c r="K25" s="12">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)/K8))</f>
+        <v/>
+      </c>
+      <c r="L25" s="12">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)/L8))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)/M8))</f>
+        <v/>
+      </c>
+      <c r="N25" s="12">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
+        <v/>
+      </c>
+      <c r="O25" s="17">
+        <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
+        <v/>
+      </c>
+      <c r="P25" s="17">
+        <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="17">
+        <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ROAS sobre cash neto (cobranza completa)</t>
+        </is>
+      </c>
+      <c r="C26" s="10">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
+        <v/>
+      </c>
+      <c r="I26" s="10">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
+        <v/>
+      </c>
+      <c r="J26" s="10">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
+        <v/>
+      </c>
+      <c r="K26" s="10">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
+        <v/>
+      </c>
+      <c r="L26" s="10">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
+        <v/>
+      </c>
+      <c r="M26" s="10">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
+        <v/>
+      </c>
+      <c r="N26" s="10">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
+        <v/>
+      </c>
+      <c r="O26" s="26">
+        <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
+        <v/>
+      </c>
+      <c r="P26" s="26">
+        <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="26">
+        <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ROAS de caja (cobrado hasta ahora)</t>
+        </is>
+      </c>
+      <c r="C27" s="26">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
+        <v/>
+      </c>
+      <c r="D27" s="26">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
+        <v/>
+      </c>
+      <c r="E27" s="26">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
+        <v/>
+      </c>
+      <c r="F27" s="26">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
+        <v/>
+      </c>
+      <c r="G27" s="26">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
+        <v/>
+      </c>
+      <c r="H27" s="26">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
+        <v/>
+      </c>
+      <c r="I27" s="26">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
+        <v/>
+      </c>
+      <c r="J27" s="26">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
+        <v/>
+      </c>
+      <c r="K27" s="26">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
+        <v/>
+      </c>
+      <c r="L27" s="26">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
+        <v/>
+      </c>
+      <c r="M27" s="26">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
+        <v/>
+      </c>
+      <c r="N27" s="26">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
+        <v/>
+      </c>
+      <c r="O27" s="26">
+        <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
+        <v/>
+      </c>
+      <c r="P27" s="26">
+        <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="26">
+        <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
+        </is>
+      </c>
+      <c r="C28" s="17">
+        <f>IF(COUNT(C7:C15)&lt;9,"",'Modelo'!$C$48)</f>
+        <v/>
+      </c>
+      <c r="D28" s="17">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(COUNT(C22:C22)&gt;0,MEDIAN(C22:C22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="E28" s="17">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(COUNT(C22:D22)&gt;0,MEDIAN(C22:D22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="F28" s="17">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(COUNT(C22:E22)&gt;0,MEDIAN(C22:E22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="G28" s="17">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(COUNT(C22:F22)&gt;0,MEDIAN(C22:F22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="H28" s="17">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(COUNT(D22:G22)&gt;0,MEDIAN(D22:G22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="I28" s="17">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(COUNT(E22:H22)&gt;0,MEDIAN(E22:H22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="J28" s="17">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(COUNT(F22:I22)&gt;0,MEDIAN(F22:I22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="K28" s="17">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(COUNT(G22:J22)&gt;0,MEDIAN(G22:J22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="L28" s="17">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(COUNT(H22:K22)&gt;0,MEDIAN(H22:K22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="M28" s="17">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(COUNT(I22:L22)&gt;0,MEDIAN(I22:L22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="N28" s="17">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(COUNT(J22:M22)&gt;0,MEDIAN(J22:M22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="O28" s="17">
+        <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
+        <v/>
+      </c>
+      <c r="P28" s="17">
+        <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="17">
+        <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
+        </is>
+      </c>
+      <c r="C29" s="13">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C17&gt;C28,"ROJO",IF(AND(C17&lt;=C28/(1+'Supuestos'!$C$46),C26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="D29" s="13">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D17&gt;D28,"ROJO",IF(AND(D17&lt;=D28/(1+'Supuestos'!$C$46),D26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="E29" s="13">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E17&gt;E28,"ROJO",IF(AND(E17&lt;=E28/(1+'Supuestos'!$C$46),E26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="F29" s="13">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F17&gt;F28,"ROJO",IF(AND(F17&lt;=F28/(1+'Supuestos'!$C$46),F26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="G29" s="13">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G17&gt;G28,"ROJO",IF(AND(G17&lt;=G28/(1+'Supuestos'!$C$46),G26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="H29" s="13">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H17&gt;H28,"ROJO",IF(AND(H17&lt;=H28/(1+'Supuestos'!$C$46),H26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="I29" s="13">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I17&gt;I28,"ROJO",IF(AND(I17&lt;=I28/(1+'Supuestos'!$C$46),I26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="J29" s="13">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J17&gt;J28,"ROJO",IF(AND(J17&lt;=J28/(1+'Supuestos'!$C$46),J26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="K29" s="13">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K17&gt;K28,"ROJO",IF(AND(K17&lt;=K28/(1+'Supuestos'!$C$46),K26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="13">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L17&gt;L28,"ROJO",IF(AND(L17&lt;=L28/(1+'Supuestos'!$C$46),L26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="M29" s="13">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M17&gt;M28,"ROJO",IF(AND(M17&lt;=M28/(1+'Supuestos'!$C$46),M26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="N29" s="13">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N17&gt;N28,"ROJO",IF(AND(N17&lt;=N28/(1+'Supuestos'!$C$46),N26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C5:N30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT(C5,5)="VERDE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>LEFT(C5,8)="AMARILLO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>LEFT(C5,4)="ROJO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -982,7 +2382,7 @@
           <t>&lt;0,20</t>
         </is>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="17">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -1018,7 +2418,7 @@
           <t>&gt;5 %</t>
         </is>
       </c>
-      <c r="G7" s="18">
+      <c r="G7" s="23">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -1054,7 +2454,7 @@
           <t>&gt;30 %</t>
         </is>
       </c>
-      <c r="G8" s="18">
+      <c r="G8" s="23">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -1090,7 +2490,7 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G9" s="17">
+      <c r="G9" s="25">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
@@ -1126,7 +2526,7 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G10" s="18">
+      <c r="G10" s="23">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -1162,7 +2562,7 @@
           <t>&gt;14 %</t>
         </is>
       </c>
-      <c r="G11" s="18">
+      <c r="G11" s="23">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -1198,7 +2598,7 @@
           <t>&gt;4 %</t>
         </is>
       </c>
-      <c r="G12" s="18">
+      <c r="G12" s="23">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -1234,7 +2634,7 @@
           <t>&gt;1,7</t>
         </is>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="26">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
@@ -1270,7 +2670,7 @@
           <t>&gt;2,5</t>
         </is>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="26">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
@@ -1306,691 +2706,13 @@
           <t>&lt;4 %</t>
         </is>
       </c>
-      <c r="G15" s="18">
+      <c r="G15" s="23">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Más de 10 % es un problema de oferta.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
-    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
-    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
-    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Glosario</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Los términos que usa este modelo, en el orden del embudo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Término</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Qué es</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Dónde aparece</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CPM</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Clic → visita</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Unidad de adquisición</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Costo por unidad</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Modelo, Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Conversión</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Supuestos, Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Show rate</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>OTO / upsell</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>AOV</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>CPA / CAC</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Facturado</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Cash cobrado</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Modelo, Proyección</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Cash neto</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>ROAS</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Valor neto por unidad (VPU)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Techo</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Modelo, Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Margen de seguridad</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Semáforo</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Resumen, Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Techo móvil</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Escenario</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Sensibilidad</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sensibilidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia por visita / por lead / por cliente</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Modelo, Embudo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Order value (AOV)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Caja necesaria</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Proyección</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Unit economics</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Resumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Tráfico frío</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Benchmarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Front / producto principal</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Pitch</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Inicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>VSL</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Benchmarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Self-serve</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>OTO 1 a 4</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>La secuencia de hasta cuatro páginas después del pago: upsell, downsell, upsell, downsell. Cada una se mide como % de los compradores del principal.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Ascensión</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>El upsell de mayor valor que se ofrece después del embudo (un programa de 300 a 1.000 USD), por checkout o por llamada.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2735,685 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Glosario</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Los términos que usa este modelo, en el orden del embudo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Término</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Qué es</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Dónde aparece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Clic → visita</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Unidad de adquisición</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Costo por unidad</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Modelo, Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Conversión</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Supuestos, Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Show rate</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>OTO / upsell</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CPA / CAC</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Cash cobrado</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Modelo, Proyección</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Cash neto</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Valor neto por unidad (VPU)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Techo</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Modelo, Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Margen de seguridad</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Semáforo</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Resumen, Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Techo móvil</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Escenario</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Sensibilidad</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sensibilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia por visita / por lead / por cliente</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Modelo, Embudo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Order value (AOV)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Caja necesaria</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Proyección</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Unit economics</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Tráfico frío</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Front / producto principal</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Pitch</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>VSL</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Self-serve</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>OTO 1 a 4</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>La secuencia de hasta cuatro páginas después del pago: upsell, downsell, upsell, downsell. Cada una se mide como % de los compradores del principal.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Ascensión</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>El upsell de mayor valor que se ofrece después del embudo (un programa de 300 a 1.000 USD), por checkout o por llamada.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -2079,11 +3479,11 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Embudo</t>
+          <t>Ninguna celda con error en Simulador</t>
         </is>
       </c>
       <c r="C7" s="36">
-        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Simulador'!C5:G220)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -2095,11 +3495,11 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Resumen</t>
+          <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
       <c r="C8" s="36">
-        <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -2111,11 +3511,11 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Proyección 12 meses</t>
+          <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
       <c r="C9" s="36">
-        <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -2127,11 +3527,11 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Escenarios</t>
+          <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
       <c r="C10" s="36">
-        <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -2143,11 +3543,11 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Seguimiento</t>
+          <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
       <c r="C11" s="36">
-        <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
+        <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -2159,168 +3559,184 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Los supuestos de tráfico son mayores a cero</t>
+          <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
       <c r="C12" s="36">
-        <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$12&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
+        <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
+          <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>La curva de cobranza suma 100 %</t>
+          <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
       <c r="C13" s="36">
-        <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
+        <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$12&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
+          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comisiones + reembolsos menores al 60 %</t>
+          <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
       <c r="C14" s="36">
-        <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
+        <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Si suman más, revisá los porcentajes.</t>
+          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>El escenario en uso es 1, 2 o 3</t>
+          <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
       <c r="C15" s="36">
-        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
+        <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Supuestos → celda 'Escenario en uso'.</t>
+          <t>Si suman más, revisá los porcentajes.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>La inversión es mayor a cero</t>
+          <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
       <c r="C16" s="36">
-        <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D16" s="5" t="inlineStr"/>
+        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → celda 'Escenario en uso'.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
+          <t>La inversión es mayor a cero</t>
         </is>
       </c>
       <c r="C17" s="36">
-        <f>IF('Modelo'!$C$11&gt;0,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
-        </is>
-      </c>
+        <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>Las conversiones están entre 0 y 100 %</t>
+          <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
       <c r="C18" s="36">
-        <f>IF(AND('Supuestos'!$C$12&gt;=0,'Supuestos'!$C$12&lt;=1,'Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$28&gt;=0,'Supuestos'!$C$28&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
+        <f>IF('Modelo'!$C$11&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
+          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>El margen de seguridad está entre 0 y 100 %</t>
+          <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
       <c r="C19" s="36">
-        <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D19" s="5" t="inlineStr"/>
+        <f>IF(AND('Supuestos'!$C$12&gt;=0,'Supuestos'!$C$12&lt;=1,'Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$28&gt;=0,'Supuestos'!$C$28&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>El crecimiento mensual está entre −50 % y 100 %</t>
+          <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
       <c r="C20" s="36">
-        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>Más de 100 % por mes no es realista para una proyección.</t>
-        </is>
-      </c>
+        <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
+          <t>El crecimiento mensual está entre −50 % y 100 %</t>
+        </is>
+      </c>
+      <c r="C21" s="36">
+        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>Más de 100 % por mes no es realista para una proyección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C21" s="36">
+      <c r="C22" s="36">
         <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$8,'Modelo'!$C$10&lt;='Modelo'!$C$9),"OK","REVISAR")</f>
         <v/>
       </c>
-      <c r="D21" s="5" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Si falla, alguna conversión está por encima de 100 %.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C23" s="37">
-        <f>IF(COUNTIF(C6:C21,"REVISAR")=0,"OK","REVISAR")</f>
+      <c r="C24" s="37">
+        <f>IF(COUNTIF(C6:C22,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C23">
+  <conditionalFormatting sqref="C6:C24">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -2340,7 +3756,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F3864"/>
@@ -2916,6 +4332,2195 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H97"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="62" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Simulador: movés un número y ves cómo se mueve todo el embudo</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Amarillo = tu número: arranca igual a Supuestos; escribí encima para probar (CPM, CTR, conversiones, precios, costos). Al lado, la base. 'Con tus números' se recalcula al instante y se compara con el Modelo. Para volver a la base, borrá la celda amarilla y escribí =D seguido del número de fila (por ejemplo =D9).</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Paso / métrica</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Tu número (editable)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Base (Supuestos)</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Con tus números</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Base (Modelo)</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Diferencia</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Cómo se calcula</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Tráfico y unidades</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Costo por visita a la página de ventas (VSL)</t>
+        </is>
+      </c>
+      <c r="C7" s="16">
+        <f>'Supuestos'!$C$9</f>
+        <v/>
+      </c>
+      <c r="D7" s="17">
+        <f>'Supuestos'!$C$9</f>
+        <v/>
+      </c>
+      <c r="G7">
+        <f>IF(C7&lt;&gt;D7,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Costo por visita (unidad de adquisición)</t>
+        </is>
+      </c>
+      <c r="E8" s="17">
+        <f>$C$7</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>'Modelo'!$C$7</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>IF(AND(ISNUMBER(E8),ISNUMBER(F8)),E8-F8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>El supuesto 'costo por visita'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Inversión en publicidad por mes</t>
+        </is>
+      </c>
+      <c r="C9" s="18">
+        <f>'Supuestos'!$C$8</f>
+        <v/>
+      </c>
+      <c r="D9" s="19">
+        <f>'Supuestos'!$C$8</f>
+        <v/>
+      </c>
+      <c r="G9">
+        <f>IF(C9&lt;&gt;D9,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Visitas a la página de ventas</t>
+        </is>
+      </c>
+      <c r="E10" s="20">
+        <f>IF($E$8=0,0,$C$9/$E$8)</f>
+        <v/>
+      </c>
+      <c r="F10" s="21">
+        <f>'Modelo'!$C$8</f>
+        <v/>
+      </c>
+      <c r="G10" s="21">
+        <f>IF(AND(ISNUMBER(E10),ISNUMBER(F10)),E10-F10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="5" t="inlineStr">
+        <is>
+          <t>Inversión ÷ costo por visita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>% de visitas que llegan al checkout</t>
+        </is>
+      </c>
+      <c r="C11" s="22">
+        <f>'Supuestos'!$C$12</f>
+        <v/>
+      </c>
+      <c r="D11" s="23">
+        <f>'Supuestos'!$C$12</f>
+        <v/>
+      </c>
+      <c r="G11">
+        <f>IF(C11&lt;&gt;D11,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Checkouts iniciados</t>
+        </is>
+      </c>
+      <c r="E12" s="21">
+        <f>$E$10*$C$11</f>
+        <v/>
+      </c>
+      <c r="F12" s="21">
+        <f>'Modelo'!$C$9</f>
+        <v/>
+      </c>
+      <c r="G12" s="21">
+        <f>IF(AND(ISNUMBER(E12),ISNUMBER(F12)),E12-F12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Visitas × % que llega al checkout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>% de checkouts que terminan en compra</t>
+        </is>
+      </c>
+      <c r="C13" s="22">
+        <f>'Supuestos'!$C$13</f>
+        <v/>
+      </c>
+      <c r="D13" s="23">
+        <f>'Supuestos'!$C$13</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>IF(C13&lt;&gt;D13,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Ventas del producto principal</t>
+        </is>
+      </c>
+      <c r="E14" s="11">
+        <f>$E$12*$C$13</f>
+        <v/>
+      </c>
+      <c r="F14" s="24">
+        <f>'Modelo'!$C$10</f>
+        <v/>
+      </c>
+      <c r="G14" s="24">
+        <f>IF(AND(ISNUMBER(E14),ISNUMBER(F14)),E14-F14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>Checkouts × % que compra.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>% de visitas que compran</t>
+        </is>
+      </c>
+      <c r="E15" s="25">
+        <f>IF($E$10=0,0,$E$14/$E$10)</f>
+        <v/>
+      </c>
+      <c r="F15" s="25">
+        <f>'Modelo'!$C$11</f>
+        <v/>
+      </c>
+      <c r="G15" s="25">
+        <f>IF(AND(ISNUMBER(E15),ISNUMBER(F15)),E15-F15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>Ventas ÷ visitas. Las dos conversiones multiplicadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Costo por comprador (CPA)</t>
+        </is>
+      </c>
+      <c r="E16" s="12">
+        <f>IF($E$14=0,0,$C$9/$E$14)</f>
+        <v/>
+      </c>
+      <c r="F16" s="17">
+        <f>'Modelo'!$C$12</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>IF(AND(ISNUMBER(E16),ISNUMBER(F16)),E16-F16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>Inversión ÷ ventas del principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Facturación por producto</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="n"/>
+      <c r="D17" s="8" t="n"/>
+      <c r="E17" s="8" t="n"/>
+      <c r="F17" s="8" t="n"/>
+      <c r="G17" s="8" t="n"/>
+      <c r="H17" s="8" t="n"/>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Producto principal: precio</t>
+        </is>
+      </c>
+      <c r="C18" s="16">
+        <f>'Supuestos'!$C$16</f>
+        <v/>
+      </c>
+      <c r="D18" s="17">
+        <f>'Supuestos'!$C$16</f>
+        <v/>
+      </c>
+      <c r="G18">
+        <f>IF(C18&lt;&gt;D18,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Facturado: producto principal</t>
+        </is>
+      </c>
+      <c r="E19" s="19">
+        <f>$E$14*$C$18</f>
+        <v/>
+      </c>
+      <c r="F19" s="19">
+        <f>'Modelo'!$C$14</f>
+        <v/>
+      </c>
+      <c r="G19" s="19">
+        <f>IF(AND(ISNUMBER(E19),ISNUMBER(F19)),E19-F19,"")</f>
+        <v/>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bump 1: % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C20" s="22">
+        <f>'Supuestos'!$C$18</f>
+        <v/>
+      </c>
+      <c r="D20" s="23">
+        <f>'Supuestos'!$C$18</f>
+        <v/>
+      </c>
+      <c r="G20">
+        <f>IF(C20&lt;&gt;D20,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Ventas: Bump 1</t>
+        </is>
+      </c>
+      <c r="E21" s="24">
+        <f>$E$14*$C$20</f>
+        <v/>
+      </c>
+      <c r="F21" s="24">
+        <f>'Modelo'!$C$15</f>
+        <v/>
+      </c>
+      <c r="G21" s="24">
+        <f>IF(AND(ISNUMBER(E21),ISNUMBER(F21)),E21-F21,"")</f>
+        <v/>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Bump 1: precio</t>
+        </is>
+      </c>
+      <c r="C22" s="16">
+        <f>'Supuestos'!$C$17</f>
+        <v/>
+      </c>
+      <c r="D22" s="17">
+        <f>'Supuestos'!$C$17</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IF(C22&lt;&gt;D22,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Facturado: Bump 1</t>
+        </is>
+      </c>
+      <c r="E23" s="19">
+        <f>$E$21*$C$22</f>
+        <v/>
+      </c>
+      <c r="F23" s="19">
+        <f>'Modelo'!$C$16</f>
+        <v/>
+      </c>
+      <c r="G23" s="19">
+        <f>IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23-F23,"")</f>
+        <v/>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bump 2: % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C24" s="22">
+        <f>'Supuestos'!$C$20</f>
+        <v/>
+      </c>
+      <c r="D24" s="23">
+        <f>'Supuestos'!$C$20</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>IF(C24&lt;&gt;D24,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ventas: Bump 2</t>
+        </is>
+      </c>
+      <c r="E25" s="24">
+        <f>$E$14*$C$24</f>
+        <v/>
+      </c>
+      <c r="F25" s="24">
+        <f>'Modelo'!$C$17</f>
+        <v/>
+      </c>
+      <c r="G25" s="24">
+        <f>IF(AND(ISNUMBER(E25),ISNUMBER(F25)),E25-F25,"")</f>
+        <v/>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Bump 2: precio</t>
+        </is>
+      </c>
+      <c r="C26" s="16">
+        <f>'Supuestos'!$C$19</f>
+        <v/>
+      </c>
+      <c r="D26" s="17">
+        <f>'Supuestos'!$C$19</f>
+        <v/>
+      </c>
+      <c r="G26">
+        <f>IF(C26&lt;&gt;D26,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Facturado: Bump 2</t>
+        </is>
+      </c>
+      <c r="E27" s="19">
+        <f>$E$25*$C$26</f>
+        <v/>
+      </c>
+      <c r="F27" s="19">
+        <f>'Modelo'!$C$18</f>
+        <v/>
+      </c>
+      <c r="G27" s="19">
+        <f>IF(AND(ISNUMBER(E27),ISNUMBER(F27)),E27-F27,"")</f>
+        <v/>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>OTO 1: % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C28" s="22">
+        <f>'Supuestos'!$C$22</f>
+        <v/>
+      </c>
+      <c r="D28" s="23">
+        <f>'Supuestos'!$C$22</f>
+        <v/>
+      </c>
+      <c r="G28">
+        <f>IF(C28&lt;&gt;D28,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ventas: OTO 1</t>
+        </is>
+      </c>
+      <c r="E29" s="24">
+        <f>$E$14*$C$28</f>
+        <v/>
+      </c>
+      <c r="F29" s="24">
+        <f>'Modelo'!$C$19</f>
+        <v/>
+      </c>
+      <c r="G29" s="24">
+        <f>IF(AND(ISNUMBER(E29),ISNUMBER(F29)),E29-F29,"")</f>
+        <v/>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>OTO 1: precio</t>
+        </is>
+      </c>
+      <c r="C30" s="16">
+        <f>'Supuestos'!$C$21</f>
+        <v/>
+      </c>
+      <c r="D30" s="17">
+        <f>'Supuestos'!$C$21</f>
+        <v/>
+      </c>
+      <c r="G30">
+        <f>IF(C30&lt;&gt;D30,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Facturado: OTO 1</t>
+        </is>
+      </c>
+      <c r="E31" s="19">
+        <f>$E$29*$C$30</f>
+        <v/>
+      </c>
+      <c r="F31" s="19">
+        <f>'Modelo'!$C$20</f>
+        <v/>
+      </c>
+      <c r="G31" s="19">
+        <f>IF(AND(ISNUMBER(E31),ISNUMBER(F31)),E31-F31,"")</f>
+        <v/>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>OTO 2: % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C32" s="22">
+        <f>'Supuestos'!$C$24</f>
+        <v/>
+      </c>
+      <c r="D32" s="23">
+        <f>'Supuestos'!$C$24</f>
+        <v/>
+      </c>
+      <c r="G32">
+        <f>IF(C32&lt;&gt;D32,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Ventas: OTO 2</t>
+        </is>
+      </c>
+      <c r="E33" s="24">
+        <f>$E$14*$C$32</f>
+        <v/>
+      </c>
+      <c r="F33" s="24">
+        <f>'Modelo'!$C$21</f>
+        <v/>
+      </c>
+      <c r="G33" s="24">
+        <f>IF(AND(ISNUMBER(E33),ISNUMBER(F33)),E33-F33,"")</f>
+        <v/>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>OTO 2: precio</t>
+        </is>
+      </c>
+      <c r="C34" s="16">
+        <f>'Supuestos'!$C$23</f>
+        <v/>
+      </c>
+      <c r="D34" s="17">
+        <f>'Supuestos'!$C$23</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IF(C34&lt;&gt;D34,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Facturado: OTO 2</t>
+        </is>
+      </c>
+      <c r="E35" s="19">
+        <f>$E$33*$C$34</f>
+        <v/>
+      </c>
+      <c r="F35" s="19">
+        <f>'Modelo'!$C$22</f>
+        <v/>
+      </c>
+      <c r="G35" s="19">
+        <f>IF(AND(ISNUMBER(E35),ISNUMBER(F35)),E35-F35,"")</f>
+        <v/>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>OTO 3: % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C36" s="22">
+        <f>'Supuestos'!$C$26</f>
+        <v/>
+      </c>
+      <c r="D36" s="23">
+        <f>'Supuestos'!$C$26</f>
+        <v/>
+      </c>
+      <c r="G36">
+        <f>IF(C36&lt;&gt;D36,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Ventas: OTO 3</t>
+        </is>
+      </c>
+      <c r="E37" s="24">
+        <f>$E$14*$C$36</f>
+        <v/>
+      </c>
+      <c r="F37" s="24">
+        <f>'Modelo'!$C$23</f>
+        <v/>
+      </c>
+      <c r="G37" s="24">
+        <f>IF(AND(ISNUMBER(E37),ISNUMBER(F37)),E37-F37,"")</f>
+        <v/>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OTO 3: precio</t>
+        </is>
+      </c>
+      <c r="C38" s="16">
+        <f>'Supuestos'!$C$25</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>'Supuestos'!$C$25</f>
+        <v/>
+      </c>
+      <c r="G38">
+        <f>IF(C38&lt;&gt;D38,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Facturado: OTO 3</t>
+        </is>
+      </c>
+      <c r="E39" s="19">
+        <f>$E$37*$C$38</f>
+        <v/>
+      </c>
+      <c r="F39" s="19">
+        <f>'Modelo'!$C$24</f>
+        <v/>
+      </c>
+      <c r="G39" s="19">
+        <f>IF(AND(ISNUMBER(E39),ISNUMBER(F39)),E39-F39,"")</f>
+        <v/>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OTO 4: % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C40" s="22">
+        <f>'Supuestos'!$C$28</f>
+        <v/>
+      </c>
+      <c r="D40" s="23">
+        <f>'Supuestos'!$C$28</f>
+        <v/>
+      </c>
+      <c r="G40">
+        <f>IF(C40&lt;&gt;D40,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ventas: OTO 4</t>
+        </is>
+      </c>
+      <c r="E41" s="24">
+        <f>$E$14*$C$40</f>
+        <v/>
+      </c>
+      <c r="F41" s="24">
+        <f>'Modelo'!$C$25</f>
+        <v/>
+      </c>
+      <c r="G41" s="24">
+        <f>IF(AND(ISNUMBER(E41),ISNUMBER(F41)),E41-F41,"")</f>
+        <v/>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OTO 4: precio</t>
+        </is>
+      </c>
+      <c r="C42" s="16">
+        <f>'Supuestos'!$C$27</f>
+        <v/>
+      </c>
+      <c r="D42" s="17">
+        <f>'Supuestos'!$C$27</f>
+        <v/>
+      </c>
+      <c r="G42">
+        <f>IF(C42&lt;&gt;D42,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Facturado: OTO 4</t>
+        </is>
+      </c>
+      <c r="E43" s="19">
+        <f>$E$41*$C$42</f>
+        <v/>
+      </c>
+      <c r="F43" s="19">
+        <f>'Modelo'!$C$26</f>
+        <v/>
+      </c>
+      <c r="G43" s="19">
+        <f>IF(AND(ISNUMBER(E43),ISNUMBER(F43)),E43-F43,"")</f>
+        <v/>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
+        </is>
+      </c>
+      <c r="C44" s="22">
+        <f>'Supuestos'!$C$30</f>
+        <v/>
+      </c>
+      <c r="D44" s="23">
+        <f>'Supuestos'!$C$30</f>
+        <v/>
+      </c>
+      <c r="G44">
+        <f>IF(C44&lt;&gt;D44,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ventas: Ascensión (programa de mayor valor)</t>
+        </is>
+      </c>
+      <c r="E45" s="24">
+        <f>$E$14*$C$44</f>
+        <v/>
+      </c>
+      <c r="F45" s="24">
+        <f>'Modelo'!$C$27</f>
+        <v/>
+      </c>
+      <c r="G45" s="24">
+        <f>IF(AND(ISNUMBER(E45),ISNUMBER(F45)),E45-F45,"")</f>
+        <v/>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>Compradores del principal × % que lo toma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Ascensión (programa de mayor valor): precio</t>
+        </is>
+      </c>
+      <c r="C46" s="16">
+        <f>'Supuestos'!$C$29</f>
+        <v/>
+      </c>
+      <c r="D46" s="17">
+        <f>'Supuestos'!$C$29</f>
+        <v/>
+      </c>
+      <c r="G46">
+        <f>IF(C46&lt;&gt;D46,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Facturado: Ascensión (programa de mayor valor)</t>
+        </is>
+      </c>
+      <c r="E47" s="19">
+        <f>$E$45*$C$46</f>
+        <v/>
+      </c>
+      <c r="F47" s="19">
+        <f>'Modelo'!$C$28</f>
+        <v/>
+      </c>
+      <c r="G47" s="19">
+        <f>IF(AND(ISNUMBER(E47),ISNUMBER(F47)),E47-F47,"")</f>
+        <v/>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>Ventas × precio.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Facturado total</t>
+        </is>
+      </c>
+      <c r="E48" s="9">
+        <f>$E$19+$E$23+$E$27+$E$31+$E$35+$E$39+$E$43+$E$47</f>
+        <v/>
+      </c>
+      <c r="F48" s="19">
+        <f>'Modelo'!$C$29</f>
+        <v/>
+      </c>
+      <c r="G48" s="19">
+        <f>IF(AND(ISNUMBER(E48),ISNUMBER(F48)),E48-F48,"")</f>
+        <v/>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>Suma de todos los productos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Facturado por comprador (AOV)</t>
+        </is>
+      </c>
+      <c r="E49" s="12">
+        <f>IF($E$14=0,0,$E$48/$E$14)</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>'Modelo'!$C$30</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>IF(AND(ISNUMBER(E49),ISNUMBER(F49)),E49-F49,"")</f>
+        <v/>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>Facturado total ÷ ventas del principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>AOV ÷ precio del principal</t>
+        </is>
+      </c>
+      <c r="E50" s="26">
+        <f>IF($C$18=0,0,$E$49/$C$18)</f>
+        <v/>
+      </c>
+      <c r="F50" s="26">
+        <f>'Modelo'!$C$31</f>
+        <v/>
+      </c>
+      <c r="G50" s="26">
+        <f>IF(AND(ISNUMBER(E50),ISNUMBER(F50)),E50-F50,"")</f>
+        <v/>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>Cuánto multiplica la escalera al precio del front.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Ventas del principal por visita (para la proyección)</t>
+        </is>
+      </c>
+      <c r="E51" s="25">
+        <f>IF($E$10=0,0,$E$14/$E$10)</f>
+        <v/>
+      </c>
+      <c r="F51" s="25">
+        <f>'Modelo'!$C$32</f>
+        <v/>
+      </c>
+      <c r="G51" s="25">
+        <f>IF(AND(ISNUMBER(E51),ISNUMBER(F51)),E51-F51,"")</f>
+        <v/>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>Igual a '% de visitas que compran'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Facturado por visita</t>
+        </is>
+      </c>
+      <c r="E52" s="17">
+        <f>IF($E$10=0,0,$E$48/$E$10)</f>
+        <v/>
+      </c>
+      <c r="F52" s="17">
+        <f>'Modelo'!$C$33</f>
+        <v/>
+      </c>
+      <c r="G52" s="17">
+        <f>IF(AND(ISNUMBER(E52),ISNUMBER(F52)),E52-F52,"")</f>
+        <v/>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>Facturado total ÷ visitas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>Cash, costos y ganancia del período</t>
+        </is>
+      </c>
+      <c r="C53" s="8" t="n"/>
+      <c r="D53" s="8" t="n"/>
+      <c r="E53" s="8" t="n"/>
+      <c r="F53" s="8" t="n"/>
+      <c r="G53" s="8" t="n"/>
+      <c r="H53" s="8" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>% del facturado que entra en el mes 1</t>
+        </is>
+      </c>
+      <c r="C54" s="22">
+        <f>'Supuestos'!$C$40</f>
+        <v/>
+      </c>
+      <c r="D54" s="23">
+        <f>'Supuestos'!$C$40</f>
+        <v/>
+      </c>
+      <c r="G54">
+        <f>IF(C54&lt;&gt;D54,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>% que entra en el mes 2</t>
+        </is>
+      </c>
+      <c r="C55" s="22">
+        <f>'Supuestos'!$C$41</f>
+        <v/>
+      </c>
+      <c r="D55" s="23">
+        <f>'Supuestos'!$C$41</f>
+        <v/>
+      </c>
+      <c r="G55">
+        <f>IF(C55&lt;&gt;D55,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>% que entra en el mes 3</t>
+        </is>
+      </c>
+      <c r="C56" s="22">
+        <f>'Supuestos'!$C$42</f>
+        <v/>
+      </c>
+      <c r="D56" s="23">
+        <f>'Supuestos'!$C$42</f>
+        <v/>
+      </c>
+      <c r="G56">
+        <f>IF(C56&lt;&gt;D56,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Cash a cobrar (facturado × cobranza completa)</t>
+        </is>
+      </c>
+      <c r="E57" s="19">
+        <f>$E$48*($C$54+$C$55+$C$56)</f>
+        <v/>
+      </c>
+      <c r="F57" s="19">
+        <f>'Modelo'!$C$35</f>
+        <v/>
+      </c>
+      <c r="G57" s="19">
+        <f>IF(AND(ISNUMBER(E57),ISNUMBER(F57)),E57-F57,"")</f>
+        <v/>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>Facturado × (mes 1 + mes 2 + mes 3). Si la cobranza suma 100 %, es igual al facturado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Cash que entra en el primer mes</t>
+        </is>
+      </c>
+      <c r="E58" s="19">
+        <f>$E$48*$C$54</f>
+        <v/>
+      </c>
+      <c r="F58" s="19">
+        <f>'Modelo'!$C$36</f>
+        <v/>
+      </c>
+      <c r="G58" s="19">
+        <f>IF(AND(ISNUMBER(E58),ISNUMBER(F58)),E58-F58,"")</f>
+        <v/>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>Facturado × % del mes 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Comisión de la pasarela o plataforma de pago</t>
+        </is>
+      </c>
+      <c r="C59" s="22">
+        <f>'Supuestos'!$C$33</f>
+        <v/>
+      </c>
+      <c r="D59" s="23">
+        <f>'Supuestos'!$C$33</f>
+        <v/>
+      </c>
+      <c r="G59">
+        <f>IF(C59&lt;&gt;D59,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Comisión del equipo de ventas</t>
+        </is>
+      </c>
+      <c r="C60" s="22">
+        <f>'Supuestos'!$C$34</f>
+        <v/>
+      </c>
+      <c r="D60" s="23">
+        <f>'Supuestos'!$C$34</f>
+        <v/>
+      </c>
+      <c r="G60">
+        <f>IF(C60&lt;&gt;D60,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Comisiones (pasarela + ventas)</t>
+        </is>
+      </c>
+      <c r="E61" s="19">
+        <f>$E$57*($C$59+$C$60)</f>
+        <v/>
+      </c>
+      <c r="F61" s="19">
+        <f>'Modelo'!$C$37</f>
+        <v/>
+      </c>
+      <c r="G61" s="19">
+        <f>IF(AND(ISNUMBER(E61),ISNUMBER(F61)),E61-F61,"")</f>
+        <v/>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>Cash × (pasarela + equipo de ventas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Reembolsos y contracargos</t>
+        </is>
+      </c>
+      <c r="C62" s="22">
+        <f>'Supuestos'!$C$35</f>
+        <v/>
+      </c>
+      <c r="D62" s="23">
+        <f>'Supuestos'!$C$35</f>
+        <v/>
+      </c>
+      <c r="G62">
+        <f>IF(C62&lt;&gt;D62,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Reembolsos</t>
+        </is>
+      </c>
+      <c r="E63" s="19">
+        <f>$E$57*$C$62</f>
+        <v/>
+      </c>
+      <c r="F63" s="19">
+        <f>'Modelo'!$C$38</f>
+        <v/>
+      </c>
+      <c r="G63" s="19">
+        <f>IF(AND(ISNUMBER(E63),ISNUMBER(F63)),E63-F63,"")</f>
+        <v/>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>Cash × % de reembolsos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Cash neto</t>
+        </is>
+      </c>
+      <c r="E64" s="9">
+        <f>$E$57*(1-$C$59-$C$60-$C$62)</f>
+        <v/>
+      </c>
+      <c r="F64" s="19">
+        <f>'Modelo'!$C$39</f>
+        <v/>
+      </c>
+      <c r="G64" s="19">
+        <f>IF(AND(ISNUMBER(E64),ISNUMBER(F64)),E64-F64,"")</f>
+        <v/>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>Cash − comisiones − reembolsos. La base de verdad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Costos por visita (herramientas, WhatsApp, IA)</t>
+        </is>
+      </c>
+      <c r="C65" s="16">
+        <f>'Supuestos'!$C$36</f>
+        <v/>
+      </c>
+      <c r="D65" s="17">
+        <f>'Supuestos'!$C$36</f>
+        <v/>
+      </c>
+      <c r="G65">
+        <f>IF(C65&lt;&gt;D65,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H65" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Costos por visita (herramientas, WhatsApp, IA)</t>
+        </is>
+      </c>
+      <c r="E66" s="19">
+        <f>$E$10*$C$65</f>
+        <v/>
+      </c>
+      <c r="F66" s="19">
+        <f>'Modelo'!$C$40</f>
+        <v/>
+      </c>
+      <c r="G66" s="19">
+        <f>IF(AND(ISNUMBER(E66),ISNUMBER(F66)),E66-F66,"")</f>
+        <v/>
+      </c>
+      <c r="H66" s="5" t="inlineStr">
+        <is>
+          <t>Visitas × costo por visita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Costos fijos por mes</t>
+        </is>
+      </c>
+      <c r="C67" s="18">
+        <f>'Supuestos'!$C$37</f>
+        <v/>
+      </c>
+      <c r="D67" s="19">
+        <f>'Supuestos'!$C$37</f>
+        <v/>
+      </c>
+      <c r="G67">
+        <f>IF(C67&lt;&gt;D67,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H67" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia del período</t>
+        </is>
+      </c>
+      <c r="E68" s="9">
+        <f>$E$64-$E$66-$C$67-$C$9</f>
+        <v/>
+      </c>
+      <c r="F68" s="19">
+        <f>'Modelo'!$C$41</f>
+        <v/>
+      </c>
+      <c r="G68" s="19">
+        <f>IF(AND(ISNUMBER(E68),ISNUMBER(F68)),E68-F68,"")</f>
+        <v/>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>Cash neto − costos por unidad − fijos − inversión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>ROAS sobre facturado</t>
+        </is>
+      </c>
+      <c r="E69" s="26">
+        <f>IF($C$9=0,0,$E$48/$C$9)</f>
+        <v/>
+      </c>
+      <c r="F69" s="26">
+        <f>'Modelo'!$C$42</f>
+        <v/>
+      </c>
+      <c r="G69" s="26">
+        <f>IF(AND(ISNUMBER(E69),ISNUMBER(F69)),E69-F69,"")</f>
+        <v/>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>Facturado ÷ inversión. El número que más se infla: no decidas con este.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>ROAS sobre cash neto</t>
+        </is>
+      </c>
+      <c r="E70" s="10">
+        <f>IF($C$9=0,0,$E$64/$C$9)</f>
+        <v/>
+      </c>
+      <c r="F70" s="26">
+        <f>'Modelo'!$C$43</f>
+        <v/>
+      </c>
+      <c r="G70" s="26">
+        <f>IF(AND(ISNUMBER(E70),ISNUMBER(F70)),E70-F70,"")</f>
+        <v/>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>Cash neto ÷ inversión. Con este se decide.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Margen sobre cash</t>
+        </is>
+      </c>
+      <c r="E71" s="23">
+        <f>IF($E$57=0,0,$E$68/$E$57)</f>
+        <v/>
+      </c>
+      <c r="F71" s="23">
+        <f>'Modelo'!$C$44</f>
+        <v/>
+      </c>
+      <c r="G71" s="23">
+        <f>IF(AND(ISNUMBER(E71),ISNUMBER(F71)),E71-F71,"")</f>
+        <v/>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>Ganancia ÷ cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>ROAS objetivo sobre cash neto</t>
+        </is>
+      </c>
+      <c r="C72" s="27">
+        <f>'Supuestos'!$C$45</f>
+        <v/>
+      </c>
+      <c r="D72" s="26">
+        <f>'Supuestos'!$C$45</f>
+        <v/>
+      </c>
+      <c r="G72">
+        <f>IF(C72&lt;&gt;D72,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>¿Cumple el ROAS objetivo?</t>
+        </is>
+      </c>
+      <c r="E73" s="28">
+        <f>IF($E$70&gt;=$C$72,"SÍ","NO")</f>
+        <v/>
+      </c>
+      <c r="F73" s="28">
+        <f>'Modelo'!$C$45</f>
+        <v/>
+      </c>
+      <c r="G73">
+        <f>IF(E73=F73,"","≠ base")</f>
+        <v/>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>ROAS sobre cash neto contra el objetivo de Supuestos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>Cuánto vale cada unidad y hasta cuánto pagar</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="n"/>
+      <c r="D74" s="8" t="n"/>
+      <c r="E74" s="8" t="n"/>
+      <c r="F74" s="8" t="n"/>
+      <c r="G74" s="8" t="n"/>
+      <c r="H74" s="8" t="n"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Valor neto por visita</t>
+        </is>
+      </c>
+      <c r="E75" s="12">
+        <f>IF($E$10=0,0,($E$64-$E$66)/$E$10)</f>
+        <v/>
+      </c>
+      <c r="F75" s="17">
+        <f>'Modelo'!$C$47</f>
+        <v/>
+      </c>
+      <c r="G75" s="17">
+        <f>IF(AND(ISNUMBER(E75),ISNUMBER(F75)),E75-F75,"")</f>
+        <v/>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>(Cash neto − costos por unidad) ÷ visitas. Lo que vale una visita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Techo de costo por visita (break-even)</t>
+        </is>
+      </c>
+      <c r="E76" s="12">
+        <f>$E$75</f>
+        <v/>
+      </c>
+      <c r="F76" s="17">
+        <f>'Modelo'!$C$48</f>
+        <v/>
+      </c>
+      <c r="G76" s="17">
+        <f>IF(AND(ISNUMBER(E76),ISNUMBER(F76)),E76-F76,"")</f>
+        <v/>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>Igual al valor neto por visita: pagando esto no ganás ni perdés.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Margen de seguridad</t>
+        </is>
+      </c>
+      <c r="C77" s="22">
+        <f>'Supuestos'!$C$46</f>
+        <v/>
+      </c>
+      <c r="D77" s="23">
+        <f>'Supuestos'!$C$46</f>
+        <v/>
+      </c>
+      <c r="G77">
+        <f>IF(C77&lt;&gt;D77,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Objetivo de costo por visita</t>
+        </is>
+      </c>
+      <c r="E78" s="12">
+        <f>$E$76/(1+$C$77)</f>
+        <v/>
+      </c>
+      <c r="F78" s="17">
+        <f>'Modelo'!$C$49</f>
+        <v/>
+      </c>
+      <c r="G78" s="17">
+        <f>IF(AND(ISNUMBER(E78),ISNUMBER(F78)),E78-F78,"")</f>
+        <v/>
+      </c>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>Techo ÷ (1 + margen de seguridad).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Techo de costo por checkout</t>
+        </is>
+      </c>
+      <c r="E79" s="17">
+        <f>IF($C$11=0,0,$E$75/$C$11)</f>
+        <v/>
+      </c>
+      <c r="F79" s="17">
+        <f>'Modelo'!$C$50</f>
+        <v/>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(AND(ISNUMBER(E79),ISNUMBER(F79)),E79-F79,"")</f>
+        <v/>
+      </c>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>Valor por visita ÷ % que llega al checkout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Techo de costo por comprador (CPA máximo)</t>
+        </is>
+      </c>
+      <c r="E80" s="12">
+        <f>IF($E$15=0,0,$E$75/$E$15)</f>
+        <v/>
+      </c>
+      <c r="F80" s="17">
+        <f>'Modelo'!$C$51</f>
+        <v/>
+      </c>
+      <c r="G80" s="17">
+        <f>IF(AND(ISNUMBER(E80),ISNUMBER(F80)),E80-F80,"")</f>
+        <v/>
+      </c>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>Valor por visita ÷ % de visitas que compran.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Objetivo de CPA</t>
+        </is>
+      </c>
+      <c r="E81" s="17">
+        <f>$E$80/(1+$C$77)</f>
+        <v/>
+      </c>
+      <c r="F81" s="17">
+        <f>'Modelo'!$C$52</f>
+        <v/>
+      </c>
+      <c r="G81" s="17">
+        <f>IF(AND(ISNUMBER(E81),ISNUMBER(F81)),E81-F81,"")</f>
+        <v/>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>CPA máximo ÷ (1 + margen de seguridad).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Cash neto por comprador (AOV neto)</t>
+        </is>
+      </c>
+      <c r="E82" s="17">
+        <f>IF($E$14=0,0,($E$64-$E$66)/$E$14)</f>
+        <v/>
+      </c>
+      <c r="F82" s="17">
+        <f>'Modelo'!$C$53</f>
+        <v/>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(AND(ISNUMBER(E82),ISNUMBER(F82)),E82-F82,"")</f>
+        <v/>
+      </c>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>Lo que deja cada comprador después de comisiones y reembolsos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>AOV neto − CPA (lo que queda por comprador)</t>
+        </is>
+      </c>
+      <c r="E83" s="12">
+        <f>$E$82-$E$16</f>
+        <v/>
+      </c>
+      <c r="F83" s="17">
+        <f>'Modelo'!$C$54</f>
+        <v/>
+      </c>
+      <c r="G83" s="17">
+        <f>IF(AND(ISNUMBER(E83),ISNUMBER(F83)),E83-F83,"")</f>
+        <v/>
+      </c>
+      <c r="H83" s="5" t="inlineStr">
+        <is>
+          <t>Si es negativo, perdés plata con cada venta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>Semáforo y cuánto invertir</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="n"/>
+      <c r="D84" s="8" t="n"/>
+      <c r="E84" s="8" t="n"/>
+      <c r="F84" s="8" t="n"/>
+      <c r="G84" s="8" t="n"/>
+      <c r="H84" s="8" t="n"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Semáforo del costo por visita actual</t>
+        </is>
+      </c>
+      <c r="E85" s="13">
+        <f>IF($E$8&gt;$E$76,"ROJO",IF(AND($E$8&lt;=$E$78,$E$70&gt;=$C$72),"VERDE","AMARILLO"))</f>
+        <v/>
+      </c>
+      <c r="F85" s="28">
+        <f>'Modelo'!$C$56</f>
+        <v/>
+      </c>
+      <c r="G85">
+        <f>IF(E85=F85,"","≠ base")</f>
+        <v/>
+      </c>
+      <c r="H85" s="5" t="inlineStr">
+        <is>
+          <t>Rojo: costo &gt; techo. Verde: costo ≤ objetivo y ROAS sobre cash neto ≥ objetivo. Amarillo: el resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Meta de ventas del producto principal</t>
+        </is>
+      </c>
+      <c r="C86" s="29">
+        <f>'Supuestos'!$C$47</f>
+        <v/>
+      </c>
+      <c r="D86" s="21">
+        <f>'Supuestos'!$C$47</f>
+        <v/>
+      </c>
+      <c r="G86">
+        <f>IF(C86&lt;&gt;D86,"← cambiado","")</f>
+        <v/>
+      </c>
+      <c r="H86" s="5" t="inlineStr">
+        <is>
+          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Inversión necesaria para la meta de ventas (al costo actual)</t>
+        </is>
+      </c>
+      <c r="E87" s="9">
+        <f>IF($E$15=0,"inalcanzable con estos supuestos",$C$86/$E$15*$E$8)</f>
+        <v/>
+      </c>
+      <c r="F87" s="19">
+        <f>'Modelo'!$C$57</f>
+        <v/>
+      </c>
+      <c r="G87" s="19">
+        <f>IF(AND(ISNUMBER(E87),ISNUMBER(F87)),E87-F87,"")</f>
+        <v/>
+      </c>
+      <c r="H87" s="5" t="inlineStr">
+        <is>
+          <t>Meta ÷ % de visitas que compran × costo por visita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
+        </is>
+      </c>
+      <c r="E88" s="19">
+        <f>IF($E$15=0,"inalcanzable con estos supuestos",$C$86/$E$15*$E$78)</f>
+        <v/>
+      </c>
+      <c r="F88" s="19">
+        <f>'Modelo'!$C$58</f>
+        <v/>
+      </c>
+      <c r="G88" s="19">
+        <f>IF(AND(ISNUMBER(E88),ISNUMBER(F88)),E88-F88,"")</f>
+        <v/>
+      </c>
+      <c r="H88" s="5" t="inlineStr">
+        <is>
+          <t>Lo mismo, al costo objetivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>Ganancia por paso (las dos caras de cada número)</t>
+        </is>
+      </c>
+      <c r="C89" s="8" t="n"/>
+      <c r="D89" s="8" t="n"/>
+      <c r="E89" s="8" t="n"/>
+      <c r="F89" s="8" t="n"/>
+      <c r="G89" s="8" t="n"/>
+      <c r="H89" s="8" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Cash neto por comprador (AOV neto)</t>
+        </is>
+      </c>
+      <c r="E90" s="12">
+        <f>IF($E$14=0,0,($E$64-$E$66)/$E$14)</f>
+        <v/>
+      </c>
+      <c r="F90" s="17">
+        <f>'Modelo'!$C$53</f>
+        <v/>
+      </c>
+      <c r="G90" s="17">
+        <f>IF(AND(ISNUMBER(E90),ISNUMBER(F90)),E90-F90,"")</f>
+        <v/>
+      </c>
+      <c r="H90" s="5" t="inlineStr">
+        <is>
+          <t>Lo que deja cada comprador después de comisiones, reembolsos y costos por unidad. Su par es el CPA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia por visita</t>
+        </is>
+      </c>
+      <c r="E91" s="12">
+        <f>IF($E$10=0,0,$E$68/$E$10)</f>
+        <v/>
+      </c>
+      <c r="F91" s="17">
+        <f>'Modelo'!$C$60</f>
+        <v/>
+      </c>
+      <c r="G91" s="17">
+        <f>IF(AND(ISNUMBER(E91),ISNUMBER(F91)),E91-F91,"")</f>
+        <v/>
+      </c>
+      <c r="H91" s="5" t="inlineStr">
+        <is>
+          <t>Ganancia del período ÷ visitas. La métrica más valiosa del embudo: resume todo lo que pasa después de la página. Su par es el costo por visita.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ganancia por checkout</t>
+        </is>
+      </c>
+      <c r="E92" s="17">
+        <f>IF($E$12=0,0,$E$68/$E$12)</f>
+        <v/>
+      </c>
+      <c r="F92" s="17">
+        <f>'Modelo'!$C$61</f>
+        <v/>
+      </c>
+      <c r="G92" s="17">
+        <f>IF(AND(ISNUMBER(E92),ISNUMBER(F92)),E92-F92,"")</f>
+        <v/>
+      </c>
+      <c r="H92" s="5" t="inlineStr">
+        <is>
+          <t>Ganancia del período ÷ checkouts. Su par es el costo por checkout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia por cliente</t>
+        </is>
+      </c>
+      <c r="E93" s="12">
+        <f>IF($E$14=0,0,$E$68/$E$14)</f>
+        <v/>
+      </c>
+      <c r="F93" s="17">
+        <f>'Modelo'!$C$62</f>
+        <v/>
+      </c>
+      <c r="G93" s="17">
+        <f>IF(AND(ISNUMBER(E93),ISNUMBER(F93)),E93-F93,"")</f>
+        <v/>
+      </c>
+      <c r="H93" s="5" t="inlineStr">
+        <is>
+          <t>Ganancia del período ÷ compradores del principal. Su par es el CPA; la diferencia entre AOV neto y CPA es lo que queda por cliente antes de fijos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="B95" s="5" t="inlineStr">
+        <is>
+          <t>Cómo se lee: cambiá una celda amarilla (por ejemplo el CPM, el CTR, la conversión de la landing, el show, el cierre o el precio) y mirá cómo se mueven la cantidad de cada paso, el costo por paso, el facturado, el cash neto, la ganancia, el ROAS, el techo y el semáforo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="B96" s="5" t="inlineStr">
+        <is>
+          <t>Una variable por vez: si cambiás tres cosas no sabés cuál movió el resultado. La columna Diferencia te muestra exactamente cuánto cambió cada número contra la base.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="B97" s="5" t="inlineStr">
+        <is>
+          <t>El Simulador no modifica Supuestos ni Modelo: es tu mesa de pruebas. Cuando una prueba te convence, pasá ese número a Supuestos.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B95:H95"/>
+    <mergeCell ref="B96:H96"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C6:C93">
+    <cfRule type="expression" priority="1" dxfId="3">
+      <formula>AND(ISNUMBER(C6),C6&lt;&gt;D6)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E73:F73">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>LEFT(E73,5)="VERDE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="1">
+      <formula>LEFT(E73,8)="AMARILLO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" dxfId="2">
+      <formula>LEFT(E73,4)="ROJO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E85:F85">
+    <cfRule type="expression" priority="5" dxfId="0">
+      <formula>LEFT(E85,5)="VERDE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="6" dxfId="1">
+      <formula>LEFT(E85,8)="AMARILLO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="7" dxfId="2">
+      <formula>LEFT(E85,4)="ROJO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2999,7 +6604,7 @@
           <t>Visitas a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C6" s="16">
+      <c r="C6" s="21">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
@@ -3008,7 +6613,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$8/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3036,15 +6641,15 @@
           <t>Abren el checkout</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="21">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="18">
+      <c r="D7" s="23">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="17">
+      <c r="E7" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3072,15 +6677,15 @@
           <t>Compran el producto principal</t>
         </is>
       </c>
-      <c r="C8" s="16">
+      <c r="C8" s="21">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="23">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$10/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="17">
+      <c r="E8" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3108,15 +6713,15 @@
           <t>Toman el bump 1</t>
         </is>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="21">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$15/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E9" s="17">
+      <c r="E9" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$15/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3147,15 +6752,15 @@
           <t>Toman el bump 2</t>
         </is>
       </c>
-      <c r="C10" s="16">
+      <c r="C10" s="21">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D10" s="18">
+      <c r="D10" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$17/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E10" s="17">
+      <c r="E10" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$17/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3186,15 +6791,15 @@
           <t>Toman la OTO 1</t>
         </is>
       </c>
-      <c r="C11" s="16">
+      <c r="C11" s="21">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="18">
+      <c r="D11" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$19/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E11" s="17">
+      <c r="E11" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$19/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3225,15 +6830,15 @@
           <t>Toman la OTO 2</t>
         </is>
       </c>
-      <c r="C12" s="16">
+      <c r="C12" s="21">
         <f>'Modelo'!$C$21</f>
         <v/>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$21/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E12" s="17">
+      <c r="E12" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$21/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3264,15 +6869,15 @@
           <t>Toman la OTO 3</t>
         </is>
       </c>
-      <c r="C13" s="16">
+      <c r="C13" s="21">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="18">
+      <c r="D13" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$23/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E13" s="17">
+      <c r="E13" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$23/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3303,15 +6908,15 @@
           <t>Toman la OTO 4</t>
         </is>
       </c>
-      <c r="C14" s="16">
+      <c r="C14" s="21">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$25/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$25/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3342,15 +6947,15 @@
           <t>Ascienden al programa</t>
         </is>
       </c>
-      <c r="C15" s="16">
+      <c r="C15" s="21">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="18">
+      <c r="D15" s="23">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$27/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E15" s="17">
+      <c r="E15" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$27/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -3381,11 +6986,11 @@
           <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
         </is>
       </c>
-      <c r="F17" s="19">
+      <c r="F17" s="17">
         <f>F6</f>
         <v/>
       </c>
-      <c r="G17" s="19">
+      <c r="G17" s="17">
         <f>G6</f>
         <v/>
       </c>
@@ -3469,7 +7074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3552,7 +7157,7 @@
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="20" t="n">
+      <c r="C6" s="29" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -3585,7 +7190,7 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="18" t="n">
         <v>9000</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -3605,17 +7210,17 @@
           <t>Costo por visita a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="17">
         <f>IF('Supuestos'!$C$6=1,D9,IF('Supuestos'!$C$6=2,E9,F9))</f>
         <v/>
       </c>
-      <c r="D9" s="22" t="n">
+      <c r="D9" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="22" t="n">
+      <c r="E9" s="16" t="n">
         <v>0.3</v>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="16" t="n">
         <v>0.22</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -3648,17 +7253,17 @@
           <t>% de visitas que llegan al checkout</t>
         </is>
       </c>
-      <c r="C12" s="18">
+      <c r="C12" s="23">
         <f>IF('Supuestos'!$C$6=1,D12,IF('Supuestos'!$C$6=2,E12,F12))</f>
         <v/>
       </c>
-      <c r="D12" s="23" t="n">
+      <c r="D12" s="22" t="n">
         <v>0.025</v>
       </c>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="22" t="n">
         <v>0.035</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="22" t="n">
         <v>0.045</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -3678,17 +7283,17 @@
           <t>% de checkouts que terminan en compra</t>
         </is>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="23">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
-      <c r="D13" s="23" t="n">
+      <c r="D13" s="22" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="23" t="n">
+      <c r="E13" s="22" t="n">
         <v>0.26</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -3721,7 +7326,7 @@
           <t>Producto principal: precio</t>
         </is>
       </c>
-      <c r="C16" s="22" t="n">
+      <c r="C16" s="16" t="n">
         <v>37</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -3741,7 +7346,7 @@
           <t>Bump 1: precio</t>
         </is>
       </c>
-      <c r="C17" s="22" t="n">
+      <c r="C17" s="16" t="n">
         <v>17</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -3761,17 +7366,17 @@
           <t>Bump 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="23">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
-      <c r="D18" s="23" t="n">
+      <c r="D18" s="22" t="n">
         <v>0.18</v>
       </c>
-      <c r="E18" s="23" t="n">
+      <c r="E18" s="22" t="n">
         <v>0.25</v>
       </c>
-      <c r="F18" s="23" t="n">
+      <c r="F18" s="22" t="n">
         <v>0.35</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -3787,7 +7392,7 @@
           <t>Bump 2: precio</t>
         </is>
       </c>
-      <c r="C19" s="22" t="n">
+      <c r="C19" s="16" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -3807,17 +7412,17 @@
           <t>Bump 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="23">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
-      <c r="D20" s="23" t="n">
+      <c r="D20" s="22" t="n">
         <v>0.12</v>
       </c>
-      <c r="E20" s="23" t="n">
+      <c r="E20" s="22" t="n">
         <v>0.18</v>
       </c>
-      <c r="F20" s="23" t="n">
+      <c r="F20" s="22" t="n">
         <v>0.25</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -3833,7 +7438,7 @@
           <t>OTO 1: precio</t>
         </is>
       </c>
-      <c r="C21" s="22" t="n">
+      <c r="C21" s="16" t="n">
         <v>47</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -3853,17 +7458,17 @@
           <t>OTO 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C22" s="18">
+      <c r="C22" s="23">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
-      <c r="D22" s="23" t="n">
+      <c r="D22" s="22" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E22" s="23" t="n">
+      <c r="E22" s="22" t="n">
         <v>0.1</v>
       </c>
-      <c r="F22" s="23" t="n">
+      <c r="F22" s="22" t="n">
         <v>0.14</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -3879,7 +7484,7 @@
           <t>OTO 2: precio</t>
         </is>
       </c>
-      <c r="C23" s="22" t="n">
+      <c r="C23" s="16" t="n">
         <v>17</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -3899,17 +7504,17 @@
           <t>OTO 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C24" s="18">
+      <c r="C24" s="23">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
-      <c r="D24" s="23" t="n">
+      <c r="D24" s="22" t="n">
         <v>0.04</v>
       </c>
-      <c r="E24" s="23" t="n">
+      <c r="E24" s="22" t="n">
         <v>0.06</v>
       </c>
-      <c r="F24" s="23" t="n">
+      <c r="F24" s="22" t="n">
         <v>0.09</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -3925,7 +7530,7 @@
           <t>OTO 3: precio</t>
         </is>
       </c>
-      <c r="C25" s="22" t="n">
+      <c r="C25" s="16" t="n">
         <v>97</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -3945,17 +7550,17 @@
           <t>OTO 3: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C26" s="18">
+      <c r="C26" s="23">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
-      <c r="D26" s="23" t="n">
+      <c r="D26" s="22" t="n">
         <v>0.02</v>
       </c>
-      <c r="E26" s="23" t="n">
+      <c r="E26" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="22" t="n">
         <v>0.05</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -3971,7 +7576,7 @@
           <t>OTO 4: precio</t>
         </is>
       </c>
-      <c r="C27" s="22" t="n">
+      <c r="C27" s="16" t="n">
         <v>27</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -3991,17 +7596,17 @@
           <t>OTO 4: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C28" s="18">
+      <c r="C28" s="23">
         <f>IF('Supuestos'!$C$6=1,D28,IF('Supuestos'!$C$6=2,E28,F28))</f>
         <v/>
       </c>
-      <c r="D28" s="23" t="n">
+      <c r="D28" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="E28" s="23" t="n">
+      <c r="E28" s="22" t="n">
         <v>0.04</v>
       </c>
-      <c r="F28" s="23" t="n">
+      <c r="F28" s="22" t="n">
         <v>0.06</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -4017,7 +7622,7 @@
           <t>Ascensión (programa de mayor valor): precio</t>
         </is>
       </c>
-      <c r="C29" s="22" t="n">
+      <c r="C29" s="16" t="n">
         <v>297</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -4037,17 +7642,17 @@
           <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="18">
+      <c r="C30" s="23">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
-      <c r="D30" s="23" t="n">
+      <c r="D30" s="22" t="n">
         <v>0.01</v>
       </c>
-      <c r="E30" s="23" t="n">
+      <c r="E30" s="22" t="n">
         <v>0.02</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F30" s="22" t="n">
         <v>0.04</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -4076,7 +7681,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C33" s="23" t="n">
+      <c r="C33" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -4096,7 +7701,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C34" s="23" t="n">
+      <c r="C34" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -4116,7 +7721,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C35" s="23" t="n">
+      <c r="C35" s="22" t="n">
         <v>0.05</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -4136,7 +7741,7 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C36" s="22" t="n">
+      <c r="C36" s="16" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -4156,7 +7761,7 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C37" s="21" t="n">
+      <c r="C37" s="18" t="n">
         <v>1500</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -4189,7 +7794,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C40" s="23" t="n">
+      <c r="C40" s="22" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -4209,7 +7814,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C41" s="23" t="n">
+      <c r="C41" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -4229,7 +7834,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C42" s="23" t="n">
+      <c r="C42" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -4262,7 +7867,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C45" s="24" t="n">
+      <c r="C45" s="27" t="n">
         <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -4282,7 +7887,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C46" s="23" t="n">
+      <c r="C46" s="22" t="n">
         <v>0.3</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -4302,7 +7907,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C47" s="20" t="n">
+      <c r="C47" s="29" t="n">
         <v>500</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -4322,7 +7927,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C48" s="23" t="n">
+      <c r="C48" s="22" t="n">
         <v>0.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -4342,7 +7947,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C49" s="21" t="n">
+      <c r="C49" s="18" t="n">
         <v>5000</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -4369,7 +7974,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4437,7 +8042,7 @@
           <t>Costo por visita (unidad de adquisición)</t>
         </is>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="17">
         <f>'Supuestos'!$C$9</f>
         <v/>
       </c>
@@ -4453,7 +8058,7 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="20">
         <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
@@ -4469,7 +8074,7 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="C9" s="16">
+      <c r="C9" s="21">
         <f>'Modelo'!$C$8*'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -4501,7 +8106,7 @@
           <t>% de visitas que compran</t>
         </is>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -4542,7 +8147,7 @@
           <t>Facturado: producto principal</t>
         </is>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="19">
         <f>'Modelo'!$C$10*'Supuestos'!$C$16</f>
         <v/>
       </c>
@@ -4558,7 +8163,7 @@
           <t>Ventas: Bump 1</t>
         </is>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -4574,7 +8179,7 @@
           <t>Facturado: Bump 1</t>
         </is>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="19">
         <f>'Modelo'!$C$15*'Supuestos'!$C$17</f>
         <v/>
       </c>
@@ -4590,7 +8195,7 @@
           <t>Ventas: Bump 2</t>
         </is>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -4606,7 +8211,7 @@
           <t>Facturado: Bump 2</t>
         </is>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="19">
         <f>'Modelo'!$C$17*'Supuestos'!$C$19</f>
         <v/>
       </c>
@@ -4622,7 +8227,7 @@
           <t>Ventas: OTO 1</t>
         </is>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -4638,7 +8243,7 @@
           <t>Facturado: OTO 1</t>
         </is>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="19">
         <f>'Modelo'!$C$19*'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -4654,7 +8259,7 @@
           <t>Ventas: OTO 2</t>
         </is>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -4670,7 +8275,7 @@
           <t>Facturado: OTO 2</t>
         </is>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="19">
         <f>'Modelo'!$C$21*'Supuestos'!$C$23</f>
         <v/>
       </c>
@@ -4686,7 +8291,7 @@
           <t>Ventas: OTO 3</t>
         </is>
       </c>
-      <c r="C23" s="27">
+      <c r="C23" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$26</f>
         <v/>
       </c>
@@ -4702,7 +8307,7 @@
           <t>Facturado: OTO 3</t>
         </is>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="19">
         <f>'Modelo'!$C$23*'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -4718,7 +8323,7 @@
           <t>Ventas: OTO 4</t>
         </is>
       </c>
-      <c r="C25" s="27">
+      <c r="C25" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$28</f>
         <v/>
       </c>
@@ -4734,7 +8339,7 @@
           <t>Facturado: OTO 4</t>
         </is>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="19">
         <f>'Modelo'!$C$25*'Supuestos'!$C$27</f>
         <v/>
       </c>
@@ -4750,7 +8355,7 @@
           <t>Ventas: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C27" s="27">
+      <c r="C27" s="24">
         <f>'Modelo'!$C$10*'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -4766,7 +8371,7 @@
           <t>Facturado: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="19">
         <f>'Modelo'!$C$27*'Supuestos'!$C$29</f>
         <v/>
       </c>
@@ -4814,7 +8419,7 @@
           <t>AOV ÷ precio del principal</t>
         </is>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="26">
         <f>IF('Supuestos'!$C$16=0,0,'Modelo'!$C$30/'Supuestos'!$C$16)</f>
         <v/>
       </c>
@@ -4830,7 +8435,7 @@
           <t>Ventas del principal por visita (para la proyección)</t>
         </is>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="25">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -4846,7 +8451,7 @@
           <t>Facturado por visita</t>
         </is>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$29/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -4871,7 +8476,7 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="19">
         <f>'Modelo'!$C$29*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42)</f>
         <v/>
       </c>
@@ -4887,7 +8492,7 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="19">
         <f>'Modelo'!$C$29*'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -4903,7 +8508,7 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C37" s="26">
+      <c r="C37" s="19">
         <f>'Modelo'!$C$35*('Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
@@ -4919,7 +8524,7 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C38" s="26">
+      <c r="C38" s="19">
         <f>'Modelo'!$C$35*'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -4951,7 +8556,7 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C40" s="26">
+      <c r="C40" s="19">
         <f>'Modelo'!$C$8*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -4983,7 +8588,7 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C42" s="28">
+      <c r="C42" s="26">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$29/'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5015,7 +8620,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C44" s="18">
+      <c r="C44" s="23">
         <f>IF('Modelo'!$C$35=0,0,'Modelo'!$C$41/'Modelo'!$C$35)</f>
         <v/>
       </c>
@@ -5031,7 +8636,7 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="28">
         <f>IF('Modelo'!$C$43&gt;='Supuestos'!$C$45,"SÍ","NO")</f>
         <v/>
       </c>
@@ -5104,7 +8709,7 @@
           <t>Techo de costo por checkout</t>
         </is>
       </c>
-      <c r="C50" s="19">
+      <c r="C50" s="17">
         <f>IF('Supuestos'!$C$12=0,0,'Modelo'!$C$47/'Supuestos'!$C$12)</f>
         <v/>
       </c>
@@ -5136,7 +8741,7 @@
           <t>Objetivo de CPA</t>
         </is>
       </c>
-      <c r="C52" s="19">
+      <c r="C52" s="17">
         <f>'Modelo'!$C$51/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
@@ -5152,7 +8757,7 @@
           <t>Cash neto por comprador (AOV neto)</t>
         </is>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="17">
         <f>IF('Modelo'!$C$10=0,0,('Modelo'!$C$39-'Modelo'!$C$40)/'Modelo'!$C$10)</f>
         <v/>
       </c>
@@ -5225,7 +8830,7 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C58" s="26">
+      <c r="C58" s="19">
         <f>IF('Modelo'!$C$11=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$11*'Modelo'!$C$49)</f>
         <v/>
       </c>
@@ -5266,7 +8871,7 @@
           <t>Ganancia por checkout</t>
         </is>
       </c>
-      <c r="C61" s="19">
+      <c r="C61" s="17">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -5316,7 +8921,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5365,7 +8970,7 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="26">
+      <c r="C5" s="19">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -5410,23 +9015,23 @@
       <c r="B10" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5435,23 +9040,23 @@
       <c r="B11" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5460,23 +9065,23 @@
       <c r="B12" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5485,23 +9090,23 @@
       <c r="B13" s="31" t="n">
         <v>67</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5510,23 +9115,23 @@
       <c r="B14" s="31" t="n">
         <v>97</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5574,27 +9179,27 @@
       <c r="B20" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="26">
+      <c r="C20" s="19">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D20" s="26">
+      <c r="D20" s="19">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="19">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="26">
+      <c r="F20" s="19">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G20" s="26">
+      <c r="G20" s="19">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H20" s="26">
+      <c r="H20" s="19">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5603,27 +9208,27 @@
       <c r="B21" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="26">
+      <c r="C21" s="19">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="26">
+      <c r="D21" s="19">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="19">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="26">
+      <c r="F21" s="19">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="26">
+      <c r="G21" s="19">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H21" s="26">
+      <c r="H21" s="19">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5632,27 +9237,27 @@
       <c r="B22" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="19">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="19">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="19">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="19">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="26">
+      <c r="G22" s="19">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H22" s="26">
+      <c r="H22" s="19">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5661,27 +9266,27 @@
       <c r="B23" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="C23" s="26">
+      <c r="C23" s="19">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="26">
+      <c r="D23" s="19">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="19">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="26">
+      <c r="F23" s="19">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="26">
+      <c r="G23" s="19">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H23" s="26">
+      <c r="H23" s="19">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5690,27 +9295,27 @@
       <c r="B24" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="C24" s="26">
+      <c r="C24" s="19">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="26">
+      <c r="D24" s="19">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="19">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="26">
+      <c r="F24" s="19">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="26">
+      <c r="G24" s="19">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H24" s="26">
+      <c r="H24" s="19">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5719,27 +9324,27 @@
       <c r="B25" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="26">
+      <c r="C25" s="19">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="26">
+      <c r="D25" s="19">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="19">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="26">
+      <c r="F25" s="19">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="26">
+      <c r="G25" s="19">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H25" s="26">
+      <c r="H25" s="19">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5748,27 +9353,27 @@
       <c r="B26" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="C26" s="26">
+      <c r="C26" s="19">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D26" s="26">
+      <c r="D26" s="19">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="19">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F26" s="26">
+      <c r="F26" s="19">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G26" s="26">
+      <c r="G26" s="19">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H26" s="26">
+      <c r="H26" s="19">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -5813,23 +9418,23 @@
       <c r="B32" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="19">
         <f>$B32/C$31</f>
         <v/>
       </c>
-      <c r="D32" s="26">
+      <c r="D32" s="19">
         <f>$B32/D$31</f>
         <v/>
       </c>
-      <c r="E32" s="26">
+      <c r="E32" s="19">
         <f>$B32/E$31</f>
         <v/>
       </c>
-      <c r="F32" s="26">
+      <c r="F32" s="19">
         <f>$B32/F$31</f>
         <v/>
       </c>
-      <c r="G32" s="26">
+      <c r="G32" s="19">
         <f>$B32/G$31</f>
         <v/>
       </c>
@@ -5838,23 +9443,23 @@
       <c r="B33" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="26">
+      <c r="C33" s="19">
         <f>$B33/C$31</f>
         <v/>
       </c>
-      <c r="D33" s="26">
+      <c r="D33" s="19">
         <f>$B33/D$31</f>
         <v/>
       </c>
-      <c r="E33" s="26">
+      <c r="E33" s="19">
         <f>$B33/E$31</f>
         <v/>
       </c>
-      <c r="F33" s="26">
+      <c r="F33" s="19">
         <f>$B33/F$31</f>
         <v/>
       </c>
-      <c r="G33" s="26">
+      <c r="G33" s="19">
         <f>$B33/G$31</f>
         <v/>
       </c>
@@ -5863,23 +9468,23 @@
       <c r="B34" s="31" t="n">
         <v>30000</v>
       </c>
-      <c r="C34" s="26">
+      <c r="C34" s="19">
         <f>$B34/C$31</f>
         <v/>
       </c>
-      <c r="D34" s="26">
+      <c r="D34" s="19">
         <f>$B34/D$31</f>
         <v/>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="19">
         <f>$B34/E$31</f>
         <v/>
       </c>
-      <c r="F34" s="26">
+      <c r="F34" s="19">
         <f>$B34/F$31</f>
         <v/>
       </c>
-      <c r="G34" s="26">
+      <c r="G34" s="19">
         <f>$B34/G$31</f>
         <v/>
       </c>
@@ -5888,23 +9493,23 @@
       <c r="B35" s="31" t="n">
         <v>50000</v>
       </c>
-      <c r="C35" s="26">
+      <c r="C35" s="19">
         <f>$B35/C$31</f>
         <v/>
       </c>
-      <c r="D35" s="26">
+      <c r="D35" s="19">
         <f>$B35/D$31</f>
         <v/>
       </c>
-      <c r="E35" s="26">
+      <c r="E35" s="19">
         <f>$B35/E$31</f>
         <v/>
       </c>
-      <c r="F35" s="26">
+      <c r="F35" s="19">
         <f>$B35/F$31</f>
         <v/>
       </c>
-      <c r="G35" s="26">
+      <c r="G35" s="19">
         <f>$B35/G$31</f>
         <v/>
       </c>
@@ -5913,23 +9518,23 @@
       <c r="B36" s="31" t="n">
         <v>100000</v>
       </c>
-      <c r="C36" s="26">
+      <c r="C36" s="19">
         <f>$B36/C$31</f>
         <v/>
       </c>
-      <c r="D36" s="26">
+      <c r="D36" s="19">
         <f>$B36/D$31</f>
         <v/>
       </c>
-      <c r="E36" s="26">
+      <c r="E36" s="19">
         <f>$B36/E$31</f>
         <v/>
       </c>
-      <c r="F36" s="26">
+      <c r="F36" s="19">
         <f>$B36/F$31</f>
         <v/>
       </c>
-      <c r="G36" s="26">
+      <c r="G36" s="19">
         <f>$B36/G$31</f>
         <v/>
       </c>
@@ -5946,7 +9551,7 @@
         <f>$B32</f>
         <v/>
       </c>
-      <c r="C38" s="16">
+      <c r="C38" s="21">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B32/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -5956,7 +9561,7 @@
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="16">
+      <c r="C39" s="21">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B33/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -5966,7 +9571,7 @@
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="16">
+      <c r="C40" s="21">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B34/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -5976,7 +9581,7 @@
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="16">
+      <c r="C41" s="21">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B35/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -5986,7 +9591,7 @@
         <f>$B36</f>
         <v/>
       </c>
-      <c r="C42" s="16">
+      <c r="C42" s="21">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B36/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -6021,23 +9626,23 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C46" s="19">
+      <c r="C46" s="17">
         <f>IF(C45=0,0,'Modelo'!$C$33/C45)</f>
         <v/>
       </c>
-      <c r="D46" s="19">
+      <c r="D46" s="17">
         <f>IF(D45=0,0,'Modelo'!$C$33/D45)</f>
         <v/>
       </c>
-      <c r="E46" s="19">
+      <c r="E46" s="17">
         <f>IF(E45=0,0,'Modelo'!$C$33/E45)</f>
         <v/>
       </c>
-      <c r="F46" s="19">
+      <c r="F46" s="17">
         <f>IF(F45=0,0,'Modelo'!$C$33/F45)</f>
         <v/>
       </c>
-      <c r="G46" s="19">
+      <c r="G46" s="17">
         <f>IF(G45=0,0,'Modelo'!$C$33/G45)</f>
         <v/>
       </c>
@@ -6091,15 +9696,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C53" s="26">
+      <c r="C53" s="19">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D53" s="28">
+      <c r="D53" s="26">
         <f>IF(C53=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C53-'Supuestos'!$C$8))/C53)</f>
         <v/>
       </c>
-      <c r="E53" s="26">
+      <c r="E53" s="19">
         <f>C53*(D53-1)</f>
         <v/>
       </c>
@@ -6110,15 +9715,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C54" s="26">
+      <c r="C54" s="19">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D54" s="28">
+      <c r="D54" s="26">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="26">
+      <c r="E54" s="19">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -6129,15 +9734,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C55" s="26">
+      <c r="C55" s="19">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D55" s="28">
+      <c r="D55" s="26">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="26">
+      <c r="E55" s="19">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -6148,15 +9753,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C56" s="26">
+      <c r="C56" s="19">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D56" s="28">
+      <c r="D56" s="26">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="26">
+      <c r="E56" s="19">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -6167,15 +9772,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C57" s="26">
+      <c r="C57" s="19">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D57" s="28">
+      <c r="D57" s="26">
         <f>IF(C57=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C57-'Supuestos'!$C$8))/C57)</f>
         <v/>
       </c>
-      <c r="E57" s="26">
+      <c r="E57" s="19">
         <f>C57*(D57-1)</f>
         <v/>
       </c>
@@ -6217,7 +9822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6310,19 +9915,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="19">
         <f>((((((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="19">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="18">
+      <c r="F7" s="23">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="21">
         <f>RANK(E7,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6338,19 +9943,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="26">
+      <c r="D8" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="19">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="18">
+      <c r="F8" s="23">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="21">
         <f>RANK(E8,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6366,19 +9971,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="19">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="18">
+      <c r="F9" s="23">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="21">
         <f>RANK(E9,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6394,19 +9999,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$16*1.1))+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="19">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="18">
+      <c r="F10" s="23">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="21">
         <f>RANK(E10,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6422,19 +10027,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$18*1.1))*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="19">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="18">
+      <c r="F11" s="23">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="21">
         <f>RANK(E11,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6450,19 +10055,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$22*1.1))*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="19">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="18">
+      <c r="F12" s="23">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="21">
         <f>RANK(E12,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6478,19 +10083,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$30*1.1))*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="19">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="18">
+      <c r="F13" s="23">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="21">
         <f>RANK(E13,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6506,19 +10111,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="19">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-('Supuestos'!$C$35*0.9)))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="19">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="18">
+      <c r="F14" s="23">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="21">
         <f>RANK(E14,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -6536,7 +10141,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6661,51 +10266,51 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="19">
         <f>'Supuestos'!$C$8*1</f>
         <v/>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="19">
         <f>C6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="19">
         <f>D6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="19">
         <f>E6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="19">
         <f>F6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="19">
         <f>G6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="19">
         <f>H6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="J6" s="26">
+      <c r="J6" s="19">
         <f>I6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="K6" s="26">
+      <c r="K6" s="19">
         <f>J6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="L6" s="26">
+      <c r="L6" s="19">
         <f>K6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="M6" s="26">
+      <c r="M6" s="19">
         <f>L6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="N6" s="26">
+      <c r="N6" s="19">
         <f>M6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
@@ -6720,55 +10325,55 @@
           <t>Visitas compradas</t>
         </is>
       </c>
-      <c r="C7" s="16">
+      <c r="C7" s="21">
         <f>IF('Modelo'!$C$7=0,0,C6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D7" s="16">
+      <c r="D7" s="21">
         <f>IF('Modelo'!$C$7=0,0,D6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="16">
+      <c r="E7" s="21">
         <f>IF('Modelo'!$C$7=0,0,E6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="21">
         <f>IF('Modelo'!$C$7=0,0,F6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="21">
         <f>IF('Modelo'!$C$7=0,0,G6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="H7" s="16">
+      <c r="H7" s="21">
         <f>IF('Modelo'!$C$7=0,0,H6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I7" s="16">
+      <c r="I7" s="21">
         <f>IF('Modelo'!$C$7=0,0,I6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="J7" s="16">
+      <c r="J7" s="21">
         <f>IF('Modelo'!$C$7=0,0,J6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="K7" s="16">
+      <c r="K7" s="21">
         <f>IF('Modelo'!$C$7=0,0,K6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="L7" s="16">
+      <c r="L7" s="21">
         <f>IF('Modelo'!$C$7=0,0,L6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="M7" s="16">
+      <c r="M7" s="21">
         <f>IF('Modelo'!$C$7=0,0,M6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="N7" s="16">
+      <c r="N7" s="21">
         <f>IF('Modelo'!$C$7=0,0,N6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="O7" s="25">
+      <c r="O7" s="20">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
@@ -6779,51 +10384,51 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="24">
         <f>C7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="24">
         <f>D7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="24">
         <f>E7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="24">
         <f>F7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="24">
         <f>G7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="24">
         <f>H7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="24">
         <f>I7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="24">
         <f>J7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="K8" s="27">
+      <c r="K8" s="24">
         <f>K7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="L8" s="27">
+      <c r="L8" s="24">
         <f>L7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="M8" s="27">
+      <c r="M8" s="24">
         <f>M7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="N8" s="27">
+      <c r="N8" s="24">
         <f>N7*'Modelo'!$C$32</f>
         <v/>
       </c>
@@ -6838,51 +10443,51 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="19">
         <f>C7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="D9" s="26">
+      <c r="D9" s="19">
         <f>D7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="19">
         <f>E7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="19">
         <f>F7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="19">
         <f>G7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="H9" s="26">
+      <c r="H9" s="19">
         <f>H7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="19">
         <f>I7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="J9" s="26">
+      <c r="J9" s="19">
         <f>J7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="K9" s="26">
+      <c r="K9" s="19">
         <f>K7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="L9" s="26">
+      <c r="L9" s="19">
         <f>L7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="M9" s="26">
+      <c r="M9" s="19">
         <f>M7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="N9" s="26">
+      <c r="N9" s="19">
         <f>N7*'Modelo'!$C$33</f>
         <v/>
       </c>
@@ -6897,51 +10502,51 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="26">
+      <c r="C10" s="19">
         <f>C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="19">
         <f>D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="19">
         <f>E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41+C9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="F10" s="26">
+      <c r="F10" s="19">
         <f>F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41+D9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="G10" s="26">
+      <c r="G10" s="19">
         <f>G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41+E9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="H10" s="26">
+      <c r="H10" s="19">
         <f>H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41+F9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="19">
         <f>I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41+G9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="J10" s="26">
+      <c r="J10" s="19">
         <f>J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41+H9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="K10" s="26">
+      <c r="K10" s="19">
         <f>K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41+I9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="L10" s="26">
+      <c r="L10" s="19">
         <f>L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41+J9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="M10" s="26">
+      <c r="M10" s="19">
         <f>M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41+K9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="N10" s="26">
+      <c r="N10" s="19">
         <f>N9*'Supuestos'!$C$40+M9*'Supuestos'!$C$41+L9*'Supuestos'!$C$42</f>
         <v/>
       </c>
@@ -6956,51 +10561,51 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="19">
         <f>C10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="19">
         <f>D10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="19">
         <f>E10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="19">
         <f>F10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="G11" s="26">
+      <c r="G11" s="19">
         <f>G10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="H11" s="26">
+      <c r="H11" s="19">
         <f>H10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="19">
         <f>I10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="19">
         <f>J10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="K11" s="26">
+      <c r="K11" s="19">
         <f>K10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="L11" s="26">
+      <c r="L11" s="19">
         <f>L10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="M11" s="26">
+      <c r="M11" s="19">
         <f>M10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="N11" s="26">
+      <c r="N11" s="19">
         <f>N10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
@@ -7015,51 +10620,51 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="19">
         <f>C7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="19">
         <f>D7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="19">
         <f>E7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="19">
         <f>F7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="G12" s="26">
+      <c r="G12" s="19">
         <f>G7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="H12" s="26">
+      <c r="H12" s="19">
         <f>H7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="19">
         <f>I7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="J12" s="26">
+      <c r="J12" s="19">
         <f>J7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="K12" s="26">
+      <c r="K12" s="19">
         <f>K7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="L12" s="26">
+      <c r="L12" s="19">
         <f>L7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="M12" s="26">
+      <c r="M12" s="19">
         <f>M7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="N12" s="26">
+      <c r="N12" s="19">
         <f>N7*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -7074,51 +10679,51 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="H13" s="26">
+      <c r="H13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="K13" s="26">
+      <c r="K13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="L13" s="26">
+      <c r="L13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="M13" s="26">
+      <c r="M13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="N13" s="26">
+      <c r="N13" s="19">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
@@ -7247,51 +10852,51 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="26">
+      <c r="C16" s="19">
         <f>'Supuestos'!$C$49+C15</f>
         <v/>
       </c>
-      <c r="D16" s="26">
+      <c r="D16" s="19">
         <f>'Supuestos'!$C$49+D15</f>
         <v/>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="19">
         <f>'Supuestos'!$C$49+E15</f>
         <v/>
       </c>
-      <c r="F16" s="26">
+      <c r="F16" s="19">
         <f>'Supuestos'!$C$49+F15</f>
         <v/>
       </c>
-      <c r="G16" s="26">
+      <c r="G16" s="19">
         <f>'Supuestos'!$C$49+G15</f>
         <v/>
       </c>
-      <c r="H16" s="26">
+      <c r="H16" s="19">
         <f>'Supuestos'!$C$49+H15</f>
         <v/>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="19">
         <f>'Supuestos'!$C$49+I15</f>
         <v/>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="19">
         <f>'Supuestos'!$C$49+J15</f>
         <v/>
       </c>
-      <c r="K16" s="26">
+      <c r="K16" s="19">
         <f>'Supuestos'!$C$49+K15</f>
         <v/>
       </c>
-      <c r="L16" s="26">
+      <c r="L16" s="19">
         <f>'Supuestos'!$C$49+L15</f>
         <v/>
       </c>
-      <c r="M16" s="26">
+      <c r="M16" s="19">
         <f>'Supuestos'!$C$49+M15</f>
         <v/>
       </c>
-      <c r="N16" s="26">
+      <c r="N16" s="19">
         <f>'Supuestos'!$C$49+N15</f>
         <v/>
       </c>
@@ -7352,1389 +10957,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Seguimiento: una columna por mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por visita con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 4</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 5</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 6</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 7</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 8</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 9</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 10</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 11</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 12</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>Promedio</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Máximo</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>Mínimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Datos que cargás</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Inversión en publicidad</t>
-        </is>
-      </c>
-      <c r="C7" s="21" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D7" s="21" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>10500</v>
-      </c>
-      <c r="F7" s="21" t="n"/>
-      <c r="G7" s="21" t="n"/>
-      <c r="H7" s="21" t="n"/>
-      <c r="I7" s="21" t="n"/>
-      <c r="J7" s="21" t="n"/>
-      <c r="K7" s="21" t="n"/>
-      <c r="L7" s="21" t="n"/>
-      <c r="M7" s="21" t="n"/>
-      <c r="N7" s="21" t="n"/>
-      <c r="O7" s="26">
-        <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
-        <v/>
-      </c>
-      <c r="P7" s="26">
-        <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="26">
-        <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Visitas a la página</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D8" s="20" t="n">
-        <v>30200</v>
-      </c>
-      <c r="E8" s="20" t="n">
-        <v>29000</v>
-      </c>
-      <c r="F8" s="20" t="n"/>
-      <c r="G8" s="20" t="n"/>
-      <c r="H8" s="20" t="n"/>
-      <c r="I8" s="20" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="20" t="n"/>
-      <c r="L8" s="20" t="n"/>
-      <c r="M8" s="20" t="n"/>
-      <c r="N8" s="20" t="n"/>
-      <c r="O8" s="16">
-        <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
-        <v/>
-      </c>
-      <c r="P8" s="16">
-        <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="16">
-        <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Checkouts iniciados</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D9" s="20" t="n">
-        <v>1030</v>
-      </c>
-      <c r="E9" s="20" t="n">
-        <v>980</v>
-      </c>
-      <c r="F9" s="20" t="n"/>
-      <c r="G9" s="20" t="n"/>
-      <c r="H9" s="20" t="n"/>
-      <c r="I9" s="20" t="n"/>
-      <c r="J9" s="20" t="n"/>
-      <c r="K9" s="20" t="n"/>
-      <c r="L9" s="20" t="n"/>
-      <c r="M9" s="20" t="n"/>
-      <c r="N9" s="20" t="n"/>
-      <c r="O9" s="16">
-        <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
-        <v/>
-      </c>
-      <c r="P9" s="16">
-        <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="16">
-        <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ventas del producto principal</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="n">
-        <v>273</v>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>262</v>
-      </c>
-      <c r="E10" s="20" t="n">
-        <v>240</v>
-      </c>
-      <c r="F10" s="20" t="n"/>
-      <c r="G10" s="20" t="n"/>
-      <c r="H10" s="20" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="20" t="n"/>
-      <c r="K10" s="20" t="n"/>
-      <c r="L10" s="20" t="n"/>
-      <c r="M10" s="20" t="n"/>
-      <c r="N10" s="20" t="n"/>
-      <c r="O10" s="16">
-        <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
-        <v/>
-      </c>
-      <c r="P10" s="16">
-        <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="16">
-        <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ventas de bumps (1 + 2)</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="n">
-        <v>117</v>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>110</v>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>95</v>
-      </c>
-      <c r="F11" s="20" t="n"/>
-      <c r="G11" s="20" t="n"/>
-      <c r="H11" s="20" t="n"/>
-      <c r="I11" s="20" t="n"/>
-      <c r="J11" s="20" t="n"/>
-      <c r="K11" s="20" t="n"/>
-      <c r="L11" s="20" t="n"/>
-      <c r="M11" s="20" t="n"/>
-      <c r="N11" s="20" t="n"/>
-      <c r="O11" s="16">
-        <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
-        <v/>
-      </c>
-      <c r="P11" s="16">
-        <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="16">
-        <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ventas de OTOs (1 a 4)</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="n">
-        <v>63</v>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>58</v>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>52</v>
-      </c>
-      <c r="F12" s="20" t="n"/>
-      <c r="G12" s="20" t="n"/>
-      <c r="H12" s="20" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="20" t="n"/>
-      <c r="K12" s="20" t="n"/>
-      <c r="L12" s="20" t="n"/>
-      <c r="M12" s="20" t="n"/>
-      <c r="N12" s="20" t="n"/>
-      <c r="O12" s="16">
-        <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
-        <v/>
-      </c>
-      <c r="P12" s="16">
-        <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="16">
-        <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ventas de la ascensión (programa)</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="20" t="n"/>
-      <c r="G13" s="20" t="n"/>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
-      <c r="J13" s="20" t="n"/>
-      <c r="K13" s="20" t="n"/>
-      <c r="L13" s="20" t="n"/>
-      <c r="M13" s="20" t="n"/>
-      <c r="N13" s="20" t="n"/>
-      <c r="O13" s="16">
-        <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
-        <v/>
-      </c>
-      <c r="P13" s="16">
-        <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="16">
-        <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Facturado del mes (a precio de lista)</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="n">
-        <v>15900</v>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>15400</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>13700</v>
-      </c>
-      <c r="F14" s="21" t="n"/>
-      <c r="G14" s="21" t="n"/>
-      <c r="H14" s="21" t="n"/>
-      <c r="I14" s="21" t="n"/>
-      <c r="J14" s="21" t="n"/>
-      <c r="K14" s="21" t="n"/>
-      <c r="L14" s="21" t="n"/>
-      <c r="M14" s="21" t="n"/>
-      <c r="N14" s="21" t="n"/>
-      <c r="O14" s="26">
-        <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
-        <v/>
-      </c>
-      <c r="P14" s="26">
-        <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="26">
-        <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cash cobrado en el mes</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="n">
-        <v>15900</v>
-      </c>
-      <c r="D15" s="21" t="n">
-        <v>15400</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>13700</v>
-      </c>
-      <c r="F15" s="21" t="n"/>
-      <c r="G15" s="21" t="n"/>
-      <c r="H15" s="21" t="n"/>
-      <c r="I15" s="21" t="n"/>
-      <c r="J15" s="21" t="n"/>
-      <c r="K15" s="21" t="n"/>
-      <c r="L15" s="21" t="n"/>
-      <c r="M15" s="21" t="n"/>
-      <c r="N15" s="21" t="n"/>
-      <c r="O15" s="26">
-        <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
-        <v/>
-      </c>
-      <c r="P15" s="26">
-        <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="26">
-        <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Lo que calcula el modelo</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Costo por visita real</t>
-        </is>
-      </c>
-      <c r="C17" s="12">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C7/C8))</f>
-        <v/>
-      </c>
-      <c r="D17" s="12">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D7/D8))</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E7/E8))</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F7/F8))</f>
-        <v/>
-      </c>
-      <c r="G17" s="12">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G7/G8))</f>
-        <v/>
-      </c>
-      <c r="H17" s="12">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H7/H8))</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I7/I8))</f>
-        <v/>
-      </c>
-      <c r="J17" s="12">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J7/J8))</f>
-        <v/>
-      </c>
-      <c r="K17" s="12">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K7/K8))</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L7/L8))</f>
-        <v/>
-      </c>
-      <c r="M17" s="12">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M7/M8))</f>
-        <v/>
-      </c>
-      <c r="N17" s="12">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N7/N8))</f>
-        <v/>
-      </c>
-      <c r="O17" s="19">
-        <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
-        <v/>
-      </c>
-      <c r="P17" s="19">
-        <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="19">
-        <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>% visitas → checkout</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
-        <v/>
-      </c>
-      <c r="D18" s="18">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
-        <v/>
-      </c>
-      <c r="E18" s="18">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
-        <v/>
-      </c>
-      <c r="F18" s="18">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
-        <v/>
-      </c>
-      <c r="G18" s="18">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
-        <v/>
-      </c>
-      <c r="H18" s="18">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
-        <v/>
-      </c>
-      <c r="I18" s="18">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
-        <v/>
-      </c>
-      <c r="J18" s="18">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
-        <v/>
-      </c>
-      <c r="K18" s="18">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
-        <v/>
-      </c>
-      <c r="L18" s="18">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
-        <v/>
-      </c>
-      <c r="M18" s="18">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
-        <v/>
-      </c>
-      <c r="N18" s="18">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
-        <v/>
-      </c>
-      <c r="O18" s="18">
-        <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
-        <v/>
-      </c>
-      <c r="P18" s="18">
-        <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="18">
-        <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>% checkout → compra</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
-        <v/>
-      </c>
-      <c r="D19" s="18">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
-        <v/>
-      </c>
-      <c r="E19" s="18">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
-        <v/>
-      </c>
-      <c r="F19" s="18">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
-        <v/>
-      </c>
-      <c r="G19" s="18">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
-        <v/>
-      </c>
-      <c r="H19" s="18">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
-        <v/>
-      </c>
-      <c r="I19" s="18">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
-        <v/>
-      </c>
-      <c r="J19" s="18">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
-        <v/>
-      </c>
-      <c r="K19" s="18">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
-        <v/>
-      </c>
-      <c r="L19" s="18">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
-        <v/>
-      </c>
-      <c r="M19" s="18">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
-        <v/>
-      </c>
-      <c r="N19" s="18">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
-        <v/>
-      </c>
-      <c r="O19" s="18">
-        <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
-        <v/>
-      </c>
-      <c r="P19" s="18">
-        <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="18">
-        <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CPA real</t>
-        </is>
-      </c>
-      <c r="C20" s="19">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C7/C10))</f>
-        <v/>
-      </c>
-      <c r="D20" s="19">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D7/D10))</f>
-        <v/>
-      </c>
-      <c r="E20" s="19">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E7/E10))</f>
-        <v/>
-      </c>
-      <c r="F20" s="19">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F7/F10))</f>
-        <v/>
-      </c>
-      <c r="G20" s="19">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G7/G10))</f>
-        <v/>
-      </c>
-      <c r="H20" s="19">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H7/H10))</f>
-        <v/>
-      </c>
-      <c r="I20" s="19">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I7/I10))</f>
-        <v/>
-      </c>
-      <c r="J20" s="19">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J7/J10))</f>
-        <v/>
-      </c>
-      <c r="K20" s="19">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K7/K10))</f>
-        <v/>
-      </c>
-      <c r="L20" s="19">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L7/L10))</f>
-        <v/>
-      </c>
-      <c r="M20" s="19">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M7/M10))</f>
-        <v/>
-      </c>
-      <c r="N20" s="19">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N7/N10))</f>
-        <v/>
-      </c>
-      <c r="O20" s="19">
-        <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
-        <v/>
-      </c>
-      <c r="P20" s="19">
-        <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="19">
-        <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cash por comprador</t>
-        </is>
-      </c>
-      <c r="C21" s="19">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C15/C10))</f>
-        <v/>
-      </c>
-      <c r="D21" s="19">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D15/D10))</f>
-        <v/>
-      </c>
-      <c r="E21" s="19">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E15/E10))</f>
-        <v/>
-      </c>
-      <c r="F21" s="19">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F15/F10))</f>
-        <v/>
-      </c>
-      <c r="G21" s="19">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G15/G10))</f>
-        <v/>
-      </c>
-      <c r="H21" s="19">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H15/H10))</f>
-        <v/>
-      </c>
-      <c r="I21" s="19">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I15/I10))</f>
-        <v/>
-      </c>
-      <c r="J21" s="19">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J15/J10))</f>
-        <v/>
-      </c>
-      <c r="K21" s="19">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K15/K10))</f>
-        <v/>
-      </c>
-      <c r="L21" s="19">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L15/L10))</f>
-        <v/>
-      </c>
-      <c r="M21" s="19">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M15/M10))</f>
-        <v/>
-      </c>
-      <c r="N21" s="19">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N15/N10))</f>
-        <v/>
-      </c>
-      <c r="O21" s="19">
-        <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
-        <v/>
-      </c>
-      <c r="P21" s="19">
-        <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="19">
-        <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
-        </is>
-      </c>
-      <c r="C22" s="12">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36)/C8))</f>
-        <v/>
-      </c>
-      <c r="D22" s="12">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36)/D8))</f>
-        <v/>
-      </c>
-      <c r="E22" s="12">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36)/E8))</f>
-        <v/>
-      </c>
-      <c r="F22" s="12">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36)/F8))</f>
-        <v/>
-      </c>
-      <c r="G22" s="12">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36)/G8))</f>
-        <v/>
-      </c>
-      <c r="H22" s="12">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36)/H8))</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36)/I8))</f>
-        <v/>
-      </c>
-      <c r="J22" s="12">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36)/J8))</f>
-        <v/>
-      </c>
-      <c r="K22" s="12">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36)/K8))</f>
-        <v/>
-      </c>
-      <c r="L22" s="12">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36)/L8))</f>
-        <v/>
-      </c>
-      <c r="M22" s="12">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36)/M8))</f>
-        <v/>
-      </c>
-      <c r="N22" s="12">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
-        <v/>
-      </c>
-      <c r="O22" s="19">
-        <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
-        <v/>
-      </c>
-      <c r="P22" s="19">
-        <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
-        <v/>
-      </c>
-      <c r="Q22" s="19">
-        <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia del período al completar la cobranza</t>
-        </is>
-      </c>
-      <c r="C23" s="9">
-        <f>IF(COUNT(C7:C15)&lt;9,"",C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
-        <v/>
-      </c>
-      <c r="D23" s="9">
-        <f>IF(COUNT(D7:D15)&lt;9,"",D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>IF(COUNT(E7:E15)&lt;9,"",E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
-        <v/>
-      </c>
-      <c r="F23" s="9">
-        <f>IF(COUNT(F7:F15)&lt;9,"",F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>IF(COUNT(G7:G15)&lt;9,"",G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>IF(COUNT(H7:H15)&lt;9,"",H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>IF(COUNT(I7:I15)&lt;9,"",I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
-        <v/>
-      </c>
-      <c r="J23" s="9">
-        <f>IF(COUNT(J7:J15)&lt;9,"",J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
-        <v/>
-      </c>
-      <c r="K23" s="9">
-        <f>IF(COUNT(K7:K15)&lt;9,"",K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
-        <v/>
-      </c>
-      <c r="L23" s="9">
-        <f>IF(COUNT(L7:L15)&lt;9,"",L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>IF(COUNT(M7:M15)&lt;9,"",M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
-        <v/>
-      </c>
-      <c r="N23" s="9">
-        <f>IF(COUNT(N7:N15)&lt;9,"",N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
-        <v/>
-      </c>
-      <c r="O23" s="26">
-        <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
-        <v/>
-      </c>
-      <c r="P23" s="26">
-        <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
-        <v/>
-      </c>
-      <c r="Q23" s="26">
-        <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
-        </is>
-      </c>
-      <c r="C24" s="26">
-        <f>IF(COUNT(C7:C15)&lt;9,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
-        <v/>
-      </c>
-      <c r="D24" s="26">
-        <f>IF(COUNT(D7:D15)&lt;9,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
-        <v/>
-      </c>
-      <c r="E24" s="26">
-        <f>IF(COUNT(E7:E15)&lt;9,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
-        <v/>
-      </c>
-      <c r="F24" s="26">
-        <f>IF(COUNT(F7:F15)&lt;9,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
-        <v/>
-      </c>
-      <c r="G24" s="26">
-        <f>IF(COUNT(G7:G15)&lt;9,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
-        <v/>
-      </c>
-      <c r="H24" s="26">
-        <f>IF(COUNT(H7:H15)&lt;9,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
-        <v/>
-      </c>
-      <c r="I24" s="26">
-        <f>IF(COUNT(I7:I15)&lt;9,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
-        <v/>
-      </c>
-      <c r="J24" s="26">
-        <f>IF(COUNT(J7:J15)&lt;9,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
-        <v/>
-      </c>
-      <c r="K24" s="26">
-        <f>IF(COUNT(K7:K15)&lt;9,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
-        <v/>
-      </c>
-      <c r="L24" s="26">
-        <f>IF(COUNT(L7:L15)&lt;9,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
-        <v/>
-      </c>
-      <c r="M24" s="26">
-        <f>IF(COUNT(M7:M15)&lt;9,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
-        <v/>
-      </c>
-      <c r="N24" s="26">
-        <f>IF(COUNT(N7:N15)&lt;9,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
-        <v/>
-      </c>
-      <c r="O24" s="26">
-        <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
-        <v/>
-      </c>
-      <c r="P24" s="26">
-        <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="26">
-        <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
-        </is>
-      </c>
-      <c r="C25" s="12">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)/C8))</f>
-        <v/>
-      </c>
-      <c r="D25" s="12">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)/D8))</f>
-        <v/>
-      </c>
-      <c r="E25" s="12">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)/E8))</f>
-        <v/>
-      </c>
-      <c r="F25" s="12">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)/F8))</f>
-        <v/>
-      </c>
-      <c r="G25" s="12">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)/G8))</f>
-        <v/>
-      </c>
-      <c r="H25" s="12">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)/H8))</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)/I8))</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)/J8))</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)/K8))</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)/L8))</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)/M8))</f>
-        <v/>
-      </c>
-      <c r="N25" s="12">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
-        <v/>
-      </c>
-      <c r="O25" s="19">
-        <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
-        <v/>
-      </c>
-      <c r="P25" s="19">
-        <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="19">
-        <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>ROAS sobre cash neto (cobranza completa)</t>
-        </is>
-      </c>
-      <c r="C26" s="10">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
-        <v/>
-      </c>
-      <c r="D26" s="10">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
-        <v/>
-      </c>
-      <c r="E26" s="10">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
-        <v/>
-      </c>
-      <c r="F26" s="10">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
-        <v/>
-      </c>
-      <c r="G26" s="10">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
-        <v/>
-      </c>
-      <c r="H26" s="10">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
-        <v/>
-      </c>
-      <c r="I26" s="10">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
-        <v/>
-      </c>
-      <c r="J26" s="10">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
-        <v/>
-      </c>
-      <c r="K26" s="10">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
-        <v/>
-      </c>
-      <c r="L26" s="10">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
-        <v/>
-      </c>
-      <c r="M26" s="10">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
-        <v/>
-      </c>
-      <c r="N26" s="10">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
-        <v/>
-      </c>
-      <c r="O26" s="28">
-        <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
-        <v/>
-      </c>
-      <c r="P26" s="28">
-        <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="28">
-        <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ROAS de caja (cobrado hasta ahora)</t>
-        </is>
-      </c>
-      <c r="C27" s="28">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
-        <v/>
-      </c>
-      <c r="D27" s="28">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
-        <v/>
-      </c>
-      <c r="E27" s="28">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
-        <v/>
-      </c>
-      <c r="F27" s="28">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
-        <v/>
-      </c>
-      <c r="G27" s="28">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
-        <v/>
-      </c>
-      <c r="H27" s="28">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
-        <v/>
-      </c>
-      <c r="I27" s="28">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
-        <v/>
-      </c>
-      <c r="J27" s="28">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
-        <v/>
-      </c>
-      <c r="K27" s="28">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
-        <v/>
-      </c>
-      <c r="L27" s="28">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
-        <v/>
-      </c>
-      <c r="M27" s="28">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
-        <v/>
-      </c>
-      <c r="N27" s="28">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
-        <v/>
-      </c>
-      <c r="O27" s="28">
-        <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
-        <v/>
-      </c>
-      <c r="P27" s="28">
-        <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
-        <v/>
-      </c>
-      <c r="Q27" s="28">
-        <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
-        </is>
-      </c>
-      <c r="C28" s="19">
-        <f>IF(COUNT(C7:C15)&lt;9,"",'Modelo'!$C$48)</f>
-        <v/>
-      </c>
-      <c r="D28" s="19">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(COUNT(C22:C22)&gt;0,MEDIAN(C22:C22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="E28" s="19">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(COUNT(C22:D22)&gt;0,MEDIAN(C22:D22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="F28" s="19">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(COUNT(C22:E22)&gt;0,MEDIAN(C22:E22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="G28" s="19">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(COUNT(C22:F22)&gt;0,MEDIAN(C22:F22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="H28" s="19">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(COUNT(D22:G22)&gt;0,MEDIAN(D22:G22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="I28" s="19">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(COUNT(E22:H22)&gt;0,MEDIAN(E22:H22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="J28" s="19">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(COUNT(F22:I22)&gt;0,MEDIAN(F22:I22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="K28" s="19">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(COUNT(G22:J22)&gt;0,MEDIAN(G22:J22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="L28" s="19">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(COUNT(H22:K22)&gt;0,MEDIAN(H22:K22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="M28" s="19">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(COUNT(I22:L22)&gt;0,MEDIAN(I22:L22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="N28" s="19">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(COUNT(J22:M22)&gt;0,MEDIAN(J22:M22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="O28" s="19">
-        <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
-        <v/>
-      </c>
-      <c r="P28" s="19">
-        <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
-        <v/>
-      </c>
-      <c r="Q28" s="19">
-        <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
-        </is>
-      </c>
-      <c r="C29" s="13">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C17&gt;C28,"ROJO",IF(AND(C17&lt;=C28/(1+'Supuestos'!$C$46),C26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="D29" s="13">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D17&gt;D28,"ROJO",IF(AND(D17&lt;=D28/(1+'Supuestos'!$C$46),D26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="E29" s="13">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E17&gt;E28,"ROJO",IF(AND(E17&lt;=E28/(1+'Supuestos'!$C$46),E26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="F29" s="13">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F17&gt;F28,"ROJO",IF(AND(F17&lt;=F28/(1+'Supuestos'!$C$46),F26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="G29" s="13">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G17&gt;G28,"ROJO",IF(AND(G17&lt;=G28/(1+'Supuestos'!$C$46),G26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="H29" s="13">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H17&gt;H28,"ROJO",IF(AND(H17&lt;=H28/(1+'Supuestos'!$C$46),H26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="I29" s="13">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I17&gt;I28,"ROJO",IF(AND(I17&lt;=I28/(1+'Supuestos'!$C$46),I26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="J29" s="13">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J17&gt;J28,"ROJO",IF(AND(J17&lt;=J28/(1+'Supuestos'!$C$46),J26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="K29" s="13">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K17&gt;K28,"ROJO",IF(AND(K17&lt;=K28/(1+'Supuestos'!$C$46),K26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="L29" s="13">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L17&gt;L28,"ROJO",IF(AND(L17&lt;=L28/(1+'Supuestos'!$C$46),L26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="M29" s="13">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M17&gt;M28,"ROJO",IF(AND(M17&lt;=M28/(1+'Supuestos'!$C$46),M26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="N29" s="13">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N17&gt;N28,"ROJO",IF(AND(N17&lt;=N28/(1+'Supuestos'!$C$46),N26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C5:N30">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>LEFT(C5,5)="VERDE"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>LEFT(C5,8)="AMARILLO"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>LEFT(C5,4)="ROJO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
-    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
-    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
-    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>
--- a/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
+++ b/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
@@ -179,6 +179,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -197,7 +198,6 @@
     <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1050,33 +1050,33 @@
           <t>Inversión en publicidad</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n">
+      <c r="C7" s="19" t="n">
         <v>9000</v>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="19" t="n">
         <v>9500</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="19" t="n">
         <v>10500</v>
       </c>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="18" t="n"/>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="19">
+      <c r="F7" s="19" t="n"/>
+      <c r="G7" s="19" t="n"/>
+      <c r="H7" s="19" t="n"/>
+      <c r="I7" s="19" t="n"/>
+      <c r="J7" s="19" t="n"/>
+      <c r="K7" s="19" t="n"/>
+      <c r="L7" s="19" t="n"/>
+      <c r="M7" s="19" t="n"/>
+      <c r="N7" s="19" t="n"/>
+      <c r="O7" s="20">
         <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
         <v/>
       </c>
-      <c r="P7" s="19">
+      <c r="P7" s="20">
         <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
         <v/>
       </c>
-      <c r="Q7" s="19">
+      <c r="Q7" s="20">
         <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
         <v/>
       </c>
@@ -1087,33 +1087,33 @@
           <t>Visitas a la página</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="30" t="n">
         <v>30000</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="30" t="n">
         <v>30200</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="30" t="n">
         <v>29000</v>
       </c>
-      <c r="F8" s="29" t="n"/>
-      <c r="G8" s="29" t="n"/>
-      <c r="H8" s="29" t="n"/>
-      <c r="I8" s="29" t="n"/>
-      <c r="J8" s="29" t="n"/>
-      <c r="K8" s="29" t="n"/>
-      <c r="L8" s="29" t="n"/>
-      <c r="M8" s="29" t="n"/>
-      <c r="N8" s="29" t="n"/>
-      <c r="O8" s="21">
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="30" t="n"/>
+      <c r="H8" s="30" t="n"/>
+      <c r="I8" s="30" t="n"/>
+      <c r="J8" s="30" t="n"/>
+      <c r="K8" s="30" t="n"/>
+      <c r="L8" s="30" t="n"/>
+      <c r="M8" s="30" t="n"/>
+      <c r="N8" s="30" t="n"/>
+      <c r="O8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
         <v/>
       </c>
-      <c r="P8" s="21">
+      <c r="P8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
         <v/>
       </c>
-      <c r="Q8" s="21">
+      <c r="Q8" s="22">
         <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
         <v/>
       </c>
@@ -1124,33 +1124,33 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="30" t="n">
         <v>1050</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="30" t="n">
         <v>1030</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="30" t="n">
         <v>980</v>
       </c>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="29" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="29" t="n"/>
-      <c r="K9" s="29" t="n"/>
-      <c r="L9" s="29" t="n"/>
-      <c r="M9" s="29" t="n"/>
-      <c r="N9" s="29" t="n"/>
-      <c r="O9" s="21">
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="30" t="n"/>
+      <c r="I9" s="30" t="n"/>
+      <c r="J9" s="30" t="n"/>
+      <c r="K9" s="30" t="n"/>
+      <c r="L9" s="30" t="n"/>
+      <c r="M9" s="30" t="n"/>
+      <c r="N9" s="30" t="n"/>
+      <c r="O9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
         <v/>
       </c>
-      <c r="P9" s="21">
+      <c r="P9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
         <v/>
       </c>
-      <c r="Q9" s="21">
+      <c r="Q9" s="22">
         <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
         <v/>
       </c>
@@ -1161,33 +1161,33 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="30" t="n">
         <v>273</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="30" t="n">
         <v>262</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="30" t="n">
         <v>240</v>
       </c>
-      <c r="F10" s="29" t="n"/>
-      <c r="G10" s="29" t="n"/>
-      <c r="H10" s="29" t="n"/>
-      <c r="I10" s="29" t="n"/>
-      <c r="J10" s="29" t="n"/>
-      <c r="K10" s="29" t="n"/>
-      <c r="L10" s="29" t="n"/>
-      <c r="M10" s="29" t="n"/>
-      <c r="N10" s="29" t="n"/>
-      <c r="O10" s="21">
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="30" t="n"/>
+      <c r="H10" s="30" t="n"/>
+      <c r="I10" s="30" t="n"/>
+      <c r="J10" s="30" t="n"/>
+      <c r="K10" s="30" t="n"/>
+      <c r="L10" s="30" t="n"/>
+      <c r="M10" s="30" t="n"/>
+      <c r="N10" s="30" t="n"/>
+      <c r="O10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
         <v/>
       </c>
-      <c r="P10" s="21">
+      <c r="P10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
         <v/>
       </c>
-      <c r="Q10" s="21">
+      <c r="Q10" s="22">
         <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
         <v/>
       </c>
@@ -1198,33 +1198,33 @@
           <t>Ventas de bumps (1 + 2)</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="30" t="n">
         <v>117</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="30" t="n">
         <v>110</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="30" t="n">
         <v>95</v>
       </c>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="29" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="29" t="n"/>
-      <c r="K11" s="29" t="n"/>
-      <c r="L11" s="29" t="n"/>
-      <c r="M11" s="29" t="n"/>
-      <c r="N11" s="29" t="n"/>
-      <c r="O11" s="21">
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="30" t="n"/>
+      <c r="I11" s="30" t="n"/>
+      <c r="J11" s="30" t="n"/>
+      <c r="K11" s="30" t="n"/>
+      <c r="L11" s="30" t="n"/>
+      <c r="M11" s="30" t="n"/>
+      <c r="N11" s="30" t="n"/>
+      <c r="O11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
         <v/>
       </c>
-      <c r="P11" s="21">
+      <c r="P11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
         <v/>
       </c>
-      <c r="Q11" s="21">
+      <c r="Q11" s="22">
         <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
         <v/>
       </c>
@@ -1235,33 +1235,33 @@
           <t>Ventas de OTOs (1 a 4)</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="30" t="n">
         <v>63</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="30" t="n">
         <v>58</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="30" t="n">
         <v>52</v>
       </c>
-      <c r="F12" s="29" t="n"/>
-      <c r="G12" s="29" t="n"/>
-      <c r="H12" s="29" t="n"/>
-      <c r="I12" s="29" t="n"/>
-      <c r="J12" s="29" t="n"/>
-      <c r="K12" s="29" t="n"/>
-      <c r="L12" s="29" t="n"/>
-      <c r="M12" s="29" t="n"/>
-      <c r="N12" s="29" t="n"/>
-      <c r="O12" s="21">
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="30" t="n"/>
+      <c r="H12" s="30" t="n"/>
+      <c r="I12" s="30" t="n"/>
+      <c r="J12" s="30" t="n"/>
+      <c r="K12" s="30" t="n"/>
+      <c r="L12" s="30" t="n"/>
+      <c r="M12" s="30" t="n"/>
+      <c r="N12" s="30" t="n"/>
+      <c r="O12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
         <v/>
       </c>
-      <c r="P12" s="21">
+      <c r="P12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
         <v/>
       </c>
-      <c r="Q12" s="21">
+      <c r="Q12" s="22">
         <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
         <v/>
       </c>
@@ -1272,33 +1272,33 @@
           <t>Ventas de la ascensión (programa)</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="29" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="29" t="n"/>
-      <c r="L13" s="29" t="n"/>
-      <c r="M13" s="29" t="n"/>
-      <c r="N13" s="29" t="n"/>
-      <c r="O13" s="21">
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="30" t="n"/>
+      <c r="I13" s="30" t="n"/>
+      <c r="J13" s="30" t="n"/>
+      <c r="K13" s="30" t="n"/>
+      <c r="L13" s="30" t="n"/>
+      <c r="M13" s="30" t="n"/>
+      <c r="N13" s="30" t="n"/>
+      <c r="O13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
         <v/>
       </c>
-      <c r="P13" s="21">
+      <c r="P13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
         <v/>
       </c>
-      <c r="Q13" s="21">
+      <c r="Q13" s="22">
         <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
         <v/>
       </c>
@@ -1309,33 +1309,33 @@
           <t>Facturado del mes (a precio de lista)</t>
         </is>
       </c>
-      <c r="C14" s="18" t="n">
+      <c r="C14" s="19" t="n">
         <v>15900</v>
       </c>
-      <c r="D14" s="18" t="n">
+      <c r="D14" s="19" t="n">
         <v>15400</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="19" t="n">
         <v>13700</v>
       </c>
-      <c r="F14" s="18" t="n"/>
-      <c r="G14" s="18" t="n"/>
-      <c r="H14" s="18" t="n"/>
-      <c r="I14" s="18" t="n"/>
-      <c r="J14" s="18" t="n"/>
-      <c r="K14" s="18" t="n"/>
-      <c r="L14" s="18" t="n"/>
-      <c r="M14" s="18" t="n"/>
-      <c r="N14" s="18" t="n"/>
-      <c r="O14" s="19">
+      <c r="F14" s="19" t="n"/>
+      <c r="G14" s="19" t="n"/>
+      <c r="H14" s="19" t="n"/>
+      <c r="I14" s="19" t="n"/>
+      <c r="J14" s="19" t="n"/>
+      <c r="K14" s="19" t="n"/>
+      <c r="L14" s="19" t="n"/>
+      <c r="M14" s="19" t="n"/>
+      <c r="N14" s="19" t="n"/>
+      <c r="O14" s="20">
         <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
         <v/>
       </c>
-      <c r="P14" s="19">
+      <c r="P14" s="20">
         <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
         <v/>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="20">
         <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
         <v/>
       </c>
@@ -1346,33 +1346,33 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n">
+      <c r="C15" s="19" t="n">
         <v>15900</v>
       </c>
-      <c r="D15" s="18" t="n">
+      <c r="D15" s="19" t="n">
         <v>15400</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="19" t="n">
         <v>13700</v>
       </c>
-      <c r="F15" s="18" t="n"/>
-      <c r="G15" s="18" t="n"/>
-      <c r="H15" s="18" t="n"/>
-      <c r="I15" s="18" t="n"/>
-      <c r="J15" s="18" t="n"/>
-      <c r="K15" s="18" t="n"/>
-      <c r="L15" s="18" t="n"/>
-      <c r="M15" s="18" t="n"/>
-      <c r="N15" s="18" t="n"/>
-      <c r="O15" s="19">
+      <c r="F15" s="19" t="n"/>
+      <c r="G15" s="19" t="n"/>
+      <c r="H15" s="19" t="n"/>
+      <c r="I15" s="19" t="n"/>
+      <c r="J15" s="19" t="n"/>
+      <c r="K15" s="19" t="n"/>
+      <c r="L15" s="19" t="n"/>
+      <c r="M15" s="19" t="n"/>
+      <c r="N15" s="19" t="n"/>
+      <c r="O15" s="20">
         <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
         <v/>
       </c>
-      <c r="P15" s="19">
+      <c r="P15" s="20">
         <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
         <v/>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="20">
         <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
         <v/>
       </c>
@@ -1469,63 +1469,63 @@
           <t>% visitas → checkout</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="24">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
         <v/>
       </c>
-      <c r="D18" s="23">
+      <c r="D18" s="24">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
         <v/>
       </c>
-      <c r="E18" s="23">
+      <c r="E18" s="24">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
         <v/>
       </c>
-      <c r="F18" s="23">
+      <c r="F18" s="24">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
         <v/>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="24">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
         <v/>
       </c>
-      <c r="H18" s="23">
+      <c r="H18" s="24">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
         <v/>
       </c>
-      <c r="I18" s="23">
+      <c r="I18" s="24">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
         <v/>
       </c>
-      <c r="J18" s="23">
+      <c r="J18" s="24">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
         <v/>
       </c>
-      <c r="K18" s="23">
+      <c r="K18" s="24">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
         <v/>
       </c>
-      <c r="L18" s="23">
+      <c r="L18" s="24">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
         <v/>
       </c>
-      <c r="M18" s="23">
+      <c r="M18" s="24">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
         <v/>
       </c>
-      <c r="N18" s="23">
+      <c r="N18" s="24">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
         <v/>
       </c>
-      <c r="O18" s="23">
+      <c r="O18" s="24">
         <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
         <v/>
       </c>
-      <c r="P18" s="23">
+      <c r="P18" s="24">
         <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
         <v/>
       </c>
-      <c r="Q18" s="23">
+      <c r="Q18" s="24">
         <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
         <v/>
       </c>
@@ -1536,63 +1536,63 @@
           <t>% checkout → compra</t>
         </is>
       </c>
-      <c r="C19" s="23">
+      <c r="C19" s="24">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
         <v/>
       </c>
-      <c r="D19" s="23">
+      <c r="D19" s="24">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
         <v/>
       </c>
-      <c r="E19" s="23">
+      <c r="E19" s="24">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
         <v/>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="24">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
         <v/>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="24">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
         <v/>
       </c>
-      <c r="H19" s="23">
+      <c r="H19" s="24">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
         <v/>
       </c>
-      <c r="I19" s="23">
+      <c r="I19" s="24">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
         <v/>
       </c>
-      <c r="J19" s="23">
+      <c r="J19" s="24">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
         <v/>
       </c>
-      <c r="K19" s="23">
+      <c r="K19" s="24">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
         <v/>
       </c>
-      <c r="L19" s="23">
+      <c r="L19" s="24">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
         <v/>
       </c>
-      <c r="M19" s="23">
+      <c r="M19" s="24">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
         <v/>
       </c>
-      <c r="N19" s="23">
+      <c r="N19" s="24">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
         <v/>
       </c>
-      <c r="O19" s="23">
+      <c r="O19" s="24">
         <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
         <v/>
       </c>
-      <c r="P19" s="23">
+      <c r="P19" s="24">
         <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
         <v/>
       </c>
-      <c r="Q19" s="23">
+      <c r="Q19" s="24">
         <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
         <v/>
       </c>
@@ -1852,15 +1852,15 @@
         <f>IF(COUNT(N7:N15)&lt;9,"",N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O23" s="19">
+      <c r="O23" s="20">
         <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
         <v/>
       </c>
-      <c r="P23" s="19">
+      <c r="P23" s="20">
         <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
         <v/>
       </c>
-      <c r="Q23" s="19">
+      <c r="Q23" s="20">
         <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
         <v/>
       </c>
@@ -1871,63 +1871,63 @@
           <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>IF(COUNT(C7:C15)&lt;9,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>IF(COUNT(D7:D15)&lt;9,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>IF(COUNT(E7:E15)&lt;9,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>IF(COUNT(F7:F15)&lt;9,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>IF(COUNT(G7:G15)&lt;9,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>IF(COUNT(H7:H15)&lt;9,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
         <v/>
       </c>
-      <c r="I24" s="19">
+      <c r="I24" s="20">
         <f>IF(COUNT(I7:I15)&lt;9,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
         <v/>
       </c>
-      <c r="J24" s="19">
+      <c r="J24" s="20">
         <f>IF(COUNT(J7:J15)&lt;9,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
         <v/>
       </c>
-      <c r="K24" s="19">
+      <c r="K24" s="20">
         <f>IF(COUNT(K7:K15)&lt;9,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
         <v/>
       </c>
-      <c r="L24" s="19">
+      <c r="L24" s="20">
         <f>IF(COUNT(L7:L15)&lt;9,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
         <v/>
       </c>
-      <c r="M24" s="19">
+      <c r="M24" s="20">
         <f>IF(COUNT(M7:M15)&lt;9,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
         <v/>
       </c>
-      <c r="N24" s="19">
+      <c r="N24" s="20">
         <f>IF(COUNT(N7:N15)&lt;9,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
         <v/>
       </c>
-      <c r="O24" s="19">
+      <c r="O24" s="20">
         <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
         <v/>
       </c>
-      <c r="P24" s="19">
+      <c r="P24" s="20">
         <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
         <v/>
       </c>
-      <c r="Q24" s="19">
+      <c r="Q24" s="20">
         <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
         <v/>
       </c>
@@ -2053,15 +2053,15 @@
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O26" s="26">
+      <c r="O26" s="27">
         <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
         <v/>
       </c>
-      <c r="P26" s="26">
+      <c r="P26" s="27">
         <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
         <v/>
       </c>
-      <c r="Q26" s="26">
+      <c r="Q26" s="27">
         <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
         <v/>
       </c>
@@ -2072,63 +2072,63 @@
           <t>ROAS de caja (cobrado hasta ahora)</t>
         </is>
       </c>
-      <c r="C27" s="26">
+      <c r="C27" s="27">
         <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
         <v/>
       </c>
-      <c r="D27" s="26">
+      <c r="D27" s="27">
         <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
         <v/>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
         <v/>
       </c>
-      <c r="F27" s="26">
+      <c r="F27" s="27">
         <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
         <v/>
       </c>
-      <c r="G27" s="26">
+      <c r="G27" s="27">
         <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
         <v/>
       </c>
-      <c r="H27" s="26">
+      <c r="H27" s="27">
         <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
         <v/>
       </c>
-      <c r="I27" s="26">
+      <c r="I27" s="27">
         <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
         <v/>
       </c>
-      <c r="J27" s="26">
+      <c r="J27" s="27">
         <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
         <v/>
       </c>
-      <c r="K27" s="26">
+      <c r="K27" s="27">
         <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
         <v/>
       </c>
-      <c r="L27" s="26">
+      <c r="L27" s="27">
         <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
         <v/>
       </c>
-      <c r="M27" s="26">
+      <c r="M27" s="27">
         <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
         <v/>
       </c>
-      <c r="N27" s="26">
+      <c r="N27" s="27">
         <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
         <v/>
       </c>
-      <c r="O27" s="26">
+      <c r="O27" s="27">
         <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
         <v/>
       </c>
-      <c r="P27" s="26">
+      <c r="P27" s="27">
         <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
         <v/>
       </c>
-      <c r="Q27" s="26">
+      <c r="Q27" s="27">
         <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
         <v/>
       </c>
@@ -2418,7 +2418,7 @@
           <t>&gt;5 %</t>
         </is>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="24">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -2454,7 +2454,7 @@
           <t>&gt;30 %</t>
         </is>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -2490,7 +2490,7 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
@@ -2526,7 +2526,7 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="24">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -2562,7 +2562,7 @@
           <t>&gt;14 %</t>
         </is>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="24">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -2598,7 +2598,7 @@
           <t>&gt;4 %</t>
         </is>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="24">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -2634,7 +2634,7 @@
           <t>&gt;1,7</t>
         </is>
       </c>
-      <c r="G13" s="26">
+      <c r="G13" s="27">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
@@ -2670,7 +2670,7 @@
           <t>&gt;2,5</t>
         </is>
       </c>
-      <c r="G14" s="26">
+      <c r="G14" s="27">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
@@ -2706,7 +2706,7 @@
           <t>&lt;4 %</t>
         </is>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="24">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -3413,7 +3413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3466,7 +3466,7 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="18">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3482,7 +3482,7 @@
           <t>Ninguna celda con error en Simulador</t>
         </is>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="18">
         <f>IF(ISERROR(SUM('Simulador'!C5:G220)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3498,7 +3498,7 @@
           <t>Ninguna celda con error en Embudo</t>
         </is>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="18">
         <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3514,7 +3514,7 @@
           <t>Ninguna celda con error en Resumen</t>
         </is>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="18">
         <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3530,7 +3530,7 @@
           <t>Ninguna celda con error en Proyección 12 meses</t>
         </is>
       </c>
-      <c r="C10" s="36">
+      <c r="C10" s="18">
         <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3546,7 +3546,7 @@
           <t>Ninguna celda con error en Escenarios</t>
         </is>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="18">
         <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3562,7 +3562,7 @@
           <t>Ninguna celda con error en Seguimiento</t>
         </is>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="18">
         <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3578,7 +3578,7 @@
           <t>Los supuestos de tráfico son mayores a cero</t>
         </is>
       </c>
-      <c r="C13" s="36">
+      <c r="C13" s="18">
         <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$12&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3594,7 +3594,7 @@
           <t>La curva de cobranza suma 100 %</t>
         </is>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="18">
         <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3610,7 +3610,7 @@
           <t>Comisiones + reembolsos menores al 60 %</t>
         </is>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="18">
         <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3626,7 +3626,7 @@
           <t>El escenario en uso es 1, 2 o 3</t>
         </is>
       </c>
-      <c r="C16" s="36">
+      <c r="C16" s="18">
         <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3642,7 +3642,7 @@
           <t>La inversión es mayor a cero</t>
         </is>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="18">
         <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3654,7 +3654,7 @@
           <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
         </is>
       </c>
-      <c r="C18" s="36">
+      <c r="C18" s="18">
         <f>IF('Modelo'!$C$11&gt;0,"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3670,7 +3670,7 @@
           <t>Las conversiones están entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="18">
         <f>IF(AND('Supuestos'!$C$12&gt;=0,'Supuestos'!$C$12&lt;=1,'Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$28&gt;=0,'Supuestos'!$C$28&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3686,7 +3686,7 @@
           <t>El margen de seguridad está entre 0 y 100 %</t>
         </is>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="18">
         <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3698,7 +3698,7 @@
           <t>El crecimiento mensual está entre −50 % y 100 %</t>
         </is>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="18">
         <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3714,7 +3714,7 @@
           <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
         </is>
       </c>
-      <c r="C22" s="36">
+      <c r="C22" s="18">
         <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$8,'Modelo'!$C$10&lt;='Modelo'!$C$9),"OK","REVISAR")</f>
         <v/>
       </c>
@@ -3724,19 +3724,196 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Simulador: lo que escribiste en las celdas amarillas</t>
+        </is>
+      </c>
+      <c r="C23" s="8" t="n"/>
+      <c r="D23" s="8" t="n"/>
+    </row>
     <row r="24">
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ningún supuesto del Simulador fuera de rango (porcentajes entre 0 y 1, números no negativos)</t>
+        </is>
+      </c>
+      <c r="C24" s="18">
+        <f>IF(COUNTIF('Simulador'!$I$6:$I$93,"REVISAR")=0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>La columna Rango del Simulador marca la fila con el problema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Simulador: Los supuestos de tráfico son mayores a cero</t>
+        </is>
+      </c>
+      <c r="C25" s="18">
+        <f>IF(AND('Simulador'!$C$7&gt;0,'Simulador'!$C$11&gt;0,'Simulador'!$C$13&gt;0),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Simulador: La curva de cobranza suma 100 %</t>
+        </is>
+      </c>
+      <c r="C26" s="18">
+        <f>IF(ABS('Simulador'!$C$54+'Simulador'!$C$55+'Simulador'!$C$56-1)&lt;0.001,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Simulador: Comisiones + reembolsos menores al 60 %</t>
+        </is>
+      </c>
+      <c r="C27" s="18">
+        <f>IF(('Simulador'!$C$59+'Simulador'!$C$60+'Simulador'!$C$62)&lt;0.6,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Si suman más, revisá los porcentajes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Simulador: El escenario en uso es 1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="C28" s="18">
+        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Supuestos → celda 'Escenario en uso'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Simulador: La inversión es mayor a cero</t>
+        </is>
+      </c>
+      <c r="C29" s="18">
+        <f>IF('Simulador'!$C$9&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Simulador: La meta de ventas es alcanzable (hay conversión a venta)</t>
+        </is>
+      </c>
+      <c r="C30" s="18">
+        <f>IF('Simulador'!$E$15&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Simulador: Las conversiones están entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C31" s="18">
+        <f>IF(AND('Simulador'!$C$11&gt;=0,'Simulador'!$C$11&lt;=1,'Simulador'!$C$13&gt;=0,'Simulador'!$C$13&lt;=1,'Simulador'!$C$20&gt;=0,'Simulador'!$C$20&lt;=1,'Simulador'!$C$24&gt;=0,'Simulador'!$C$24&lt;=1,'Simulador'!$C$28&gt;=0,'Simulador'!$C$28&lt;=1,'Simulador'!$C$32&gt;=0,'Simulador'!$C$32&lt;=1,'Simulador'!$C$36&gt;=0,'Simulador'!$C$36&lt;=1,'Simulador'!$C$40&gt;=0,'Simulador'!$C$40&lt;=1,'Simulador'!$C$44&gt;=0,'Simulador'!$C$44&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Simulador: El margen de seguridad está entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C32" s="18">
+        <f>IF(AND('Simulador'!$C$77&gt;=0,'Simulador'!$C$77&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Simulador: El crecimiento mensual está entre −50 % y 100 %</t>
+        </is>
+      </c>
+      <c r="C33" s="18">
+        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>Más de 100 % por mes no es realista para una proyección.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Simulador: La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
+        </is>
+      </c>
+      <c r="C34" s="18">
+        <f>IF(AND('Simulador'!$E$12&lt;='Simulador'!$E$10,'Simulador'!$E$14&lt;='Simulador'!$E$12),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>Si falla, alguna conversión está por encima de 100 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C24" s="37">
-        <f>IF(COUNTIF(C6:C22,"REVISAR")=0,"OK","REVISAR")</f>
+      <c r="C36" s="37">
+        <f>IF(COUNTIF(C6:C34,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C24">
+  <conditionalFormatting sqref="C6:C36">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -4332,7 +4509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H97"/>
+  <dimension ref="A1:I98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -4343,6 +4520,7 @@
     <col width="19" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="62" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4400,6 +4578,11 @@
       <c r="H5" s="6" t="inlineStr">
         <is>
           <t>Cómo se calcula</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Rango</t>
         </is>
       </c>
     </row>
@@ -4439,6 +4622,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I7" s="18">
+        <f>IF(AND(ISNUMBER(C7),C7&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
@@ -4470,11 +4657,11 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="19">
         <f>'Supuestos'!$C$8</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>'Supuestos'!$C$8</f>
         <v/>
       </c>
@@ -4487,6 +4674,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I9" s="18">
+        <f>IF(AND(ISNUMBER(C9),C9&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
@@ -4494,15 +4685,15 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="21">
         <f>IF($E$8=0,0,$C$9/$E$8)</f>
         <v/>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="22">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="22">
         <f>IF(AND(ISNUMBER(E10),ISNUMBER(F10)),E10-F10,"")</f>
         <v/>
       </c>
@@ -4518,11 +4709,11 @@
           <t>% de visitas que llegan al checkout</t>
         </is>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -4535,6 +4726,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I11" s="18">
+        <f>IF(AND(ISNUMBER(C11),C11&gt;=0,C11&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="B12" t="inlineStr">
@@ -4542,15 +4737,15 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="22">
         <f>$E$10*$C$11</f>
         <v/>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="22">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <f>IF(AND(ISNUMBER(E12),ISNUMBER(F12)),E12-F12,"")</f>
         <v/>
       </c>
@@ -4566,11 +4761,11 @@
           <t>% de checkouts que terminan en compra</t>
         </is>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="23">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -4583,6 +4778,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I13" s="18">
+        <f>IF(AND(ISNUMBER(C13),C13&gt;=0,C13&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
@@ -4594,11 +4793,11 @@
         <f>$E$12*$C$13</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="G14" s="24">
+      <c r="G14" s="25">
         <f>IF(AND(ISNUMBER(E14),ISNUMBER(F14)),E14-F14,"")</f>
         <v/>
       </c>
@@ -4614,15 +4813,15 @@
           <t>% de visitas que compran</t>
         </is>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>IF($E$10=0,0,$E$14/$E$10)</f>
         <v/>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="26">
         <f>IF(AND(ISNUMBER(E15),ISNUMBER(F15)),E15-F15,"")</f>
         <v/>
       </c>
@@ -4692,6 +4891,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I18" s="18">
+        <f>IF(AND(ISNUMBER(C18),C18&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
@@ -4699,15 +4902,15 @@
           <t>Facturado: producto principal</t>
         </is>
       </c>
-      <c r="E19" s="19">
+      <c r="E19" s="20">
         <f>$E$14*$C$18</f>
         <v/>
       </c>
-      <c r="F19" s="19">
+      <c r="F19" s="20">
         <f>'Modelo'!$C$14</f>
         <v/>
       </c>
-      <c r="G19" s="19">
+      <c r="G19" s="20">
         <f>IF(AND(ISNUMBER(E19),ISNUMBER(F19)),E19-F19,"")</f>
         <v/>
       </c>
@@ -4723,11 +4926,11 @@
           <t>Bump 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="23">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="24">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -4740,6 +4943,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I20" s="18">
+        <f>IF(AND(ISNUMBER(C20),C20&gt;=0,C20&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
@@ -4747,15 +4954,15 @@
           <t>Ventas: Bump 1</t>
         </is>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <f>$E$14*$C$20</f>
         <v/>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="25">
         <f>IF(AND(ISNUMBER(E21),ISNUMBER(F21)),E21-F21,"")</f>
         <v/>
       </c>
@@ -4788,6 +4995,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I22" s="18">
+        <f>IF(AND(ISNUMBER(C22),C22&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
@@ -4795,15 +5006,15 @@
           <t>Facturado: Bump 1</t>
         </is>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>$E$21*$C$22</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>'Modelo'!$C$16</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23-F23,"")</f>
         <v/>
       </c>
@@ -4819,11 +5030,11 @@
           <t>Bump 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C24" s="22">
+      <c r="C24" s="23">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="24">
         <f>'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -4836,6 +5047,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I24" s="18">
+        <f>IF(AND(ISNUMBER(C24),C24&gt;=0,C24&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="B25" t="inlineStr">
@@ -4843,15 +5058,15 @@
           <t>Ventas: Bump 2</t>
         </is>
       </c>
-      <c r="E25" s="24">
+      <c r="E25" s="25">
         <f>$E$14*$C$24</f>
         <v/>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="25">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="G25" s="24">
+      <c r="G25" s="25">
         <f>IF(AND(ISNUMBER(E25),ISNUMBER(F25)),E25-F25,"")</f>
         <v/>
       </c>
@@ -4884,6 +5099,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I26" s="18">
+        <f>IF(AND(ISNUMBER(C26),C26&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="B27" t="inlineStr">
@@ -4891,15 +5110,15 @@
           <t>Facturado: Bump 2</t>
         </is>
       </c>
-      <c r="E27" s="19">
+      <c r="E27" s="20">
         <f>$E$25*$C$26</f>
         <v/>
       </c>
-      <c r="F27" s="19">
+      <c r="F27" s="20">
         <f>'Modelo'!$C$18</f>
         <v/>
       </c>
-      <c r="G27" s="19">
+      <c r="G27" s="20">
         <f>IF(AND(ISNUMBER(E27),ISNUMBER(F27)),E27-F27,"")</f>
         <v/>
       </c>
@@ -4915,11 +5134,11 @@
           <t>OTO 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C28" s="22">
+      <c r="C28" s="23">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="24">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -4932,6 +5151,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I28" s="18">
+        <f>IF(AND(ISNUMBER(C28),C28&gt;=0,C28&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="B29" t="inlineStr">
@@ -4939,15 +5162,15 @@
           <t>Ventas: OTO 1</t>
         </is>
       </c>
-      <c r="E29" s="24">
+      <c r="E29" s="25">
         <f>$E$14*$C$28</f>
         <v/>
       </c>
-      <c r="F29" s="24">
+      <c r="F29" s="25">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="G29" s="24">
+      <c r="G29" s="25">
         <f>IF(AND(ISNUMBER(E29),ISNUMBER(F29)),E29-F29,"")</f>
         <v/>
       </c>
@@ -4980,6 +5203,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I30" s="18">
+        <f>IF(AND(ISNUMBER(C30),C30&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="B31" t="inlineStr">
@@ -4987,15 +5214,15 @@
           <t>Facturado: OTO 1</t>
         </is>
       </c>
-      <c r="E31" s="19">
+      <c r="E31" s="20">
         <f>$E$29*$C$30</f>
         <v/>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="20">
         <f>'Modelo'!$C$20</f>
         <v/>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="20">
         <f>IF(AND(ISNUMBER(E31),ISNUMBER(F31)),E31-F31,"")</f>
         <v/>
       </c>
@@ -5011,11 +5238,11 @@
           <t>OTO 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C32" s="22">
+      <c r="C32" s="23">
         <f>'Supuestos'!$C$24</f>
         <v/>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="24">
         <f>'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -5028,6 +5255,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I32" s="18">
+        <f>IF(AND(ISNUMBER(C32),C32&gt;=0,C32&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="B33" t="inlineStr">
@@ -5035,15 +5266,15 @@
           <t>Ventas: OTO 2</t>
         </is>
       </c>
-      <c r="E33" s="24">
+      <c r="E33" s="25">
         <f>$E$14*$C$32</f>
         <v/>
       </c>
-      <c r="F33" s="24">
+      <c r="F33" s="25">
         <f>'Modelo'!$C$21</f>
         <v/>
       </c>
-      <c r="G33" s="24">
+      <c r="G33" s="25">
         <f>IF(AND(ISNUMBER(E33),ISNUMBER(F33)),E33-F33,"")</f>
         <v/>
       </c>
@@ -5076,6 +5307,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I34" s="18">
+        <f>IF(AND(ISNUMBER(C34),C34&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="B35" t="inlineStr">
@@ -5083,15 +5318,15 @@
           <t>Facturado: OTO 2</t>
         </is>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="20">
         <f>$E$33*$C$34</f>
         <v/>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="20">
         <f>'Modelo'!$C$22</f>
         <v/>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="20">
         <f>IF(AND(ISNUMBER(E35),ISNUMBER(F35)),E35-F35,"")</f>
         <v/>
       </c>
@@ -5107,11 +5342,11 @@
           <t>OTO 3: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C36" s="22">
+      <c r="C36" s="23">
         <f>'Supuestos'!$C$26</f>
         <v/>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="24">
         <f>'Supuestos'!$C$26</f>
         <v/>
       </c>
@@ -5124,6 +5359,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I36" s="18">
+        <f>IF(AND(ISNUMBER(C36),C36&gt;=0,C36&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="B37" t="inlineStr">
@@ -5131,15 +5370,15 @@
           <t>Ventas: OTO 3</t>
         </is>
       </c>
-      <c r="E37" s="24">
+      <c r="E37" s="25">
         <f>$E$14*$C$36</f>
         <v/>
       </c>
-      <c r="F37" s="24">
+      <c r="F37" s="25">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="G37" s="24">
+      <c r="G37" s="25">
         <f>IF(AND(ISNUMBER(E37),ISNUMBER(F37)),E37-F37,"")</f>
         <v/>
       </c>
@@ -5172,6 +5411,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I38" s="18">
+        <f>IF(AND(ISNUMBER(C38),C38&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="B39" t="inlineStr">
@@ -5179,15 +5422,15 @@
           <t>Facturado: OTO 3</t>
         </is>
       </c>
-      <c r="E39" s="19">
+      <c r="E39" s="20">
         <f>$E$37*$C$38</f>
         <v/>
       </c>
-      <c r="F39" s="19">
+      <c r="F39" s="20">
         <f>'Modelo'!$C$24</f>
         <v/>
       </c>
-      <c r="G39" s="19">
+      <c r="G39" s="20">
         <f>IF(AND(ISNUMBER(E39),ISNUMBER(F39)),E39-F39,"")</f>
         <v/>
       </c>
@@ -5203,11 +5446,11 @@
           <t>OTO 4: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="23">
         <f>'Supuestos'!$C$28</f>
         <v/>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="24">
         <f>'Supuestos'!$C$28</f>
         <v/>
       </c>
@@ -5220,6 +5463,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I40" s="18">
+        <f>IF(AND(ISNUMBER(C40),C40&gt;=0,C40&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="B41" t="inlineStr">
@@ -5227,15 +5474,15 @@
           <t>Ventas: OTO 4</t>
         </is>
       </c>
-      <c r="E41" s="24">
+      <c r="E41" s="25">
         <f>$E$14*$C$40</f>
         <v/>
       </c>
-      <c r="F41" s="24">
+      <c r="F41" s="25">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="G41" s="24">
+      <c r="G41" s="25">
         <f>IF(AND(ISNUMBER(E41),ISNUMBER(F41)),E41-F41,"")</f>
         <v/>
       </c>
@@ -5268,6 +5515,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I42" s="18">
+        <f>IF(AND(ISNUMBER(C42),C42&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="B43" t="inlineStr">
@@ -5275,15 +5526,15 @@
           <t>Facturado: OTO 4</t>
         </is>
       </c>
-      <c r="E43" s="19">
+      <c r="E43" s="20">
         <f>$E$41*$C$42</f>
         <v/>
       </c>
-      <c r="F43" s="19">
+      <c r="F43" s="20">
         <f>'Modelo'!$C$26</f>
         <v/>
       </c>
-      <c r="G43" s="19">
+      <c r="G43" s="20">
         <f>IF(AND(ISNUMBER(E43),ISNUMBER(F43)),E43-F43,"")</f>
         <v/>
       </c>
@@ -5299,11 +5550,11 @@
           <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C44" s="22">
+      <c r="C44" s="23">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
-      <c r="D44" s="23">
+      <c r="D44" s="24">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -5316,6 +5567,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I44" s="18">
+        <f>IF(AND(ISNUMBER(C44),C44&gt;=0,C44&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="B45" t="inlineStr">
@@ -5323,15 +5578,15 @@
           <t>Ventas: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="E45" s="24">
+      <c r="E45" s="25">
         <f>$E$14*$C$44</f>
         <v/>
       </c>
-      <c r="F45" s="24">
+      <c r="F45" s="25">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="G45" s="24">
+      <c r="G45" s="25">
         <f>IF(AND(ISNUMBER(E45),ISNUMBER(F45)),E45-F45,"")</f>
         <v/>
       </c>
@@ -5364,6 +5619,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I46" s="18">
+        <f>IF(AND(ISNUMBER(C46),C46&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="B47" t="inlineStr">
@@ -5371,15 +5630,15 @@
           <t>Facturado: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="E47" s="19">
+      <c r="E47" s="20">
         <f>$E$45*$C$46</f>
         <v/>
       </c>
-      <c r="F47" s="19">
+      <c r="F47" s="20">
         <f>'Modelo'!$C$28</f>
         <v/>
       </c>
-      <c r="G47" s="19">
+      <c r="G47" s="20">
         <f>IF(AND(ISNUMBER(E47),ISNUMBER(F47)),E47-F47,"")</f>
         <v/>
       </c>
@@ -5399,11 +5658,11 @@
         <f>$E$19+$E$23+$E$27+$E$31+$E$35+$E$39+$E$43+$E$47</f>
         <v/>
       </c>
-      <c r="F48" s="19">
+      <c r="F48" s="20">
         <f>'Modelo'!$C$29</f>
         <v/>
       </c>
-      <c r="G48" s="19">
+      <c r="G48" s="20">
         <f>IF(AND(ISNUMBER(E48),ISNUMBER(F48)),E48-F48,"")</f>
         <v/>
       </c>
@@ -5443,15 +5702,15 @@
           <t>AOV ÷ precio del principal</t>
         </is>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="27">
         <f>IF($C$18=0,0,$E$49/$C$18)</f>
         <v/>
       </c>
-      <c r="F50" s="26">
+      <c r="F50" s="27">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
-      <c r="G50" s="26">
+      <c r="G50" s="27">
         <f>IF(AND(ISNUMBER(E50),ISNUMBER(F50)),E50-F50,"")</f>
         <v/>
       </c>
@@ -5467,15 +5726,15 @@
           <t>Ventas del principal por visita (para la proyección)</t>
         </is>
       </c>
-      <c r="E51" s="25">
+      <c r="E51" s="26">
         <f>IF($E$10=0,0,$E$14/$E$10)</f>
         <v/>
       </c>
-      <c r="F51" s="25">
+      <c r="F51" s="26">
         <f>'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G51" s="25">
+      <c r="G51" s="26">
         <f>IF(AND(ISNUMBER(E51),ISNUMBER(F51)),E51-F51,"")</f>
         <v/>
       </c>
@@ -5528,11 +5787,11 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C54" s="22">
+      <c r="C54" s="23">
         <f>'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="24">
         <f>'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -5545,6 +5804,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I54" s="18">
+        <f>IF(AND(ISNUMBER(C54),C54&gt;=0,C54&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="B55" t="inlineStr">
@@ -5552,11 +5815,11 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C55" s="22">
+      <c r="C55" s="23">
         <f>'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="24">
         <f>'Supuestos'!$C$41</f>
         <v/>
       </c>
@@ -5569,6 +5832,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I55" s="18">
+        <f>IF(AND(ISNUMBER(C55),C55&gt;=0,C55&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="B56" t="inlineStr">
@@ -5576,11 +5843,11 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C56" s="22">
+      <c r="C56" s="23">
         <f>'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="D56" s="23">
+      <c r="D56" s="24">
         <f>'Supuestos'!$C$42</f>
         <v/>
       </c>
@@ -5593,6 +5860,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I56" s="18">
+        <f>IF(AND(ISNUMBER(C56),C56&gt;=0,C56&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="B57" t="inlineStr">
@@ -5600,15 +5871,15 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="E57" s="19">
+      <c r="E57" s="20">
         <f>$E$48*($C$54+$C$55+$C$56)</f>
         <v/>
       </c>
-      <c r="F57" s="19">
+      <c r="F57" s="20">
         <f>'Modelo'!$C$35</f>
         <v/>
       </c>
-      <c r="G57" s="19">
+      <c r="G57" s="20">
         <f>IF(AND(ISNUMBER(E57),ISNUMBER(F57)),E57-F57,"")</f>
         <v/>
       </c>
@@ -5624,15 +5895,15 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="E58" s="19">
+      <c r="E58" s="20">
         <f>$E$48*$C$54</f>
         <v/>
       </c>
-      <c r="F58" s="19">
+      <c r="F58" s="20">
         <f>'Modelo'!$C$36</f>
         <v/>
       </c>
-      <c r="G58" s="19">
+      <c r="G58" s="20">
         <f>IF(AND(ISNUMBER(E58),ISNUMBER(F58)),E58-F58,"")</f>
         <v/>
       </c>
@@ -5648,11 +5919,11 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C59" s="22">
+      <c r="C59" s="23">
         <f>'Supuestos'!$C$33</f>
         <v/>
       </c>
-      <c r="D59" s="23">
+      <c r="D59" s="24">
         <f>'Supuestos'!$C$33</f>
         <v/>
       </c>
@@ -5665,6 +5936,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I59" s="18">
+        <f>IF(AND(ISNUMBER(C59),C59&gt;=0,C59&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="B60" t="inlineStr">
@@ -5672,11 +5947,11 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="23">
         <f>'Supuestos'!$C$34</f>
         <v/>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="24">
         <f>'Supuestos'!$C$34</f>
         <v/>
       </c>
@@ -5689,6 +5964,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I60" s="18">
+        <f>IF(AND(ISNUMBER(C60),C60&gt;=0,C60&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="B61" t="inlineStr">
@@ -5696,15 +5975,15 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="E61" s="19">
+      <c r="E61" s="20">
         <f>$E$57*($C$59+$C$60)</f>
         <v/>
       </c>
-      <c r="F61" s="19">
+      <c r="F61" s="20">
         <f>'Modelo'!$C$37</f>
         <v/>
       </c>
-      <c r="G61" s="19">
+      <c r="G61" s="20">
         <f>IF(AND(ISNUMBER(E61),ISNUMBER(F61)),E61-F61,"")</f>
         <v/>
       </c>
@@ -5720,11 +5999,11 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C62" s="22">
+      <c r="C62" s="23">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="24">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -5737,6 +6016,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I62" s="18">
+        <f>IF(AND(ISNUMBER(C62),C62&gt;=0,C62&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="B63" t="inlineStr">
@@ -5744,15 +6027,15 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="E63" s="19">
+      <c r="E63" s="20">
         <f>$E$57*$C$62</f>
         <v/>
       </c>
-      <c r="F63" s="19">
+      <c r="F63" s="20">
         <f>'Modelo'!$C$38</f>
         <v/>
       </c>
-      <c r="G63" s="19">
+      <c r="G63" s="20">
         <f>IF(AND(ISNUMBER(E63),ISNUMBER(F63)),E63-F63,"")</f>
         <v/>
       </c>
@@ -5772,11 +6055,11 @@
         <f>$E$57*(1-$C$59-$C$60-$C$62)</f>
         <v/>
       </c>
-      <c r="F64" s="19">
+      <c r="F64" s="20">
         <f>'Modelo'!$C$39</f>
         <v/>
       </c>
-      <c r="G64" s="19">
+      <c r="G64" s="20">
         <f>IF(AND(ISNUMBER(E64),ISNUMBER(F64)),E64-F64,"")</f>
         <v/>
       </c>
@@ -5809,6 +6092,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I65" s="18">
+        <f>IF(AND(ISNUMBER(C65),C65&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="B66" t="inlineStr">
@@ -5816,15 +6103,15 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="E66" s="19">
+      <c r="E66" s="20">
         <f>$E$10*$C$65</f>
         <v/>
       </c>
-      <c r="F66" s="19">
+      <c r="F66" s="20">
         <f>'Modelo'!$C$40</f>
         <v/>
       </c>
-      <c r="G66" s="19">
+      <c r="G66" s="20">
         <f>IF(AND(ISNUMBER(E66),ISNUMBER(F66)),E66-F66,"")</f>
         <v/>
       </c>
@@ -5840,11 +6127,11 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C67" s="18">
+      <c r="C67" s="19">
         <f>'Supuestos'!$C$37</f>
         <v/>
       </c>
-      <c r="D67" s="19">
+      <c r="D67" s="20">
         <f>'Supuestos'!$C$37</f>
         <v/>
       </c>
@@ -5857,6 +6144,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I67" s="18">
+        <f>IF(AND(ISNUMBER(C67),C67&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="B68" s="4" t="inlineStr">
@@ -5868,11 +6159,11 @@
         <f>$E$64-$E$66-$C$67-$C$9</f>
         <v/>
       </c>
-      <c r="F68" s="19">
+      <c r="F68" s="20">
         <f>'Modelo'!$C$41</f>
         <v/>
       </c>
-      <c r="G68" s="19">
+      <c r="G68" s="20">
         <f>IF(AND(ISNUMBER(E68),ISNUMBER(F68)),E68-F68,"")</f>
         <v/>
       </c>
@@ -5888,15 +6179,15 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="27">
         <f>IF($C$9=0,0,$E$48/$C$9)</f>
         <v/>
       </c>
-      <c r="F69" s="26">
+      <c r="F69" s="27">
         <f>'Modelo'!$C$42</f>
         <v/>
       </c>
-      <c r="G69" s="26">
+      <c r="G69" s="27">
         <f>IF(AND(ISNUMBER(E69),ISNUMBER(F69)),E69-F69,"")</f>
         <v/>
       </c>
@@ -5916,11 +6207,11 @@
         <f>IF($C$9=0,0,$E$64/$C$9)</f>
         <v/>
       </c>
-      <c r="F70" s="26">
+      <c r="F70" s="27">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
-      <c r="G70" s="26">
+      <c r="G70" s="27">
         <f>IF(AND(ISNUMBER(E70),ISNUMBER(F70)),E70-F70,"")</f>
         <v/>
       </c>
@@ -5936,15 +6227,15 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="E71" s="23">
+      <c r="E71" s="24">
         <f>IF($E$57=0,0,$E$68/$E$57)</f>
         <v/>
       </c>
-      <c r="F71" s="23">
+      <c r="F71" s="24">
         <f>'Modelo'!$C$44</f>
         <v/>
       </c>
-      <c r="G71" s="23">
+      <c r="G71" s="24">
         <f>IF(AND(ISNUMBER(E71),ISNUMBER(F71)),E71-F71,"")</f>
         <v/>
       </c>
@@ -5960,11 +6251,11 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C72" s="27">
+      <c r="C72" s="28">
         <f>'Supuestos'!$C$45</f>
         <v/>
       </c>
-      <c r="D72" s="26">
+      <c r="D72" s="27">
         <f>'Supuestos'!$C$45</f>
         <v/>
       </c>
@@ -5977,6 +6268,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I72" s="18">
+        <f>IF(AND(ISNUMBER(C72),C72&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="B73" t="inlineStr">
@@ -5984,11 +6279,11 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="E73" s="28">
+      <c r="E73" s="29">
         <f>IF($E$70&gt;=$C$72,"SÍ","NO")</f>
         <v/>
       </c>
-      <c r="F73" s="28">
+      <c r="F73" s="29">
         <f>'Modelo'!$C$45</f>
         <v/>
       </c>
@@ -6069,11 +6364,11 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C77" s="22">
+      <c r="C77" s="23">
         <f>'Supuestos'!$C$46</f>
         <v/>
       </c>
-      <c r="D77" s="23">
+      <c r="D77" s="24">
         <f>'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -6085,6 +6380,10 @@
         <is>
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
+      </c>
+      <c r="I77" s="18">
+        <f>IF(AND(ISNUMBER(C77),C77&gt;=0,C77&lt;=1),"OK","REVISAR")</f>
+        <v/>
       </c>
     </row>
     <row r="78">
@@ -6254,7 +6553,7 @@
         <f>IF($E$8&gt;$E$76,"ROJO",IF(AND($E$8&lt;=$E$78,$E$70&gt;=$C$72),"VERDE","AMARILLO"))</f>
         <v/>
       </c>
-      <c r="F85" s="28">
+      <c r="F85" s="29">
         <f>'Modelo'!$C$56</f>
         <v/>
       </c>
@@ -6274,11 +6573,11 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C86" s="29">
+      <c r="C86" s="30">
         <f>'Supuestos'!$C$47</f>
         <v/>
       </c>
-      <c r="D86" s="21">
+      <c r="D86" s="22">
         <f>'Supuestos'!$C$47</f>
         <v/>
       </c>
@@ -6291,6 +6590,10 @@
           <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
         </is>
       </c>
+      <c r="I86" s="18">
+        <f>IF(AND(ISNUMBER(C86),C86&gt;=0),"OK","REVISAR")</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="4" t="inlineStr">
@@ -6302,11 +6605,11 @@
         <f>IF($E$15=0,"inalcanzable con estos supuestos",$C$86/$E$15*$E$8)</f>
         <v/>
       </c>
-      <c r="F87" s="19">
+      <c r="F87" s="20">
         <f>'Modelo'!$C$57</f>
         <v/>
       </c>
-      <c r="G87" s="19">
+      <c r="G87" s="20">
         <f>IF(AND(ISNUMBER(E87),ISNUMBER(F87)),E87-F87,"")</f>
         <v/>
       </c>
@@ -6322,15 +6625,15 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="E88" s="19">
+      <c r="E88" s="20">
         <f>IF($E$15=0,"inalcanzable con estos supuestos",$C$86/$E$15*$E$78)</f>
         <v/>
       </c>
-      <c r="F88" s="19">
+      <c r="F88" s="20">
         <f>'Modelo'!$C$58</f>
         <v/>
       </c>
-      <c r="G88" s="19">
+      <c r="G88" s="20">
         <f>IF(AND(ISNUMBER(E88),ISNUMBER(F88)),E88-F88,"")</f>
         <v/>
       </c>
@@ -6470,39 +6773,61 @@
         </is>
       </c>
     </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="B98" s="5" t="inlineStr">
+        <is>
+          <t>La columna Rango avisa si escribiste algo imposible (un porcentaje fuera de 0 a 1, un negativo, texto) y Chequeos repite los chequeos del modelo con tus números del Simulador.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B97:H97"/>
+    <mergeCell ref="B98:H98"/>
     <mergeCell ref="B95:H95"/>
     <mergeCell ref="B96:H96"/>
   </mergeCells>
+  <conditionalFormatting sqref="I6:I93">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
+      <formula>"REVISAR"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="C6:C93">
-    <cfRule type="expression" priority="1" dxfId="3">
+    <cfRule type="expression" priority="2" dxfId="3">
       <formula>AND(ISNUMBER(C6),C6&lt;&gt;D6)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E73:F73">
-    <cfRule type="expression" priority="2" dxfId="0">
+    <cfRule type="expression" priority="3" dxfId="0">
       <formula>LEFT(E73,5)="VERDE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" dxfId="1">
+    <cfRule type="expression" priority="4" dxfId="1">
       <formula>LEFT(E73,8)="AMARILLO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" dxfId="2">
+    <cfRule type="expression" priority="5" dxfId="2">
       <formula>LEFT(E73,4)="ROJO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E85:F85">
-    <cfRule type="expression" priority="5" dxfId="0">
+    <cfRule type="expression" priority="6" dxfId="0">
       <formula>LEFT(E85,5)="VERDE"</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" dxfId="1">
+    <cfRule type="expression" priority="7" dxfId="1">
       <formula>LEFT(E85,8)="AMARILLO"</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" dxfId="2">
+    <cfRule type="expression" priority="8" dxfId="2">
       <formula>LEFT(E85,4)="ROJO"</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="C11 C13 C20 C24 C28 C32 C36 C40 C44 C54 C55 C56 C59 C60 C62 C77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Porcentaje fuera de rango" error="Escribí el porcentaje como fracción entre 0 y 1 (15 % = 0,15)." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation sqref="C7 C9 C18 C22 C26 C30 C34 C38 C42 C46 C65 C67 C72 C86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Tiene que ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
@@ -6604,7 +6929,7 @@
           <t>Visitas a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C6" s="21">
+      <c r="C6" s="22">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
@@ -6613,7 +6938,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$8/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6641,15 +6966,15 @@
           <t>Abren el checkout</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="24">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6677,15 +7002,15 @@
           <t>Compran el producto principal</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="22">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="24">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$10/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6713,15 +7038,15 @@
           <t>Toman el bump 1</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$15/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$15/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6752,15 +7077,15 @@
           <t>Toman el bump 2</t>
         </is>
       </c>
-      <c r="C10" s="21">
+      <c r="C10" s="22">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$17/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$17/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6791,15 +7116,15 @@
           <t>Toman la OTO 1</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C11" s="22">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$19/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$19/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6830,15 +7155,15 @@
           <t>Toman la OTO 2</t>
         </is>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="22">
         <f>'Modelo'!$C$21</f>
         <v/>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$21/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$21/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6869,15 +7194,15 @@
           <t>Toman la OTO 3</t>
         </is>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="22">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$23/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$23/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6908,15 +7233,15 @@
           <t>Toman la OTO 4</t>
         </is>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="22">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$25/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$25/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6947,15 +7272,15 @@
           <t>Ascienden al programa</t>
         </is>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="22">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="24">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$27/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$27/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7157,7 +7482,7 @@
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="30" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -7190,7 +7515,7 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="19" t="n">
         <v>9000</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -7253,17 +7578,17 @@
           <t>% de visitas que llegan al checkout</t>
         </is>
       </c>
-      <c r="C12" s="23">
+      <c r="C12" s="24">
         <f>IF('Supuestos'!$C$6=1,D12,IF('Supuestos'!$C$6=2,E12,F12))</f>
         <v/>
       </c>
-      <c r="D12" s="22" t="n">
+      <c r="D12" s="23" t="n">
         <v>0.025</v>
       </c>
-      <c r="E12" s="22" t="n">
+      <c r="E12" s="23" t="n">
         <v>0.035</v>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="23" t="n">
         <v>0.045</v>
       </c>
       <c r="G12" t="inlineStr">
@@ -7283,17 +7608,17 @@
           <t>% de checkouts que terminan en compra</t>
         </is>
       </c>
-      <c r="C13" s="23">
+      <c r="C13" s="24">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
-      <c r="D13" s="22" t="n">
+      <c r="D13" s="23" t="n">
         <v>0.2</v>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="23" t="n">
         <v>0.26</v>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G13" t="inlineStr">
@@ -7366,17 +7691,17 @@
           <t>Bump 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C18" s="23">
+      <c r="C18" s="24">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
-      <c r="D18" s="22" t="n">
+      <c r="D18" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="E18" s="22" t="n">
+      <c r="E18" s="23" t="n">
         <v>0.25</v>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="23" t="n">
         <v>0.35</v>
       </c>
       <c r="G18" t="inlineStr">
@@ -7412,17 +7737,17 @@
           <t>Bump 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="24">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
-      <c r="D20" s="22" t="n">
+      <c r="D20" s="23" t="n">
         <v>0.12</v>
       </c>
-      <c r="E20" s="22" t="n">
+      <c r="E20" s="23" t="n">
         <v>0.18</v>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F20" s="23" t="n">
         <v>0.25</v>
       </c>
       <c r="G20" t="inlineStr">
@@ -7458,17 +7783,17 @@
           <t>OTO 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="24">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
-      <c r="D22" s="22" t="n">
+      <c r="D22" s="23" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="E22" s="22" t="n">
+      <c r="E22" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="23" t="n">
         <v>0.14</v>
       </c>
       <c r="G22" t="inlineStr">
@@ -7504,17 +7829,17 @@
           <t>OTO 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="24">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
-      <c r="D24" s="22" t="n">
+      <c r="D24" s="23" t="n">
         <v>0.04</v>
       </c>
-      <c r="E24" s="22" t="n">
+      <c r="E24" s="23" t="n">
         <v>0.06</v>
       </c>
-      <c r="F24" s="22" t="n">
+      <c r="F24" s="23" t="n">
         <v>0.09</v>
       </c>
       <c r="G24" t="inlineStr">
@@ -7550,17 +7875,17 @@
           <t>OTO 3: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="24">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="23" t="n">
         <v>0.02</v>
       </c>
-      <c r="E26" s="22" t="n">
+      <c r="E26" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G26" t="inlineStr">
@@ -7596,17 +7921,17 @@
           <t>OTO 4: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="24">
         <f>IF('Supuestos'!$C$6=1,D28,IF('Supuestos'!$C$6=2,E28,F28))</f>
         <v/>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="23" t="n">
         <v>0.03</v>
       </c>
-      <c r="E28" s="22" t="n">
+      <c r="E28" s="23" t="n">
         <v>0.04</v>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="23" t="n">
         <v>0.06</v>
       </c>
       <c r="G28" t="inlineStr">
@@ -7642,17 +7967,17 @@
           <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="23">
+      <c r="C30" s="24">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="23" t="n">
         <v>0.01</v>
       </c>
-      <c r="E30" s="22" t="n">
+      <c r="E30" s="23" t="n">
         <v>0.02</v>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="23" t="n">
         <v>0.04</v>
       </c>
       <c r="G30" t="inlineStr">
@@ -7681,7 +8006,7 @@
           <t>Comisión de la pasarela o plataforma de pago</t>
         </is>
       </c>
-      <c r="C33" s="22" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G33" t="inlineStr">
@@ -7701,7 +8026,7 @@
           <t>Comisión del equipo de ventas</t>
         </is>
       </c>
-      <c r="C34" s="22" t="n">
+      <c r="C34" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
@@ -7721,7 +8046,7 @@
           <t>Reembolsos y contracargos</t>
         </is>
       </c>
-      <c r="C35" s="22" t="n">
+      <c r="C35" s="23" t="n">
         <v>0.05</v>
       </c>
       <c r="G35" t="inlineStr">
@@ -7761,7 +8086,7 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n">
+      <c r="C37" s="19" t="n">
         <v>1500</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -7794,7 +8119,7 @@
           <t>% del facturado que entra en el mes 1</t>
         </is>
       </c>
-      <c r="C40" s="22" t="n">
+      <c r="C40" s="23" t="n">
         <v>1</v>
       </c>
       <c r="G40" t="inlineStr">
@@ -7814,7 +8139,7 @@
           <t>% que entra en el mes 2</t>
         </is>
       </c>
-      <c r="C41" s="22" t="n">
+      <c r="C41" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="inlineStr">
@@ -7834,7 +8159,7 @@
           <t>% que entra en el mes 3</t>
         </is>
       </c>
-      <c r="C42" s="22" t="n">
+      <c r="C42" s="23" t="n">
         <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
@@ -7867,7 +8192,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C45" s="27" t="n">
+      <c r="C45" s="28" t="n">
         <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -7887,7 +8212,7 @@
           <t>Margen de seguridad</t>
         </is>
       </c>
-      <c r="C46" s="22" t="n">
+      <c r="C46" s="23" t="n">
         <v>0.3</v>
       </c>
       <c r="G46" t="inlineStr">
@@ -7907,7 +8232,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="30" t="n">
         <v>500</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -7927,7 +8252,7 @@
           <t>Crecimiento de la inversión por mes (proyección)</t>
         </is>
       </c>
-      <c r="C48" s="22" t="n">
+      <c r="C48" s="23" t="n">
         <v>0.1</v>
       </c>
       <c r="G48" t="inlineStr">
@@ -7947,7 +8272,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C49" s="18" t="n">
+      <c r="C49" s="19" t="n">
         <v>5000</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -8058,7 +8383,7 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C8" s="20">
+      <c r="C8" s="21">
         <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
@@ -8074,7 +8399,7 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C9" s="22">
         <f>'Modelo'!$C$8*'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -8106,7 +8431,7 @@
           <t>% de visitas que compran</t>
         </is>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -8147,7 +8472,7 @@
           <t>Facturado: producto principal</t>
         </is>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>'Modelo'!$C$10*'Supuestos'!$C$16</f>
         <v/>
       </c>
@@ -8163,7 +8488,7 @@
           <t>Ventas: Bump 1</t>
         </is>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -8179,7 +8504,7 @@
           <t>Facturado: Bump 1</t>
         </is>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>'Modelo'!$C$15*'Supuestos'!$C$17</f>
         <v/>
       </c>
@@ -8195,7 +8520,7 @@
           <t>Ventas: Bump 2</t>
         </is>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -8211,7 +8536,7 @@
           <t>Facturado: Bump 2</t>
         </is>
       </c>
-      <c r="C18" s="19">
+      <c r="C18" s="20">
         <f>'Modelo'!$C$17*'Supuestos'!$C$19</f>
         <v/>
       </c>
@@ -8227,7 +8552,7 @@
           <t>Ventas: OTO 1</t>
         </is>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -8243,7 +8568,7 @@
           <t>Facturado: OTO 1</t>
         </is>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>'Modelo'!$C$19*'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -8259,7 +8584,7 @@
           <t>Ventas: OTO 2</t>
         </is>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -8275,7 +8600,7 @@
           <t>Facturado: OTO 2</t>
         </is>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>'Modelo'!$C$21*'Supuestos'!$C$23</f>
         <v/>
       </c>
@@ -8291,7 +8616,7 @@
           <t>Ventas: OTO 3</t>
         </is>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$26</f>
         <v/>
       </c>
@@ -8307,7 +8632,7 @@
           <t>Facturado: OTO 3</t>
         </is>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>'Modelo'!$C$23*'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -8323,7 +8648,7 @@
           <t>Ventas: OTO 4</t>
         </is>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$28</f>
         <v/>
       </c>
@@ -8339,7 +8664,7 @@
           <t>Facturado: OTO 4</t>
         </is>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>'Modelo'!$C$25*'Supuestos'!$C$27</f>
         <v/>
       </c>
@@ -8355,7 +8680,7 @@
           <t>Ventas: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="25">
         <f>'Modelo'!$C$10*'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -8371,7 +8696,7 @@
           <t>Facturado: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="20">
         <f>'Modelo'!$C$27*'Supuestos'!$C$29</f>
         <v/>
       </c>
@@ -8419,7 +8744,7 @@
           <t>AOV ÷ precio del principal</t>
         </is>
       </c>
-      <c r="C31" s="26">
+      <c r="C31" s="27">
         <f>IF('Supuestos'!$C$16=0,0,'Modelo'!$C$30/'Supuestos'!$C$16)</f>
         <v/>
       </c>
@@ -8435,7 +8760,7 @@
           <t>Ventas del principal por visita (para la proyección)</t>
         </is>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -8476,7 +8801,7 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="20">
         <f>'Modelo'!$C$29*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42)</f>
         <v/>
       </c>
@@ -8492,7 +8817,7 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <f>'Modelo'!$C$29*'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -8508,7 +8833,7 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C37" s="19">
+      <c r="C37" s="20">
         <f>'Modelo'!$C$35*('Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
@@ -8524,7 +8849,7 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C38" s="19">
+      <c r="C38" s="20">
         <f>'Modelo'!$C$35*'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -8556,7 +8881,7 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C40" s="19">
+      <c r="C40" s="20">
         <f>'Modelo'!$C$8*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -8588,7 +8913,7 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C42" s="26">
+      <c r="C42" s="27">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$29/'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -8620,7 +8945,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C44" s="23">
+      <c r="C44" s="24">
         <f>IF('Modelo'!$C$35=0,0,'Modelo'!$C$41/'Modelo'!$C$35)</f>
         <v/>
       </c>
@@ -8636,7 +8961,7 @@
           <t>¿Cumple el ROAS objetivo?</t>
         </is>
       </c>
-      <c r="C45" s="28">
+      <c r="C45" s="29">
         <f>IF('Modelo'!$C$43&gt;='Supuestos'!$C$45,"SÍ","NO")</f>
         <v/>
       </c>
@@ -8830,7 +9155,7 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C58" s="19">
+      <c r="C58" s="20">
         <f>IF('Modelo'!$C$11=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$11*'Modelo'!$C$49)</f>
         <v/>
       </c>
@@ -8970,7 +9295,7 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="20">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -8995,143 +9320,143 @@
           <t>Precio ↓  /  % checkout → compra →</t>
         </is>
       </c>
-      <c r="C9" s="30" t="n">
+      <c r="C9" s="31" t="n">
         <v>0.18</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="31" t="n">
         <v>0.22</v>
       </c>
-      <c r="E9" s="30" t="n">
+      <c r="E9" s="31" t="n">
         <v>0.26</v>
       </c>
-      <c r="F9" s="30" t="n">
+      <c r="F9" s="31" t="n">
         <v>0.3</v>
       </c>
-      <c r="G9" s="30" t="n">
+      <c r="G9" s="31" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="32" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="31" t="n">
+      <c r="B11" s="32" t="n">
         <v>37</v>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="31" t="n">
+      <c r="B12" s="32" t="n">
         <v>47</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="31" t="n">
+      <c r="B13" s="32" t="n">
         <v>67</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="31" t="n">
+      <c r="B14" s="32" t="n">
         <v>97</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="19">
+      <c r="G14" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9156,224 +9481,224 @@
           <t>Costo por visita ↓  /  % visita → checkout →</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n">
+      <c r="C19" s="31" t="n">
         <v>0.02</v>
       </c>
-      <c r="D19" s="30" t="n">
+      <c r="D19" s="31" t="n">
         <v>0.025</v>
       </c>
-      <c r="E19" s="30" t="n">
+      <c r="E19" s="31" t="n">
         <v>0.03</v>
       </c>
-      <c r="F19" s="30" t="n">
+      <c r="F19" s="31" t="n">
         <v>0.035</v>
       </c>
-      <c r="G19" s="30" t="n">
+      <c r="G19" s="31" t="n">
         <v>0.04</v>
       </c>
-      <c r="H19" s="30" t="n">
+      <c r="H19" s="31" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="32" t="n">
+      <c r="B20" s="33" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="19">
+      <c r="C20" s="20">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D20" s="19">
+      <c r="D20" s="20">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E20" s="19">
+      <c r="E20" s="20">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="20">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G20" s="19">
+      <c r="G20" s="20">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H20" s="19">
+      <c r="H20" s="20">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="32" t="n">
+      <c r="B21" s="33" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="19">
+      <c r="C21" s="20">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="19">
+      <c r="D21" s="20">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="19">
+      <c r="E21" s="20">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="19">
+      <c r="F21" s="20">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="19">
+      <c r="G21" s="20">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H21" s="19">
+      <c r="H21" s="20">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="32" t="n">
+      <c r="B22" s="33" t="n">
         <v>0.25</v>
       </c>
-      <c r="C22" s="19">
+      <c r="C22" s="20">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="19">
+      <c r="D22" s="20">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="19">
+      <c r="E22" s="20">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="20">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="19">
+      <c r="G22" s="20">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H22" s="19">
+      <c r="H22" s="20">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="32" t="n">
+      <c r="B23" s="33" t="n">
         <v>0.3</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="19">
+      <c r="D23" s="20">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="19">
+      <c r="E23" s="20">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="19">
+      <c r="F23" s="20">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="19">
+      <c r="G23" s="20">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H23" s="19">
+      <c r="H23" s="20">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="32" t="n">
+      <c r="B24" s="33" t="n">
         <v>0.4</v>
       </c>
-      <c r="C24" s="19">
+      <c r="C24" s="20">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="19">
+      <c r="D24" s="20">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="19">
+      <c r="E24" s="20">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="19">
+      <c r="F24" s="20">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="19">
+      <c r="G24" s="20">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H24" s="19">
+      <c r="H24" s="20">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="32" t="n">
+      <c r="B25" s="33" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="19">
+      <c r="C25" s="20">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="19">
+      <c r="D25" s="20">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="19">
+      <c r="E25" s="20">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="20">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="19">
+      <c r="G25" s="20">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H25" s="19">
+      <c r="H25" s="20">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="32" t="n">
+      <c r="B26" s="33" t="n">
         <v>0.6</v>
       </c>
-      <c r="C26" s="19">
+      <c r="C26" s="20">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D26" s="19">
+      <c r="D26" s="20">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E26" s="19">
+      <c r="E26" s="20">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F26" s="19">
+      <c r="F26" s="20">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G26" s="19">
+      <c r="G26" s="20">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H26" s="19">
+      <c r="H26" s="20">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9398,143 +9723,143 @@
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C31" s="33" t="n">
+      <c r="C31" s="34" t="n">
         <v>1.5</v>
       </c>
-      <c r="D31" s="33" t="n">
+      <c r="D31" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="33" t="n">
+      <c r="E31" s="34" t="n">
         <v>2.5</v>
       </c>
-      <c r="F31" s="33" t="n">
+      <c r="F31" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="33" t="n">
+      <c r="G31" s="34" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="31" t="n">
+      <c r="B32" s="32" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="19">
+      <c r="C32" s="20">
         <f>$B32/C$31</f>
         <v/>
       </c>
-      <c r="D32" s="19">
+      <c r="D32" s="20">
         <f>$B32/D$31</f>
         <v/>
       </c>
-      <c r="E32" s="19">
+      <c r="E32" s="20">
         <f>$B32/E$31</f>
         <v/>
       </c>
-      <c r="F32" s="19">
+      <c r="F32" s="20">
         <f>$B32/F$31</f>
         <v/>
       </c>
-      <c r="G32" s="19">
+      <c r="G32" s="20">
         <f>$B32/G$31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="31" t="n">
+      <c r="B33" s="32" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C33" s="20">
         <f>$B33/C$31</f>
         <v/>
       </c>
-      <c r="D33" s="19">
+      <c r="D33" s="20">
         <f>$B33/D$31</f>
         <v/>
       </c>
-      <c r="E33" s="19">
+      <c r="E33" s="20">
         <f>$B33/E$31</f>
         <v/>
       </c>
-      <c r="F33" s="19">
+      <c r="F33" s="20">
         <f>$B33/F$31</f>
         <v/>
       </c>
-      <c r="G33" s="19">
+      <c r="G33" s="20">
         <f>$B33/G$31</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="31" t="n">
+      <c r="B34" s="32" t="n">
         <v>30000</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <f>$B34/C$31</f>
         <v/>
       </c>
-      <c r="D34" s="19">
+      <c r="D34" s="20">
         <f>$B34/D$31</f>
         <v/>
       </c>
-      <c r="E34" s="19">
+      <c r="E34" s="20">
         <f>$B34/E$31</f>
         <v/>
       </c>
-      <c r="F34" s="19">
+      <c r="F34" s="20">
         <f>$B34/F$31</f>
         <v/>
       </c>
-      <c r="G34" s="19">
+      <c r="G34" s="20">
         <f>$B34/G$31</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="31" t="n">
+      <c r="B35" s="32" t="n">
         <v>50000</v>
       </c>
-      <c r="C35" s="19">
+      <c r="C35" s="20">
         <f>$B35/C$31</f>
         <v/>
       </c>
-      <c r="D35" s="19">
+      <c r="D35" s="20">
         <f>$B35/D$31</f>
         <v/>
       </c>
-      <c r="E35" s="19">
+      <c r="E35" s="20">
         <f>$B35/E$31</f>
         <v/>
       </c>
-      <c r="F35" s="19">
+      <c r="F35" s="20">
         <f>$B35/F$31</f>
         <v/>
       </c>
-      <c r="G35" s="19">
+      <c r="G35" s="20">
         <f>$B35/G$31</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="31" t="n">
+      <c r="B36" s="32" t="n">
         <v>100000</v>
       </c>
-      <c r="C36" s="19">
+      <c r="C36" s="20">
         <f>$B36/C$31</f>
         <v/>
       </c>
-      <c r="D36" s="19">
+      <c r="D36" s="20">
         <f>$B36/D$31</f>
         <v/>
       </c>
-      <c r="E36" s="19">
+      <c r="E36" s="20">
         <f>$B36/E$31</f>
         <v/>
       </c>
-      <c r="F36" s="19">
+      <c r="F36" s="20">
         <f>$B36/F$31</f>
         <v/>
       </c>
-      <c r="G36" s="19">
+      <c r="G36" s="20">
         <f>$B36/G$31</f>
         <v/>
       </c>
@@ -9547,51 +9872,51 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="34">
+      <c r="B38" s="35">
         <f>$B32</f>
         <v/>
       </c>
-      <c r="C38" s="21">
+      <c r="C38" s="22">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B32/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="34">
+      <c r="B39" s="35">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="21">
+      <c r="C39" s="22">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B33/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="34">
+      <c r="B40" s="35">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="21">
+      <c r="C40" s="22">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B34/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="34">
+      <c r="B41" s="35">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="21">
+      <c r="C41" s="22">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B35/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="34">
+      <c r="B42" s="35">
         <f>$B36</f>
         <v/>
       </c>
-      <c r="C42" s="21">
+      <c r="C42" s="22">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B36/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -9604,19 +9929,19 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="35" t="n">
+      <c r="C45" s="36" t="n">
         <v>1.5</v>
       </c>
-      <c r="D45" s="35" t="n">
+      <c r="D45" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="35" t="n">
+      <c r="E45" s="36" t="n">
         <v>2.5</v>
       </c>
-      <c r="F45" s="35" t="n">
+      <c r="F45" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="35" t="n">
+      <c r="G45" s="36" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9696,15 +10021,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C53" s="19">
+      <c r="C53" s="20">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D53" s="26">
+      <c r="D53" s="27">
         <f>IF(C53=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C53-'Supuestos'!$C$8))/C53)</f>
         <v/>
       </c>
-      <c r="E53" s="19">
+      <c r="E53" s="20">
         <f>C53*(D53-1)</f>
         <v/>
       </c>
@@ -9715,15 +10040,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C54" s="19">
+      <c r="C54" s="20">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D54" s="26">
+      <c r="D54" s="27">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="19">
+      <c r="E54" s="20">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -9734,15 +10059,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C55" s="19">
+      <c r="C55" s="20">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D55" s="26">
+      <c r="D55" s="27">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="19">
+      <c r="E55" s="20">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -9753,15 +10078,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C56" s="19">
+      <c r="C56" s="20">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D56" s="26">
+      <c r="D56" s="27">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="19">
+      <c r="E56" s="20">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -9772,15 +10097,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C57" s="19">
+      <c r="C57" s="20">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D57" s="26">
+      <c r="D57" s="27">
         <f>IF(C57=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C57-'Supuestos'!$C$8))/C57)</f>
         <v/>
       </c>
-      <c r="E57" s="19">
+      <c r="E57" s="20">
         <f>C57*(D57-1)</f>
         <v/>
       </c>
@@ -9915,19 +10240,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="20">
         <f>((((((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="19">
+      <c r="E7" s="20">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="24">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>RANK(E7,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -9943,19 +10268,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="19">
+      <c r="D8" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="20">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <f>RANK(E8,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -9971,19 +10296,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="24">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="22">
         <f>RANK(E9,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -9999,19 +10324,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$16*1.1))+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="24">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="22">
         <f>RANK(E10,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10027,19 +10352,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$18*1.1))*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="24">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="22">
         <f>RANK(E11,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10055,19 +10380,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$22*1.1))*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="24">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <f>RANK(E12,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10083,19 +10408,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$30*1.1))*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="24">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="22">
         <f>RANK(E13,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10111,19 +10436,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D14" s="19">
+      <c r="D14" s="20">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-('Supuestos'!$C$35*0.9)))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="19">
+      <c r="E14" s="20">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="24">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="22">
         <f>RANK(E14,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10266,51 +10591,51 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <f>'Supuestos'!$C$8*1</f>
         <v/>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <f>C6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="20">
         <f>D6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="F6" s="19">
+      <c r="F6" s="20">
         <f>E6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="20">
         <f>F6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="H6" s="19">
+      <c r="H6" s="20">
         <f>G6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="20">
         <f>H6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="20">
         <f>I6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="K6" s="19">
+      <c r="K6" s="20">
         <f>J6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="20">
         <f>K6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="M6" s="19">
+      <c r="M6" s="20">
         <f>L6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="N6" s="19">
+      <c r="N6" s="20">
         <f>M6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
@@ -10325,55 +10650,55 @@
           <t>Visitas compradas</t>
         </is>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="22">
         <f>IF('Modelo'!$C$7=0,0,C6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D7" s="21">
+      <c r="D7" s="22">
         <f>IF('Modelo'!$C$7=0,0,D6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="22">
         <f>IF('Modelo'!$C$7=0,0,E6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="F7" s="21">
+      <c r="F7" s="22">
         <f>IF('Modelo'!$C$7=0,0,F6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="G7" s="21">
+      <c r="G7" s="22">
         <f>IF('Modelo'!$C$7=0,0,G6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="H7" s="21">
+      <c r="H7" s="22">
         <f>IF('Modelo'!$C$7=0,0,H6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I7" s="21">
+      <c r="I7" s="22">
         <f>IF('Modelo'!$C$7=0,0,I6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="J7" s="21">
+      <c r="J7" s="22">
         <f>IF('Modelo'!$C$7=0,0,J6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="K7" s="21">
+      <c r="K7" s="22">
         <f>IF('Modelo'!$C$7=0,0,K6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="L7" s="21">
+      <c r="L7" s="22">
         <f>IF('Modelo'!$C$7=0,0,L6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="M7" s="21">
+      <c r="M7" s="22">
         <f>IF('Modelo'!$C$7=0,0,M6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="N7" s="21">
+      <c r="N7" s="22">
         <f>IF('Modelo'!$C$7=0,0,N6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="O7" s="20">
+      <c r="O7" s="21">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
@@ -10384,51 +10709,51 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="25">
         <f>C7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="25">
         <f>D7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <f>E7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <f>F7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="25">
         <f>G7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="H8" s="24">
+      <c r="H8" s="25">
         <f>H7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="I8" s="24">
+      <c r="I8" s="25">
         <f>I7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="J8" s="24">
+      <c r="J8" s="25">
         <f>J7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="K8" s="24">
+      <c r="K8" s="25">
         <f>K7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="L8" s="24">
+      <c r="L8" s="25">
         <f>L7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="M8" s="24">
+      <c r="M8" s="25">
         <f>M7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="N8" s="24">
+      <c r="N8" s="25">
         <f>N7*'Modelo'!$C$32</f>
         <v/>
       </c>
@@ -10443,51 +10768,51 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="20">
         <f>C7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="D9" s="19">
+      <c r="D9" s="20">
         <f>D7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="E9" s="19">
+      <c r="E9" s="20">
         <f>E7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="F9" s="19">
+      <c r="F9" s="20">
         <f>F7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="G9" s="19">
+      <c r="G9" s="20">
         <f>G7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="H9" s="19">
+      <c r="H9" s="20">
         <f>H7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="I9" s="19">
+      <c r="I9" s="20">
         <f>I7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="J9" s="19">
+      <c r="J9" s="20">
         <f>J7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="K9" s="19">
+      <c r="K9" s="20">
         <f>K7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="L9" s="19">
+      <c r="L9" s="20">
         <f>L7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="M9" s="19">
+      <c r="M9" s="20">
         <f>M7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="N9" s="19">
+      <c r="N9" s="20">
         <f>N7*'Modelo'!$C$33</f>
         <v/>
       </c>
@@ -10502,51 +10827,51 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="20">
         <f>C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D10" s="19">
+      <c r="D10" s="20">
         <f>D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="20">
         <f>E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41+C9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="F10" s="19">
+      <c r="F10" s="20">
         <f>F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41+D9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="G10" s="19">
+      <c r="G10" s="20">
         <f>G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41+E9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="H10" s="19">
+      <c r="H10" s="20">
         <f>H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41+F9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="I10" s="19">
+      <c r="I10" s="20">
         <f>I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41+G9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="J10" s="19">
+      <c r="J10" s="20">
         <f>J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41+H9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="K10" s="19">
+      <c r="K10" s="20">
         <f>K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41+I9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="L10" s="19">
+      <c r="L10" s="20">
         <f>L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41+J9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="M10" s="19">
+      <c r="M10" s="20">
         <f>M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41+K9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="N10" s="19">
+      <c r="N10" s="20">
         <f>N9*'Supuestos'!$C$40+M9*'Supuestos'!$C$41+L9*'Supuestos'!$C$42</f>
         <v/>
       </c>
@@ -10561,51 +10886,51 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="19">
+      <c r="C11" s="20">
         <f>C10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D11" s="19">
+      <c r="D11" s="20">
         <f>D10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="E11" s="19">
+      <c r="E11" s="20">
         <f>E10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="20">
         <f>F10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="G11" s="19">
+      <c r="G11" s="20">
         <f>G10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="H11" s="19">
+      <c r="H11" s="20">
         <f>H10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="I11" s="19">
+      <c r="I11" s="20">
         <f>I10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="20">
         <f>J10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="K11" s="19">
+      <c r="K11" s="20">
         <f>K10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="L11" s="19">
+      <c r="L11" s="20">
         <f>L10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="M11" s="19">
+      <c r="M11" s="20">
         <f>M10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="N11" s="19">
+      <c r="N11" s="20">
         <f>N10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
@@ -10620,51 +10945,51 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <f>C7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D12" s="19">
+      <c r="D12" s="20">
         <f>D7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="20">
         <f>E7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="20">
         <f>F7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="G12" s="19">
+      <c r="G12" s="20">
         <f>G7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="H12" s="19">
+      <c r="H12" s="20">
         <f>H7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="I12" s="19">
+      <c r="I12" s="20">
         <f>I7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="20">
         <f>J7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="K12" s="19">
+      <c r="K12" s="20">
         <f>K7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="L12" s="19">
+      <c r="L12" s="20">
         <f>L7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="M12" s="19">
+      <c r="M12" s="20">
         <f>M7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="N12" s="19">
+      <c r="N12" s="20">
         <f>N7*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -10679,51 +11004,51 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="E13" s="19">
+      <c r="E13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="G13" s="19">
+      <c r="G13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="H13" s="19">
+      <c r="H13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="I13" s="19">
+      <c r="I13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="K13" s="19">
+      <c r="K13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="M13" s="19">
+      <c r="M13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="N13" s="19">
+      <c r="N13" s="20">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
@@ -10852,51 +11177,51 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="19">
+      <c r="C16" s="20">
         <f>'Supuestos'!$C$49+C15</f>
         <v/>
       </c>
-      <c r="D16" s="19">
+      <c r="D16" s="20">
         <f>'Supuestos'!$C$49+D15</f>
         <v/>
       </c>
-      <c r="E16" s="19">
+      <c r="E16" s="20">
         <f>'Supuestos'!$C$49+E15</f>
         <v/>
       </c>
-      <c r="F16" s="19">
+      <c r="F16" s="20">
         <f>'Supuestos'!$C$49+F15</f>
         <v/>
       </c>
-      <c r="G16" s="19">
+      <c r="G16" s="20">
         <f>'Supuestos'!$C$49+G15</f>
         <v/>
       </c>
-      <c r="H16" s="19">
+      <c r="H16" s="20">
         <f>'Supuestos'!$C$49+H15</f>
         <v/>
       </c>
-      <c r="I16" s="19">
+      <c r="I16" s="20">
         <f>'Supuestos'!$C$49+I15</f>
         <v/>
       </c>
-      <c r="J16" s="19">
+      <c r="J16" s="20">
         <f>'Supuestos'!$C$49+J15</f>
         <v/>
       </c>
-      <c r="K16" s="19">
+      <c r="K16" s="20">
         <f>'Supuestos'!$C$49+K15</f>
         <v/>
       </c>
-      <c r="L16" s="19">
+      <c r="L16" s="20">
         <f>'Supuestos'!$C$49+L15</f>
         <v/>
       </c>
-      <c r="M16" s="19">
+      <c r="M16" s="20">
         <f>'Supuestos'!$C$49+M15</f>
         <v/>
       </c>
-      <c r="N16" s="19">
+      <c r="N16" s="20">
         <f>'Supuestos'!$C$49+N15</f>
         <v/>
       </c>

--- a/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
+++ b/excel/01_Modelo_Financiero_Embudo_Low_Ticket_Bumps_Upsells.xlsx
@@ -9,18 +9,17 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inicio" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simulador" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embudo" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyección 12 meses" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Embudo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supuestos" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modelo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Escenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensibilidad" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proyección 12 meses" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Seguimiento" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Glosario" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chequeos" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Licencia" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="Autor_Jesus_Tassarolo">"Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro"</definedName>
@@ -177,33 +176,33 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -222,13 +221,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00F8CBAD"/>
         </patternFill>
       </fill>
     </dxf>
@@ -667,7 +659,7 @@
     <row r="12" ht="45" customHeight="1">
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>3. Abrí Simulador para jugar: cada supuesto está en orden de embudo (inversión, CPM, CTR, visitas, conversión de la landing, asistencia, solicitudes, cierre, precios, costos) con tu número en amarillo al lado de la base. Cambiá uno y mirá cómo se mueven todos los demás contra la base; la columna Diferencia te dice cuánto. No toca Supuestos.</t>
+          <t>3. Para jugar con los números, usá el Excel de Simulación de este embudo (archivo aparte): es esta misma cadena, idéntica a la hoja Modelo, con todos los supuestos editables en su lugar. Cambiá uno y se recalcula todo. No se conecta con este archivo: cuando una prueba te convence, pasá ese número a Supuestos.</t>
         </is>
       </c>
     </row>
@@ -716,7 +708,7 @@
     <row r="20" ht="45" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Resumen, Embudo y Modelo leen de Supuestos. Simulador es la mesa de pruebas: copia Supuestos en orden de embudo y vos escribís encima. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
+          <t>Resumen, Embudo y Modelo leen de Supuestos. Escenarios y Sensibilidad recalculan el modelo entero cambiando una o dos variables. Proyección usa los mismos supuestos mes a mes. Seguimiento es la única hoja, además de Supuestos, donde cargás datos.</t>
         </is>
       </c>
     </row>
@@ -895,1391 +887,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="13" customWidth="1" min="14" max="14"/>
-    <col width="13" customWidth="1" min="15" max="15"/>
-    <col width="13" customWidth="1" min="16" max="16"/>
-    <col width="13" customWidth="1" min="17" max="17"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Seguimiento: una columna por mes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por visita con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 1</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 2</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 3</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 4</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 5</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 6</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 7</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 8</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 9</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 10</t>
-        </is>
-      </c>
-      <c r="M5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 11</t>
-        </is>
-      </c>
-      <c r="N5" s="6" t="inlineStr">
-        <is>
-          <t>Mes 12</t>
-        </is>
-      </c>
-      <c r="O5" s="6" t="inlineStr">
-        <is>
-          <t>Promedio</t>
-        </is>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>Máximo</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>Mínimo</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Datos que cargás</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-      <c r="I6" s="8" t="n"/>
-      <c r="J6" s="8" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="8" t="n"/>
-      <c r="M6" s="8" t="n"/>
-      <c r="N6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Inversión en publicidad</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>9000</v>
-      </c>
-      <c r="D7" s="19" t="n">
-        <v>9500</v>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>10500</v>
-      </c>
-      <c r="F7" s="19" t="n"/>
-      <c r="G7" s="19" t="n"/>
-      <c r="H7" s="19" t="n"/>
-      <c r="I7" s="19" t="n"/>
-      <c r="J7" s="19" t="n"/>
-      <c r="K7" s="19" t="n"/>
-      <c r="L7" s="19" t="n"/>
-      <c r="M7" s="19" t="n"/>
-      <c r="N7" s="19" t="n"/>
-      <c r="O7" s="20">
-        <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
-        <v/>
-      </c>
-      <c r="P7" s="20">
-        <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
-        <v/>
-      </c>
-      <c r="Q7" s="20">
-        <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Visitas a la página</t>
-        </is>
-      </c>
-      <c r="C8" s="30" t="n">
-        <v>30000</v>
-      </c>
-      <c r="D8" s="30" t="n">
-        <v>30200</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>29000</v>
-      </c>
-      <c r="F8" s="30" t="n"/>
-      <c r="G8" s="30" t="n"/>
-      <c r="H8" s="30" t="n"/>
-      <c r="I8" s="30" t="n"/>
-      <c r="J8" s="30" t="n"/>
-      <c r="K8" s="30" t="n"/>
-      <c r="L8" s="30" t="n"/>
-      <c r="M8" s="30" t="n"/>
-      <c r="N8" s="30" t="n"/>
-      <c r="O8" s="22">
-        <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
-        <v/>
-      </c>
-      <c r="P8" s="22">
-        <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
-        <v/>
-      </c>
-      <c r="Q8" s="22">
-        <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Checkouts iniciados</t>
-        </is>
-      </c>
-      <c r="C9" s="30" t="n">
-        <v>1050</v>
-      </c>
-      <c r="D9" s="30" t="n">
-        <v>1030</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>980</v>
-      </c>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="30" t="n"/>
-      <c r="H9" s="30" t="n"/>
-      <c r="I9" s="30" t="n"/>
-      <c r="J9" s="30" t="n"/>
-      <c r="K9" s="30" t="n"/>
-      <c r="L9" s="30" t="n"/>
-      <c r="M9" s="30" t="n"/>
-      <c r="N9" s="30" t="n"/>
-      <c r="O9" s="22">
-        <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
-        <v/>
-      </c>
-      <c r="P9" s="22">
-        <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
-        <v/>
-      </c>
-      <c r="Q9" s="22">
-        <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Ventas del producto principal</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="n">
-        <v>273</v>
-      </c>
-      <c r="D10" s="30" t="n">
-        <v>262</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>240</v>
-      </c>
-      <c r="F10" s="30" t="n"/>
-      <c r="G10" s="30" t="n"/>
-      <c r="H10" s="30" t="n"/>
-      <c r="I10" s="30" t="n"/>
-      <c r="J10" s="30" t="n"/>
-      <c r="K10" s="30" t="n"/>
-      <c r="L10" s="30" t="n"/>
-      <c r="M10" s="30" t="n"/>
-      <c r="N10" s="30" t="n"/>
-      <c r="O10" s="22">
-        <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
-        <v/>
-      </c>
-      <c r="P10" s="22">
-        <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
-        <v/>
-      </c>
-      <c r="Q10" s="22">
-        <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Ventas de bumps (1 + 2)</t>
-        </is>
-      </c>
-      <c r="C11" s="30" t="n">
-        <v>117</v>
-      </c>
-      <c r="D11" s="30" t="n">
-        <v>110</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>95</v>
-      </c>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
-      <c r="H11" s="30" t="n"/>
-      <c r="I11" s="30" t="n"/>
-      <c r="J11" s="30" t="n"/>
-      <c r="K11" s="30" t="n"/>
-      <c r="L11" s="30" t="n"/>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="22">
-        <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
-        <v/>
-      </c>
-      <c r="P11" s="22">
-        <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
-        <v/>
-      </c>
-      <c r="Q11" s="22">
-        <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Ventas de OTOs (1 a 4)</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="n">
-        <v>63</v>
-      </c>
-      <c r="D12" s="30" t="n">
-        <v>58</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>52</v>
-      </c>
-      <c r="F12" s="30" t="n"/>
-      <c r="G12" s="30" t="n"/>
-      <c r="H12" s="30" t="n"/>
-      <c r="I12" s="30" t="n"/>
-      <c r="J12" s="30" t="n"/>
-      <c r="K12" s="30" t="n"/>
-      <c r="L12" s="30" t="n"/>
-      <c r="M12" s="30" t="n"/>
-      <c r="N12" s="30" t="n"/>
-      <c r="O12" s="22">
-        <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
-        <v/>
-      </c>
-      <c r="P12" s="22">
-        <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
-        <v/>
-      </c>
-      <c r="Q12" s="22">
-        <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Ventas de la ascensión (programa)</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="30" t="n">
-        <v>6</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
-      <c r="H13" s="30" t="n"/>
-      <c r="I13" s="30" t="n"/>
-      <c r="J13" s="30" t="n"/>
-      <c r="K13" s="30" t="n"/>
-      <c r="L13" s="30" t="n"/>
-      <c r="M13" s="30" t="n"/>
-      <c r="N13" s="30" t="n"/>
-      <c r="O13" s="22">
-        <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
-        <v/>
-      </c>
-      <c r="P13" s="22">
-        <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
-        <v/>
-      </c>
-      <c r="Q13" s="22">
-        <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Facturado del mes (a precio de lista)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="n">
-        <v>15900</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <v>15400</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>13700</v>
-      </c>
-      <c r="F14" s="19" t="n"/>
-      <c r="G14" s="19" t="n"/>
-      <c r="H14" s="19" t="n"/>
-      <c r="I14" s="19" t="n"/>
-      <c r="J14" s="19" t="n"/>
-      <c r="K14" s="19" t="n"/>
-      <c r="L14" s="19" t="n"/>
-      <c r="M14" s="19" t="n"/>
-      <c r="N14" s="19" t="n"/>
-      <c r="O14" s="20">
-        <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
-        <v/>
-      </c>
-      <c r="P14" s="20">
-        <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
-        <v/>
-      </c>
-      <c r="Q14" s="20">
-        <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Cash cobrado en el mes</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>15900</v>
-      </c>
-      <c r="D15" s="19" t="n">
-        <v>15400</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>13700</v>
-      </c>
-      <c r="F15" s="19" t="n"/>
-      <c r="G15" s="19" t="n"/>
-      <c r="H15" s="19" t="n"/>
-      <c r="I15" s="19" t="n"/>
-      <c r="J15" s="19" t="n"/>
-      <c r="K15" s="19" t="n"/>
-      <c r="L15" s="19" t="n"/>
-      <c r="M15" s="19" t="n"/>
-      <c r="N15" s="19" t="n"/>
-      <c r="O15" s="20">
-        <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
-        <v/>
-      </c>
-      <c r="P15" s="20">
-        <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
-        <v/>
-      </c>
-      <c r="Q15" s="20">
-        <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Lo que calcula el modelo</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
-      <c r="E16" s="8" t="n"/>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Costo por visita real</t>
-        </is>
-      </c>
-      <c r="C17" s="12">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C7/C8))</f>
-        <v/>
-      </c>
-      <c r="D17" s="12">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D7/D8))</f>
-        <v/>
-      </c>
-      <c r="E17" s="12">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E7/E8))</f>
-        <v/>
-      </c>
-      <c r="F17" s="12">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F7/F8))</f>
-        <v/>
-      </c>
-      <c r="G17" s="12">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G7/G8))</f>
-        <v/>
-      </c>
-      <c r="H17" s="12">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H7/H8))</f>
-        <v/>
-      </c>
-      <c r="I17" s="12">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I7/I8))</f>
-        <v/>
-      </c>
-      <c r="J17" s="12">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J7/J8))</f>
-        <v/>
-      </c>
-      <c r="K17" s="12">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K7/K8))</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L7/L8))</f>
-        <v/>
-      </c>
-      <c r="M17" s="12">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M7/M8))</f>
-        <v/>
-      </c>
-      <c r="N17" s="12">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N7/N8))</f>
-        <v/>
-      </c>
-      <c r="O17" s="17">
-        <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
-        <v/>
-      </c>
-      <c r="P17" s="17">
-        <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
-        <v/>
-      </c>
-      <c r="Q17" s="17">
-        <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>% visitas → checkout</t>
-        </is>
-      </c>
-      <c r="C18" s="24">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
-        <v/>
-      </c>
-      <c r="F18" s="24">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
-        <v/>
-      </c>
-      <c r="G18" s="24">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
-        <v/>
-      </c>
-      <c r="H18" s="24">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
-        <v/>
-      </c>
-      <c r="I18" s="24">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
-        <v/>
-      </c>
-      <c r="J18" s="24">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
-        <v/>
-      </c>
-      <c r="K18" s="24">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
-        <v/>
-      </c>
-      <c r="L18" s="24">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
-        <v/>
-      </c>
-      <c r="M18" s="24">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
-        <v/>
-      </c>
-      <c r="N18" s="24">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
-        <v/>
-      </c>
-      <c r="O18" s="24">
-        <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
-        <v/>
-      </c>
-      <c r="P18" s="24">
-        <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
-        <v/>
-      </c>
-      <c r="Q18" s="24">
-        <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>% checkout → compra</t>
-        </is>
-      </c>
-      <c r="C19" s="24">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
-        <v/>
-      </c>
-      <c r="F19" s="24">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
-        <v/>
-      </c>
-      <c r="G19" s="24">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
-        <v/>
-      </c>
-      <c r="H19" s="24">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
-        <v/>
-      </c>
-      <c r="I19" s="24">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
-        <v/>
-      </c>
-      <c r="J19" s="24">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
-        <v/>
-      </c>
-      <c r="K19" s="24">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
-        <v/>
-      </c>
-      <c r="L19" s="24">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
-        <v/>
-      </c>
-      <c r="M19" s="24">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
-        <v/>
-      </c>
-      <c r="N19" s="24">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
-        <v/>
-      </c>
-      <c r="O19" s="24">
-        <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
-        <v/>
-      </c>
-      <c r="P19" s="24">
-        <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
-        <v/>
-      </c>
-      <c r="Q19" s="24">
-        <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CPA real</t>
-        </is>
-      </c>
-      <c r="C20" s="17">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C7/C10))</f>
-        <v/>
-      </c>
-      <c r="D20" s="17">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D7/D10))</f>
-        <v/>
-      </c>
-      <c r="E20" s="17">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E7/E10))</f>
-        <v/>
-      </c>
-      <c r="F20" s="17">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F7/F10))</f>
-        <v/>
-      </c>
-      <c r="G20" s="17">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G7/G10))</f>
-        <v/>
-      </c>
-      <c r="H20" s="17">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H7/H10))</f>
-        <v/>
-      </c>
-      <c r="I20" s="17">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I7/I10))</f>
-        <v/>
-      </c>
-      <c r="J20" s="17">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J7/J10))</f>
-        <v/>
-      </c>
-      <c r="K20" s="17">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K7/K10))</f>
-        <v/>
-      </c>
-      <c r="L20" s="17">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L7/L10))</f>
-        <v/>
-      </c>
-      <c r="M20" s="17">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M7/M10))</f>
-        <v/>
-      </c>
-      <c r="N20" s="17">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N7/N10))</f>
-        <v/>
-      </c>
-      <c r="O20" s="17">
-        <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
-        <v/>
-      </c>
-      <c r="P20" s="17">
-        <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
-        <v/>
-      </c>
-      <c r="Q20" s="17">
-        <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Cash por comprador</t>
-        </is>
-      </c>
-      <c r="C21" s="17">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C15/C10))</f>
-        <v/>
-      </c>
-      <c r="D21" s="17">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D15/D10))</f>
-        <v/>
-      </c>
-      <c r="E21" s="17">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E15/E10))</f>
-        <v/>
-      </c>
-      <c r="F21" s="17">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F15/F10))</f>
-        <v/>
-      </c>
-      <c r="G21" s="17">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G15/G10))</f>
-        <v/>
-      </c>
-      <c r="H21" s="17">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H15/H10))</f>
-        <v/>
-      </c>
-      <c r="I21" s="17">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I15/I10))</f>
-        <v/>
-      </c>
-      <c r="J21" s="17">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J15/J10))</f>
-        <v/>
-      </c>
-      <c r="K21" s="17">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K15/K10))</f>
-        <v/>
-      </c>
-      <c r="L21" s="17">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L15/L10))</f>
-        <v/>
-      </c>
-      <c r="M21" s="17">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M15/M10))</f>
-        <v/>
-      </c>
-      <c r="N21" s="17">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N15/N10))</f>
-        <v/>
-      </c>
-      <c r="O21" s="17">
-        <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
-        <v/>
-      </c>
-      <c r="P21" s="17">
-        <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
-        <v/>
-      </c>
-      <c r="Q21" s="17">
-        <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
-        </is>
-      </c>
-      <c r="C22" s="12">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36)/C8))</f>
-        <v/>
-      </c>
-      <c r="D22" s="12">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36)/D8))</f>
-        <v/>
-      </c>
-      <c r="E22" s="12">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36)/E8))</f>
-        <v/>
-      </c>
-      <c r="F22" s="12">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36)/F8))</f>
-        <v/>
-      </c>
-      <c r="G22" s="12">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36)/G8))</f>
-        <v/>
-      </c>
-      <c r="H22" s="12">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36)/H8))</f>
-        <v/>
-      </c>
-      <c r="I22" s="12">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36)/I8))</f>
-        <v/>
-      </c>
-      <c r="J22" s="12">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36)/J8))</f>
-        <v/>
-      </c>
-      <c r="K22" s="12">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36)/K8))</f>
-        <v/>
-      </c>
-      <c r="L22" s="12">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36)/L8))</f>
-        <v/>
-      </c>
-      <c r="M22" s="12">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36)/M8))</f>
-        <v/>
-      </c>
-      <c r="N22" s="12">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
-        <v/>
-      </c>
-      <c r="O22" s="17">
-        <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
-        <v/>
-      </c>
-      <c r="P22" s="17">
-        <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
-        <v/>
-      </c>
-      <c r="Q22" s="17">
-        <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia del período al completar la cobranza</t>
-        </is>
-      </c>
-      <c r="C23" s="9">
-        <f>IF(COUNT(C7:C15)&lt;9,"",C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
-        <v/>
-      </c>
-      <c r="D23" s="9">
-        <f>IF(COUNT(D7:D15)&lt;9,"",D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
-        <v/>
-      </c>
-      <c r="E23" s="9">
-        <f>IF(COUNT(E7:E15)&lt;9,"",E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
-        <v/>
-      </c>
-      <c r="F23" s="9">
-        <f>IF(COUNT(F7:F15)&lt;9,"",F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
-        <v/>
-      </c>
-      <c r="G23" s="9">
-        <f>IF(COUNT(G7:G15)&lt;9,"",G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
-        <v/>
-      </c>
-      <c r="H23" s="9">
-        <f>IF(COUNT(H7:H15)&lt;9,"",H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
-        <v/>
-      </c>
-      <c r="I23" s="9">
-        <f>IF(COUNT(I7:I15)&lt;9,"",I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
-        <v/>
-      </c>
-      <c r="J23" s="9">
-        <f>IF(COUNT(J7:J15)&lt;9,"",J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
-        <v/>
-      </c>
-      <c r="K23" s="9">
-        <f>IF(COUNT(K7:K15)&lt;9,"",K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
-        <v/>
-      </c>
-      <c r="L23" s="9">
-        <f>IF(COUNT(L7:L15)&lt;9,"",L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
-        <v/>
-      </c>
-      <c r="M23" s="9">
-        <f>IF(COUNT(M7:M15)&lt;9,"",M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
-        <v/>
-      </c>
-      <c r="N23" s="9">
-        <f>IF(COUNT(N7:N15)&lt;9,"",N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
-        <v/>
-      </c>
-      <c r="O23" s="20">
-        <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
-        <v/>
-      </c>
-      <c r="P23" s="20">
-        <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
-        <v/>
-      </c>
-      <c r="Q23" s="20">
-        <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
-        </is>
-      </c>
-      <c r="C24" s="20">
-        <f>IF(COUNT(C7:C15)&lt;9,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
-        <v/>
-      </c>
-      <c r="D24" s="20">
-        <f>IF(COUNT(D7:D15)&lt;9,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
-        <v/>
-      </c>
-      <c r="E24" s="20">
-        <f>IF(COUNT(E7:E15)&lt;9,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f>IF(COUNT(F7:F15)&lt;9,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
-        <v/>
-      </c>
-      <c r="G24" s="20">
-        <f>IF(COUNT(G7:G15)&lt;9,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
-        <v/>
-      </c>
-      <c r="H24" s="20">
-        <f>IF(COUNT(H7:H15)&lt;9,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
-        <v/>
-      </c>
-      <c r="I24" s="20">
-        <f>IF(COUNT(I7:I15)&lt;9,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
-        <v/>
-      </c>
-      <c r="J24" s="20">
-        <f>IF(COUNT(J7:J15)&lt;9,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
-        <v/>
-      </c>
-      <c r="K24" s="20">
-        <f>IF(COUNT(K7:K15)&lt;9,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
-        <v/>
-      </c>
-      <c r="L24" s="20">
-        <f>IF(COUNT(L7:L15)&lt;9,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
-        <v/>
-      </c>
-      <c r="M24" s="20">
-        <f>IF(COUNT(M7:M15)&lt;9,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
-        <v/>
-      </c>
-      <c r="N24" s="20">
-        <f>IF(COUNT(N7:N15)&lt;9,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
-        <v/>
-      </c>
-      <c r="O24" s="20">
-        <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
-        <v/>
-      </c>
-      <c r="P24" s="20">
-        <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
-        <v/>
-      </c>
-      <c r="Q24" s="20">
-        <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
-        </is>
-      </c>
-      <c r="C25" s="12">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)/C8))</f>
-        <v/>
-      </c>
-      <c r="D25" s="12">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)/D8))</f>
-        <v/>
-      </c>
-      <c r="E25" s="12">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)/E8))</f>
-        <v/>
-      </c>
-      <c r="F25" s="12">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)/F8))</f>
-        <v/>
-      </c>
-      <c r="G25" s="12">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)/G8))</f>
-        <v/>
-      </c>
-      <c r="H25" s="12">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)/H8))</f>
-        <v/>
-      </c>
-      <c r="I25" s="12">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)/I8))</f>
-        <v/>
-      </c>
-      <c r="J25" s="12">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)/J8))</f>
-        <v/>
-      </c>
-      <c r="K25" s="12">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)/K8))</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)/L8))</f>
-        <v/>
-      </c>
-      <c r="M25" s="12">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)/M8))</f>
-        <v/>
-      </c>
-      <c r="N25" s="12">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
-        <v/>
-      </c>
-      <c r="O25" s="17">
-        <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
-        <v/>
-      </c>
-      <c r="P25" s="17">
-        <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
-        <v/>
-      </c>
-      <c r="Q25" s="17">
-        <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>ROAS sobre cash neto (cobranza completa)</t>
-        </is>
-      </c>
-      <c r="C26" s="10">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
-        <v/>
-      </c>
-      <c r="D26" s="10">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
-        <v/>
-      </c>
-      <c r="E26" s="10">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
-        <v/>
-      </c>
-      <c r="F26" s="10">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
-        <v/>
-      </c>
-      <c r="G26" s="10">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
-        <v/>
-      </c>
-      <c r="H26" s="10">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
-        <v/>
-      </c>
-      <c r="I26" s="10">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
-        <v/>
-      </c>
-      <c r="J26" s="10">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
-        <v/>
-      </c>
-      <c r="K26" s="10">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
-        <v/>
-      </c>
-      <c r="L26" s="10">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
-        <v/>
-      </c>
-      <c r="M26" s="10">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
-        <v/>
-      </c>
-      <c r="N26" s="10">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
-        <v/>
-      </c>
-      <c r="O26" s="27">
-        <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
-        <v/>
-      </c>
-      <c r="P26" s="27">
-        <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
-        <v/>
-      </c>
-      <c r="Q26" s="27">
-        <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>ROAS de caja (cobrado hasta ahora)</t>
-        </is>
-      </c>
-      <c r="C27" s="27">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
-        <v/>
-      </c>
-      <c r="D27" s="27">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
-        <v/>
-      </c>
-      <c r="E27" s="27">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
-        <v/>
-      </c>
-      <c r="F27" s="27">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
-        <v/>
-      </c>
-      <c r="G27" s="27">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
-        <v/>
-      </c>
-      <c r="H27" s="27">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
-        <v/>
-      </c>
-      <c r="I27" s="27">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
-        <v/>
-      </c>
-      <c r="J27" s="27">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
-        <v/>
-      </c>
-      <c r="K27" s="27">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
-        <v/>
-      </c>
-      <c r="L27" s="27">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
-        <v/>
-      </c>
-      <c r="M27" s="27">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
-        <v/>
-      </c>
-      <c r="N27" s="27">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
-        <v/>
-      </c>
-      <c r="O27" s="27">
-        <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
-        <v/>
-      </c>
-      <c r="P27" s="27">
-        <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
-        <v/>
-      </c>
-      <c r="Q27" s="27">
-        <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
-        </is>
-      </c>
-      <c r="C28" s="17">
-        <f>IF(COUNT(C7:C15)&lt;9,"",'Modelo'!$C$48)</f>
-        <v/>
-      </c>
-      <c r="D28" s="17">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(COUNT(C22:C22)&gt;0,MEDIAN(C22:C22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="E28" s="17">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(COUNT(C22:D22)&gt;0,MEDIAN(C22:D22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="F28" s="17">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(COUNT(C22:E22)&gt;0,MEDIAN(C22:E22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="G28" s="17">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(COUNT(C22:F22)&gt;0,MEDIAN(C22:F22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="H28" s="17">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(COUNT(D22:G22)&gt;0,MEDIAN(D22:G22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="I28" s="17">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(COUNT(E22:H22)&gt;0,MEDIAN(E22:H22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="J28" s="17">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(COUNT(F22:I22)&gt;0,MEDIAN(F22:I22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="K28" s="17">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(COUNT(G22:J22)&gt;0,MEDIAN(G22:J22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="L28" s="17">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(COUNT(H22:K22)&gt;0,MEDIAN(H22:K22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="M28" s="17">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(COUNT(I22:L22)&gt;0,MEDIAN(I22:L22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="N28" s="17">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(COUNT(J22:M22)&gt;0,MEDIAN(J22:M22),'Modelo'!$C$48))</f>
-        <v/>
-      </c>
-      <c r="O28" s="17">
-        <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
-        <v/>
-      </c>
-      <c r="P28" s="17">
-        <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
-        <v/>
-      </c>
-      <c r="Q28" s="17">
-        <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
-        </is>
-      </c>
-      <c r="C29" s="13">
-        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C17&gt;C28,"ROJO",IF(AND(C17&lt;=C28/(1+'Supuestos'!$C$46),C26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="D29" s="13">
-        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D17&gt;D28,"ROJO",IF(AND(D17&lt;=D28/(1+'Supuestos'!$C$46),D26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="E29" s="13">
-        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E17&gt;E28,"ROJO",IF(AND(E17&lt;=E28/(1+'Supuestos'!$C$46),E26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="F29" s="13">
-        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F17&gt;F28,"ROJO",IF(AND(F17&lt;=F28/(1+'Supuestos'!$C$46),F26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="G29" s="13">
-        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G17&gt;G28,"ROJO",IF(AND(G17&lt;=G28/(1+'Supuestos'!$C$46),G26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="H29" s="13">
-        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H17&gt;H28,"ROJO",IF(AND(H17&lt;=H28/(1+'Supuestos'!$C$46),H26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="I29" s="13">
-        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I17&gt;I28,"ROJO",IF(AND(I17&lt;=I28/(1+'Supuestos'!$C$46),I26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="J29" s="13">
-        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J17&gt;J28,"ROJO",IF(AND(J17&lt;=J28/(1+'Supuestos'!$C$46),J26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="K29" s="13">
-        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K17&gt;K28,"ROJO",IF(AND(K17&lt;=K28/(1+'Supuestos'!$C$46),K26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="L29" s="13">
-        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L17&gt;L28,"ROJO",IF(AND(L17&lt;=L28/(1+'Supuestos'!$C$46),L26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="M29" s="13">
-        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M17&gt;M28,"ROJO",IF(AND(M17&lt;=M28/(1+'Supuestos'!$C$46),M26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-      <c r="N29" s="13">
-        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N17&gt;N28,"ROJO",IF(AND(N17&lt;=N28/(1+'Supuestos'!$C$46),N26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="C5:N30">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>LEFT(C5,5)="VERDE"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="2" dxfId="1">
-      <formula>LEFT(C5,8)="AMARILLO"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>LEFT(C5,4)="ROJO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
-    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
-    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
-    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2382,7 +989,7 @@
           <t>&lt;0,20</t>
         </is>
       </c>
-      <c r="G6" s="17">
+      <c r="G6" s="19">
         <f>'Modelo'!$C$7</f>
         <v/>
       </c>
@@ -2418,7 +1025,7 @@
           <t>&gt;5 %</t>
         </is>
       </c>
-      <c r="G7" s="24">
+      <c r="G7" s="18">
         <f>'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -2454,7 +1061,7 @@
           <t>&gt;30 %</t>
         </is>
       </c>
-      <c r="G8" s="24">
+      <c r="G8" s="18">
         <f>'Supuestos'!$C$13</f>
         <v/>
       </c>
@@ -2490,7 +1097,7 @@
           <t>&gt;1,5 %</t>
         </is>
       </c>
-      <c r="G9" s="26">
+      <c r="G9" s="17">
         <f>'Modelo'!$C$11</f>
         <v/>
       </c>
@@ -2526,7 +1133,7 @@
           <t>&gt;35 %</t>
         </is>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="18">
         <f>'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -2562,7 +1169,7 @@
           <t>&gt;14 %</t>
         </is>
       </c>
-      <c r="G11" s="24">
+      <c r="G11" s="18">
         <f>'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -2598,7 +1205,7 @@
           <t>&gt;4 %</t>
         </is>
       </c>
-      <c r="G12" s="24">
+      <c r="G12" s="18">
         <f>'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -2634,7 +1241,7 @@
           <t>&gt;1,7</t>
         </is>
       </c>
-      <c r="G13" s="27">
+      <c r="G13" s="28">
         <f>'Modelo'!$C$31</f>
         <v/>
       </c>
@@ -2670,7 +1277,7 @@
           <t>&gt;2,5</t>
         </is>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="28">
         <f>'Modelo'!$C$43</f>
         <v/>
       </c>
@@ -2706,13 +1313,691 @@
           <t>&lt;4 %</t>
         </is>
       </c>
-      <c r="G15" s="24">
+      <c r="G15" s="18">
         <f>'Supuestos'!$C$35</f>
         <v/>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
           <t>Más de 10 % es un problema de oferta.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Glosario</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Los términos que usa este modelo, en el orden del embudo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Término</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Qué es</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Dónde aparece</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>CPM</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>CTR</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Clic → visita</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Unidad de adquisición</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Costo por unidad</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Modelo, Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Conversión</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Supuestos, Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Show rate</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>OTO / upsell</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>AOV</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>CPA / CAC</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Facturado</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Cash cobrado</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Modelo, Proyección</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Cash neto</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ROAS</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Valor neto por unidad (VPU)</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Techo</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Modelo, Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1">
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Margen de seguridad</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Semáforo</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Resumen, Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Techo móvil</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Seguimiento</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Escenario</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Sensibilidad</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Sensibilidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia por visita / por lead / por cliente</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Modelo, Embudo</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Order value (AOV)</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Modelo</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Caja necesaria</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Proyección</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Unit economics</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Resumen</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Tráfico frío</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Front / producto principal</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Pitch</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Inicio</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1">
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>VSL</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="30" customHeight="1">
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>B2B</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Benchmarks</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1">
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Self-serve</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>OTO 1 a 4</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>La secuencia de hasta cuatro páginas después del pago: upsell, downsell, upsell, downsell. Cada una se mide como % de los compradores del principal.</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Ascensión</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>El upsell de mayor valor que se ofrece después del embudo (un programa de 300 a 1.000 USD), por checkout o por llamada.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Supuestos</t>
         </is>
       </c>
     </row>
@@ -2735,685 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Glosario</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Los términos que usa este modelo, en el orden del embudo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Término</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Qué es</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Dónde aparece</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>CPM</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Costo por mil impresiones: lo que cobra la plataforma de anuncios por mostrar el aviso mil veces.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>CTR</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje de impresiones que terminan en clic al enlace.</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Clic → visita</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje de clics que llegan a cargar la página. Siempre menor a 100 % (cierran antes de que cargue).</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Unidad de adquisición</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Lo que compra la publicidad en este embudo (visita, registro o entrada). Todo el modelo se mide por unidad.</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Costo por unidad</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Inversión dividida por unidades compradas: costo por visita, CPL (costo por lead o registro) o costo por entrada.</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Modelo, Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Conversión</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje que pasa de una etapa a la siguiente. Las conversiones se multiplican: 15 % × 14 % × 44 % = 0,9 %.</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Supuestos, Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Show rate</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Porcentaje de registrados (o compradores) que asisten en vivo. El replay se cuenta aparte.</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Oferta extra en el mismo checkout, con una casilla. Se mide como % de los compradores.</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>OTO / upsell</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Oferta que aparece después de pagar (one-time offer). Downsell: la oferta más barata para quien rechaza la OTO.</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Backend</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>Producto de mayor valor que se vende después del primero, por ascenso o por llamada.</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>AOV</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>Facturado promedio por comprador del producto principal, sumando toda la escalera.</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>CPA / CAC</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Costo por comprador: inversión dividida por ventas del producto principal.</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Facturado</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>Lo vendido a precio de lista, aunque todavía no se haya cobrado (cuotas).</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Cash cobrado</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Lo que efectivamente entró. Con cuotas, entra en varios meses según la curva de cobranza.</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Modelo, Proyección</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Cash neto</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>Cash cobrado menos comisiones de pasarela, comisiones de ventas y reembolsos. Es la base de verdad del modelo.</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>ROAS</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Retorno sobre la inversión en publicidad. Sobre facturado, sobre cash o sobre cash neto: siempre decí cuál.</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Valor neto por unidad (VPU)</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Cash neto que deja cada unidad de adquisición, descontando los costos que crecen con el volumen. Es lo que vale un lead, una visita o una entrada.</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Techo</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Costo por unidad al que no ganás ni perdés (break-even). Es igual al valor neto por unidad.</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Modelo, Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Objetivo</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>Techo dividido por (1 + margen de seguridad). Si pagás eso o menos, estás en verde.</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Margen de seguridad</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Colchón entre el techo y el objetivo para absorber varianza, reembolsos y costos que no viste. 30 % es el estándar.</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Semáforo</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Rojo: el costo por unidad está por encima del techo (perdés con cada unidad). Verde: el costo está en el objetivo o por debajo y el ROAS sobre cash neto llega al objetivo. Amarillo: todo lo demás (el costo está entre objetivo y techo, o el ROAS no llega).</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Resumen, Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Techo móvil</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Mediana del valor neto por unidad de tus últimas 4 columnas de Seguimiento. Es el techo que se usa para decidir, porque refleja tu rendimiento reciente.</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Seguimiento</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Escenario</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Conjunto de supuestos conservador, base u optimista. Se elige con una celda en Supuestos.</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Sensibilidad</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>Cuánto cambia la ganancia si mejorás una sola variable un 10 %. Dice qué palanca trabajar primero.</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Sensibilidad</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="45" customHeight="1">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia por visita / por lead / por cliente</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>La ganancia del período dividida por la cantidad de ese paso. Es la otra cara del costo por paso. La ganancia por visita es la métrica que más vale: resume todo lo que pasa después de la página.</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Modelo, Embudo</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="30" customHeight="1">
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Order value (AOV)</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>Facturado promedio por comprador del principal sumando toda la escalera. El AOV neto es lo mismo después de comisiones y reembolsos, y su par es el CPA.</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Modelo</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Caja necesaria</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="inlineStr">
-        <is>
-          <t>El peor momento de la ganancia acumulada en la proyección, en positivo. Es la plata que necesitás tener para no frenar la pauta mientras cobrás. Si da 0, el embudo se autofinancia.</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Proyección</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Unit economics</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>Los números por unidad: cuánto cuesta y cuánto deja cada visita, registro, entrada o comprador.</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Resumen</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Tráfico frío</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="inlineStr">
-        <is>
-          <t>Gente que no te conoce y llega desde un anuncio. Convierte menos que tu audiencia propia.</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Benchmarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Front / producto principal</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
-        <is>
-          <t>El primer producto que se vende en el embudo. Todo lo demás (bumps, OTOs, programa) se mide como % de sus compradores.</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Pitch</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t>La parte del webinar o la llamada donde se presenta la oferta.</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Inicio</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="15" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>VSL</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Video de ventas: la página de ventas es un video largo que vende el producto.</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="30" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>B2B</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="inlineStr">
-        <is>
-          <t>Negocios que venden a empresas. Sus benchmarks de asistencia son más altos que los de tráfico frío a personas.</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Benchmarks</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="15" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Self-serve</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
-        <is>
-          <t>Venta sin llamada: la persona compra sola desde una página de pago.</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>OTO 1 a 4</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>La secuencia de hasta cuatro páginas después del pago: upsell, downsell, upsell, downsell. Cada una se mide como % de los compradores del principal.</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Ascensión</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>El upsell de mayor valor que se ofrece después del embudo (un programa de 300 a 1.000 USD), por checkout o por llamada.</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Supuestos</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
-    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
-    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
-    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -3466,7 +2073,7 @@
           <t>Ninguna celda con error en Modelo</t>
         </is>
       </c>
-      <c r="C6" s="18">
+      <c r="C6" s="36">
         <f>IF(ISERROR(SUM('Modelo'!C5:C160)),"REVISAR","OK")</f>
         <v/>
       </c>
@@ -3479,11 +2086,11 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Simulador</t>
-        </is>
-      </c>
-      <c r="C7" s="18">
-        <f>IF(ISERROR(SUM('Simulador'!C5:G220)),"REVISAR","OK")</f>
+          <t>Ninguna celda con error en Embudo</t>
+        </is>
+      </c>
+      <c r="C7" s="36">
+        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -3495,11 +2102,11 @@
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Embudo</t>
-        </is>
-      </c>
-      <c r="C8" s="18">
-        <f>IF(ISERROR(SUM('Embudo'!C5:H60)),"REVISAR","OK")</f>
+          <t>Ninguna celda con error en Resumen</t>
+        </is>
+      </c>
+      <c r="C8" s="36">
+        <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -3511,11 +2118,11 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Resumen</t>
-        </is>
-      </c>
-      <c r="C9" s="18">
-        <f>IF(ISERROR(SUM('Resumen'!C5:C60)),"REVISAR","OK")</f>
+          <t>Ninguna celda con error en Proyección 12 meses</t>
+        </is>
+      </c>
+      <c r="C9" s="36">
+        <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -3527,11 +2134,11 @@
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Proyección 12 meses</t>
-        </is>
-      </c>
-      <c r="C10" s="18">
-        <f>IF(ISERROR(SUM('Proyección 12 meses'!C5:O40)),"REVISAR","OK")</f>
+          <t>Ninguna celda con error en Escenarios</t>
+        </is>
+      </c>
+      <c r="C10" s="36">
+        <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -3543,11 +2150,11 @@
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Escenarios</t>
-        </is>
-      </c>
-      <c r="C11" s="18">
-        <f>IF(ISERROR(SUM('Escenarios'!C5:L120)),"REVISAR","OK")</f>
+          <t>Ninguna celda con error en Seguimiento</t>
+        </is>
+      </c>
+      <c r="C11" s="36">
+        <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
         <v/>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -3559,361 +2166,168 @@
     <row r="12">
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ninguna celda con error en Seguimiento</t>
-        </is>
-      </c>
-      <c r="C12" s="18">
-        <f>IF(ISERROR(SUM('Seguimiento'!C5:Q80)),"REVISAR","OK")</f>
+          <t>Los supuestos de tráfico son mayores a cero</t>
+        </is>
+      </c>
+      <c r="C12" s="36">
+        <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$12&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Si dice REVISAR, hay un #DIV/0! o #REF!: casi siempre un supuesto en 0 o una fila borrada.</t>
+          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Los supuestos de tráfico son mayores a cero</t>
-        </is>
-      </c>
-      <c r="C13" s="18">
-        <f>IF(AND('Supuestos'!$C$9&gt;0,'Supuestos'!$C$12&gt;0,'Supuestos'!$C$13&gt;0),"OK","REVISAR")</f>
+          <t>La curva de cobranza suma 100 %</t>
+        </is>
+      </c>
+      <c r="C13" s="36">
+        <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
+          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="inlineStr">
         <is>
-          <t>La curva de cobranza suma 100 %</t>
-        </is>
-      </c>
-      <c r="C14" s="18">
-        <f>IF(ABS('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42-1)&lt;0.001,"OK","REVISAR")</f>
+          <t>Comisiones + reembolsos menores al 60 %</t>
+        </is>
+      </c>
+      <c r="C14" s="36">
+        <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
+          <t>Si suman más, revisá los porcentajes.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Comisiones + reembolsos menores al 60 %</t>
-        </is>
-      </c>
-      <c r="C15" s="18">
-        <f>IF(('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)&lt;0.6,"OK","REVISAR")</f>
+          <t>El escenario en uso es 1, 2 o 3</t>
+        </is>
+      </c>
+      <c r="C15" s="36">
+        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Si suman más, revisá los porcentajes.</t>
+          <t>Supuestos → celda 'Escenario en uso'.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>El escenario en uso es 1, 2 o 3</t>
-        </is>
-      </c>
-      <c r="C16" s="18">
-        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>Supuestos → celda 'Escenario en uso'.</t>
-        </is>
-      </c>
+          <t>La inversión es mayor a cero</t>
+        </is>
+      </c>
+      <c r="C16" s="36">
+        <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>La inversión es mayor a cero</t>
-        </is>
-      </c>
-      <c r="C17" s="18">
-        <f>IF('Supuestos'!$C$8&gt;0,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D17" s="5" t="inlineStr"/>
+          <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
+        </is>
+      </c>
+      <c r="C17" s="36">
+        <f>IF('Modelo'!$C$11&gt;0,"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>La meta de ventas es alcanzable (hay conversión a venta)</t>
-        </is>
-      </c>
-      <c r="C18" s="18">
-        <f>IF('Modelo'!$C$11&gt;0,"OK","REVISAR")</f>
+          <t>Las conversiones están entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C18" s="36">
+        <f>IF(AND('Supuestos'!$C$12&gt;=0,'Supuestos'!$C$12&lt;=1,'Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$28&gt;=0,'Supuestos'!$C$28&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
+          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>Las conversiones están entre 0 y 100 %</t>
-        </is>
-      </c>
-      <c r="C19" s="18">
-        <f>IF(AND('Supuestos'!$C$12&gt;=0,'Supuestos'!$C$12&lt;=1,'Supuestos'!$C$13&gt;=0,'Supuestos'!$C$13&lt;=1,'Supuestos'!$C$18&gt;=0,'Supuestos'!$C$18&lt;=1,'Supuestos'!$C$20&gt;=0,'Supuestos'!$C$20&lt;=1,'Supuestos'!$C$22&gt;=0,'Supuestos'!$C$22&lt;=1,'Supuestos'!$C$24&gt;=0,'Supuestos'!$C$24&lt;=1,'Supuestos'!$C$26&gt;=0,'Supuestos'!$C$26&lt;=1,'Supuestos'!$C$28&gt;=0,'Supuestos'!$C$28&lt;=1,'Supuestos'!$C$30&gt;=0,'Supuestos'!$C$30&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
-        </is>
-      </c>
+          <t>El margen de seguridad está entre 0 y 100 %</t>
+        </is>
+      </c>
+      <c r="C19" s="36">
+        <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>El margen de seguridad está entre 0 y 100 %</t>
-        </is>
-      </c>
-      <c r="C20" s="18">
-        <f>IF(AND('Supuestos'!$C$46&gt;=0,'Supuestos'!$C$46&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D20" s="5" t="inlineStr"/>
+          <t>El crecimiento mensual está entre −50 % y 100 %</t>
+        </is>
+      </c>
+      <c r="C20" s="36">
+        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
+        <v/>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>Más de 100 % por mes no es realista para una proyección.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>El crecimiento mensual está entre −50 % y 100 %</t>
-        </is>
-      </c>
-      <c r="C21" s="18">
-        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
+          <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
+        </is>
+      </c>
+      <c r="C21" s="36">
+        <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$8,'Modelo'!$C$10&lt;='Modelo'!$C$9),"OK","REVISAR")</f>
         <v/>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Más de 100 % por mes no es realista para una proyección.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
-        </is>
-      </c>
-      <c r="C22" s="18">
-        <f>IF(AND('Modelo'!$C$9&lt;='Modelo'!$C$8,'Modelo'!$C$10&lt;='Modelo'!$C$9),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
           <t>Si falla, alguna conversión está por encima de 100 %.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Simulador: lo que escribiste en las celdas amarillas</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Ningún supuesto del Simulador fuera de rango (porcentajes entre 0 y 1, números no negativos)</t>
-        </is>
-      </c>
-      <c r="C24" s="18">
-        <f>IF(COUNTIF('Simulador'!$I$6:$I$93,"REVISAR")=0,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>La columna Rango del Simulador marca la fila con el problema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Simulador: Los supuestos de tráfico son mayores a cero</t>
-        </is>
-      </c>
-      <c r="C25" s="18">
-        <f>IF(AND('Simulador'!$C$7&gt;0,'Simulador'!$C$11&gt;0,'Simulador'!$C$13&gt;0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Con un 0 en el tráfico o en la conversión de la página no hay unidades y el modelo no dice nada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Simulador: La curva de cobranza suma 100 %</t>
-        </is>
-      </c>
-      <c r="C26" s="18">
-        <f>IF(ABS('Simulador'!$C$54+'Simulador'!$C$55+'Simulador'!$C$56-1)&lt;0.001,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Supuestos → cobranza mes 1 + mes 2 + mes 3 = 100 %.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Simulador: Comisiones + reembolsos menores al 60 %</t>
-        </is>
-      </c>
-      <c r="C27" s="18">
-        <f>IF(('Simulador'!$C$59+'Simulador'!$C$60+'Simulador'!$C$62)&lt;0.6,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Si suman más, revisá los porcentajes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Simulador: El escenario en uso es 1, 2 o 3</t>
-        </is>
-      </c>
-      <c r="C28" s="18">
-        <f>IF(OR('Supuestos'!$C$6=1,'Supuestos'!$C$6=2,'Supuestos'!$C$6=3),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Supuestos → celda 'Escenario en uso'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Simulador: La inversión es mayor a cero</t>
-        </is>
-      </c>
-      <c r="C29" s="18">
-        <f>IF('Simulador'!$C$9&gt;0,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D29" s="5" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Simulador: La meta de ventas es alcanzable (hay conversión a venta)</t>
-        </is>
-      </c>
-      <c r="C30" s="18">
-        <f>IF('Simulador'!$E$15&gt;0,"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Con conversión a venta en 0, la inversión para la meta dice 'inalcanzable con estos supuestos'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Simulador: Las conversiones están entre 0 y 100 %</t>
-        </is>
-      </c>
-      <c r="C31" s="18">
-        <f>IF(AND('Simulador'!$C$11&gt;=0,'Simulador'!$C$11&lt;=1,'Simulador'!$C$13&gt;=0,'Simulador'!$C$13&lt;=1,'Simulador'!$C$20&gt;=0,'Simulador'!$C$20&lt;=1,'Simulador'!$C$24&gt;=0,'Simulador'!$C$24&lt;=1,'Simulador'!$C$28&gt;=0,'Simulador'!$C$28&lt;=1,'Simulador'!$C$32&gt;=0,'Simulador'!$C$32&lt;=1,'Simulador'!$C$36&gt;=0,'Simulador'!$C$36&lt;=1,'Simulador'!$C$40&gt;=0,'Simulador'!$C$40&lt;=1,'Simulador'!$C$44&gt;=0,'Simulador'!$C$44&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Un 25 % se escribe 25 % (o 0,25), no 25.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Simulador: El margen de seguridad está entre 0 y 100 %</t>
-        </is>
-      </c>
-      <c r="C32" s="18">
-        <f>IF(AND('Simulador'!$C$77&gt;=0,'Simulador'!$C$77&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D32" s="5" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Simulador: El crecimiento mensual está entre −50 % y 100 %</t>
-        </is>
-      </c>
-      <c r="C33" s="18">
-        <f>IF(AND('Supuestos'!$C$48&gt;=-0.5,'Supuestos'!$C$48&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Más de 100 % por mes no es realista para una proyección.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Simulador: La cadena es decreciente (cada etapa tiene menos gente que la anterior)</t>
-        </is>
-      </c>
-      <c r="C34" s="18">
-        <f>IF(AND('Simulador'!$E$12&lt;='Simulador'!$E$10,'Simulador'!$E$14&lt;='Simulador'!$E$12),"OK","REVISAR")</f>
-        <v/>
-      </c>
-      <c r="D34" s="5" t="inlineStr">
-        <is>
-          <t>Si falla, alguna conversión está por encima de 100 %.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>Estado general del modelo</t>
         </is>
       </c>
-      <c r="C36" s="37">
-        <f>IF(COUNTIF(C6:C34,"REVISAR")=0,"OK","REVISAR")</f>
+      <c r="C23" s="37">
+        <f>IF(COUNTIF(C6:C21,"REVISAR")=0,"OK","REVISAR")</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="C6:C36">
+  <conditionalFormatting sqref="C6:C23">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"OK"</formula>
     </cfRule>
@@ -3933,7 +2347,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F3864"/>
@@ -4509,2343 +2923,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I98"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2" customWidth="1" min="1" max="1"/>
-    <col width="56" customWidth="1" min="2" max="2"/>
-    <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="62" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Simulador: movés un número y ves cómo se mueve todo el embudo</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>Amarillo = tu número: arranca igual a Supuestos; escribí encima para probar (CPM, CTR, conversiones, precios, costos). Al lado, la base. 'Con tus números' se recalcula al instante y se compara con el Modelo. Para volver a la base, borrá la celda amarilla y escribí =D seguido del número de fila (por ejemplo =D9).</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>Paso / métrica</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>Tu número (editable)</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>Base (Supuestos)</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
-        <is>
-          <t>Con tus números</t>
-        </is>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>Base (Modelo)</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
-        <is>
-          <t>Diferencia</t>
-        </is>
-      </c>
-      <c r="H5" s="6" t="inlineStr">
-        <is>
-          <t>Cómo se calcula</t>
-        </is>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>Rango</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="7" t="inlineStr">
-        <is>
-          <t>Tráfico y unidades</t>
-        </is>
-      </c>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
-      <c r="E6" s="8" t="n"/>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="8" t="n"/>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Costo por visita a la página de ventas (VSL)</t>
-        </is>
-      </c>
-      <c r="C7" s="16">
-        <f>'Supuestos'!$C$9</f>
-        <v/>
-      </c>
-      <c r="D7" s="17">
-        <f>'Supuestos'!$C$9</f>
-        <v/>
-      </c>
-      <c r="G7">
-        <f>IF(C7&lt;&gt;D7,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H7" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I7" s="18">
-        <f>IF(AND(ISNUMBER(C7),C7&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Costo por visita (unidad de adquisición)</t>
-        </is>
-      </c>
-      <c r="E8" s="17">
-        <f>$C$7</f>
-        <v/>
-      </c>
-      <c r="F8" s="17">
-        <f>'Modelo'!$C$7</f>
-        <v/>
-      </c>
-      <c r="G8" s="17">
-        <f>IF(AND(ISNUMBER(E8),ISNUMBER(F8)),E8-F8,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="5" t="inlineStr">
-        <is>
-          <t>El supuesto 'costo por visita'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Inversión en publicidad por mes</t>
-        </is>
-      </c>
-      <c r="C9" s="19">
-        <f>'Supuestos'!$C$8</f>
-        <v/>
-      </c>
-      <c r="D9" s="20">
-        <f>'Supuestos'!$C$8</f>
-        <v/>
-      </c>
-      <c r="G9">
-        <f>IF(C9&lt;&gt;D9,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H9" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I9" s="18">
-        <f>IF(AND(ISNUMBER(C9),C9&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Visitas a la página de ventas</t>
-        </is>
-      </c>
-      <c r="E10" s="21">
-        <f>IF($E$8=0,0,$C$9/$E$8)</f>
-        <v/>
-      </c>
-      <c r="F10" s="22">
-        <f>'Modelo'!$C$8</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
-        <f>IF(AND(ISNUMBER(E10),ISNUMBER(F10)),E10-F10,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="5" t="inlineStr">
-        <is>
-          <t>Inversión ÷ costo por visita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>% de visitas que llegan al checkout</t>
-        </is>
-      </c>
-      <c r="C11" s="23">
-        <f>'Supuestos'!$C$12</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>'Supuestos'!$C$12</f>
-        <v/>
-      </c>
-      <c r="G11">
-        <f>IF(C11&lt;&gt;D11,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I11" s="18">
-        <f>IF(AND(ISNUMBER(C11),C11&gt;=0,C11&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Checkouts iniciados</t>
-        </is>
-      </c>
-      <c r="E12" s="22">
-        <f>$E$10*$C$11</f>
-        <v/>
-      </c>
-      <c r="F12" s="22">
-        <f>'Modelo'!$C$9</f>
-        <v/>
-      </c>
-      <c r="G12" s="22">
-        <f>IF(AND(ISNUMBER(E12),ISNUMBER(F12)),E12-F12,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>Visitas × % que llega al checkout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>% de checkouts que terminan en compra</t>
-        </is>
-      </c>
-      <c r="C13" s="23">
-        <f>'Supuestos'!$C$13</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>'Supuestos'!$C$13</f>
-        <v/>
-      </c>
-      <c r="G13">
-        <f>IF(C13&lt;&gt;D13,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I13" s="18">
-        <f>IF(AND(ISNUMBER(C13),C13&gt;=0,C13&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Ventas del producto principal</t>
-        </is>
-      </c>
-      <c r="E14" s="11">
-        <f>$E$12*$C$13</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>'Modelo'!$C$10</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>IF(AND(ISNUMBER(E14),ISNUMBER(F14)),E14-F14,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>Checkouts × % que compra.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>% de visitas que compran</t>
-        </is>
-      </c>
-      <c r="E15" s="26">
-        <f>IF($E$10=0,0,$E$14/$E$10)</f>
-        <v/>
-      </c>
-      <c r="F15" s="26">
-        <f>'Modelo'!$C$11</f>
-        <v/>
-      </c>
-      <c r="G15" s="26">
-        <f>IF(AND(ISNUMBER(E15),ISNUMBER(F15)),E15-F15,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="5" t="inlineStr">
-        <is>
-          <t>Ventas ÷ visitas. Las dos conversiones multiplicadas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Costo por comprador (CPA)</t>
-        </is>
-      </c>
-      <c r="E16" s="12">
-        <f>IF($E$14=0,0,$C$9/$E$14)</f>
-        <v/>
-      </c>
-      <c r="F16" s="17">
-        <f>'Modelo'!$C$12</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>IF(AND(ISNUMBER(E16),ISNUMBER(F16)),E16-F16,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="5" t="inlineStr">
-        <is>
-          <t>Inversión ÷ ventas del principal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Facturación por producto</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
-      <c r="E17" s="8" t="n"/>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="8" t="n"/>
-    </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Producto principal: precio</t>
-        </is>
-      </c>
-      <c r="C18" s="16">
-        <f>'Supuestos'!$C$16</f>
-        <v/>
-      </c>
-      <c r="D18" s="17">
-        <f>'Supuestos'!$C$16</f>
-        <v/>
-      </c>
-      <c r="G18">
-        <f>IF(C18&lt;&gt;D18,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I18" s="18">
-        <f>IF(AND(ISNUMBER(C18),C18&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Facturado: producto principal</t>
-        </is>
-      </c>
-      <c r="E19" s="20">
-        <f>$E$14*$C$18</f>
-        <v/>
-      </c>
-      <c r="F19" s="20">
-        <f>'Modelo'!$C$14</f>
-        <v/>
-      </c>
-      <c r="G19" s="20">
-        <f>IF(AND(ISNUMBER(E19),ISNUMBER(F19)),E19-F19,"")</f>
-        <v/>
-      </c>
-      <c r="H19" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Bump 1: % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C20" s="23">
-        <f>'Supuestos'!$C$18</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>'Supuestos'!$C$18</f>
-        <v/>
-      </c>
-      <c r="G20">
-        <f>IF(C20&lt;&gt;D20,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H20" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I20" s="18">
-        <f>IF(AND(ISNUMBER(C20),C20&gt;=0,C20&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Ventas: Bump 1</t>
-        </is>
-      </c>
-      <c r="E21" s="25">
-        <f>$E$14*$C$20</f>
-        <v/>
-      </c>
-      <c r="F21" s="25">
-        <f>'Modelo'!$C$15</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
-        <f>IF(AND(ISNUMBER(E21),ISNUMBER(F21)),E21-F21,"")</f>
-        <v/>
-      </c>
-      <c r="H21" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Bump 1: precio</t>
-        </is>
-      </c>
-      <c r="C22" s="16">
-        <f>'Supuestos'!$C$17</f>
-        <v/>
-      </c>
-      <c r="D22" s="17">
-        <f>'Supuestos'!$C$17</f>
-        <v/>
-      </c>
-      <c r="G22">
-        <f>IF(C22&lt;&gt;D22,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H22" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I22" s="18">
-        <f>IF(AND(ISNUMBER(C22),C22&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Facturado: Bump 1</t>
-        </is>
-      </c>
-      <c r="E23" s="20">
-        <f>$E$21*$C$22</f>
-        <v/>
-      </c>
-      <c r="F23" s="20">
-        <f>'Modelo'!$C$16</f>
-        <v/>
-      </c>
-      <c r="G23" s="20">
-        <f>IF(AND(ISNUMBER(E23),ISNUMBER(F23)),E23-F23,"")</f>
-        <v/>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Bump 2: % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C24" s="23">
-        <f>'Supuestos'!$C$20</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>'Supuestos'!$C$20</f>
-        <v/>
-      </c>
-      <c r="G24">
-        <f>IF(C24&lt;&gt;D24,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I24" s="18">
-        <f>IF(AND(ISNUMBER(C24),C24&gt;=0,C24&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Ventas: Bump 2</t>
-        </is>
-      </c>
-      <c r="E25" s="25">
-        <f>$E$14*$C$24</f>
-        <v/>
-      </c>
-      <c r="F25" s="25">
-        <f>'Modelo'!$C$17</f>
-        <v/>
-      </c>
-      <c r="G25" s="25">
-        <f>IF(AND(ISNUMBER(E25),ISNUMBER(F25)),E25-F25,"")</f>
-        <v/>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Bump 2: precio</t>
-        </is>
-      </c>
-      <c r="C26" s="16">
-        <f>'Supuestos'!$C$19</f>
-        <v/>
-      </c>
-      <c r="D26" s="17">
-        <f>'Supuestos'!$C$19</f>
-        <v/>
-      </c>
-      <c r="G26">
-        <f>IF(C26&lt;&gt;D26,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I26" s="18">
-        <f>IF(AND(ISNUMBER(C26),C26&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Facturado: Bump 2</t>
-        </is>
-      </c>
-      <c r="E27" s="20">
-        <f>$E$25*$C$26</f>
-        <v/>
-      </c>
-      <c r="F27" s="20">
-        <f>'Modelo'!$C$18</f>
-        <v/>
-      </c>
-      <c r="G27" s="20">
-        <f>IF(AND(ISNUMBER(E27),ISNUMBER(F27)),E27-F27,"")</f>
-        <v/>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>OTO 1: % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C28" s="23">
-        <f>'Supuestos'!$C$22</f>
-        <v/>
-      </c>
-      <c r="D28" s="24">
-        <f>'Supuestos'!$C$22</f>
-        <v/>
-      </c>
-      <c r="G28">
-        <f>IF(C28&lt;&gt;D28,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I28" s="18">
-        <f>IF(AND(ISNUMBER(C28),C28&gt;=0,C28&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Ventas: OTO 1</t>
-        </is>
-      </c>
-      <c r="E29" s="25">
-        <f>$E$14*$C$28</f>
-        <v/>
-      </c>
-      <c r="F29" s="25">
-        <f>'Modelo'!$C$19</f>
-        <v/>
-      </c>
-      <c r="G29" s="25">
-        <f>IF(AND(ISNUMBER(E29),ISNUMBER(F29)),E29-F29,"")</f>
-        <v/>
-      </c>
-      <c r="H29" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>OTO 1: precio</t>
-        </is>
-      </c>
-      <c r="C30" s="16">
-        <f>'Supuestos'!$C$21</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>'Supuestos'!$C$21</f>
-        <v/>
-      </c>
-      <c r="G30">
-        <f>IF(C30&lt;&gt;D30,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I30" s="18">
-        <f>IF(AND(ISNUMBER(C30),C30&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Facturado: OTO 1</t>
-        </is>
-      </c>
-      <c r="E31" s="20">
-        <f>$E$29*$C$30</f>
-        <v/>
-      </c>
-      <c r="F31" s="20">
-        <f>'Modelo'!$C$20</f>
-        <v/>
-      </c>
-      <c r="G31" s="20">
-        <f>IF(AND(ISNUMBER(E31),ISNUMBER(F31)),E31-F31,"")</f>
-        <v/>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>OTO 2: % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C32" s="23">
-        <f>'Supuestos'!$C$24</f>
-        <v/>
-      </c>
-      <c r="D32" s="24">
-        <f>'Supuestos'!$C$24</f>
-        <v/>
-      </c>
-      <c r="G32">
-        <f>IF(C32&lt;&gt;D32,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H32" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I32" s="18">
-        <f>IF(AND(ISNUMBER(C32),C32&gt;=0,C32&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Ventas: OTO 2</t>
-        </is>
-      </c>
-      <c r="E33" s="25">
-        <f>$E$14*$C$32</f>
-        <v/>
-      </c>
-      <c r="F33" s="25">
-        <f>'Modelo'!$C$21</f>
-        <v/>
-      </c>
-      <c r="G33" s="25">
-        <f>IF(AND(ISNUMBER(E33),ISNUMBER(F33)),E33-F33,"")</f>
-        <v/>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>OTO 2: precio</t>
-        </is>
-      </c>
-      <c r="C34" s="16">
-        <f>'Supuestos'!$C$23</f>
-        <v/>
-      </c>
-      <c r="D34" s="17">
-        <f>'Supuestos'!$C$23</f>
-        <v/>
-      </c>
-      <c r="G34">
-        <f>IF(C34&lt;&gt;D34,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I34" s="18">
-        <f>IF(AND(ISNUMBER(C34),C34&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Facturado: OTO 2</t>
-        </is>
-      </c>
-      <c r="E35" s="20">
-        <f>$E$33*$C$34</f>
-        <v/>
-      </c>
-      <c r="F35" s="20">
-        <f>'Modelo'!$C$22</f>
-        <v/>
-      </c>
-      <c r="G35" s="20">
-        <f>IF(AND(ISNUMBER(E35),ISNUMBER(F35)),E35-F35,"")</f>
-        <v/>
-      </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>OTO 3: % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C36" s="23">
-        <f>'Supuestos'!$C$26</f>
-        <v/>
-      </c>
-      <c r="D36" s="24">
-        <f>'Supuestos'!$C$26</f>
-        <v/>
-      </c>
-      <c r="G36">
-        <f>IF(C36&lt;&gt;D36,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I36" s="18">
-        <f>IF(AND(ISNUMBER(C36),C36&gt;=0,C36&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Ventas: OTO 3</t>
-        </is>
-      </c>
-      <c r="E37" s="25">
-        <f>$E$14*$C$36</f>
-        <v/>
-      </c>
-      <c r="F37" s="25">
-        <f>'Modelo'!$C$23</f>
-        <v/>
-      </c>
-      <c r="G37" s="25">
-        <f>IF(AND(ISNUMBER(E37),ISNUMBER(F37)),E37-F37,"")</f>
-        <v/>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>OTO 3: precio</t>
-        </is>
-      </c>
-      <c r="C38" s="16">
-        <f>'Supuestos'!$C$25</f>
-        <v/>
-      </c>
-      <c r="D38" s="17">
-        <f>'Supuestos'!$C$25</f>
-        <v/>
-      </c>
-      <c r="G38">
-        <f>IF(C38&lt;&gt;D38,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H38" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I38" s="18">
-        <f>IF(AND(ISNUMBER(C38),C38&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Facturado: OTO 3</t>
-        </is>
-      </c>
-      <c r="E39" s="20">
-        <f>$E$37*$C$38</f>
-        <v/>
-      </c>
-      <c r="F39" s="20">
-        <f>'Modelo'!$C$24</f>
-        <v/>
-      </c>
-      <c r="G39" s="20">
-        <f>IF(AND(ISNUMBER(E39),ISNUMBER(F39)),E39-F39,"")</f>
-        <v/>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>OTO 4: % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C40" s="23">
-        <f>'Supuestos'!$C$28</f>
-        <v/>
-      </c>
-      <c r="D40" s="24">
-        <f>'Supuestos'!$C$28</f>
-        <v/>
-      </c>
-      <c r="G40">
-        <f>IF(C40&lt;&gt;D40,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I40" s="18">
-        <f>IF(AND(ISNUMBER(C40),C40&gt;=0,C40&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Ventas: OTO 4</t>
-        </is>
-      </c>
-      <c r="E41" s="25">
-        <f>$E$14*$C$40</f>
-        <v/>
-      </c>
-      <c r="F41" s="25">
-        <f>'Modelo'!$C$25</f>
-        <v/>
-      </c>
-      <c r="G41" s="25">
-        <f>IF(AND(ISNUMBER(E41),ISNUMBER(F41)),E41-F41,"")</f>
-        <v/>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>OTO 4: precio</t>
-        </is>
-      </c>
-      <c r="C42" s="16">
-        <f>'Supuestos'!$C$27</f>
-        <v/>
-      </c>
-      <c r="D42" s="17">
-        <f>'Supuestos'!$C$27</f>
-        <v/>
-      </c>
-      <c r="G42">
-        <f>IF(C42&lt;&gt;D42,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I42" s="18">
-        <f>IF(AND(ISNUMBER(C42),C42&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Facturado: OTO 4</t>
-        </is>
-      </c>
-      <c r="E43" s="20">
-        <f>$E$41*$C$42</f>
-        <v/>
-      </c>
-      <c r="F43" s="20">
-        <f>'Modelo'!$C$26</f>
-        <v/>
-      </c>
-      <c r="G43" s="20">
-        <f>IF(AND(ISNUMBER(E43),ISNUMBER(F43)),E43-F43,"")</f>
-        <v/>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
-        </is>
-      </c>
-      <c r="C44" s="23">
-        <f>'Supuestos'!$C$30</f>
-        <v/>
-      </c>
-      <c r="D44" s="24">
-        <f>'Supuestos'!$C$30</f>
-        <v/>
-      </c>
-      <c r="G44">
-        <f>IF(C44&lt;&gt;D44,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I44" s="18">
-        <f>IF(AND(ISNUMBER(C44),C44&gt;=0,C44&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Ventas: Ascensión (programa de mayor valor)</t>
-        </is>
-      </c>
-      <c r="E45" s="25">
-        <f>$E$14*$C$44</f>
-        <v/>
-      </c>
-      <c r="F45" s="25">
-        <f>'Modelo'!$C$27</f>
-        <v/>
-      </c>
-      <c r="G45" s="25">
-        <f>IF(AND(ISNUMBER(E45),ISNUMBER(F45)),E45-F45,"")</f>
-        <v/>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Compradores del principal × % que lo toma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Ascensión (programa de mayor valor): precio</t>
-        </is>
-      </c>
-      <c r="C46" s="16">
-        <f>'Supuestos'!$C$29</f>
-        <v/>
-      </c>
-      <c r="D46" s="17">
-        <f>'Supuestos'!$C$29</f>
-        <v/>
-      </c>
-      <c r="G46">
-        <f>IF(C46&lt;&gt;D46,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I46" s="18">
-        <f>IF(AND(ISNUMBER(C46),C46&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Facturado: Ascensión (programa de mayor valor)</t>
-        </is>
-      </c>
-      <c r="E47" s="20">
-        <f>$E$45*$C$46</f>
-        <v/>
-      </c>
-      <c r="F47" s="20">
-        <f>'Modelo'!$C$28</f>
-        <v/>
-      </c>
-      <c r="G47" s="20">
-        <f>IF(AND(ISNUMBER(E47),ISNUMBER(F47)),E47-F47,"")</f>
-        <v/>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Ventas × precio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Facturado total</t>
-        </is>
-      </c>
-      <c r="E48" s="9">
-        <f>$E$19+$E$23+$E$27+$E$31+$E$35+$E$39+$E$43+$E$47</f>
-        <v/>
-      </c>
-      <c r="F48" s="20">
-        <f>'Modelo'!$C$29</f>
-        <v/>
-      </c>
-      <c r="G48" s="20">
-        <f>IF(AND(ISNUMBER(E48),ISNUMBER(F48)),E48-F48,"")</f>
-        <v/>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>Suma de todos los productos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Facturado por comprador (AOV)</t>
-        </is>
-      </c>
-      <c r="E49" s="12">
-        <f>IF($E$14=0,0,$E$48/$E$14)</f>
-        <v/>
-      </c>
-      <c r="F49" s="17">
-        <f>'Modelo'!$C$30</f>
-        <v/>
-      </c>
-      <c r="G49" s="17">
-        <f>IF(AND(ISNUMBER(E49),ISNUMBER(F49)),E49-F49,"")</f>
-        <v/>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>Facturado total ÷ ventas del principal.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>AOV ÷ precio del principal</t>
-        </is>
-      </c>
-      <c r="E50" s="27">
-        <f>IF($C$18=0,0,$E$49/$C$18)</f>
-        <v/>
-      </c>
-      <c r="F50" s="27">
-        <f>'Modelo'!$C$31</f>
-        <v/>
-      </c>
-      <c r="G50" s="27">
-        <f>IF(AND(ISNUMBER(E50),ISNUMBER(F50)),E50-F50,"")</f>
-        <v/>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Cuánto multiplica la escalera al precio del front.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Ventas del principal por visita (para la proyección)</t>
-        </is>
-      </c>
-      <c r="E51" s="26">
-        <f>IF($E$10=0,0,$E$14/$E$10)</f>
-        <v/>
-      </c>
-      <c r="F51" s="26">
-        <f>'Modelo'!$C$32</f>
-        <v/>
-      </c>
-      <c r="G51" s="26">
-        <f>IF(AND(ISNUMBER(E51),ISNUMBER(F51)),E51-F51,"")</f>
-        <v/>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>Igual a '% de visitas que compran'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Facturado por visita</t>
-        </is>
-      </c>
-      <c r="E52" s="17">
-        <f>IF($E$10=0,0,$E$48/$E$10)</f>
-        <v/>
-      </c>
-      <c r="F52" s="17">
-        <f>'Modelo'!$C$33</f>
-        <v/>
-      </c>
-      <c r="G52" s="17">
-        <f>IF(AND(ISNUMBER(E52),ISNUMBER(F52)),E52-F52,"")</f>
-        <v/>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Facturado total ÷ visitas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Cash, costos y ganancia del período</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="n"/>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="8" t="n"/>
-      <c r="H53" s="8" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>% del facturado que entra en el mes 1</t>
-        </is>
-      </c>
-      <c r="C54" s="23">
-        <f>'Supuestos'!$C$40</f>
-        <v/>
-      </c>
-      <c r="D54" s="24">
-        <f>'Supuestos'!$C$40</f>
-        <v/>
-      </c>
-      <c r="G54">
-        <f>IF(C54&lt;&gt;D54,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I54" s="18">
-        <f>IF(AND(ISNUMBER(C54),C54&gt;=0,C54&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>% que entra en el mes 2</t>
-        </is>
-      </c>
-      <c r="C55" s="23">
-        <f>'Supuestos'!$C$41</f>
-        <v/>
-      </c>
-      <c r="D55" s="24">
-        <f>'Supuestos'!$C$41</f>
-        <v/>
-      </c>
-      <c r="G55">
-        <f>IF(C55&lt;&gt;D55,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I55" s="18">
-        <f>IF(AND(ISNUMBER(C55),C55&gt;=0,C55&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>% que entra en el mes 3</t>
-        </is>
-      </c>
-      <c r="C56" s="23">
-        <f>'Supuestos'!$C$42</f>
-        <v/>
-      </c>
-      <c r="D56" s="24">
-        <f>'Supuestos'!$C$42</f>
-        <v/>
-      </c>
-      <c r="G56">
-        <f>IF(C56&lt;&gt;D56,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I56" s="18">
-        <f>IF(AND(ISNUMBER(C56),C56&gt;=0,C56&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Cash a cobrar (facturado × cobranza completa)</t>
-        </is>
-      </c>
-      <c r="E57" s="20">
-        <f>$E$48*($C$54+$C$55+$C$56)</f>
-        <v/>
-      </c>
-      <c r="F57" s="20">
-        <f>'Modelo'!$C$35</f>
-        <v/>
-      </c>
-      <c r="G57" s="20">
-        <f>IF(AND(ISNUMBER(E57),ISNUMBER(F57)),E57-F57,"")</f>
-        <v/>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>Facturado × (mes 1 + mes 2 + mes 3). Si la cobranza suma 100 %, es igual al facturado.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Cash que entra en el primer mes</t>
-        </is>
-      </c>
-      <c r="E58" s="20">
-        <f>$E$48*$C$54</f>
-        <v/>
-      </c>
-      <c r="F58" s="20">
-        <f>'Modelo'!$C$36</f>
-        <v/>
-      </c>
-      <c r="G58" s="20">
-        <f>IF(AND(ISNUMBER(E58),ISNUMBER(F58)),E58-F58,"")</f>
-        <v/>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>Facturado × % del mes 1.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Comisión de la pasarela o plataforma de pago</t>
-        </is>
-      </c>
-      <c r="C59" s="23">
-        <f>'Supuestos'!$C$33</f>
-        <v/>
-      </c>
-      <c r="D59" s="24">
-        <f>'Supuestos'!$C$33</f>
-        <v/>
-      </c>
-      <c r="G59">
-        <f>IF(C59&lt;&gt;D59,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I59" s="18">
-        <f>IF(AND(ISNUMBER(C59),C59&gt;=0,C59&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Comisión del equipo de ventas</t>
-        </is>
-      </c>
-      <c r="C60" s="23">
-        <f>'Supuestos'!$C$34</f>
-        <v/>
-      </c>
-      <c r="D60" s="24">
-        <f>'Supuestos'!$C$34</f>
-        <v/>
-      </c>
-      <c r="G60">
-        <f>IF(C60&lt;&gt;D60,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I60" s="18">
-        <f>IF(AND(ISNUMBER(C60),C60&gt;=0,C60&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Comisiones (pasarela + ventas)</t>
-        </is>
-      </c>
-      <c r="E61" s="20">
-        <f>$E$57*($C$59+$C$60)</f>
-        <v/>
-      </c>
-      <c r="F61" s="20">
-        <f>'Modelo'!$C$37</f>
-        <v/>
-      </c>
-      <c r="G61" s="20">
-        <f>IF(AND(ISNUMBER(E61),ISNUMBER(F61)),E61-F61,"")</f>
-        <v/>
-      </c>
-      <c r="H61" s="5" t="inlineStr">
-        <is>
-          <t>Cash × (pasarela + equipo de ventas).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Reembolsos y contracargos</t>
-        </is>
-      </c>
-      <c r="C62" s="23">
-        <f>'Supuestos'!$C$35</f>
-        <v/>
-      </c>
-      <c r="D62" s="24">
-        <f>'Supuestos'!$C$35</f>
-        <v/>
-      </c>
-      <c r="G62">
-        <f>IF(C62&lt;&gt;D62,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H62" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I62" s="18">
-        <f>IF(AND(ISNUMBER(C62),C62&gt;=0,C62&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Reembolsos</t>
-        </is>
-      </c>
-      <c r="E63" s="20">
-        <f>$E$57*$C$62</f>
-        <v/>
-      </c>
-      <c r="F63" s="20">
-        <f>'Modelo'!$C$38</f>
-        <v/>
-      </c>
-      <c r="G63" s="20">
-        <f>IF(AND(ISNUMBER(E63),ISNUMBER(F63)),E63-F63,"")</f>
-        <v/>
-      </c>
-      <c r="H63" s="5" t="inlineStr">
-        <is>
-          <t>Cash × % de reembolsos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="B64" s="4" t="inlineStr">
-        <is>
-          <t>Cash neto</t>
-        </is>
-      </c>
-      <c r="E64" s="9">
-        <f>$E$57*(1-$C$59-$C$60-$C$62)</f>
-        <v/>
-      </c>
-      <c r="F64" s="20">
-        <f>'Modelo'!$C$39</f>
-        <v/>
-      </c>
-      <c r="G64" s="20">
-        <f>IF(AND(ISNUMBER(E64),ISNUMBER(F64)),E64-F64,"")</f>
-        <v/>
-      </c>
-      <c r="H64" s="5" t="inlineStr">
-        <is>
-          <t>Cash − comisiones − reembolsos. La base de verdad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Costos por visita (herramientas, WhatsApp, IA)</t>
-        </is>
-      </c>
-      <c r="C65" s="16">
-        <f>'Supuestos'!$C$36</f>
-        <v/>
-      </c>
-      <c r="D65" s="17">
-        <f>'Supuestos'!$C$36</f>
-        <v/>
-      </c>
-      <c r="G65">
-        <f>IF(C65&lt;&gt;D65,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H65" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I65" s="18">
-        <f>IF(AND(ISNUMBER(C65),C65&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Costos por visita (herramientas, WhatsApp, IA)</t>
-        </is>
-      </c>
-      <c r="E66" s="20">
-        <f>$E$10*$C$65</f>
-        <v/>
-      </c>
-      <c r="F66" s="20">
-        <f>'Modelo'!$C$40</f>
-        <v/>
-      </c>
-      <c r="G66" s="20">
-        <f>IF(AND(ISNUMBER(E66),ISNUMBER(F66)),E66-F66,"")</f>
-        <v/>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>Visitas × costo por visita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Costos fijos por mes</t>
-        </is>
-      </c>
-      <c r="C67" s="19">
-        <f>'Supuestos'!$C$37</f>
-        <v/>
-      </c>
-      <c r="D67" s="20">
-        <f>'Supuestos'!$C$37</f>
-        <v/>
-      </c>
-      <c r="G67">
-        <f>IF(C67&lt;&gt;D67,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H67" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I67" s="18">
-        <f>IF(AND(ISNUMBER(C67),C67&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia del período</t>
-        </is>
-      </c>
-      <c r="E68" s="9">
-        <f>$E$64-$E$66-$C$67-$C$9</f>
-        <v/>
-      </c>
-      <c r="F68" s="20">
-        <f>'Modelo'!$C$41</f>
-        <v/>
-      </c>
-      <c r="G68" s="20">
-        <f>IF(AND(ISNUMBER(E68),ISNUMBER(F68)),E68-F68,"")</f>
-        <v/>
-      </c>
-      <c r="H68" s="5" t="inlineStr">
-        <is>
-          <t>Cash neto − costos por unidad − fijos − inversión.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>ROAS sobre facturado</t>
-        </is>
-      </c>
-      <c r="E69" s="27">
-        <f>IF($C$9=0,0,$E$48/$C$9)</f>
-        <v/>
-      </c>
-      <c r="F69" s="27">
-        <f>'Modelo'!$C$42</f>
-        <v/>
-      </c>
-      <c r="G69" s="27">
-        <f>IF(AND(ISNUMBER(E69),ISNUMBER(F69)),E69-F69,"")</f>
-        <v/>
-      </c>
-      <c r="H69" s="5" t="inlineStr">
-        <is>
-          <t>Facturado ÷ inversión. El número que más se infla: no decidas con este.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t>ROAS sobre cash neto</t>
-        </is>
-      </c>
-      <c r="E70" s="10">
-        <f>IF($C$9=0,0,$E$64/$C$9)</f>
-        <v/>
-      </c>
-      <c r="F70" s="27">
-        <f>'Modelo'!$C$43</f>
-        <v/>
-      </c>
-      <c r="G70" s="27">
-        <f>IF(AND(ISNUMBER(E70),ISNUMBER(F70)),E70-F70,"")</f>
-        <v/>
-      </c>
-      <c r="H70" s="5" t="inlineStr">
-        <is>
-          <t>Cash neto ÷ inversión. Con este se decide.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Margen sobre cash</t>
-        </is>
-      </c>
-      <c r="E71" s="24">
-        <f>IF($E$57=0,0,$E$68/$E$57)</f>
-        <v/>
-      </c>
-      <c r="F71" s="24">
-        <f>'Modelo'!$C$44</f>
-        <v/>
-      </c>
-      <c r="G71" s="24">
-        <f>IF(AND(ISNUMBER(E71),ISNUMBER(F71)),E71-F71,"")</f>
-        <v/>
-      </c>
-      <c r="H71" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia ÷ cash.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>ROAS objetivo sobre cash neto</t>
-        </is>
-      </c>
-      <c r="C72" s="28">
-        <f>'Supuestos'!$C$45</f>
-        <v/>
-      </c>
-      <c r="D72" s="27">
-        <f>'Supuestos'!$C$45</f>
-        <v/>
-      </c>
-      <c r="G72">
-        <f>IF(C72&lt;&gt;D72,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H72" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I72" s="18">
-        <f>IF(AND(ISNUMBER(C72),C72&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>¿Cumple el ROAS objetivo?</t>
-        </is>
-      </c>
-      <c r="E73" s="29">
-        <f>IF($E$70&gt;=$C$72,"SÍ","NO")</f>
-        <v/>
-      </c>
-      <c r="F73" s="29">
-        <f>'Modelo'!$C$45</f>
-        <v/>
-      </c>
-      <c r="G73">
-        <f>IF(E73=F73,"","≠ base")</f>
-        <v/>
-      </c>
-      <c r="H73" s="5" t="inlineStr">
-        <is>
-          <t>ROAS sobre cash neto contra el objetivo de Supuestos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Cuánto vale cada unidad y hasta cuánto pagar</t>
-        </is>
-      </c>
-      <c r="C74" s="8" t="n"/>
-      <c r="D74" s="8" t="n"/>
-      <c r="E74" s="8" t="n"/>
-      <c r="F74" s="8" t="n"/>
-      <c r="G74" s="8" t="n"/>
-      <c r="H74" s="8" t="n"/>
-    </row>
-    <row r="75">
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t>Valor neto por visita</t>
-        </is>
-      </c>
-      <c r="E75" s="12">
-        <f>IF($E$10=0,0,($E$64-$E$66)/$E$10)</f>
-        <v/>
-      </c>
-      <c r="F75" s="17">
-        <f>'Modelo'!$C$47</f>
-        <v/>
-      </c>
-      <c r="G75" s="17">
-        <f>IF(AND(ISNUMBER(E75),ISNUMBER(F75)),E75-F75,"")</f>
-        <v/>
-      </c>
-      <c r="H75" s="5" t="inlineStr">
-        <is>
-          <t>(Cash neto − costos por unidad) ÷ visitas. Lo que vale una visita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Techo de costo por visita (break-even)</t>
-        </is>
-      </c>
-      <c r="E76" s="12">
-        <f>$E$75</f>
-        <v/>
-      </c>
-      <c r="F76" s="17">
-        <f>'Modelo'!$C$48</f>
-        <v/>
-      </c>
-      <c r="G76" s="17">
-        <f>IF(AND(ISNUMBER(E76),ISNUMBER(F76)),E76-F76,"")</f>
-        <v/>
-      </c>
-      <c r="H76" s="5" t="inlineStr">
-        <is>
-          <t>Igual al valor neto por visita: pagando esto no ganás ni perdés.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Margen de seguridad</t>
-        </is>
-      </c>
-      <c r="C77" s="23">
-        <f>'Supuestos'!$C$46</f>
-        <v/>
-      </c>
-      <c r="D77" s="24">
-        <f>'Supuestos'!$C$46</f>
-        <v/>
-      </c>
-      <c r="G77">
-        <f>IF(C77&lt;&gt;D77,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H77" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I77" s="18">
-        <f>IF(AND(ISNUMBER(C77),C77&gt;=0,C77&lt;=1),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Objetivo de costo por visita</t>
-        </is>
-      </c>
-      <c r="E78" s="12">
-        <f>$E$76/(1+$C$77)</f>
-        <v/>
-      </c>
-      <c r="F78" s="17">
-        <f>'Modelo'!$C$49</f>
-        <v/>
-      </c>
-      <c r="G78" s="17">
-        <f>IF(AND(ISNUMBER(E78),ISNUMBER(F78)),E78-F78,"")</f>
-        <v/>
-      </c>
-      <c r="H78" s="5" t="inlineStr">
-        <is>
-          <t>Techo ÷ (1 + margen de seguridad).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Techo de costo por checkout</t>
-        </is>
-      </c>
-      <c r="E79" s="17">
-        <f>IF($C$11=0,0,$E$75/$C$11)</f>
-        <v/>
-      </c>
-      <c r="F79" s="17">
-        <f>'Modelo'!$C$50</f>
-        <v/>
-      </c>
-      <c r="G79" s="17">
-        <f>IF(AND(ISNUMBER(E79),ISNUMBER(F79)),E79-F79,"")</f>
-        <v/>
-      </c>
-      <c r="H79" s="5" t="inlineStr">
-        <is>
-          <t>Valor por visita ÷ % que llega al checkout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="B80" s="4" t="inlineStr">
-        <is>
-          <t>Techo de costo por comprador (CPA máximo)</t>
-        </is>
-      </c>
-      <c r="E80" s="12">
-        <f>IF($E$15=0,0,$E$75/$E$15)</f>
-        <v/>
-      </c>
-      <c r="F80" s="17">
-        <f>'Modelo'!$C$51</f>
-        <v/>
-      </c>
-      <c r="G80" s="17">
-        <f>IF(AND(ISNUMBER(E80),ISNUMBER(F80)),E80-F80,"")</f>
-        <v/>
-      </c>
-      <c r="H80" s="5" t="inlineStr">
-        <is>
-          <t>Valor por visita ÷ % de visitas que compran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Objetivo de CPA</t>
-        </is>
-      </c>
-      <c r="E81" s="17">
-        <f>$E$80/(1+$C$77)</f>
-        <v/>
-      </c>
-      <c r="F81" s="17">
-        <f>'Modelo'!$C$52</f>
-        <v/>
-      </c>
-      <c r="G81" s="17">
-        <f>IF(AND(ISNUMBER(E81),ISNUMBER(F81)),E81-F81,"")</f>
-        <v/>
-      </c>
-      <c r="H81" s="5" t="inlineStr">
-        <is>
-          <t>CPA máximo ÷ (1 + margen de seguridad).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Cash neto por comprador (AOV neto)</t>
-        </is>
-      </c>
-      <c r="E82" s="17">
-        <f>IF($E$14=0,0,($E$64-$E$66)/$E$14)</f>
-        <v/>
-      </c>
-      <c r="F82" s="17">
-        <f>'Modelo'!$C$53</f>
-        <v/>
-      </c>
-      <c r="G82" s="17">
-        <f>IF(AND(ISNUMBER(E82),ISNUMBER(F82)),E82-F82,"")</f>
-        <v/>
-      </c>
-      <c r="H82" s="5" t="inlineStr">
-        <is>
-          <t>Lo que deja cada comprador después de comisiones y reembolsos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>AOV neto − CPA (lo que queda por comprador)</t>
-        </is>
-      </c>
-      <c r="E83" s="12">
-        <f>$E$82-$E$16</f>
-        <v/>
-      </c>
-      <c r="F83" s="17">
-        <f>'Modelo'!$C$54</f>
-        <v/>
-      </c>
-      <c r="G83" s="17">
-        <f>IF(AND(ISNUMBER(E83),ISNUMBER(F83)),E83-F83,"")</f>
-        <v/>
-      </c>
-      <c r="H83" s="5" t="inlineStr">
-        <is>
-          <t>Si es negativo, perdés plata con cada venta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Semáforo y cuánto invertir</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="n"/>
-      <c r="D84" s="8" t="n"/>
-      <c r="E84" s="8" t="n"/>
-      <c r="F84" s="8" t="n"/>
-      <c r="G84" s="8" t="n"/>
-      <c r="H84" s="8" t="n"/>
-    </row>
-    <row r="85">
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Semáforo del costo por visita actual</t>
-        </is>
-      </c>
-      <c r="E85" s="13">
-        <f>IF($E$8&gt;$E$76,"ROJO",IF(AND($E$8&lt;=$E$78,$E$70&gt;=$C$72),"VERDE","AMARILLO"))</f>
-        <v/>
-      </c>
-      <c r="F85" s="29">
-        <f>'Modelo'!$C$56</f>
-        <v/>
-      </c>
-      <c r="G85">
-        <f>IF(E85=F85,"","≠ base")</f>
-        <v/>
-      </c>
-      <c r="H85" s="5" t="inlineStr">
-        <is>
-          <t>Rojo: costo &gt; techo. Verde: costo ≤ objetivo y ROAS sobre cash neto ≥ objetivo. Amarillo: el resto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Meta de ventas del producto principal</t>
-        </is>
-      </c>
-      <c r="C86" s="30">
-        <f>'Supuestos'!$C$47</f>
-        <v/>
-      </c>
-      <c r="D86" s="22">
-        <f>'Supuestos'!$C$47</f>
-        <v/>
-      </c>
-      <c r="G86">
-        <f>IF(C86&lt;&gt;D86,"← cambiado","")</f>
-        <v/>
-      </c>
-      <c r="H86" s="5" t="inlineStr">
-        <is>
-          <t>Supuesto. Escribí encima para probar; la base queda al lado.</t>
-        </is>
-      </c>
-      <c r="I86" s="18">
-        <f>IF(AND(ISNUMBER(C86),C86&gt;=0),"OK","REVISAR")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87">
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Inversión necesaria para la meta de ventas (al costo actual)</t>
-        </is>
-      </c>
-      <c r="E87" s="9">
-        <f>IF($E$15=0,"inalcanzable con estos supuestos",$C$86/$E$15*$E$8)</f>
-        <v/>
-      </c>
-      <c r="F87" s="20">
-        <f>'Modelo'!$C$57</f>
-        <v/>
-      </c>
-      <c r="G87" s="20">
-        <f>IF(AND(ISNUMBER(E87),ISNUMBER(F87)),E87-F87,"")</f>
-        <v/>
-      </c>
-      <c r="H87" s="5" t="inlineStr">
-        <is>
-          <t>Meta ÷ % de visitas que compran × costo por visita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
-        </is>
-      </c>
-      <c r="E88" s="20">
-        <f>IF($E$15=0,"inalcanzable con estos supuestos",$C$86/$E$15*$E$78)</f>
-        <v/>
-      </c>
-      <c r="F88" s="20">
-        <f>'Modelo'!$C$58</f>
-        <v/>
-      </c>
-      <c r="G88" s="20">
-        <f>IF(AND(ISNUMBER(E88),ISNUMBER(F88)),E88-F88,"")</f>
-        <v/>
-      </c>
-      <c r="H88" s="5" t="inlineStr">
-        <is>
-          <t>Lo mismo, al costo objetivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Ganancia por paso (las dos caras de cada número)</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="n"/>
-      <c r="D89" s="8" t="n"/>
-      <c r="E89" s="8" t="n"/>
-      <c r="F89" s="8" t="n"/>
-      <c r="G89" s="8" t="n"/>
-      <c r="H89" s="8" t="n"/>
-    </row>
-    <row r="90">
-      <c r="B90" s="4" t="inlineStr">
-        <is>
-          <t>Cash neto por comprador (AOV neto)</t>
-        </is>
-      </c>
-      <c r="E90" s="12">
-        <f>IF($E$14=0,0,($E$64-$E$66)/$E$14)</f>
-        <v/>
-      </c>
-      <c r="F90" s="17">
-        <f>'Modelo'!$C$53</f>
-        <v/>
-      </c>
-      <c r="G90" s="17">
-        <f>IF(AND(ISNUMBER(E90),ISNUMBER(F90)),E90-F90,"")</f>
-        <v/>
-      </c>
-      <c r="H90" s="5" t="inlineStr">
-        <is>
-          <t>Lo que deja cada comprador después de comisiones, reembolsos y costos por unidad. Su par es el CPA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia por visita</t>
-        </is>
-      </c>
-      <c r="E91" s="12">
-        <f>IF($E$10=0,0,$E$68/$E$10)</f>
-        <v/>
-      </c>
-      <c r="F91" s="17">
-        <f>'Modelo'!$C$60</f>
-        <v/>
-      </c>
-      <c r="G91" s="17">
-        <f>IF(AND(ISNUMBER(E91),ISNUMBER(F91)),E91-F91,"")</f>
-        <v/>
-      </c>
-      <c r="H91" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia del período ÷ visitas. La métrica más valiosa del embudo: resume todo lo que pasa después de la página. Su par es el costo por visita.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Ganancia por checkout</t>
-        </is>
-      </c>
-      <c r="E92" s="17">
-        <f>IF($E$12=0,0,$E$68/$E$12)</f>
-        <v/>
-      </c>
-      <c r="F92" s="17">
-        <f>'Modelo'!$C$61</f>
-        <v/>
-      </c>
-      <c r="G92" s="17">
-        <f>IF(AND(ISNUMBER(E92),ISNUMBER(F92)),E92-F92,"")</f>
-        <v/>
-      </c>
-      <c r="H92" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia del período ÷ checkouts. Su par es el costo por checkout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Ganancia por cliente</t>
-        </is>
-      </c>
-      <c r="E93" s="12">
-        <f>IF($E$14=0,0,$E$68/$E$14)</f>
-        <v/>
-      </c>
-      <c r="F93" s="17">
-        <f>'Modelo'!$C$62</f>
-        <v/>
-      </c>
-      <c r="G93" s="17">
-        <f>IF(AND(ISNUMBER(E93),ISNUMBER(F93)),E93-F93,"")</f>
-        <v/>
-      </c>
-      <c r="H93" s="5" t="inlineStr">
-        <is>
-          <t>Ganancia del período ÷ compradores del principal. Su par es el CPA; la diferencia entre AOV neto y CPA es lo que queda por cliente antes de fijos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="B95" s="5" t="inlineStr">
-        <is>
-          <t>Cómo se lee: cambiá una celda amarilla (por ejemplo el CPM, el CTR, la conversión de la landing, el show, el cierre o el precio) y mirá cómo se mueven la cantidad de cada paso, el costo por paso, el facturado, el cash neto, la ganancia, el ROAS, el techo y el semáforo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="30" customHeight="1">
-      <c r="B96" s="5" t="inlineStr">
-        <is>
-          <t>Una variable por vez: si cambiás tres cosas no sabés cuál movió el resultado. La columna Diferencia te muestra exactamente cuánto cambió cada número contra la base.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="30" customHeight="1">
-      <c r="B97" s="5" t="inlineStr">
-        <is>
-          <t>El Simulador no modifica Supuestos ni Modelo: es tu mesa de pruebas. Cuando una prueba te convence, pasá ese número a Supuestos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="B98" s="5" t="inlineStr">
-        <is>
-          <t>La columna Rango avisa si escribiste algo imposible (un porcentaje fuera de 0 a 1, un negativo, texto) y Chequeos repite los chequeos del modelo con tus números del Simulador.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B97:H97"/>
-    <mergeCell ref="B98:H98"/>
-    <mergeCell ref="B95:H95"/>
-    <mergeCell ref="B96:H96"/>
-  </mergeCells>
-  <conditionalFormatting sqref="I6:I93">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="2">
-      <formula>"REVISAR"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C6:C93">
-    <cfRule type="expression" priority="2" dxfId="3">
-      <formula>AND(ISNUMBER(C6),C6&lt;&gt;D6)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E73:F73">
-    <cfRule type="expression" priority="3" dxfId="0">
-      <formula>LEFT(E73,5)="VERDE"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="4" dxfId="1">
-      <formula>LEFT(E73,8)="AMARILLO"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="2">
-      <formula>LEFT(E73,4)="ROJO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E85:F85">
-    <cfRule type="expression" priority="6" dxfId="0">
-      <formula>LEFT(E85,5)="VERDE"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="7" dxfId="1">
-      <formula>LEFT(E85,8)="AMARILLO"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="8" dxfId="2">
-      <formula>LEFT(E85,4)="ROJO"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="C11 C13 C20 C24 C28 C32 C36 C40 C44 C54 C55 C56 C59 C60 C62 C77" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Porcentaje fuera de rango" error="Escribí el porcentaje como fracción entre 0 y 1 (15 % = 0,15)." type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1</formula2>
-    </dataValidation>
-    <dataValidation sqref="C7 C9 C18 C22 C26 C30 C34 C38 C42 C46 C65 C67 C72 C86" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="0" errorTitle="Valor inválido" error="Tiene que ser un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
-      <formula1>0</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter>
-    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
-    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
-    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
-    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -6929,7 +3006,7 @@
           <t>Visitas a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="16">
         <f>'Modelo'!$C$8</f>
         <v/>
       </c>
@@ -6938,7 +3015,7 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$8/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -6966,15 +3043,15 @@
           <t>Abren el checkout</t>
         </is>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="16">
         <f>'Modelo'!$C$9</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="18">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$9/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7002,15 +3079,15 @@
           <t>Compran el producto principal</t>
         </is>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="16">
         <f>'Modelo'!$C$10</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="18">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$10/'Modelo'!$C$9)</f>
         <v/>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7038,15 +3115,15 @@
           <t>Toman el bump 1</t>
         </is>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="16">
         <f>'Modelo'!$C$15</f>
         <v/>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$15/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$15/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7077,15 +3154,15 @@
           <t>Toman el bump 2</t>
         </is>
       </c>
-      <c r="C10" s="22">
+      <c r="C10" s="16">
         <f>'Modelo'!$C$17</f>
         <v/>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$17/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$17/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7116,15 +3193,15 @@
           <t>Toman la OTO 1</t>
         </is>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="16">
         <f>'Modelo'!$C$19</f>
         <v/>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$19/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$19/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7155,15 +3232,15 @@
           <t>Toman la OTO 2</t>
         </is>
       </c>
-      <c r="C12" s="22">
+      <c r="C12" s="16">
         <f>'Modelo'!$C$21</f>
         <v/>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$21/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$21/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7194,15 +3271,15 @@
           <t>Toman la OTO 3</t>
         </is>
       </c>
-      <c r="C13" s="22">
+      <c r="C13" s="16">
         <f>'Modelo'!$C$23</f>
         <v/>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$23/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$23/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7233,15 +3310,15 @@
           <t>Toman la OTO 4</t>
         </is>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="16">
         <f>'Modelo'!$C$25</f>
         <v/>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$25/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$25/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7272,15 +3349,15 @@
           <t>Ascienden al programa</t>
         </is>
       </c>
-      <c r="C15" s="22">
+      <c r="C15" s="16">
         <f>'Modelo'!$C$27</f>
         <v/>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="18">
         <f>IF('Modelo'!$C$10=0,0,'Modelo'!$C$27/'Modelo'!$C$10)</f>
         <v/>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$27/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -7311,11 +3388,11 @@
           <t>Comprobalo con la fila de la unidad: costo + ganancia + fijos repartidos = techo</t>
         </is>
       </c>
-      <c r="F17" s="17">
+      <c r="F17" s="19">
         <f>F6</f>
         <v/>
       </c>
-      <c r="G17" s="17">
+      <c r="G17" s="19">
         <f>G6</f>
         <v/>
       </c>
@@ -7399,7 +3476,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7482,7 +3559,7 @@
           <t>Escenario en uso (1 = conservador · 2 = base · 3 = optimista)</t>
         </is>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G6" t="inlineStr">
@@ -7515,7 +3592,7 @@
           <t>Inversión en publicidad por mes</t>
         </is>
       </c>
-      <c r="C8" s="19" t="n">
+      <c r="C8" s="21" t="n">
         <v>9000</v>
       </c>
       <c r="G8" t="inlineStr">
@@ -7535,17 +3612,17 @@
           <t>Costo por visita a la página de ventas (VSL)</t>
         </is>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="19">
         <f>IF('Supuestos'!$C$6=1,D9,IF('Supuestos'!$C$6=2,E9,F9))</f>
         <v/>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="22" t="n">
         <v>0.4</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="E9" s="22" t="n">
         <v>0.3</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="F9" s="22" t="n">
         <v>0.22</v>
       </c>
       <c r="G9" t="inlineStr">
@@ -7578,7 +3655,7 @@
           <t>% de visitas que llegan al checkout</t>
         </is>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="18">
         <f>IF('Supuestos'!$C$6=1,D12,IF('Supuestos'!$C$6=2,E12,F12))</f>
         <v/>
       </c>
@@ -7608,7 +3685,7 @@
           <t>% de checkouts que terminan en compra</t>
         </is>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="18">
         <f>IF('Supuestos'!$C$6=1,D13,IF('Supuestos'!$C$6=2,E13,F13))</f>
         <v/>
       </c>
@@ -7651,7 +3728,7 @@
           <t>Producto principal: precio</t>
         </is>
       </c>
-      <c r="C16" s="16" t="n">
+      <c r="C16" s="22" t="n">
         <v>37</v>
       </c>
       <c r="G16" t="inlineStr">
@@ -7671,7 +3748,7 @@
           <t>Bump 1: precio</t>
         </is>
       </c>
-      <c r="C17" s="16" t="n">
+      <c r="C17" s="22" t="n">
         <v>17</v>
       </c>
       <c r="G17" t="inlineStr">
@@ -7691,7 +3768,7 @@
           <t>Bump 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="18">
         <f>IF('Supuestos'!$C$6=1,D18,IF('Supuestos'!$C$6=2,E18,F18))</f>
         <v/>
       </c>
@@ -7717,7 +3794,7 @@
           <t>Bump 2: precio</t>
         </is>
       </c>
-      <c r="C19" s="16" t="n">
+      <c r="C19" s="22" t="n">
         <v>17</v>
       </c>
       <c r="G19" t="inlineStr">
@@ -7737,7 +3814,7 @@
           <t>Bump 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="18">
         <f>IF('Supuestos'!$C$6=1,D20,IF('Supuestos'!$C$6=2,E20,F20))</f>
         <v/>
       </c>
@@ -7763,7 +3840,7 @@
           <t>OTO 1: precio</t>
         </is>
       </c>
-      <c r="C21" s="16" t="n">
+      <c r="C21" s="22" t="n">
         <v>47</v>
       </c>
       <c r="G21" t="inlineStr">
@@ -7783,7 +3860,7 @@
           <t>OTO 1: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="18">
         <f>IF('Supuestos'!$C$6=1,D22,IF('Supuestos'!$C$6=2,E22,F22))</f>
         <v/>
       </c>
@@ -7809,7 +3886,7 @@
           <t>OTO 2: precio</t>
         </is>
       </c>
-      <c r="C23" s="16" t="n">
+      <c r="C23" s="22" t="n">
         <v>17</v>
       </c>
       <c r="G23" t="inlineStr">
@@ -7829,7 +3906,7 @@
           <t>OTO 2: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="18">
         <f>IF('Supuestos'!$C$6=1,D24,IF('Supuestos'!$C$6=2,E24,F24))</f>
         <v/>
       </c>
@@ -7855,7 +3932,7 @@
           <t>OTO 3: precio</t>
         </is>
       </c>
-      <c r="C25" s="16" t="n">
+      <c r="C25" s="22" t="n">
         <v>97</v>
       </c>
       <c r="G25" t="inlineStr">
@@ -7875,7 +3952,7 @@
           <t>OTO 3: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="18">
         <f>IF('Supuestos'!$C$6=1,D26,IF('Supuestos'!$C$6=2,E26,F26))</f>
         <v/>
       </c>
@@ -7901,7 +3978,7 @@
           <t>OTO 4: precio</t>
         </is>
       </c>
-      <c r="C27" s="16" t="n">
+      <c r="C27" s="22" t="n">
         <v>27</v>
       </c>
       <c r="G27" t="inlineStr">
@@ -7921,7 +3998,7 @@
           <t>OTO 4: % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="18">
         <f>IF('Supuestos'!$C$6=1,D28,IF('Supuestos'!$C$6=2,E28,F28))</f>
         <v/>
       </c>
@@ -7947,7 +4024,7 @@
           <t>Ascensión (programa de mayor valor): precio</t>
         </is>
       </c>
-      <c r="C29" s="16" t="n">
+      <c r="C29" s="22" t="n">
         <v>297</v>
       </c>
       <c r="G29" t="inlineStr">
@@ -7967,7 +4044,7 @@
           <t>Ascensión (programa de mayor valor): % de compradores que lo toman</t>
         </is>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="18">
         <f>IF('Supuestos'!$C$6=1,D30,IF('Supuestos'!$C$6=2,E30,F30))</f>
         <v/>
       </c>
@@ -8066,7 +4143,7 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C36" s="16" t="n">
+      <c r="C36" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="inlineStr">
@@ -8086,7 +4163,7 @@
           <t>Costos fijos por mes</t>
         </is>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="21" t="n">
         <v>1500</v>
       </c>
       <c r="G37" t="inlineStr">
@@ -8192,7 +4269,7 @@
           <t>ROAS objetivo sobre cash neto</t>
         </is>
       </c>
-      <c r="C45" s="28" t="n">
+      <c r="C45" s="24" t="n">
         <v>2</v>
       </c>
       <c r="G45" t="inlineStr">
@@ -8232,7 +4309,7 @@
           <t>Meta de ventas del producto principal</t>
         </is>
       </c>
-      <c r="C47" s="30" t="n">
+      <c r="C47" s="20" t="n">
         <v>500</v>
       </c>
       <c r="G47" t="inlineStr">
@@ -8272,7 +4349,7 @@
           <t>Caja inicial</t>
         </is>
       </c>
-      <c r="C49" s="19" t="n">
+      <c r="C49" s="21" t="n">
         <v>5000</v>
       </c>
       <c r="G49" t="inlineStr">
@@ -8299,7 +4376,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8367,7 +4444,7 @@
           <t>Costo por visita (unidad de adquisición)</t>
         </is>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="19">
         <f>'Supuestos'!$C$9</f>
         <v/>
       </c>
@@ -8383,7 +4460,7 @@
           <t>Visitas a la página de ventas</t>
         </is>
       </c>
-      <c r="C8" s="21">
+      <c r="C8" s="25">
         <f>IF('Modelo'!$C$7=0,0,'Supuestos'!$C$8/'Modelo'!$C$7)</f>
         <v/>
       </c>
@@ -8399,7 +4476,7 @@
           <t>Checkouts iniciados</t>
         </is>
       </c>
-      <c r="C9" s="22">
+      <c r="C9" s="16">
         <f>'Modelo'!$C$8*'Supuestos'!$C$12</f>
         <v/>
       </c>
@@ -8431,7 +4508,7 @@
           <t>% de visitas que compran</t>
         </is>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -8472,7 +4549,7 @@
           <t>Facturado: producto principal</t>
         </is>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="26">
         <f>'Modelo'!$C$10*'Supuestos'!$C$16</f>
         <v/>
       </c>
@@ -8488,7 +4565,7 @@
           <t>Ventas: Bump 1</t>
         </is>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$18</f>
         <v/>
       </c>
@@ -8504,7 +4581,7 @@
           <t>Facturado: Bump 1</t>
         </is>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="26">
         <f>'Modelo'!$C$15*'Supuestos'!$C$17</f>
         <v/>
       </c>
@@ -8520,7 +4597,7 @@
           <t>Ventas: Bump 2</t>
         </is>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$20</f>
         <v/>
       </c>
@@ -8536,7 +4613,7 @@
           <t>Facturado: Bump 2</t>
         </is>
       </c>
-      <c r="C18" s="20">
+      <c r="C18" s="26">
         <f>'Modelo'!$C$17*'Supuestos'!$C$19</f>
         <v/>
       </c>
@@ -8552,7 +4629,7 @@
           <t>Ventas: OTO 1</t>
         </is>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$22</f>
         <v/>
       </c>
@@ -8568,7 +4645,7 @@
           <t>Facturado: OTO 1</t>
         </is>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="26">
         <f>'Modelo'!$C$19*'Supuestos'!$C$21</f>
         <v/>
       </c>
@@ -8584,7 +4661,7 @@
           <t>Ventas: OTO 2</t>
         </is>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$24</f>
         <v/>
       </c>
@@ -8600,7 +4677,7 @@
           <t>Facturado: OTO 2</t>
         </is>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="26">
         <f>'Modelo'!$C$21*'Supuestos'!$C$23</f>
         <v/>
       </c>
@@ -8616,7 +4693,7 @@
           <t>Ventas: OTO 3</t>
         </is>
       </c>
-      <c r="C23" s="25">
+      <c r="C23" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$26</f>
         <v/>
       </c>
@@ -8632,7 +4709,7 @@
           <t>Facturado: OTO 3</t>
         </is>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="26">
         <f>'Modelo'!$C$23*'Supuestos'!$C$25</f>
         <v/>
       </c>
@@ -8648,7 +4725,7 @@
           <t>Ventas: OTO 4</t>
         </is>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$28</f>
         <v/>
       </c>
@@ -8664,7 +4741,7 @@
           <t>Facturado: OTO 4</t>
         </is>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="26">
         <f>'Modelo'!$C$25*'Supuestos'!$C$27</f>
         <v/>
       </c>
@@ -8680,7 +4757,7 @@
           <t>Ventas: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="27">
         <f>'Modelo'!$C$10*'Supuestos'!$C$30</f>
         <v/>
       </c>
@@ -8696,7 +4773,7 @@
           <t>Facturado: Ascensión (programa de mayor valor)</t>
         </is>
       </c>
-      <c r="C28" s="20">
+      <c r="C28" s="26">
         <f>'Modelo'!$C$27*'Supuestos'!$C$29</f>
         <v/>
       </c>
@@ -8744,7 +4821,7 @@
           <t>AOV ÷ precio del principal</t>
         </is>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <f>IF('Supuestos'!$C$16=0,0,'Modelo'!$C$30/'Supuestos'!$C$16)</f>
         <v/>
       </c>
@@ -8760,7 +4837,7 @@
           <t>Ventas del principal por visita (para la proyección)</t>
         </is>
       </c>
-      <c r="C32" s="26">
+      <c r="C32" s="17">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$10/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -8776,7 +4853,7 @@
           <t>Facturado por visita</t>
         </is>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="19">
         <f>IF('Modelo'!$C$8=0,0,'Modelo'!$C$29/'Modelo'!$C$8)</f>
         <v/>
       </c>
@@ -8801,7 +4878,7 @@
           <t>Cash a cobrar (facturado × cobranza completa)</t>
         </is>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="26">
         <f>'Modelo'!$C$29*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42)</f>
         <v/>
       </c>
@@ -8817,7 +4894,7 @@
           <t>Cash que entra en el primer mes</t>
         </is>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="26">
         <f>'Modelo'!$C$29*'Supuestos'!$C$40</f>
         <v/>
       </c>
@@ -8833,7 +4910,7 @@
           <t>Comisiones (pasarela + ventas)</t>
         </is>
       </c>
-      <c r="C37" s="20">
+      <c r="C37" s="26">
         <f>'Modelo'!$C$35*('Supuestos'!$C$33+'Supuestos'!$C$34)</f>
         <v/>
       </c>
@@ -8849,7 +4926,7 @@
           <t>Reembolsos</t>
         </is>
       </c>
-      <c r="C38" s="20">
+      <c r="C38" s="26">
         <f>'Modelo'!$C$35*'Supuestos'!$C$35</f>
         <v/>
       </c>
@@ -8881,7 +4958,7 @@
           <t>Costos por visita (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C40" s="20">
+      <c r="C40" s="26">
         <f>'Modelo'!$C$8*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -8913,7 +4990,7 @@
           <t>ROAS sobre facturado</t>
         </is>
       </c>
-      <c r="C42" s="27">
+      <c r="C42" s="28">
         <f>IF('Supuestos'!$C$8=0,0,'Modelo'!$C$29/'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -8945,7 +5022,7 @@
           <t>Margen sobre cash</t>
         </is>
       </c>
-      <c r="C44" s="24">
+      <c r="C44" s="18">
         <f>IF('Modelo'!$C$35=0,0,'Modelo'!$C$41/'Modelo'!$C$35)</f>
         <v/>
       </c>
@@ -9034,7 +5111,7 @@
           <t>Techo de costo por checkout</t>
         </is>
       </c>
-      <c r="C50" s="17">
+      <c r="C50" s="19">
         <f>IF('Supuestos'!$C$12=0,0,'Modelo'!$C$47/'Supuestos'!$C$12)</f>
         <v/>
       </c>
@@ -9066,7 +5143,7 @@
           <t>Objetivo de CPA</t>
         </is>
       </c>
-      <c r="C52" s="17">
+      <c r="C52" s="19">
         <f>'Modelo'!$C$51/(1+'Supuestos'!$C$46)</f>
         <v/>
       </c>
@@ -9082,7 +5159,7 @@
           <t>Cash neto por comprador (AOV neto)</t>
         </is>
       </c>
-      <c r="C53" s="17">
+      <c r="C53" s="19">
         <f>IF('Modelo'!$C$10=0,0,('Modelo'!$C$39-'Modelo'!$C$40)/'Modelo'!$C$10)</f>
         <v/>
       </c>
@@ -9155,7 +5232,7 @@
           <t>Inversión para la meta al costo objetivo (lo máximo que conviene pagar)</t>
         </is>
       </c>
-      <c r="C58" s="20">
+      <c r="C58" s="26">
         <f>IF('Modelo'!$C$11=0,"inalcanzable con estos supuestos",'Supuestos'!$C$47/'Modelo'!$C$11*'Modelo'!$C$49)</f>
         <v/>
       </c>
@@ -9196,7 +5273,7 @@
           <t>Ganancia por checkout</t>
         </is>
       </c>
-      <c r="C61" s="17">
+      <c r="C61" s="19">
         <f>IF('Modelo'!$C$9=0,0,'Modelo'!$C$41/'Modelo'!$C$9)</f>
         <v/>
       </c>
@@ -9246,7 +5323,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9295,7 +5372,7 @@
           <t>Umbral de 'cerca del cero' (inversión × margen de seguridad)</t>
         </is>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="26">
         <f>'Supuestos'!$C$8*'Supuestos'!$C$46</f>
         <v/>
       </c>
@@ -9320,143 +5397,143 @@
           <t>Precio ↓  /  % checkout → compra →</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="30" t="n">
         <v>0.18</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="30" t="n">
         <v>0.22</v>
       </c>
-      <c r="E9" s="31" t="n">
+      <c r="E9" s="30" t="n">
         <v>0.26</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="30" t="n">
         <v>0.3</v>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="30" t="n">
         <v>0.34</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="32" t="n">
+      <c r="B10" s="31" t="n">
         <v>27</v>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B10)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="32" t="n">
+      <c r="B11" s="31" t="n">
         <v>37</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B11)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="32" t="n">
+      <c r="B12" s="31" t="n">
         <v>47</v>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B12)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="32" t="n">
+      <c r="B13" s="31" t="n">
         <v>67</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B13)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="32" t="n">
+      <c r="B14" s="31" t="n">
         <v>97</v>
       </c>
-      <c r="C14" s="20">
+      <c r="C14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*C$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*D$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*E$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*F$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G14" s="20">
+      <c r="G14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*$B14)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*G$9)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9481,224 +5558,224 @@
           <t>Costo por visita ↓  /  % visita → checkout →</t>
         </is>
       </c>
-      <c r="C19" s="31" t="n">
+      <c r="C19" s="30" t="n">
         <v>0.02</v>
       </c>
-      <c r="D19" s="31" t="n">
+      <c r="D19" s="30" t="n">
         <v>0.025</v>
       </c>
-      <c r="E19" s="31" t="n">
+      <c r="E19" s="30" t="n">
         <v>0.03</v>
       </c>
-      <c r="F19" s="31" t="n">
+      <c r="F19" s="30" t="n">
         <v>0.035</v>
       </c>
-      <c r="G19" s="31" t="n">
+      <c r="G19" s="30" t="n">
         <v>0.04</v>
       </c>
-      <c r="H19" s="31" t="n">
+      <c r="H19" s="30" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="33" t="n">
+      <c r="B20" s="32" t="n">
         <v>0.15</v>
       </c>
-      <c r="C20" s="20">
+      <c r="C20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D20" s="20">
+      <c r="D20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E20" s="20">
+      <c r="E20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F20" s="20">
+      <c r="F20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G20" s="20">
+      <c r="G20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H20" s="20">
+      <c r="H20" s="26">
         <f>((((((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B20=0,0,'Supuestos'!$C$8/$B20))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B20=0,0,'Supuestos'!$C$8/$B20))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="32" t="n">
         <v>0.2</v>
       </c>
-      <c r="C21" s="20">
+      <c r="C21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F21" s="20">
+      <c r="F21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G21" s="20">
+      <c r="G21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H21" s="20">
+      <c r="H21" s="26">
         <f>((((((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B21=0,0,'Supuestos'!$C$8/$B21))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B21=0,0,'Supuestos'!$C$8/$B21))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="33" t="n">
+      <c r="B22" s="32" t="n">
         <v>0.25</v>
       </c>
-      <c r="C22" s="20">
+      <c r="C22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D22" s="20">
+      <c r="D22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G22" s="20">
+      <c r="G22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H22" s="20">
+      <c r="H22" s="26">
         <f>((((((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B22=0,0,'Supuestos'!$C$8/$B22))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B22=0,0,'Supuestos'!$C$8/$B22))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="33" t="n">
+      <c r="B23" s="32" t="n">
         <v>0.3</v>
       </c>
-      <c r="C23" s="20">
+      <c r="C23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D23" s="20">
+      <c r="D23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E23" s="20">
+      <c r="E23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F23" s="20">
+      <c r="F23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G23" s="20">
+      <c r="G23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H23" s="20">
+      <c r="H23" s="26">
         <f>((((((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B23=0,0,'Supuestos'!$C$8/$B23))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B23=0,0,'Supuestos'!$C$8/$B23))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="33" t="n">
+      <c r="B24" s="32" t="n">
         <v>0.4</v>
       </c>
-      <c r="C24" s="20">
+      <c r="C24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D24" s="20">
+      <c r="D24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E24" s="20">
+      <c r="E24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F24" s="20">
+      <c r="F24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G24" s="20">
+      <c r="G24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H24" s="20">
+      <c r="H24" s="26">
         <f>((((((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B24=0,0,'Supuestos'!$C$8/$B24))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B24=0,0,'Supuestos'!$C$8/$B24))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="33" t="n">
+      <c r="B25" s="32" t="n">
         <v>0.5</v>
       </c>
-      <c r="C25" s="20">
+      <c r="C25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D25" s="20">
+      <c r="D25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F25" s="20">
+      <c r="F25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G25" s="20">
+      <c r="G25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H25" s="20">
+      <c r="H25" s="26">
         <f>((((((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B25=0,0,'Supuestos'!$C$8/$B25))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B25=0,0,'Supuestos'!$C$8/$B25))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="33" t="n">
+      <c r="B26" s="32" t="n">
         <v>0.6</v>
       </c>
-      <c r="C26" s="20">
+      <c r="C26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*C$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="D26" s="20">
+      <c r="D26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*D$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*E$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*F$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="G26" s="20">
+      <c r="G26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*G$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="H26" s="20">
+      <c r="H26" s="26">
         <f>((((((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF($B26=0,0,'Supuestos'!$C$8/$B26))*H$19)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF($B26=0,0,'Supuestos'!$C$8/$B26))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
@@ -9723,143 +5800,143 @@
           <t>Facturación objetivo ↓ / ROAS objetivo →</t>
         </is>
       </c>
-      <c r="C31" s="34" t="n">
+      <c r="C31" s="33" t="n">
         <v>1.5</v>
       </c>
-      <c r="D31" s="34" t="n">
+      <c r="D31" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="34" t="n">
+      <c r="E31" s="33" t="n">
         <v>2.5</v>
       </c>
-      <c r="F31" s="34" t="n">
+      <c r="F31" s="33" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="34" t="n">
+      <c r="G31" s="33" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="32" t="n">
+      <c r="B32" s="31" t="n">
         <v>10000</v>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="26">
         <f>$B32/C$31</f>
         <v/>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="26">
         <f>$B32/D$31</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="26">
         <f>$B32/E$31</f>
         <v/>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="26">
         <f>$B32/F$31</f>
         <v/>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="26">
         <f>$B32/G$31</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="32" t="n">
+      <c r="B33" s="31" t="n">
         <v>20000</v>
       </c>
-      <c r="C33" s="20">
+      <c r="C33" s="26">
         <f>$B33/C$31</f>
         <v/>
       </c>
-      <c r="D33" s="20">
+      <c r="D33" s="26">
         <f>$B33/D$31</f>
         <v/>
       </c>
-      <c r="E33" s="20">
+      <c r="E33" s="26">
         <f>$B33/E$31</f>
         <v/>
       </c>
-      <c r="F33" s="20">
+      <c r="F33" s="26">
         <f>$B33/F$31</f>
         <v/>
       </c>
-      <c r="G33" s="20">
+      <c r="G33" s="26">
         <f>$B33/G$31</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="32" t="n">
+      <c r="B34" s="31" t="n">
         <v>30000</v>
       </c>
-      <c r="C34" s="20">
+      <c r="C34" s="26">
         <f>$B34/C$31</f>
         <v/>
       </c>
-      <c r="D34" s="20">
+      <c r="D34" s="26">
         <f>$B34/D$31</f>
         <v/>
       </c>
-      <c r="E34" s="20">
+      <c r="E34" s="26">
         <f>$B34/E$31</f>
         <v/>
       </c>
-      <c r="F34" s="20">
+      <c r="F34" s="26">
         <f>$B34/F$31</f>
         <v/>
       </c>
-      <c r="G34" s="20">
+      <c r="G34" s="26">
         <f>$B34/G$31</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="32" t="n">
+      <c r="B35" s="31" t="n">
         <v>50000</v>
       </c>
-      <c r="C35" s="20">
+      <c r="C35" s="26">
         <f>$B35/C$31</f>
         <v/>
       </c>
-      <c r="D35" s="20">
+      <c r="D35" s="26">
         <f>$B35/D$31</f>
         <v/>
       </c>
-      <c r="E35" s="20">
+      <c r="E35" s="26">
         <f>$B35/E$31</f>
         <v/>
       </c>
-      <c r="F35" s="20">
+      <c r="F35" s="26">
         <f>$B35/F$31</f>
         <v/>
       </c>
-      <c r="G35" s="20">
+      <c r="G35" s="26">
         <f>$B35/G$31</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="32" t="n">
+      <c r="B36" s="31" t="n">
         <v>100000</v>
       </c>
-      <c r="C36" s="20">
+      <c r="C36" s="26">
         <f>$B36/C$31</f>
         <v/>
       </c>
-      <c r="D36" s="20">
+      <c r="D36" s="26">
         <f>$B36/D$31</f>
         <v/>
       </c>
-      <c r="E36" s="20">
+      <c r="E36" s="26">
         <f>$B36/E$31</f>
         <v/>
       </c>
-      <c r="F36" s="20">
+      <c r="F36" s="26">
         <f>$B36/F$31</f>
         <v/>
       </c>
-      <c r="G36" s="20">
+      <c r="G36" s="26">
         <f>$B36/G$31</f>
         <v/>
       </c>
@@ -9872,51 +5949,51 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="35">
+      <c r="B38" s="34">
         <f>$B32</f>
         <v/>
       </c>
-      <c r="C38" s="22">
+      <c r="C38" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B32/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="35">
+      <c r="B39" s="34">
         <f>$B33</f>
         <v/>
       </c>
-      <c r="C39" s="22">
+      <c r="C39" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B33/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="35">
+      <c r="B40" s="34">
         <f>$B34</f>
         <v/>
       </c>
-      <c r="C40" s="22">
+      <c r="C40" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B34/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="35">
+      <c r="B41" s="34">
         <f>$B35</f>
         <v/>
       </c>
-      <c r="C41" s="22">
+      <c r="C41" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B35/'Modelo'!$C$33)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="35">
+      <c r="B42" s="34">
         <f>$B36</f>
         <v/>
       </c>
-      <c r="C42" s="22">
+      <c r="C42" s="16">
         <f>IF('Modelo'!$C$33=0,"inalcanzable",$B36/'Modelo'!$C$33)</f>
         <v/>
       </c>
@@ -9929,19 +6006,19 @@
       </c>
     </row>
     <row r="45">
-      <c r="C45" s="36" t="n">
+      <c r="C45" s="35" t="n">
         <v>1.5</v>
       </c>
-      <c r="D45" s="36" t="n">
+      <c r="D45" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="E45" s="36" t="n">
+      <c r="E45" s="35" t="n">
         <v>2.5</v>
       </c>
-      <c r="F45" s="36" t="n">
+      <c r="F45" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="G45" s="36" t="n">
+      <c r="G45" s="35" t="n">
         <v>4</v>
       </c>
     </row>
@@ -9951,23 +6028,23 @@
           <t>Costo máximo (facturado por unidad ÷ ROAS)</t>
         </is>
       </c>
-      <c r="C46" s="17">
+      <c r="C46" s="19">
         <f>IF(C45=0,0,'Modelo'!$C$33/C45)</f>
         <v/>
       </c>
-      <c r="D46" s="17">
+      <c r="D46" s="19">
         <f>IF(D45=0,0,'Modelo'!$C$33/D45)</f>
         <v/>
       </c>
-      <c r="E46" s="17">
+      <c r="E46" s="19">
         <f>IF(E45=0,0,'Modelo'!$C$33/E45)</f>
         <v/>
       </c>
-      <c r="F46" s="17">
+      <c r="F46" s="19">
         <f>IF(F45=0,0,'Modelo'!$C$33/F45)</f>
         <v/>
       </c>
-      <c r="G46" s="17">
+      <c r="G46" s="19">
         <f>IF(G45=0,0,'Modelo'!$C$33/G45)</f>
         <v/>
       </c>
@@ -10021,15 +6098,15 @@
           <t>actual</t>
         </is>
       </c>
-      <c r="C53" s="20">
+      <c r="C53" s="26">
         <f>'Supuestos'!$C$8*1.0</f>
         <v/>
       </c>
-      <c r="D53" s="27">
+      <c r="D53" s="28">
         <f>IF(C53=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C53-'Supuestos'!$C$8))/C53)</f>
         <v/>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="26">
         <f>C53*(D53-1)</f>
         <v/>
       </c>
@@ -10040,15 +6117,15 @@
           <t>× 1.25</t>
         </is>
       </c>
-      <c r="C54" s="20">
+      <c r="C54" s="26">
         <f>'Supuestos'!$C$8*1.25</f>
         <v/>
       </c>
-      <c r="D54" s="27">
+      <c r="D54" s="28">
         <f>IF(C54=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C54-'Supuestos'!$C$8))/C54)</f>
         <v/>
       </c>
-      <c r="E54" s="20">
+      <c r="E54" s="26">
         <f>C54*(D54-1)</f>
         <v/>
       </c>
@@ -10059,15 +6136,15 @@
           <t>× 1.5</t>
         </is>
       </c>
-      <c r="C55" s="20">
+      <c r="C55" s="26">
         <f>'Supuestos'!$C$8*1.5</f>
         <v/>
       </c>
-      <c r="D55" s="27">
+      <c r="D55" s="28">
         <f>IF(C55=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C55-'Supuestos'!$C$8))/C55)</f>
         <v/>
       </c>
-      <c r="E55" s="20">
+      <c r="E55" s="26">
         <f>C55*(D55-1)</f>
         <v/>
       </c>
@@ -10078,15 +6155,15 @@
           <t>× 2</t>
         </is>
       </c>
-      <c r="C56" s="20">
+      <c r="C56" s="26">
         <f>'Supuestos'!$C$8*2.0</f>
         <v/>
       </c>
-      <c r="D56" s="27">
+      <c r="D56" s="28">
         <f>IF(C56=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C56-'Supuestos'!$C$8))/C56)</f>
         <v/>
       </c>
-      <c r="E56" s="20">
+      <c r="E56" s="26">
         <f>C56*(D56-1)</f>
         <v/>
       </c>
@@ -10097,15 +6174,15 @@
           <t>× 3</t>
         </is>
       </c>
-      <c r="C57" s="20">
+      <c r="C57" s="26">
         <f>'Supuestos'!$C$8*3.0</f>
         <v/>
       </c>
-      <c r="D57" s="27">
+      <c r="D57" s="28">
         <f>IF(C57=0,0,('Supuestos'!$C$8*'Modelo'!$C$43+1.3*(C57-'Supuestos'!$C$8))/C57)</f>
         <v/>
       </c>
-      <c r="E57" s="20">
+      <c r="E57" s="26">
         <f>C57*(D57-1)</f>
         <v/>
       </c>
@@ -10147,7 +6224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10240,19 +6317,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D7" s="20">
+      <c r="D7" s="26">
         <f>((((((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF((('Supuestos'!$C$9*0.9))=0,0,'Supuestos'!$C$8/(('Supuestos'!$C$9*0.9))))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E7" s="20">
+      <c r="E7" s="26">
         <f>D7-$D$6</f>
         <v/>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="18">
         <f>IF($D$6=0,0,E7/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="16">
         <f>RANK(E7,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10268,19 +6345,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D8" s="20">
+      <c r="D8" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*('Supuestos'!$C$12*1.1))*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="26">
         <f>D8-$D$6</f>
         <v/>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <f>IF($D$6=0,0,E8/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="16">
         <f>RANK(E8,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10296,19 +6373,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*('Supuestos'!$C$13*1.1))*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="26">
         <f>D9-$D$6</f>
         <v/>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <f>IF($D$6=0,0,E9/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G9" s="22">
+      <c r="G9" s="16">
         <f>RANK(E9,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10324,19 +6401,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$16*1.1))+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="26">
         <f>D10-$D$6</f>
         <v/>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <f>IF($D$6=0,0,E10/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G10" s="22">
+      <c r="G10" s="16">
         <f>RANK(E10,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10352,19 +6429,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$18*1.1))*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="26">
         <f>D11-$D$6</f>
         <v/>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="18">
         <f>IF($D$6=0,0,E11/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G11" s="22">
+      <c r="G11" s="16">
         <f>RANK(E11,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10380,19 +6457,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$22*1.1))*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="26">
         <f>D12-$D$6</f>
         <v/>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="18">
         <f>IF($D$6=0,0,E12/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G12" s="22">
+      <c r="G12" s="16">
         <f>RANK(E12,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10408,19 +6485,19 @@
           <t>+10 %</t>
         </is>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*('Supuestos'!$C$30*1.1))*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="26">
         <f>D13-$D$6</f>
         <v/>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="18">
         <f>IF($D$6=0,0,E13/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G13" s="22">
+      <c r="G13" s="16">
         <f>RANK(E13,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10436,19 +6513,19 @@
           <t>−10 %</t>
         </is>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="26">
         <f>((((((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$16)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$18)*'Supuestos'!$C$17)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$20)*'Supuestos'!$C$19)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$22)*'Supuestos'!$C$21)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$24)*'Supuestos'!$C$23)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$26)*'Supuestos'!$C$25)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$28)*'Supuestos'!$C$27)+(((((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$12)*'Supuestos'!$C$13)*'Supuestos'!$C$30)*'Supuestos'!$C$29))*('Supuestos'!$C$40+'Supuestos'!$C$41+'Supuestos'!$C$42))*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-('Supuestos'!$C$35*0.9)))-((IF(('Supuestos'!$C$9)=0,0,'Supuestos'!$C$8/('Supuestos'!$C$9)))*'Supuestos'!$C$36)-'Supuestos'!$C$37-'Supuestos'!$C$8)</f>
         <v/>
       </c>
-      <c r="E14" s="20">
+      <c r="E14" s="26">
         <f>D14-$D$6</f>
         <v/>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="18">
         <f>IF($D$6=0,0,E14/ABS($D$6))</f>
         <v/>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="16">
         <f>RANK(E14,$E$7:$E$14)</f>
         <v/>
       </c>
@@ -10466,7 +6543,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10591,51 +6668,51 @@
           <t>Inversión en publicidad del mes</t>
         </is>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="26">
         <f>'Supuestos'!$C$8*1</f>
         <v/>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="26">
         <f>C6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="26">
         <f>D6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="F6" s="20">
+      <c r="F6" s="26">
         <f>E6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="G6" s="20">
+      <c r="G6" s="26">
         <f>F6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="H6" s="20">
+      <c r="H6" s="26">
         <f>G6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="I6" s="20">
+      <c r="I6" s="26">
         <f>H6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="J6" s="20">
+      <c r="J6" s="26">
         <f>I6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="K6" s="20">
+      <c r="K6" s="26">
         <f>J6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="L6" s="20">
+      <c r="L6" s="26">
         <f>K6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="26">
         <f>L6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
-      <c r="N6" s="20">
+      <c r="N6" s="26">
         <f>M6*(1+'Supuestos'!$C$48)</f>
         <v/>
       </c>
@@ -10650,55 +6727,55 @@
           <t>Visitas compradas</t>
         </is>
       </c>
-      <c r="C7" s="22">
+      <c r="C7" s="16">
         <f>IF('Modelo'!$C$7=0,0,C6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="D7" s="22">
+      <c r="D7" s="16">
         <f>IF('Modelo'!$C$7=0,0,D6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="16">
         <f>IF('Modelo'!$C$7=0,0,E6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="16">
         <f>IF('Modelo'!$C$7=0,0,F6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="G7" s="22">
+      <c r="G7" s="16">
         <f>IF('Modelo'!$C$7=0,0,G6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="16">
         <f>IF('Modelo'!$C$7=0,0,H6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="16">
         <f>IF('Modelo'!$C$7=0,0,I6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="16">
         <f>IF('Modelo'!$C$7=0,0,J6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="K7" s="22">
+      <c r="K7" s="16">
         <f>IF('Modelo'!$C$7=0,0,K6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="16">
         <f>IF('Modelo'!$C$7=0,0,L6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="M7" s="22">
+      <c r="M7" s="16">
         <f>IF('Modelo'!$C$7=0,0,M6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="N7" s="22">
+      <c r="N7" s="16">
         <f>IF('Modelo'!$C$7=0,0,N6/'Modelo'!$C$7)</f>
         <v/>
       </c>
-      <c r="O7" s="21">
+      <c r="O7" s="25">
         <f>SUM(C7:N7)</f>
         <v/>
       </c>
@@ -10709,51 +6786,51 @@
           <t>Ventas del producto principal</t>
         </is>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="27">
         <f>C7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="27">
         <f>D7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="27">
         <f>E7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="27">
         <f>F7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="27">
         <f>G7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="27">
         <f>H7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="27">
         <f>I7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="27">
         <f>J7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="27">
         <f>K7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="27">
         <f>L7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="27">
         <f>M7*'Modelo'!$C$32</f>
         <v/>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="27">
         <f>N7*'Modelo'!$C$32</f>
         <v/>
       </c>
@@ -10768,51 +6845,51 @@
           <t>Facturado (todos los productos)</t>
         </is>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="26">
         <f>C7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="D9" s="20">
+      <c r="D9" s="26">
         <f>D7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="E9" s="20">
+      <c r="E9" s="26">
         <f>E7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="F9" s="20">
+      <c r="F9" s="26">
         <f>F7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="G9" s="20">
+      <c r="G9" s="26">
         <f>G7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="H9" s="20">
+      <c r="H9" s="26">
         <f>H7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="I9" s="20">
+      <c r="I9" s="26">
         <f>I7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="J9" s="20">
+      <c r="J9" s="26">
         <f>J7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="K9" s="20">
+      <c r="K9" s="26">
         <f>K7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="L9" s="20">
+      <c r="L9" s="26">
         <f>L7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="M9" s="20">
+      <c r="M9" s="26">
         <f>M7*'Modelo'!$C$33</f>
         <v/>
       </c>
-      <c r="N9" s="20">
+      <c r="N9" s="26">
         <f>N7*'Modelo'!$C$33</f>
         <v/>
       </c>
@@ -10827,51 +6904,51 @@
           <t>Cash cobrado en el mes</t>
         </is>
       </c>
-      <c r="C10" s="20">
+      <c r="C10" s="26">
         <f>C9*'Supuestos'!$C$40</f>
         <v/>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="26">
         <f>D9*'Supuestos'!$C$40+C9*'Supuestos'!$C$41</f>
         <v/>
       </c>
-      <c r="E10" s="20">
+      <c r="E10" s="26">
         <f>E9*'Supuestos'!$C$40+D9*'Supuestos'!$C$41+C9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="26">
         <f>F9*'Supuestos'!$C$40+E9*'Supuestos'!$C$41+D9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="26">
         <f>G9*'Supuestos'!$C$40+F9*'Supuestos'!$C$41+E9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="H10" s="20">
+      <c r="H10" s="26">
         <f>H9*'Supuestos'!$C$40+G9*'Supuestos'!$C$41+F9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="I10" s="20">
+      <c r="I10" s="26">
         <f>I9*'Supuestos'!$C$40+H9*'Supuestos'!$C$41+G9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="J10" s="20">
+      <c r="J10" s="26">
         <f>J9*'Supuestos'!$C$40+I9*'Supuestos'!$C$41+H9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="K10" s="20">
+      <c r="K10" s="26">
         <f>K9*'Supuestos'!$C$40+J9*'Supuestos'!$C$41+I9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="L10" s="20">
+      <c r="L10" s="26">
         <f>L9*'Supuestos'!$C$40+K9*'Supuestos'!$C$41+J9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="M10" s="20">
+      <c r="M10" s="26">
         <f>M9*'Supuestos'!$C$40+L9*'Supuestos'!$C$41+K9*'Supuestos'!$C$42</f>
         <v/>
       </c>
-      <c r="N10" s="20">
+      <c r="N10" s="26">
         <f>N9*'Supuestos'!$C$40+M9*'Supuestos'!$C$41+L9*'Supuestos'!$C$42</f>
         <v/>
       </c>
@@ -10886,51 +6963,51 @@
           <t>Comisiones y reembolsos</t>
         </is>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="26">
         <f>C10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="D11" s="20">
+      <c r="D11" s="26">
         <f>D10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="E11" s="20">
+      <c r="E11" s="26">
         <f>E10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="26">
         <f>F10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="G11" s="20">
+      <c r="G11" s="26">
         <f>G10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="H11" s="20">
+      <c r="H11" s="26">
         <f>H10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="26">
         <f>I10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="J11" s="20">
+      <c r="J11" s="26">
         <f>J10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="K11" s="20">
+      <c r="K11" s="26">
         <f>K10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="L11" s="20">
+      <c r="L11" s="26">
         <f>L10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="M11" s="20">
+      <c r="M11" s="26">
         <f>M10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
-      <c r="N11" s="20">
+      <c r="N11" s="26">
         <f>N10*('Supuestos'!$C$33+'Supuestos'!$C$34+'Supuestos'!$C$35)</f>
         <v/>
       </c>
@@ -10945,51 +7022,51 @@
           <t>Costos por unidad (herramientas, WhatsApp, IA)</t>
         </is>
       </c>
-      <c r="C12" s="20">
+      <c r="C12" s="26">
         <f>C7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="D12" s="20">
+      <c r="D12" s="26">
         <f>D7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="E12" s="20">
+      <c r="E12" s="26">
         <f>E7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="26">
         <f>F7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="26">
         <f>G7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="H12" s="20">
+      <c r="H12" s="26">
         <f>H7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="26">
         <f>I7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="26">
         <f>J7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="K12" s="20">
+      <c r="K12" s="26">
         <f>K7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="L12" s="20">
+      <c r="L12" s="26">
         <f>L7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="M12" s="20">
+      <c r="M12" s="26">
         <f>M7*'Supuestos'!$C$36</f>
         <v/>
       </c>
-      <c r="N12" s="20">
+      <c r="N12" s="26">
         <f>N7*'Supuestos'!$C$36</f>
         <v/>
       </c>
@@ -11004,51 +7081,51 @@
           <t>Costos fijos del mes</t>
         </is>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="D13" s="20">
+      <c r="D13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="E13" s="20">
+      <c r="E13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="G13" s="20">
+      <c r="G13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="H13" s="20">
+      <c r="H13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="J13" s="20">
+      <c r="J13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="K13" s="20">
+      <c r="K13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="L13" s="20">
+      <c r="L13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="M13" s="20">
+      <c r="M13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
-      <c r="N13" s="20">
+      <c r="N13" s="26">
         <f>'Supuestos'!$C$37*1</f>
         <v/>
       </c>
@@ -11177,51 +7254,51 @@
           <t>Saldo de caja (caja inicial + ganancia acumulada)</t>
         </is>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="26">
         <f>'Supuestos'!$C$49+C15</f>
         <v/>
       </c>
-      <c r="D16" s="20">
+      <c r="D16" s="26">
         <f>'Supuestos'!$C$49+D15</f>
         <v/>
       </c>
-      <c r="E16" s="20">
+      <c r="E16" s="26">
         <f>'Supuestos'!$C$49+E15</f>
         <v/>
       </c>
-      <c r="F16" s="20">
+      <c r="F16" s="26">
         <f>'Supuestos'!$C$49+F15</f>
         <v/>
       </c>
-      <c r="G16" s="20">
+      <c r="G16" s="26">
         <f>'Supuestos'!$C$49+G15</f>
         <v/>
       </c>
-      <c r="H16" s="20">
+      <c r="H16" s="26">
         <f>'Supuestos'!$C$49+H15</f>
         <v/>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="26">
         <f>'Supuestos'!$C$49+I15</f>
         <v/>
       </c>
-      <c r="J16" s="20">
+      <c r="J16" s="26">
         <f>'Supuestos'!$C$49+J15</f>
         <v/>
       </c>
-      <c r="K16" s="20">
+      <c r="K16" s="26">
         <f>'Supuestos'!$C$49+K15</f>
         <v/>
       </c>
-      <c r="L16" s="20">
+      <c r="L16" s="26">
         <f>'Supuestos'!$C$49+L15</f>
         <v/>
       </c>
-      <c r="M16" s="20">
+      <c r="M16" s="26">
         <f>'Supuestos'!$C$49+M15</f>
         <v/>
       </c>
-      <c r="N16" s="20">
+      <c r="N16" s="26">
         <f>'Supuestos'!$C$49+N15</f>
         <v/>
       </c>
@@ -11282,4 +7359,1389 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro · uso personal; no redistribuir modificado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Seguimiento: una columna por mes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Cargá los datos reales en las celdas amarillas. El semáforo compara tu costo real por visita con el techo móvil (lo que rindieron tus últimas 4 columnas) y con el techo del modelo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 1</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 2</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 3</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 4</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 5</t>
+        </is>
+      </c>
+      <c r="H5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 6</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 7</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 8</t>
+        </is>
+      </c>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 9</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 10</t>
+        </is>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 11</t>
+        </is>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>Mes 12</t>
+        </is>
+      </c>
+      <c r="O5" s="6" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>Máximo</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>Mínimo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Datos que cargás</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="8" t="n"/>
+      <c r="F6" s="8" t="n"/>
+      <c r="G6" s="8" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
+      <c r="J6" s="8" t="n"/>
+      <c r="K6" s="8" t="n"/>
+      <c r="L6" s="8" t="n"/>
+      <c r="M6" s="8" t="n"/>
+      <c r="N6" s="8" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Inversión en publicidad</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>9000</v>
+      </c>
+      <c r="D7" s="21" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>10500</v>
+      </c>
+      <c r="F7" s="21" t="n"/>
+      <c r="G7" s="21" t="n"/>
+      <c r="H7" s="21" t="n"/>
+      <c r="I7" s="21" t="n"/>
+      <c r="J7" s="21" t="n"/>
+      <c r="K7" s="21" t="n"/>
+      <c r="L7" s="21" t="n"/>
+      <c r="M7" s="21" t="n"/>
+      <c r="N7" s="21" t="n"/>
+      <c r="O7" s="26">
+        <f>IF(COUNT(C7:N7)=0,"",AVERAGE(C7:N7))</f>
+        <v/>
+      </c>
+      <c r="P7" s="26">
+        <f>IF(COUNT(C7:N7)=0,"",MAX(C7:N7))</f>
+        <v/>
+      </c>
+      <c r="Q7" s="26">
+        <f>IF(COUNT(C7:N7)=0,"",MIN(C7:N7))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Visitas a la página</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="n">
+        <v>30000</v>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>30200</v>
+      </c>
+      <c r="E8" s="20" t="n">
+        <v>29000</v>
+      </c>
+      <c r="F8" s="20" t="n"/>
+      <c r="G8" s="20" t="n"/>
+      <c r="H8" s="20" t="n"/>
+      <c r="I8" s="20" t="n"/>
+      <c r="J8" s="20" t="n"/>
+      <c r="K8" s="20" t="n"/>
+      <c r="L8" s="20" t="n"/>
+      <c r="M8" s="20" t="n"/>
+      <c r="N8" s="20" t="n"/>
+      <c r="O8" s="16">
+        <f>IF(COUNT(C8:N8)=0,"",AVERAGE(C8:N8))</f>
+        <v/>
+      </c>
+      <c r="P8" s="16">
+        <f>IF(COUNT(C8:N8)=0,"",MAX(C8:N8))</f>
+        <v/>
+      </c>
+      <c r="Q8" s="16">
+        <f>IF(COUNT(C8:N8)=0,"",MIN(C8:N8))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Checkouts iniciados</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>980</v>
+      </c>
+      <c r="F9" s="20" t="n"/>
+      <c r="G9" s="20" t="n"/>
+      <c r="H9" s="20" t="n"/>
+      <c r="I9" s="20" t="n"/>
+      <c r="J9" s="20" t="n"/>
+      <c r="K9" s="20" t="n"/>
+      <c r="L9" s="20" t="n"/>
+      <c r="M9" s="20" t="n"/>
+      <c r="N9" s="20" t="n"/>
+      <c r="O9" s="16">
+        <f>IF(COUNT(C9:N9)=0,"",AVERAGE(C9:N9))</f>
+        <v/>
+      </c>
+      <c r="P9" s="16">
+        <f>IF(COUNT(C9:N9)=0,"",MAX(C9:N9))</f>
+        <v/>
+      </c>
+      <c r="Q9" s="16">
+        <f>IF(COUNT(C9:N9)=0,"",MIN(C9:N9))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Ventas del producto principal</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="D10" s="20" t="n">
+        <v>262</v>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>240</v>
+      </c>
+      <c r="F10" s="20" t="n"/>
+      <c r="G10" s="20" t="n"/>
+      <c r="H10" s="20" t="n"/>
+      <c r="I10" s="20" t="n"/>
+      <c r="J10" s="20" t="n"/>
+      <c r="K10" s="20" t="n"/>
+      <c r="L10" s="20" t="n"/>
+      <c r="M10" s="20" t="n"/>
+      <c r="N10" s="20" t="n"/>
+      <c r="O10" s="16">
+        <f>IF(COUNT(C10:N10)=0,"",AVERAGE(C10:N10))</f>
+        <v/>
+      </c>
+      <c r="P10" s="16">
+        <f>IF(COUNT(C10:N10)=0,"",MAX(C10:N10))</f>
+        <v/>
+      </c>
+      <c r="Q10" s="16">
+        <f>IF(COUNT(C10:N10)=0,"",MIN(C10:N10))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Ventas de bumps (1 + 2)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>110</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>95</v>
+      </c>
+      <c r="F11" s="20" t="n"/>
+      <c r="G11" s="20" t="n"/>
+      <c r="H11" s="20" t="n"/>
+      <c r="I11" s="20" t="n"/>
+      <c r="J11" s="20" t="n"/>
+      <c r="K11" s="20" t="n"/>
+      <c r="L11" s="20" t="n"/>
+      <c r="M11" s="20" t="n"/>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="16">
+        <f>IF(COUNT(C11:N11)=0,"",AVERAGE(C11:N11))</f>
+        <v/>
+      </c>
+      <c r="P11" s="16">
+        <f>IF(COUNT(C11:N11)=0,"",MAX(C11:N11))</f>
+        <v/>
+      </c>
+      <c r="Q11" s="16">
+        <f>IF(COUNT(C11:N11)=0,"",MIN(C11:N11))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Ventas de OTOs (1 a 4)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>63</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>58</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="F12" s="20" t="n"/>
+      <c r="G12" s="20" t="n"/>
+      <c r="H12" s="20" t="n"/>
+      <c r="I12" s="20" t="n"/>
+      <c r="J12" s="20" t="n"/>
+      <c r="K12" s="20" t="n"/>
+      <c r="L12" s="20" t="n"/>
+      <c r="M12" s="20" t="n"/>
+      <c r="N12" s="20" t="n"/>
+      <c r="O12" s="16">
+        <f>IF(COUNT(C12:N12)=0,"",AVERAGE(C12:N12))</f>
+        <v/>
+      </c>
+      <c r="P12" s="16">
+        <f>IF(COUNT(C12:N12)=0,"",MAX(C12:N12))</f>
+        <v/>
+      </c>
+      <c r="Q12" s="16">
+        <f>IF(COUNT(C12:N12)=0,"",MIN(C12:N12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Ventas de la ascensión (programa)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="20" t="n"/>
+      <c r="G13" s="20" t="n"/>
+      <c r="H13" s="20" t="n"/>
+      <c r="I13" s="20" t="n"/>
+      <c r="J13" s="20" t="n"/>
+      <c r="K13" s="20" t="n"/>
+      <c r="L13" s="20" t="n"/>
+      <c r="M13" s="20" t="n"/>
+      <c r="N13" s="20" t="n"/>
+      <c r="O13" s="16">
+        <f>IF(COUNT(C13:N13)=0,"",AVERAGE(C13:N13))</f>
+        <v/>
+      </c>
+      <c r="P13" s="16">
+        <f>IF(COUNT(C13:N13)=0,"",MAX(C13:N13))</f>
+        <v/>
+      </c>
+      <c r="Q13" s="16">
+        <f>IF(COUNT(C13:N13)=0,"",MIN(C13:N13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Facturado del mes (a precio de lista)</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>15400</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>13700</v>
+      </c>
+      <c r="F14" s="21" t="n"/>
+      <c r="G14" s="21" t="n"/>
+      <c r="H14" s="21" t="n"/>
+      <c r="I14" s="21" t="n"/>
+      <c r="J14" s="21" t="n"/>
+      <c r="K14" s="21" t="n"/>
+      <c r="L14" s="21" t="n"/>
+      <c r="M14" s="21" t="n"/>
+      <c r="N14" s="21" t="n"/>
+      <c r="O14" s="26">
+        <f>IF(COUNT(C14:N14)=0,"",AVERAGE(C14:N14))</f>
+        <v/>
+      </c>
+      <c r="P14" s="26">
+        <f>IF(COUNT(C14:N14)=0,"",MAX(C14:N14))</f>
+        <v/>
+      </c>
+      <c r="Q14" s="26">
+        <f>IF(COUNT(C14:N14)=0,"",MIN(C14:N14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Cash cobrado en el mes</t>
+        </is>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>15900</v>
+      </c>
+      <c r="D15" s="21" t="n">
+        <v>15400</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>13700</v>
+      </c>
+      <c r="F15" s="21" t="n"/>
+      <c r="G15" s="21" t="n"/>
+      <c r="H15" s="21" t="n"/>
+      <c r="I15" s="21" t="n"/>
+      <c r="J15" s="21" t="n"/>
+      <c r="K15" s="21" t="n"/>
+      <c r="L15" s="21" t="n"/>
+      <c r="M15" s="21" t="n"/>
+      <c r="N15" s="21" t="n"/>
+      <c r="O15" s="26">
+        <f>IF(COUNT(C15:N15)=0,"",AVERAGE(C15:N15))</f>
+        <v/>
+      </c>
+      <c r="P15" s="26">
+        <f>IF(COUNT(C15:N15)=0,"",MAX(C15:N15))</f>
+        <v/>
+      </c>
+      <c r="Q15" s="26">
+        <f>IF(COUNT(C15:N15)=0,"",MIN(C15:N15))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Lo que calcula el modelo</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="8" t="n"/>
+      <c r="F16" s="8" t="n"/>
+      <c r="G16" s="8" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
+      <c r="J16" s="8" t="n"/>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
+      <c r="N16" s="8" t="n"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Costo por visita real</t>
+        </is>
+      </c>
+      <c r="C17" s="12">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C7/C8))</f>
+        <v/>
+      </c>
+      <c r="D17" s="12">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D7/D8))</f>
+        <v/>
+      </c>
+      <c r="E17" s="12">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E7/E8))</f>
+        <v/>
+      </c>
+      <c r="F17" s="12">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F7/F8))</f>
+        <v/>
+      </c>
+      <c r="G17" s="12">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G7/G8))</f>
+        <v/>
+      </c>
+      <c r="H17" s="12">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H7/H8))</f>
+        <v/>
+      </c>
+      <c r="I17" s="12">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I7/I8))</f>
+        <v/>
+      </c>
+      <c r="J17" s="12">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J7/J8))</f>
+        <v/>
+      </c>
+      <c r="K17" s="12">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K7/K8))</f>
+        <v/>
+      </c>
+      <c r="L17" s="12">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L7/L8))</f>
+        <v/>
+      </c>
+      <c r="M17" s="12">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M7/M8))</f>
+        <v/>
+      </c>
+      <c r="N17" s="12">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N7/N8))</f>
+        <v/>
+      </c>
+      <c r="O17" s="19">
+        <f>IF(COUNT(C17:N17)=0,"",AVERAGE(C17:N17))</f>
+        <v/>
+      </c>
+      <c r="P17" s="19">
+        <f>IF(COUNT(C17:N17)=0,"",MAX(C17:N17))</f>
+        <v/>
+      </c>
+      <c r="Q17" s="19">
+        <f>IF(COUNT(C17:N17)=0,"",MIN(C17:N17))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>% visitas → checkout</t>
+        </is>
+      </c>
+      <c r="C18" s="18">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,C9/C8))</f>
+        <v/>
+      </c>
+      <c r="D18" s="18">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,D9/D8))</f>
+        <v/>
+      </c>
+      <c r="E18" s="18">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,E9/E8))</f>
+        <v/>
+      </c>
+      <c r="F18" s="18">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,F9/F8))</f>
+        <v/>
+      </c>
+      <c r="G18" s="18">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,G9/G8))</f>
+        <v/>
+      </c>
+      <c r="H18" s="18">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,H9/H8))</f>
+        <v/>
+      </c>
+      <c r="I18" s="18">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,I9/I8))</f>
+        <v/>
+      </c>
+      <c r="J18" s="18">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,J9/J8))</f>
+        <v/>
+      </c>
+      <c r="K18" s="18">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,K9/K8))</f>
+        <v/>
+      </c>
+      <c r="L18" s="18">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,L9/L8))</f>
+        <v/>
+      </c>
+      <c r="M18" s="18">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,M9/M8))</f>
+        <v/>
+      </c>
+      <c r="N18" s="18">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,N9/N8))</f>
+        <v/>
+      </c>
+      <c r="O18" s="18">
+        <f>IF(COUNT(C18:N18)=0,"",AVERAGE(C18:N18))</f>
+        <v/>
+      </c>
+      <c r="P18" s="18">
+        <f>IF(COUNT(C18:N18)=0,"",MAX(C18:N18))</f>
+        <v/>
+      </c>
+      <c r="Q18" s="18">
+        <f>IF(COUNT(C18:N18)=0,"",MIN(C18:N18))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>% checkout → compra</t>
+        </is>
+      </c>
+      <c r="C19" s="18">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C9=0,0,C10/C9))</f>
+        <v/>
+      </c>
+      <c r="D19" s="18">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D9=0,0,D10/D9))</f>
+        <v/>
+      </c>
+      <c r="E19" s="18">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E9=0,0,E10/E9))</f>
+        <v/>
+      </c>
+      <c r="F19" s="18">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F9=0,0,F10/F9))</f>
+        <v/>
+      </c>
+      <c r="G19" s="18">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G9=0,0,G10/G9))</f>
+        <v/>
+      </c>
+      <c r="H19" s="18">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H9=0,0,H10/H9))</f>
+        <v/>
+      </c>
+      <c r="I19" s="18">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I9=0,0,I10/I9))</f>
+        <v/>
+      </c>
+      <c r="J19" s="18">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J9=0,0,J10/J9))</f>
+        <v/>
+      </c>
+      <c r="K19" s="18">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K9=0,0,K10/K9))</f>
+        <v/>
+      </c>
+      <c r="L19" s="18">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L9=0,0,L10/L9))</f>
+        <v/>
+      </c>
+      <c r="M19" s="18">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M9=0,0,M10/M9))</f>
+        <v/>
+      </c>
+      <c r="N19" s="18">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N9=0,0,N10/N9))</f>
+        <v/>
+      </c>
+      <c r="O19" s="18">
+        <f>IF(COUNT(C19:N19)=0,"",AVERAGE(C19:N19))</f>
+        <v/>
+      </c>
+      <c r="P19" s="18">
+        <f>IF(COUNT(C19:N19)=0,"",MAX(C19:N19))</f>
+        <v/>
+      </c>
+      <c r="Q19" s="18">
+        <f>IF(COUNT(C19:N19)=0,"",MIN(C19:N19))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CPA real</t>
+        </is>
+      </c>
+      <c r="C20" s="19">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C7/C10))</f>
+        <v/>
+      </c>
+      <c r="D20" s="19">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D7/D10))</f>
+        <v/>
+      </c>
+      <c r="E20" s="19">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E7/E10))</f>
+        <v/>
+      </c>
+      <c r="F20" s="19">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F7/F10))</f>
+        <v/>
+      </c>
+      <c r="G20" s="19">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G7/G10))</f>
+        <v/>
+      </c>
+      <c r="H20" s="19">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H7/H10))</f>
+        <v/>
+      </c>
+      <c r="I20" s="19">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I7/I10))</f>
+        <v/>
+      </c>
+      <c r="J20" s="19">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J7/J10))</f>
+        <v/>
+      </c>
+      <c r="K20" s="19">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K7/K10))</f>
+        <v/>
+      </c>
+      <c r="L20" s="19">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L7/L10))</f>
+        <v/>
+      </c>
+      <c r="M20" s="19">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M7/M10))</f>
+        <v/>
+      </c>
+      <c r="N20" s="19">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N7/N10))</f>
+        <v/>
+      </c>
+      <c r="O20" s="19">
+        <f>IF(COUNT(C20:N20)=0,"",AVERAGE(C20:N20))</f>
+        <v/>
+      </c>
+      <c r="P20" s="19">
+        <f>IF(COUNT(C20:N20)=0,"",MAX(C20:N20))</f>
+        <v/>
+      </c>
+      <c r="Q20" s="19">
+        <f>IF(COUNT(C20:N20)=0,"",MIN(C20:N20))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Cash por comprador</t>
+        </is>
+      </c>
+      <c r="C21" s="19">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C10=0,0,C15/C10))</f>
+        <v/>
+      </c>
+      <c r="D21" s="19">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D10=0,0,D15/D10))</f>
+        <v/>
+      </c>
+      <c r="E21" s="19">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E10=0,0,E15/E10))</f>
+        <v/>
+      </c>
+      <c r="F21" s="19">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F10=0,0,F15/F10))</f>
+        <v/>
+      </c>
+      <c r="G21" s="19">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G10=0,0,G15/G10))</f>
+        <v/>
+      </c>
+      <c r="H21" s="19">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H10=0,0,H15/H10))</f>
+        <v/>
+      </c>
+      <c r="I21" s="19">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I10=0,0,I15/I10))</f>
+        <v/>
+      </c>
+      <c r="J21" s="19">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J10=0,0,J15/J10))</f>
+        <v/>
+      </c>
+      <c r="K21" s="19">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K10=0,0,K15/K10))</f>
+        <v/>
+      </c>
+      <c r="L21" s="19">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L10=0,0,L15/L10))</f>
+        <v/>
+      </c>
+      <c r="M21" s="19">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M10=0,0,M15/M10))</f>
+        <v/>
+      </c>
+      <c r="N21" s="19">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N10=0,0,N15/N10))</f>
+        <v/>
+      </c>
+      <c r="O21" s="19">
+        <f>IF(COUNT(C21:N21)=0,"",AVERAGE(C21:N21))</f>
+        <v/>
+      </c>
+      <c r="P21" s="19">
+        <f>IF(COUNT(C21:N21)=0,"",MAX(C21:N21))</f>
+        <v/>
+      </c>
+      <c r="Q21" s="19">
+        <f>IF(COUNT(C21:N21)=0,"",MIN(C21:N21))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Valor neto por unidad real (sobre facturado, cobranza completa)</t>
+        </is>
+      </c>
+      <c r="C22" s="12">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36)/C8))</f>
+        <v/>
+      </c>
+      <c r="D22" s="12">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36)/D8))</f>
+        <v/>
+      </c>
+      <c r="E22" s="12">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36)/E8))</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36)/F8))</f>
+        <v/>
+      </c>
+      <c r="G22" s="12">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36)/G8))</f>
+        <v/>
+      </c>
+      <c r="H22" s="12">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36)/H8))</f>
+        <v/>
+      </c>
+      <c r="I22" s="12">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36)/I8))</f>
+        <v/>
+      </c>
+      <c r="J22" s="12">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36)/J8))</f>
+        <v/>
+      </c>
+      <c r="K22" s="12">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36)/K8))</f>
+        <v/>
+      </c>
+      <c r="L22" s="12">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36)/L8))</f>
+        <v/>
+      </c>
+      <c r="M22" s="12">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36)/M8))</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36)/N8))</f>
+        <v/>
+      </c>
+      <c r="O22" s="19">
+        <f>IF(COUNT(C22:N22)=0,"",AVERAGE(C22:N22))</f>
+        <v/>
+      </c>
+      <c r="P22" s="19">
+        <f>IF(COUNT(C22:N22)=0,"",MAX(C22:N22))</f>
+        <v/>
+      </c>
+      <c r="Q22" s="19">
+        <f>IF(COUNT(C22:N22)=0,"",MIN(C22:N22))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia del período al completar la cobranza</t>
+        </is>
+      </c>
+      <c r="C23" s="9">
+        <f>IF(COUNT(C7:C15)&lt;9,"",C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
+        <v/>
+      </c>
+      <c r="D23" s="9">
+        <f>IF(COUNT(D7:D15)&lt;9,"",D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
+        <v/>
+      </c>
+      <c r="E23" s="9">
+        <f>IF(COUNT(E7:E15)&lt;9,"",E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
+        <v/>
+      </c>
+      <c r="F23" s="9">
+        <f>IF(COUNT(F7:F15)&lt;9,"",F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
+        <v/>
+      </c>
+      <c r="G23" s="9">
+        <f>IF(COUNT(G7:G15)&lt;9,"",G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
+        <v/>
+      </c>
+      <c r="H23" s="9">
+        <f>IF(COUNT(H7:H15)&lt;9,"",H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
+        <v/>
+      </c>
+      <c r="I23" s="9">
+        <f>IF(COUNT(I7:I15)&lt;9,"",I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
+        <v/>
+      </c>
+      <c r="J23" s="9">
+        <f>IF(COUNT(J7:J15)&lt;9,"",J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
+        <v/>
+      </c>
+      <c r="K23" s="9">
+        <f>IF(COUNT(K7:K15)&lt;9,"",K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
+        <v/>
+      </c>
+      <c r="L23" s="9">
+        <f>IF(COUNT(L7:L15)&lt;9,"",L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
+        <v/>
+      </c>
+      <c r="M23" s="9">
+        <f>IF(COUNT(M7:M15)&lt;9,"",M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
+        <v/>
+      </c>
+      <c r="N23" s="9">
+        <f>IF(COUNT(N7:N15)&lt;9,"",N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
+        <v/>
+      </c>
+      <c r="O23" s="26">
+        <f>IF(COUNT(C23:N23)=0,"",AVERAGE(C23:N23))</f>
+        <v/>
+      </c>
+      <c r="P23" s="26">
+        <f>IF(COUNT(C23:N23)=0,"",MAX(C23:N23))</f>
+        <v/>
+      </c>
+      <c r="Q23" s="26">
+        <f>IF(COUNT(C23:N23)=0,"",MIN(C23:N23))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ganancia de caja del período (con lo cobrado hasta ahora)</t>
+        </is>
+      </c>
+      <c r="C24" s="26">
+        <f>IF(COUNT(C7:C15)&lt;9,"",C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)</f>
+        <v/>
+      </c>
+      <c r="D24" s="26">
+        <f>IF(COUNT(D7:D15)&lt;9,"",D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)</f>
+        <v/>
+      </c>
+      <c r="E24" s="26">
+        <f>IF(COUNT(E7:E15)&lt;9,"",E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)</f>
+        <v/>
+      </c>
+      <c r="F24" s="26">
+        <f>IF(COUNT(F7:F15)&lt;9,"",F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)</f>
+        <v/>
+      </c>
+      <c r="G24" s="26">
+        <f>IF(COUNT(G7:G15)&lt;9,"",G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)</f>
+        <v/>
+      </c>
+      <c r="H24" s="26">
+        <f>IF(COUNT(H7:H15)&lt;9,"",H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)</f>
+        <v/>
+      </c>
+      <c r="I24" s="26">
+        <f>IF(COUNT(I7:I15)&lt;9,"",I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)</f>
+        <v/>
+      </c>
+      <c r="J24" s="26">
+        <f>IF(COUNT(J7:J15)&lt;9,"",J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)</f>
+        <v/>
+      </c>
+      <c r="K24" s="26">
+        <f>IF(COUNT(K7:K15)&lt;9,"",K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)</f>
+        <v/>
+      </c>
+      <c r="L24" s="26">
+        <f>IF(COUNT(L7:L15)&lt;9,"",L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)</f>
+        <v/>
+      </c>
+      <c r="M24" s="26">
+        <f>IF(COUNT(M7:M15)&lt;9,"",M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)</f>
+        <v/>
+      </c>
+      <c r="N24" s="26">
+        <f>IF(COUNT(N7:N15)&lt;9,"",N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)</f>
+        <v/>
+      </c>
+      <c r="O24" s="26">
+        <f>IF(COUNT(C24:N24)=0,"",AVERAGE(C24:N24))</f>
+        <v/>
+      </c>
+      <c r="P24" s="26">
+        <f>IF(COUNT(C24:N24)=0,"",MAX(C24:N24))</f>
+        <v/>
+      </c>
+      <c r="Q24" s="26">
+        <f>IF(COUNT(C24:N24)=0,"",MIN(C24:N24))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Ganancia por unidad real (ganancia ÷ unidades)</t>
+        </is>
+      </c>
+      <c r="C25" s="12">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C8=0,0,(C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-C8*'Supuestos'!$C$36-'Supuestos'!$C$37-C7)/C8))</f>
+        <v/>
+      </c>
+      <c r="D25" s="12">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D8=0,0,(D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-D8*'Supuestos'!$C$36-'Supuestos'!$C$37-D7)/D8))</f>
+        <v/>
+      </c>
+      <c r="E25" s="12">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E8=0,0,(E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-E8*'Supuestos'!$C$36-'Supuestos'!$C$37-E7)/E8))</f>
+        <v/>
+      </c>
+      <c r="F25" s="12">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F8=0,0,(F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-F8*'Supuestos'!$C$36-'Supuestos'!$C$37-F7)/F8))</f>
+        <v/>
+      </c>
+      <c r="G25" s="12">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G8=0,0,(G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-G8*'Supuestos'!$C$36-'Supuestos'!$C$37-G7)/G8))</f>
+        <v/>
+      </c>
+      <c r="H25" s="12">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H8=0,0,(H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-H8*'Supuestos'!$C$36-'Supuestos'!$C$37-H7)/H8))</f>
+        <v/>
+      </c>
+      <c r="I25" s="12">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I8=0,0,(I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-I8*'Supuestos'!$C$36-'Supuestos'!$C$37-I7)/I8))</f>
+        <v/>
+      </c>
+      <c r="J25" s="12">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J8=0,0,(J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-J8*'Supuestos'!$C$36-'Supuestos'!$C$37-J7)/J8))</f>
+        <v/>
+      </c>
+      <c r="K25" s="12">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K8=0,0,(K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-K8*'Supuestos'!$C$36-'Supuestos'!$C$37-K7)/K8))</f>
+        <v/>
+      </c>
+      <c r="L25" s="12">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L8=0,0,(L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-L8*'Supuestos'!$C$36-'Supuestos'!$C$37-L7)/L8))</f>
+        <v/>
+      </c>
+      <c r="M25" s="12">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M8=0,0,(M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-M8*'Supuestos'!$C$36-'Supuestos'!$C$37-M7)/M8))</f>
+        <v/>
+      </c>
+      <c r="N25" s="12">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N8=0,0,(N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)-N8*'Supuestos'!$C$36-'Supuestos'!$C$37-N7)/N8))</f>
+        <v/>
+      </c>
+      <c r="O25" s="19">
+        <f>IF(COUNT(C25:N25)=0,"",AVERAGE(C25:N25))</f>
+        <v/>
+      </c>
+      <c r="P25" s="19">
+        <f>IF(COUNT(C25:N25)=0,"",MAX(C25:N25))</f>
+        <v/>
+      </c>
+      <c r="Q25" s="19">
+        <f>IF(COUNT(C25:N25)=0,"",MIN(C25:N25))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>ROAS sobre cash neto (cobranza completa)</t>
+        </is>
+      </c>
+      <c r="C26" s="10">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
+        <v/>
+      </c>
+      <c r="D26" s="10">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
+        <v/>
+      </c>
+      <c r="E26" s="10">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
+        <v/>
+      </c>
+      <c r="F26" s="10">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
+        <v/>
+      </c>
+      <c r="G26" s="10">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
+        <v/>
+      </c>
+      <c r="H26" s="10">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
+        <v/>
+      </c>
+      <c r="I26" s="10">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
+        <v/>
+      </c>
+      <c r="J26" s="10">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
+        <v/>
+      </c>
+      <c r="K26" s="10">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
+        <v/>
+      </c>
+      <c r="L26" s="10">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
+        <v/>
+      </c>
+      <c r="M26" s="10">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
+        <v/>
+      </c>
+      <c r="N26" s="10">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N14*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
+        <v/>
+      </c>
+      <c r="O26" s="28">
+        <f>IF(COUNT(C26:N26)=0,"",AVERAGE(C26:N26))</f>
+        <v/>
+      </c>
+      <c r="P26" s="28">
+        <f>IF(COUNT(C26:N26)=0,"",MAX(C26:N26))</f>
+        <v/>
+      </c>
+      <c r="Q26" s="28">
+        <f>IF(COUNT(C26:N26)=0,"",MIN(C26:N26))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ROAS de caja (cobrado hasta ahora)</t>
+        </is>
+      </c>
+      <c r="C27" s="28">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C7=0,0,C15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/C7))</f>
+        <v/>
+      </c>
+      <c r="D27" s="28">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D7=0,0,D15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/D7))</f>
+        <v/>
+      </c>
+      <c r="E27" s="28">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E7=0,0,E15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/E7))</f>
+        <v/>
+      </c>
+      <c r="F27" s="28">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F7=0,0,F15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/F7))</f>
+        <v/>
+      </c>
+      <c r="G27" s="28">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G7=0,0,G15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/G7))</f>
+        <v/>
+      </c>
+      <c r="H27" s="28">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H7=0,0,H15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/H7))</f>
+        <v/>
+      </c>
+      <c r="I27" s="28">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I7=0,0,I15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/I7))</f>
+        <v/>
+      </c>
+      <c r="J27" s="28">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J7=0,0,J15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/J7))</f>
+        <v/>
+      </c>
+      <c r="K27" s="28">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K7=0,0,K15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/K7))</f>
+        <v/>
+      </c>
+      <c r="L27" s="28">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L7=0,0,L15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/L7))</f>
+        <v/>
+      </c>
+      <c r="M27" s="28">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M7=0,0,M15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/M7))</f>
+        <v/>
+      </c>
+      <c r="N27" s="28">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N7=0,0,N15*(1-'Supuestos'!$C$33-'Supuestos'!$C$34-'Supuestos'!$C$35)/N7))</f>
+        <v/>
+      </c>
+      <c r="O27" s="28">
+        <f>IF(COUNT(C27:N27)=0,"",AVERAGE(C27:N27))</f>
+        <v/>
+      </c>
+      <c r="P27" s="28">
+        <f>IF(COUNT(C27:N27)=0,"",MAX(C27:N27))</f>
+        <v/>
+      </c>
+      <c r="Q27" s="28">
+        <f>IF(COUNT(C27:N27)=0,"",MIN(C27:N27))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Techo móvil (mediana de tus últimas 4 columnas; al inicio, el del modelo)</t>
+        </is>
+      </c>
+      <c r="C28" s="19">
+        <f>IF(COUNT(C7:C15)&lt;9,"",'Modelo'!$C$48)</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(COUNT(C22:C22)&gt;0,MEDIAN(C22:C22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="E28" s="19">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(COUNT(C22:D22)&gt;0,MEDIAN(C22:D22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="F28" s="19">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(COUNT(C22:E22)&gt;0,MEDIAN(C22:E22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="G28" s="19">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(COUNT(C22:F22)&gt;0,MEDIAN(C22:F22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="H28" s="19">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(COUNT(D22:G22)&gt;0,MEDIAN(D22:G22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="I28" s="19">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(COUNT(E22:H22)&gt;0,MEDIAN(E22:H22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="J28" s="19">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(COUNT(F22:I22)&gt;0,MEDIAN(F22:I22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="K28" s="19">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(COUNT(G22:J22)&gt;0,MEDIAN(G22:J22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="L28" s="19">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(COUNT(H22:K22)&gt;0,MEDIAN(H22:K22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="M28" s="19">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(COUNT(I22:L22)&gt;0,MEDIAN(I22:L22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="N28" s="19">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(COUNT(J22:M22)&gt;0,MEDIAN(J22:M22),'Modelo'!$C$48))</f>
+        <v/>
+      </c>
+      <c r="O28" s="19">
+        <f>IF(COUNT(C28:N28)=0,"",AVERAGE(C28:N28))</f>
+        <v/>
+      </c>
+      <c r="P28" s="19">
+        <f>IF(COUNT(C28:N28)=0,"",MAX(C28:N28))</f>
+        <v/>
+      </c>
+      <c r="Q28" s="19">
+        <f>IF(COUNT(C28:N28)=0,"",MIN(C28:N28))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Semáforo (costo por unidad contra el techo móvil, y ROAS contra el objetivo)</t>
+        </is>
+      </c>
+      <c r="C29" s="13">
+        <f>IF(COUNT(C7:C15)&lt;9,"",IF(C17&gt;C28,"ROJO",IF(AND(C17&lt;=C28/(1+'Supuestos'!$C$46),C26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="D29" s="13">
+        <f>IF(COUNT(D7:D15)&lt;9,"",IF(D17&gt;D28,"ROJO",IF(AND(D17&lt;=D28/(1+'Supuestos'!$C$46),D26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="E29" s="13">
+        <f>IF(COUNT(E7:E15)&lt;9,"",IF(E17&gt;E28,"ROJO",IF(AND(E17&lt;=E28/(1+'Supuestos'!$C$46),E26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="F29" s="13">
+        <f>IF(COUNT(F7:F15)&lt;9,"",IF(F17&gt;F28,"ROJO",IF(AND(F17&lt;=F28/(1+'Supuestos'!$C$46),F26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="G29" s="13">
+        <f>IF(COUNT(G7:G15)&lt;9,"",IF(G17&gt;G28,"ROJO",IF(AND(G17&lt;=G28/(1+'Supuestos'!$C$46),G26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="H29" s="13">
+        <f>IF(COUNT(H7:H15)&lt;9,"",IF(H17&gt;H28,"ROJO",IF(AND(H17&lt;=H28/(1+'Supuestos'!$C$46),H26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="I29" s="13">
+        <f>IF(COUNT(I7:I15)&lt;9,"",IF(I17&gt;I28,"ROJO",IF(AND(I17&lt;=I28/(1+'Supuestos'!$C$46),I26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="J29" s="13">
+        <f>IF(COUNT(J7:J15)&lt;9,"",IF(J17&gt;J28,"ROJO",IF(AND(J17&lt;=J28/(1+'Supuestos'!$C$46),J26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="K29" s="13">
+        <f>IF(COUNT(K7:K15)&lt;9,"",IF(K17&gt;K28,"ROJO",IF(AND(K17&lt;=K28/(1+'Supuestos'!$C$46),K26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="L29" s="13">
+        <f>IF(COUNT(L7:L15)&lt;9,"",IF(L17&gt;L28,"ROJO",IF(AND(L17&lt;=L28/(1+'Supuestos'!$C$46),L26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="M29" s="13">
+        <f>IF(COUNT(M7:M15)&lt;9,"",IF(M17&gt;M28,"ROJO",IF(AND(M17&lt;=M28/(1+'Supuestos'!$C$46),M26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+      <c r="N29" s="13">
+        <f>IF(COUNT(N7:N15)&lt;9,"",IF(N17&gt;N28,"ROJO",IF(AND(N17&lt;=N28/(1+'Supuestos'!$C$46),N26&gt;='Supuestos'!$C$45),"VERDE","AMARILLO")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C5:N30">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>LEFT(C5,5)="VERDE"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="2" dxfId="1">
+      <formula>LEFT(C5,8)="AMARILLO"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>LEFT(C5,4)="ROJO"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;CJesús Tassarolo · TooAudience&amp;R&amp;D</oddHeader>
+    <oddFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</oddFooter>
+    <evenHeader>&amp;CJesús Tassarolo · TooAudience</evenHeader>
+    <evenFooter>&amp;LModelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;C&amp;7 Modelo financiero de embudos · creado por Jesús Tassarolo · TooAudience · youtube.com/@JesusTassaroloSinFiltro&amp;RPágina &amp;P de &amp;N</evenFooter>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
 </file>